--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -55457,6 +55457,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2396">
+      <c r="A2396" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2396" t="n">
+        <v>134975</v>
+      </c>
+      <c r="C2396" t="n">
+        <v>1.36600005626678</v>
+      </c>
+      <c r="D2396" t="n">
+        <v>1.317999958992</v>
+      </c>
+      <c r="E2396" t="n">
+        <v>1.36600005626678</v>
+      </c>
+      <c r="F2396" t="n">
+        <v>1.33399999141693</v>
+      </c>
+      <c r="G2396" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -55480,6 +55480,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2397">
+      <c r="A2397" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2397" t="n">
+        <v>77802</v>
+      </c>
+      <c r="C2397" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="D2397" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="E2397" t="n">
+        <v>1.33399999141693</v>
+      </c>
+      <c r="F2397" t="n">
+        <v>1.32200002670288</v>
+      </c>
+      <c r="G2397" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -55503,6 +55503,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2398">
+      <c r="A2398" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2398" t="n">
+        <v>112411</v>
+      </c>
+      <c r="C2398" t="n">
+        <v>1.34800004959106</v>
+      </c>
+      <c r="D2398" t="n">
+        <v>1.31599998474121</v>
+      </c>
+      <c r="E2398" t="n">
+        <v>1.33399999141693</v>
+      </c>
+      <c r="F2398" t="n">
+        <v>1.33399999141693</v>
+      </c>
+      <c r="G2398" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -55526,6 +55526,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2399">
+      <c r="A2399" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2399" t="n">
+        <v>40145</v>
+      </c>
+      <c r="C2399" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="D2399" t="n">
+        <v>1.33599996566772</v>
+      </c>
+      <c r="E2399" t="n">
+        <v>1.34200000762939</v>
+      </c>
+      <c r="F2399" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="G2399" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -55367,22 +55367,22 @@
     </row>
     <row r="2392">
       <c r="A2392" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2392" t="n">
-        <v>55908</v>
+        <v>65993</v>
       </c>
       <c r="C2392" t="n">
-        <v>1.3639999628067</v>
+        <v>1.36800003051758</v>
       </c>
       <c r="D2392" t="n">
         <v>1.35199999809265</v>
       </c>
       <c r="E2392" t="n">
-        <v>1.35199999809265</v>
+        <v>1.36800003051758</v>
       </c>
       <c r="F2392" t="n">
-        <v>1.35599994659424</v>
+        <v>1.35800004005432</v>
       </c>
       <c r="G2392" t="s">
         <v>7</v>
@@ -55390,16 +55390,16 @@
     </row>
     <row r="2393">
       <c r="A2393" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2393" t="n">
-        <v>172011</v>
+        <v>55908</v>
       </c>
       <c r="C2393" t="n">
-        <v>1.36600005626678</v>
+        <v>1.3639999628067</v>
       </c>
       <c r="D2393" t="n">
-        <v>1.33200001716614</v>
+        <v>1.35199999809265</v>
       </c>
       <c r="E2393" t="n">
         <v>1.35199999809265</v>
@@ -55413,22 +55413,22 @@
     </row>
     <row r="2394">
       <c r="A2394" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2394" t="n">
-        <v>55039</v>
+        <v>172011</v>
       </c>
       <c r="C2394" t="n">
-        <v>1.36800003051758</v>
+        <v>1.36600005626678</v>
       </c>
       <c r="D2394" t="n">
-        <v>1.34399998188019</v>
+        <v>1.33200001716614</v>
       </c>
       <c r="E2394" t="n">
-        <v>1.36800003051758</v>
+        <v>1.35199999809265</v>
       </c>
       <c r="F2394" t="n">
-        <v>1.34800004959106</v>
+        <v>1.35599994659424</v>
       </c>
       <c r="G2394" t="s">
         <v>7</v>
@@ -55436,22 +55436,22 @@
     </row>
     <row r="2395">
       <c r="A2395" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2395" t="n">
-        <v>71083</v>
+        <v>55039</v>
       </c>
       <c r="C2395" t="n">
-        <v>1.35599994659424</v>
+        <v>1.36800003051758</v>
       </c>
       <c r="D2395" t="n">
-        <v>1.33200001716614</v>
+        <v>1.34399998188019</v>
       </c>
       <c r="E2395" t="n">
-        <v>1.35000002384186</v>
+        <v>1.36800003051758</v>
       </c>
       <c r="F2395" t="n">
-        <v>1.33599996566772</v>
+        <v>1.34800004959106</v>
       </c>
       <c r="G2395" t="s">
         <v>7</v>
@@ -55459,22 +55459,22 @@
     </row>
     <row r="2396">
       <c r="A2396" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2396" t="n">
-        <v>134975</v>
+        <v>71083</v>
       </c>
       <c r="C2396" t="n">
-        <v>1.36600005626678</v>
+        <v>1.35599994659424</v>
       </c>
       <c r="D2396" t="n">
-        <v>1.317999958992</v>
+        <v>1.33200001716614</v>
       </c>
       <c r="E2396" t="n">
-        <v>1.36600005626678</v>
+        <v>1.35000002384186</v>
       </c>
       <c r="F2396" t="n">
-        <v>1.33399999141693</v>
+        <v>1.33599996566772</v>
       </c>
       <c r="G2396" t="s">
         <v>7</v>
@@ -55482,22 +55482,22 @@
     </row>
     <row r="2397">
       <c r="A2397" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2397" t="n">
-        <v>77802</v>
+        <v>134975</v>
       </c>
       <c r="C2397" t="n">
-        <v>1.35000002384186</v>
+        <v>1.36600005626678</v>
       </c>
       <c r="D2397" t="n">
-        <v>1.32000005245209</v>
+        <v>1.317999958992</v>
       </c>
       <c r="E2397" t="n">
+        <v>1.36600005626678</v>
+      </c>
+      <c r="F2397" t="n">
         <v>1.33399999141693</v>
-      </c>
-      <c r="F2397" t="n">
-        <v>1.32200002670288</v>
       </c>
       <c r="G2397" t="s">
         <v>7</v>
@@ -55505,22 +55505,22 @@
     </row>
     <row r="2398">
       <c r="A2398" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2398" t="n">
-        <v>112411</v>
+        <v>77802</v>
       </c>
       <c r="C2398" t="n">
-        <v>1.34800004959106</v>
+        <v>1.35000002384186</v>
       </c>
       <c r="D2398" t="n">
-        <v>1.31599998474121</v>
+        <v>1.32000005245209</v>
       </c>
       <c r="E2398" t="n">
         <v>1.33399999141693</v>
       </c>
       <c r="F2398" t="n">
-        <v>1.33399999141693</v>
+        <v>1.32200002670288</v>
       </c>
       <c r="G2398" t="s">
         <v>7</v>
@@ -55528,24 +55528,47 @@
     </row>
     <row r="2399">
       <c r="A2399" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2399" t="n">
-        <v>40145</v>
+        <v>112411</v>
       </c>
       <c r="C2399" t="n">
-        <v>1.36000001430511</v>
+        <v>1.34800004959106</v>
       </c>
       <c r="D2399" t="n">
-        <v>1.33599996566772</v>
+        <v>1.31599998474121</v>
       </c>
       <c r="E2399" t="n">
-        <v>1.34200000762939</v>
+        <v>1.33399999141693</v>
       </c>
       <c r="F2399" t="n">
-        <v>1.3400000333786</v>
+        <v>1.33399999141693</v>
       </c>
       <c r="G2399" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2400">
+      <c r="A2400" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2400" t="n">
+        <v>107426</v>
+      </c>
+      <c r="C2400" t="n">
+        <v>1.3639999628067</v>
+      </c>
+      <c r="D2400" t="n">
+        <v>1.32400000095367</v>
+      </c>
+      <c r="E2400" t="n">
+        <v>1.35599994659424</v>
+      </c>
+      <c r="F2400" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="G2400" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G2" t="n">
-        <v>9.1356840133667</v>
+        <v>9.13568305969238</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G3" t="n">
-        <v>9.27969551086426</v>
+        <v>9.27969360351562</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>10.25</v>
       </c>
       <c r="G4" t="n">
-        <v>9.22568988800049</v>
+        <v>9.2256908416748</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>10.5</v>
       </c>
       <c r="G6" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>9.36069965362549</v>
+        <v>9.3607006072998</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>10.5</v>
       </c>
       <c r="G8" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G9" t="n">
-        <v>9.4057035446167</v>
+        <v>9.40570259094238</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>9.81073379516602</v>
+        <v>9.8107328414917</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>9.44170665740967</v>
+        <v>9.44170570373535</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.4057035446167</v>
+        <v>9.40570259094238</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>9.4057035446167</v>
+        <v>9.40570259094238</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>10.5</v>
       </c>
       <c r="G17" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>10.5</v>
       </c>
       <c r="G18" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>10.5</v>
       </c>
       <c r="G19" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G20" t="n">
-        <v>9.54071426391602</v>
+        <v>9.54071521759033</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G21" t="n">
-        <v>9.55871486663818</v>
+        <v>9.5587158203125</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G25" t="n">
-        <v>9.54071426391602</v>
+        <v>9.54071521759033</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>9.54071426391602</v>
+        <v>9.54071521759033</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G34" t="n">
-        <v>9.69372463226318</v>
+        <v>9.6937255859375</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G35" t="n">
-        <v>9.81073379516602</v>
+        <v>9.8107328414917</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G40" t="n">
-        <v>9.90974140167236</v>
+        <v>9.90974235534668</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G41" t="n">
-        <v>9.90974140167236</v>
+        <v>9.90974235534668</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G42" t="n">
-        <v>9.91874122619629</v>
+        <v>9.91874217987061</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G43" t="n">
-        <v>9.91874122619629</v>
+        <v>9.91874217987061</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>9.94574451446533</v>
+        <v>9.94574356079102</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>11.0708293914795</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G53" t="n">
-        <v>10.6928005218506</v>
+        <v>10.6927995681763</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G58" t="n">
-        <v>10.6928005218506</v>
+        <v>10.6927995681763</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G61" t="n">
-        <v>10.7918071746826</v>
+        <v>10.7918081283569</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G66" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G74" t="n">
-        <v>10.9628200531006</v>
+        <v>10.9628210067749</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G83" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>11.0708293914795</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>11.0708293914795</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>11.0708293914795</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>11.0708293914795</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G97" t="n">
-        <v>11.0708293914795</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G98" t="n">
-        <v>11.0978307723999</v>
+        <v>11.0978298187256</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>11.0708293914795</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>11.0708293914795</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G105" t="n">
-        <v>11.1518335342407</v>
+        <v>11.1518354415894</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>11.0708293914795</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G108" t="n">
-        <v>11.0708293914795</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G111" t="n">
-        <v>11.0708293914795</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>11.0708293914795</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G113" t="n">
-        <v>11.0708293914795</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G114" t="n">
-        <v>10.9538192749023</v>
+        <v>10.953818321228</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G120" t="n">
-        <v>11.0978307723999</v>
+        <v>11.0978298187256</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G123" t="n">
-        <v>11.1518335342407</v>
+        <v>11.1518354415894</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G124" t="n">
-        <v>11.0888290405273</v>
+        <v>11.0888299942017</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G127" t="n">
-        <v>11.0528259277344</v>
+        <v>11.0528268814087</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>11.0978307723999</v>
+        <v>11.0978298187256</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G135" t="n">
-        <v>11.0528259277344</v>
+        <v>11.0528268814087</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G143" t="n">
-        <v>11.2778425216675</v>
+        <v>11.2778434753418</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G149" t="n">
-        <v>11.6018676757812</v>
+        <v>11.6018686294556</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G150" t="n">
-        <v>11.6828746795654</v>
+        <v>11.6828737258911</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G154" t="n">
-        <v>11.8178844451904</v>
+        <v>11.8178853988647</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G162" t="n">
-        <v>11.5028600692749</v>
+        <v>11.5028610229492</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>11.6108675003052</v>
+        <v>11.6108684539795</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G164" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G167" t="n">
-        <v>11.8358840942383</v>
+        <v>11.8358850479126</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>11.9708957672119</v>
+        <v>11.9708948135376</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>11.9708957672119</v>
+        <v>11.9708948135376</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G170" t="n">
-        <v>11.6828746795654</v>
+        <v>11.6828737258911</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>11.4128541946411</v>
+        <v>11.4128551483154</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G179" t="n">
-        <v>10.9898223876953</v>
+        <v>10.989821434021</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G182" t="n">
-        <v>10.7918071746826</v>
+        <v>10.7918081283569</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G183" t="n">
-        <v>10.719801902771</v>
+        <v>10.7198028564453</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G185" t="n">
-        <v>11.0708293914795</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G187" t="n">
-        <v>11.1968374252319</v>
+        <v>11.1968383789062</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G188" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G191" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G194" t="n">
-        <v>11.0708293914795</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>11.3858499526978</v>
+        <v>11.3858518600464</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>11.79088306427</v>
+        <v>11.7908840179443</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G206" t="n">
-        <v>11.6108675003052</v>
+        <v>11.6108684539795</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>11.79088306427</v>
+        <v>11.7908840179443</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>11.6108675003052</v>
+        <v>11.6108684539795</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G210" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>11.0708293914795</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G224" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>12.75</v>
       </c>
       <c r="G226" t="n">
-        <v>11.4758577346802</v>
+        <v>11.4758586883545</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G228" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G233" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G235" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>11.0708293914795</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G255" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>12.75</v>
       </c>
       <c r="G256" t="n">
-        <v>11.4758577346802</v>
+        <v>11.4758586883545</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>12.75</v>
       </c>
       <c r="G257" t="n">
-        <v>11.4758577346802</v>
+        <v>11.4758586883545</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G260" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G261" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G280" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>11.72767162323</v>
+        <v>11.7276706695557</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>12.5</v>
       </c>
       <c r="G288" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>10.6740121841431</v>
+        <v>10.6740131378174</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3991460800171</v>
+        <v>10.3991451263428</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G296" t="n">
-        <v>10.6282014846802</v>
+        <v>10.6282024383545</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>10.8114471435547</v>
+        <v>10.8114461898804</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G308" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G310" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>12.5</v>
       </c>
       <c r="G319" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G323" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>12.5</v>
       </c>
       <c r="G330" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G331" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>12.0025386810303</v>
+        <v>12.0025396347046</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>12.5</v>
       </c>
       <c r="G339" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G342" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>12.5</v>
       </c>
       <c r="G347" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G350" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G355" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G356" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G359" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>12.5</v>
       </c>
       <c r="G370" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G371" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>12.5</v>
       </c>
       <c r="G376" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G379" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G383" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>12</v>
       </c>
       <c r="G387" t="n">
-        <v>10.9946908950806</v>
+        <v>10.9946918487549</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>12</v>
       </c>
       <c r="G388" t="n">
-        <v>10.9946908950806</v>
+        <v>10.9946918487549</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>10.8114471435547</v>
+        <v>10.8114461898804</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>9.52873229980469</v>
+        <v>9.528733253479</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>9.25386619567871</v>
+        <v>9.25386524200439</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G400" t="n">
-        <v>9.25386619567871</v>
+        <v>9.25386524200439</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>10.25</v>
       </c>
       <c r="G401" t="n">
-        <v>9.39129829406738</v>
+        <v>9.3912992477417</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>9.52873229980469</v>
+        <v>9.528733253479</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>10</v>
       </c>
       <c r="G407" t="n">
-        <v>9.1622428894043</v>
+        <v>9.16224384307861</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>9.08894538879395</v>
+        <v>9.08894443511963</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.5</v>
       </c>
       <c r="G411" t="n">
-        <v>8.70413017272949</v>
+        <v>8.70413112640381</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G412" t="n">
-        <v>8.5758581161499</v>
+        <v>8.57585906982422</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G413" t="n">
-        <v>8.5758581161499</v>
+        <v>8.57585906982422</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>8.09942245483398</v>
+        <v>8.0994234085083</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9</v>
       </c>
       <c r="G417" t="n">
-        <v>8.24601745605469</v>
+        <v>8.24601936340332</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G419" t="n">
-        <v>8.46591186523438</v>
+        <v>8.46591281890869</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G420" t="n">
-        <v>8.39261531829834</v>
+        <v>8.39261436462402</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G421" t="n">
-        <v>8.35596561431885</v>
+        <v>8.35596466064453</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G422" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>9.08894538879395</v>
+        <v>9.08894443511963</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G426" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G428" t="n">
-        <v>8.90569972991943</v>
+        <v>8.90570068359375</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>9.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.70413017272949</v>
+        <v>8.70413112640381</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G432" t="n">
-        <v>8.68580627441406</v>
+        <v>8.68580532073975</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>8.28266716003418</v>
+        <v>8.2826681137085</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>8.06277465820312</v>
+        <v>8.06277370452881</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G441" t="n">
-        <v>8.15439701080322</v>
+        <v>8.15439605712891</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G443" t="n">
-        <v>8.3376407623291</v>
+        <v>8.33764171600342</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.5</v>
       </c>
       <c r="G446" t="n">
-        <v>8.70413017272949</v>
+        <v>8.70413112640381</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G449" t="n">
-        <v>8.3376407623291</v>
+        <v>8.33764171600342</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G451" t="n">
-        <v>8.44758796691895</v>
+        <v>8.44758892059326</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G453" t="n">
-        <v>8.44758796691895</v>
+        <v>8.44758892059326</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G456" t="n">
-        <v>8.61250782012939</v>
+        <v>8.61250877380371</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G457" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G458" t="n">
-        <v>8.44758796691895</v>
+        <v>8.44758892059326</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G459" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G463" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G466" t="n">
-        <v>8.61250782012939</v>
+        <v>8.61250877380371</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G467" t="n">
-        <v>8.61250782012939</v>
+        <v>8.61250877380371</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G469" t="n">
-        <v>8.64915752410889</v>
+        <v>8.64915657043457</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G470" t="n">
-        <v>8.64915752410889</v>
+        <v>8.64915657043457</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G471" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G472" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G473" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G476" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G478" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G480" t="n">
-        <v>8.30099296569824</v>
+        <v>8.30099201202393</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G484" t="n">
-        <v>8.3376407623291</v>
+        <v>8.33764171600342</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G485" t="n">
-        <v>8.26434421539307</v>
+        <v>8.26434326171875</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G488" t="n">
-        <v>8.26434421539307</v>
+        <v>8.26434326171875</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G491" t="n">
-        <v>8.09942245483398</v>
+        <v>8.0994234085083</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G492" t="n">
-        <v>8.61250782012939</v>
+        <v>8.61250877380371</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G493" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>9.25386619567871</v>
+        <v>9.25386524200439</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G495" t="n">
-        <v>9.25386619567871</v>
+        <v>9.25386524200439</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>9.2996768951416</v>
+        <v>9.29967594146729</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>9.2996768951416</v>
+        <v>9.29967594146729</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>9.2996768951416</v>
+        <v>9.29967594146729</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10</v>
       </c>
       <c r="G503" t="n">
-        <v>9.1622428894043</v>
+        <v>9.16224384307861</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G505" t="n">
-        <v>9.10726928710938</v>
+        <v>9.10726833343506</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>8.85988903045654</v>
+        <v>8.85988807678223</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G515" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G517" t="n">
-        <v>8.82324028015137</v>
+        <v>8.82324123382568</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G519" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G522" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G527" t="n">
-        <v>8.66305541992188</v>
+        <v>8.66305637359619</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>9.25</v>
       </c>
       <c r="G528" t="n">
-        <v>8.67243099212646</v>
+        <v>8.67243194580078</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G530" t="n">
-        <v>8.50367069244385</v>
+        <v>8.50366973876953</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G531" t="n">
-        <v>8.34428596496582</v>
+        <v>8.3442850112915</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G533" t="n">
-        <v>8.00676441192627</v>
+        <v>8.00676345825195</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>8.15677356719971</v>
+        <v>8.15677261352539</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>8.5</v>
       </c>
       <c r="G536" t="n">
-        <v>7.96926116943359</v>
+        <v>7.96926164627075</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>7.88488101959229</v>
+        <v>7.88488054275513</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G539" t="n">
-        <v>7.84737825393677</v>
+        <v>7.84737873077393</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G540" t="n">
-        <v>7.85675477981567</v>
+        <v>7.85675430297852</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>7.80987596511841</v>
+        <v>7.80987644195557</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G544" t="n">
-        <v>7.83800220489502</v>
+        <v>7.83800268173218</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G545" t="n">
-        <v>7.85675477981567</v>
+        <v>7.85675430297852</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>7.80987596511841</v>
+        <v>7.80987644195557</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G550" t="n">
-        <v>7.80987596511841</v>
+        <v>7.80987644195557</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G556" t="n">
-        <v>7.55673551559448</v>
+        <v>7.55673503875732</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G558" t="n">
-        <v>7.6317400932312</v>
+        <v>7.63174057006836</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G559" t="n">
-        <v>7.72549533843994</v>
+        <v>7.7254958152771</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G561" t="n">
-        <v>7.60361289978027</v>
+        <v>7.60361242294312</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G562" t="n">
-        <v>7.60361289978027</v>
+        <v>7.60361242294312</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>8.25</v>
       </c>
       <c r="G564" t="n">
-        <v>7.73487091064453</v>
+        <v>7.73487138748169</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G565" t="n">
-        <v>7.77237415313721</v>
+        <v>7.77237367630005</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G567" t="n">
-        <v>7.77237415313721</v>
+        <v>7.77237367630005</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G570" t="n">
-        <v>8.10052108764648</v>
+        <v>8.10052013397217</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G571" t="n">
-        <v>7.85675477981567</v>
+        <v>7.85675430297852</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>8.00676441192627</v>
+        <v>8.00676345825195</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>8.5</v>
       </c>
       <c r="G574" t="n">
-        <v>7.96926116943359</v>
+        <v>7.96926164627075</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G576" t="n">
-        <v>7.8755054473877</v>
+        <v>7.87550497055054</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>8.25</v>
       </c>
       <c r="G578" t="n">
-        <v>7.73487091064453</v>
+        <v>7.73487138748169</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G581" t="n">
-        <v>7.77237415313721</v>
+        <v>7.77237367630005</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>7.80987596511841</v>
+        <v>7.80987644195557</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.25</v>
       </c>
       <c r="G583" t="n">
-        <v>7.73487091064453</v>
+        <v>7.73487138748169</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.25</v>
       </c>
       <c r="G585" t="n">
-        <v>7.73487091064453</v>
+        <v>7.73487138748169</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G592" t="n">
-        <v>7.05045223236084</v>
+        <v>7.050452709198</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G595" t="n">
-        <v>6.66605281829834</v>
+        <v>6.6660532951355</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G597" t="n">
-        <v>6.54417037963867</v>
+        <v>6.54416990280151</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G605" t="n">
-        <v>6.18789720535278</v>
+        <v>6.18789672851562</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G606" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.5</v>
       </c>
       <c r="G609" t="n">
-        <v>6.09414100646973</v>
+        <v>6.09414148330688</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G610" t="n">
-        <v>6.44103813171387</v>
+        <v>6.44103860855103</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G611" t="n">
-        <v>6.21602392196655</v>
+        <v>6.21602439880371</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G612" t="n">
-        <v>6.30040454864502</v>
+        <v>6.30040407180786</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G615" t="n">
-        <v>6.49729204177856</v>
+        <v>6.49729156494141</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G617" t="n">
-        <v>6.58167219161987</v>
+        <v>6.58167266845703</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G619" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G632" t="n">
-        <v>6.40353584289551</v>
+        <v>6.40353631973267</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G634" t="n">
-        <v>6.45041418075562</v>
+        <v>6.45041370391846</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G637" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G638" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G639" t="n">
-        <v>6.41291189193726</v>
+        <v>6.4129114151001</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>6.41291189193726</v>
+        <v>6.4129114151001</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G645" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G647" t="n">
-        <v>7.09733057022095</v>
+        <v>7.09733104705811</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G649" t="n">
-        <v>6.58167219161987</v>
+        <v>6.58167266845703</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G650" t="n">
-        <v>6.54417037963867</v>
+        <v>6.54416990280151</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G652" t="n">
-        <v>6.51604270935059</v>
+        <v>6.51604318618774</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G655" t="n">
-        <v>6.54417037963867</v>
+        <v>6.54416990280151</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>6.63792562484741</v>
+        <v>6.63792610168457</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G660" t="n">
-        <v>6.54417037963867</v>
+        <v>6.54416990280151</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>6.63792562484741</v>
+        <v>6.63792610168457</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G662" t="n">
-        <v>6.51604270935059</v>
+        <v>6.51604318618774</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G666" t="n">
-        <v>5.30659055709839</v>
+        <v>5.30659008026123</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>4.88468885421753</v>
+        <v>4.88468837738037</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G674" t="n">
-        <v>5.6816143989563</v>
+        <v>5.68161487579346</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G675" t="n">
-        <v>5.84100008010864</v>
+        <v>5.84099960327148</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G677" t="n">
-        <v>6.05663919448853</v>
+        <v>6.05663871765137</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G678" t="n">
-        <v>6.27227735519409</v>
+        <v>6.27227783203125</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>6.05663919448853</v>
+        <v>6.05663871765137</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G683" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G684" t="n">
-        <v>5.76599550247192</v>
+        <v>5.76599502563477</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G685" t="n">
-        <v>5.83162403106689</v>
+        <v>5.83162450790405</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G686" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G687" t="n">
-        <v>5.83162403106689</v>
+        <v>5.83162450790405</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G689" t="n">
-        <v>5.88787841796875</v>
+        <v>5.88787794113159</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G692" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G694" t="n">
-        <v>5.86912679672241</v>
+        <v>5.86912727355957</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G696" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G697" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G706" t="n">
-        <v>6.10351705551147</v>
+        <v>6.10351657867432</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G709" t="n">
-        <v>6.04726266860962</v>
+        <v>6.04726314544678</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>5.84100008010864</v>
+        <v>5.84099960327148</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G711" t="n">
-        <v>5.88787841796875</v>
+        <v>5.88787794113159</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G714" t="n">
-        <v>5.6816143989563</v>
+        <v>5.68161487579346</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G723" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G725" t="n">
-        <v>5.83162403106689</v>
+        <v>5.83162450790405</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G726" t="n">
-        <v>5.76599550247192</v>
+        <v>5.76599502563477</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G728" t="n">
-        <v>5.33471727371216</v>
+        <v>5.33471775054932</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>5.23158597946167</v>
+        <v>5.23158550262451</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G731" t="n">
-        <v>4.69717693328857</v>
+        <v>4.69717645645142</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G732" t="n">
-        <v>4.8003077507019</v>
+        <v>4.80030822753906</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G734" t="n">
-        <v>4.73467922210693</v>
+        <v>4.73467874526978</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G739" t="n">
-        <v>3.93775272369385</v>
+        <v>3.93775248527527</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G741" t="n">
-        <v>3.7408652305603</v>
+        <v>3.74086499214172</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G750" t="n">
-        <v>3.05175852775574</v>
+        <v>3.05175828933716</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G756" t="n">
-        <v>3.15020227432251</v>
+        <v>3.15020203590393</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G764" t="n">
-        <v>3.05644631385803</v>
+        <v>3.05644607543945</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G767" t="n">
-        <v>2.75642681121826</v>
+        <v>2.75642704963684</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G770" t="n">
-        <v>2.66735863685608</v>
+        <v>2.66735887527466</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G779" t="n">
-        <v>3.11738777160645</v>
+        <v>3.11738753318787</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>3.25</v>
       </c>
       <c r="G782" t="n">
-        <v>3.04707050323486</v>
+        <v>3.04707074165344</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G783" t="n">
-        <v>3.09394860267639</v>
+        <v>3.09394836425781</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G784" t="n">
-        <v>3.05644631385803</v>
+        <v>3.05644607543945</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G788" t="n">
-        <v>2.77049040794373</v>
+        <v>2.77049016952515</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G789" t="n">
-        <v>2.75642681121826</v>
+        <v>2.75642704963684</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G790" t="n">
-        <v>2.70954918861389</v>
+        <v>2.70954895019531</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G793" t="n">
-        <v>2.95331454277039</v>
+        <v>2.95331478118896</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G794" t="n">
-        <v>2.95331454277039</v>
+        <v>2.95331478118896</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>3.37521648406982</v>
+        <v>3.3752167224884</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>3.53460192680359</v>
+        <v>3.53460168838501</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G818" t="n">
-        <v>3.65179705619812</v>
+        <v>3.65179681777954</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.63773345947266</v>
+        <v>3.63773369789124</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G833" t="n">
-        <v>3.665860414505</v>
+        <v>3.66586017608643</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G834" t="n">
-        <v>3.665860414505</v>
+        <v>3.66586017608643</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G844" t="n">
-        <v>3.32365107536316</v>
+        <v>3.32365083694458</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G845" t="n">
-        <v>3.46428465843201</v>
+        <v>3.46428489685059</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G851" t="n">
-        <v>3.7408652305603</v>
+        <v>3.74086499214172</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>3.36115336418152</v>
+        <v>3.36115312576294</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G873" t="n">
-        <v>3.48772382736206</v>
+        <v>3.48772406578064</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G874" t="n">
-        <v>3.58616757392883</v>
+        <v>3.58616781234741</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>3.53460192680359</v>
+        <v>3.53460168838501</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>3.31896281242371</v>
+        <v>3.31896305084229</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>3.36115336418152</v>
+        <v>3.36115312576294</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>3.35646533966064</v>
+        <v>3.35646557807922</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G886" t="n">
-        <v>3.29083609580994</v>
+        <v>3.29083633422852</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G887" t="n">
-        <v>3.33302640914917</v>
+        <v>3.33302664756775</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G889" t="n">
-        <v>3.58616757392883</v>
+        <v>3.58616781234741</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G892" t="n">
-        <v>3.49241161346436</v>
+        <v>3.49241137504578</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>3.36115336418152</v>
+        <v>3.36115312576294</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>3.29083609580994</v>
+        <v>3.29083633422852</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G903" t="n">
-        <v>3.02831959724426</v>
+        <v>3.02831935882568</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G906" t="n">
-        <v>2.95331454277039</v>
+        <v>2.95331478118896</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G909" t="n">
-        <v>3.18770480155945</v>
+        <v>3.18770456314087</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>3.36115336418152</v>
+        <v>3.36115312576294</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G920" t="n">
-        <v>3.87681174278259</v>
+        <v>3.87681150436401</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G921" t="n">
-        <v>3.92368912696838</v>
+        <v>3.92368936538696</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G922" t="n">
-        <v>3.82524561882019</v>
+        <v>3.82524538040161</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G924" t="n">
-        <v>3.92837738990784</v>
+        <v>3.92837715148926</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>3.97056746482849</v>
+        <v>3.97056770324707</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>3.91900110244751</v>
+        <v>3.91900134086609</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.75</v>
       </c>
       <c r="G935" t="n">
-        <v>4.45341062545776</v>
+        <v>4.45341110229492</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G942" t="n">
-        <v>4.5096640586853</v>
+        <v>4.50966453552246</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G944" t="n">
-        <v>4.51904058456421</v>
+        <v>4.51904010772705</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G948" t="n">
-        <v>4.4721622467041</v>
+        <v>4.47216176986694</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G949" t="n">
-        <v>4.50497627258301</v>
+        <v>4.50497674942017</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G953" t="n">
-        <v>4.40184545516968</v>
+        <v>4.40184497833252</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G954" t="n">
-        <v>4.34090328216553</v>
+        <v>4.34090375900269</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.5</v>
       </c>
       <c r="G955" t="n">
-        <v>4.2190203666687</v>
+        <v>4.21902084350586</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.5</v>
       </c>
       <c r="G958" t="n">
-        <v>4.2190203666687</v>
+        <v>4.21902084350586</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G961" t="n">
-        <v>4.17214298248291</v>
+        <v>4.17214250564575</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G963" t="n">
-        <v>3.93775272369385</v>
+        <v>3.93775248527527</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G966" t="n">
-        <v>3.97056746482849</v>
+        <v>3.97056770324707</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G967" t="n">
-        <v>4.01744508743286</v>
+        <v>4.01744556427002</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G969" t="n">
-        <v>4.26589870452881</v>
+        <v>4.26589918136597</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G974" t="n">
-        <v>4.61279630661011</v>
+        <v>4.61279582977295</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G978" t="n">
-        <v>5.0534496307373</v>
+        <v>5.05344915390015</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G982" t="n">
-        <v>5.22220993041992</v>
+        <v>5.22221040725708</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G985" t="n">
-        <v>5.14720487594604</v>
+        <v>5.1472053527832</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G986" t="n">
-        <v>5.02532243728638</v>
+        <v>5.02532291412354</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G990" t="n">
-        <v>5.00657176971436</v>
+        <v>5.0065712928772</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G993" t="n">
-        <v>4.95969343185425</v>
+        <v>4.95969295501709</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G995" t="n">
-        <v>5.21283435821533</v>
+        <v>5.21283483505249</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G997" t="n">
-        <v>5.10970306396484</v>
+        <v>5.10970258712769</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G999" t="n">
-        <v>5.0534496307373</v>
+        <v>5.05344915390015</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1000" t="n">
-        <v>5.10970306396484</v>
+        <v>5.10970258712769</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>5.0534496307373</v>
+        <v>5.05344915390015</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.95031785964966</v>
+        <v>4.95031833648682</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.98782014846802</v>
+        <v>4.98782062530518</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.95031785964966</v>
+        <v>4.95031833648682</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1015" t="n">
-        <v>5.0534496307373</v>
+        <v>5.05344915390015</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1019" t="n">
-        <v>5.54098081588745</v>
+        <v>5.54098033905029</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1020" t="n">
-        <v>5.51285362243652</v>
+        <v>5.51285409927368</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>5.30659055709839</v>
+        <v>5.30659008026123</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1025" t="n">
-        <v>5.3534688949585</v>
+        <v>5.35346841812134</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1026" t="n">
-        <v>5.61598539352417</v>
+        <v>5.61598491668701</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1029" t="n">
-        <v>5.4941029548645</v>
+        <v>5.49410247802734</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1035" t="n">
-        <v>5.878502368927</v>
+        <v>5.87850189208984</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1038" t="n">
-        <v>5.6816143989563</v>
+        <v>5.68161487579346</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1044" t="n">
-        <v>5.83162403106689</v>
+        <v>5.83162450790405</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1045" t="n">
-        <v>5.86912679672241</v>
+        <v>5.86912727355957</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1047" t="n">
-        <v>5.78474617004395</v>
+        <v>5.7847466468811</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1052" t="n">
-        <v>6.00976085662842</v>
+        <v>6.00976037979126</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1054" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1060" t="n">
-        <v>5.76599550247192</v>
+        <v>5.76599502563477</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>6.5</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.09414100646973</v>
+        <v>6.09414148330688</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>6.58167219161987</v>
+        <v>6.58167266845703</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G1069" t="n">
-        <v>6.49729204177856</v>
+        <v>6.49729156494141</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.41291189193726</v>
+        <v>6.4129114151001</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1072" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1073" t="n">
-        <v>6.23477554321289</v>
+        <v>6.23477506637573</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1075" t="n">
-        <v>6.23477554321289</v>
+        <v>6.23477506637573</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1081" t="n">
-        <v>6.27227735519409</v>
+        <v>6.27227783203125</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.878502368927</v>
+        <v>5.87850189208984</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1088" t="n">
-        <v>6.18789720535278</v>
+        <v>6.18789672851562</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1100" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1103" t="n">
-        <v>6.94732093811035</v>
+        <v>6.94732046127319</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1105" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1107" t="n">
-        <v>6.72230672836304</v>
+        <v>6.72230625152588</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.97544765472412</v>
+        <v>6.97544813156128</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1110" t="n">
-        <v>6.66605281829834</v>
+        <v>6.6660532951355</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1111" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>7.42547702789307</v>
+        <v>7.42547655105591</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1122" t="n">
-        <v>7.30359411239624</v>
+        <v>7.30359363555908</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1123" t="n">
-        <v>7.15358400344849</v>
+        <v>7.15358448028564</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1124" t="n">
-        <v>7.30359411239624</v>
+        <v>7.30359363555908</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1126" t="n">
-        <v>6.66605281829834</v>
+        <v>6.6660532951355</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1136" t="n">
-        <v>6.66605281829834</v>
+        <v>6.6660532951355</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1141" t="n">
-        <v>6.45041418075562</v>
+        <v>6.45041370391846</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1150" t="n">
-        <v>7.48173046112061</v>
+        <v>7.48172998428345</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1151" t="n">
-        <v>7.33172082901001</v>
+        <v>7.33172035217285</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1152" t="n">
-        <v>7.32234477996826</v>
+        <v>7.32234525680542</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1157" t="n">
-        <v>7.37859869003296</v>
+        <v>7.3785982131958</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1158" t="n">
-        <v>7.25671577453613</v>
+        <v>7.25671529769897</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1160" t="n">
-        <v>7.2848424911499</v>
+        <v>7.28484296798706</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1162" t="n">
-        <v>7.72549533843994</v>
+        <v>7.7254958152771</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1166" t="n">
-        <v>7.84737825393677</v>
+        <v>7.84737873077393</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1167" t="n">
-        <v>7.66924238204956</v>
+        <v>7.66924285888672</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1175" t="n">
-        <v>7.15358400344849</v>
+        <v>7.15358448028564</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1176" t="n">
-        <v>7.25671577453613</v>
+        <v>7.25671529769897</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1182" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1191" t="n">
-        <v>7.18171119689941</v>
+        <v>7.18171072006226</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1195" t="n">
-        <v>7.18171119689941</v>
+        <v>7.18171072006226</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1203" t="n">
-        <v>7.18171119689941</v>
+        <v>7.18171072006226</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>7.30359411239624</v>
+        <v>7.30359363555908</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1209" t="n">
-        <v>6.89106750488281</v>
+        <v>6.89106702804565</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.98482322692871</v>
+        <v>6.98482275009155</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1213" t="n">
-        <v>6.98482322692871</v>
+        <v>6.98482275009155</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1214" t="n">
-        <v>7.18171119689941</v>
+        <v>7.18171072006226</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1220" t="n">
-        <v>6.51604270935059</v>
+        <v>6.51604318618774</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.71293067932129</v>
+        <v>6.71293115615845</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1226" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1230" t="n">
-        <v>6.18789720535278</v>
+        <v>6.18789672851562</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1231" t="n">
-        <v>6.41291189193726</v>
+        <v>6.4129114151001</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>6.11289262771606</v>
+        <v>6.11289215087891</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>6.5</v>
       </c>
       <c r="G1234" t="n">
-        <v>6.09414100646973</v>
+        <v>6.09414148330688</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1235" t="n">
-        <v>6.21602392196655</v>
+        <v>6.21602439880371</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1239" t="n">
-        <v>6.18789720535278</v>
+        <v>6.18789672851562</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1242" t="n">
-        <v>5.75661897659302</v>
+        <v>5.75661945343018</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1245" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1250" t="n">
-        <v>5.21283435821533</v>
+        <v>5.21283483505249</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1255" t="n">
-        <v>5.51285362243652</v>
+        <v>5.51285409927368</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1260" t="n">
-        <v>6.23477554321289</v>
+        <v>6.23477506637573</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1262" t="n">
-        <v>6.21602392196655</v>
+        <v>6.21602439880371</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1264" t="n">
-        <v>6.30040454864502</v>
+        <v>6.30040407180786</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1265" t="n">
-        <v>6.27227735519409</v>
+        <v>6.27227783203125</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1267" t="n">
-        <v>6.16914558410645</v>
+        <v>6.1691460609436</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1268" t="n">
-        <v>6.10351705551147</v>
+        <v>6.10351657867432</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1281" t="n">
-        <v>6.04726266860962</v>
+        <v>6.04726314544678</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.878502368927</v>
+        <v>5.87850189208984</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1283" t="n">
-        <v>5.76599550247192</v>
+        <v>5.76599502563477</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -62824,6 +62824,32 @@
         <v>1.34599995613098</v>
       </c>
       <c r="H2402" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2403">
+      <c r="A2403" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2403" t="n">
+        <v>100264</v>
+      </c>
+      <c r="C2403" t="n">
+        <v>1.35399997234344</v>
+      </c>
+      <c r="D2403" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="E2403" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="F2403" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="G2403" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="H2403" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G2" t="n">
-        <v>9.13568305969238</v>
+        <v>9.1356840133667</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G3" t="n">
-        <v>9.27969360351562</v>
+        <v>9.27969455718994</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>9.28869533538818</v>
+        <v>9.28869438171387</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>10.5</v>
       </c>
       <c r="G6" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>10.5</v>
       </c>
       <c r="G8" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>9.44170570373535</v>
+        <v>9.44170665740967</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>10.5</v>
       </c>
       <c r="G17" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>10.5</v>
       </c>
       <c r="G18" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>10.5</v>
       </c>
       <c r="G19" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G21" t="n">
-        <v>9.5587158203125</v>
+        <v>9.55871486663818</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G22" t="n">
-        <v>9.48671054840088</v>
+        <v>9.48670959472656</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>9.4957103729248</v>
+        <v>9.49570941925049</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>9.4957103729248</v>
+        <v>9.49570941925049</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>9.6307201385498</v>
+        <v>9.63072109222412</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G28" t="n">
-        <v>9.6307201385498</v>
+        <v>9.63072109222412</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G29" t="n">
-        <v>9.6307201385498</v>
+        <v>9.63072109222412</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G30" t="n">
-        <v>9.62171936035156</v>
+        <v>9.62172031402588</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>9.6307201385498</v>
+        <v>9.63072109222412</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G32" t="n">
-        <v>9.6307201385498</v>
+        <v>9.63072109222412</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G40" t="n">
-        <v>9.90974235534668</v>
+        <v>9.90974140167236</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G41" t="n">
-        <v>9.90974235534668</v>
+        <v>9.90974140167236</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G42" t="n">
-        <v>9.91874217987061</v>
+        <v>9.91874313354492</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G43" t="n">
-        <v>9.91874217987061</v>
+        <v>9.91874313354492</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>9.94574356079102</v>
+        <v>9.94574546813965</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>12</v>
       </c>
       <c r="G48" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>12.5</v>
       </c>
       <c r="G49" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508411407471</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>12.5</v>
       </c>
       <c r="G50" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508411407471</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>12</v>
       </c>
       <c r="G52" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>12</v>
       </c>
       <c r="G54" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>10.9358177185059</v>
+        <v>10.9358186721802</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G57" t="n">
-        <v>10.7648048400879</v>
+        <v>10.7648057937622</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G59" t="n">
-        <v>10.7738065719604</v>
+        <v>10.7738056182861</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G60" t="n">
-        <v>10.8368120193481</v>
+        <v>10.8368110656738</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G61" t="n">
-        <v>10.7918081283569</v>
+        <v>10.7918062210083</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G63" t="n">
-        <v>10.8368120193481</v>
+        <v>10.8368110656738</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G66" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G67" t="n">
-        <v>10.9358177185059</v>
+        <v>10.9358186721802</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>12</v>
       </c>
       <c r="G77" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G79" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>12.5</v>
       </c>
       <c r="G80" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508411407471</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>12.5</v>
       </c>
       <c r="G81" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508411407471</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G86" t="n">
-        <v>11.0078229904175</v>
+        <v>11.0078239440918</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G87" t="n">
-        <v>11.0078229904175</v>
+        <v>11.0078239440918</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>12</v>
       </c>
       <c r="G89" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>12</v>
       </c>
       <c r="G90" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808206558228</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G97" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G98" t="n">
-        <v>11.0978298187256</v>
+        <v>11.0978307723999</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808206558228</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808206558228</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G105" t="n">
-        <v>11.1518354415894</v>
+        <v>11.151834487915</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G107" t="n">
-        <v>11.0348262786865</v>
+        <v>11.0348253250122</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G108" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G109" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G111" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G113" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G114" t="n">
-        <v>10.953818321228</v>
+        <v>10.9538192749023</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G115" t="n">
-        <v>11.0438261032104</v>
+        <v>11.0438270568848</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>11.2418403625488</v>
+        <v>11.2418413162231</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G120" t="n">
-        <v>11.0978298187256</v>
+        <v>11.0978307723999</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G123" t="n">
-        <v>11.1518354415894</v>
+        <v>11.151834487915</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G124" t="n">
-        <v>11.0888299942017</v>
+        <v>11.0888290405273</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>11.0978298187256</v>
+        <v>11.0978307723999</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>12</v>
       </c>
       <c r="G130" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G131" t="n">
-        <v>11.0438261032104</v>
+        <v>11.0438270568848</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>12.5</v>
       </c>
       <c r="G140" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508411407471</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>12.5</v>
       </c>
       <c r="G141" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508411407471</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G143" t="n">
-        <v>11.2778434753418</v>
+        <v>11.2778425216675</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G150" t="n">
-        <v>11.6828737258911</v>
+        <v>11.6828727722168</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G151" t="n">
-        <v>11.6738739013672</v>
+        <v>11.6738729476929</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G154" t="n">
-        <v>11.8178853988647</v>
+        <v>11.8178844451904</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G161" t="n">
-        <v>11.493860244751</v>
+        <v>11.4938611984253</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G162" t="n">
-        <v>11.5028610229492</v>
+        <v>11.5028600692749</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G165" t="n">
-        <v>11.8628883361816</v>
+        <v>11.8628873825073</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>11.9708948135376</v>
+        <v>11.9708957672119</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>11.9708948135376</v>
+        <v>11.9708957672119</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G170" t="n">
-        <v>11.6828737258911</v>
+        <v>11.6828727722168</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>12.5</v>
       </c>
       <c r="G172" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508411407471</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G173" t="n">
-        <v>11.187837600708</v>
+        <v>11.1878366470337</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G174" t="n">
-        <v>11.0348262786865</v>
+        <v>11.0348253250122</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G178" t="n">
-        <v>11.0348262786865</v>
+        <v>11.0348253250122</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>10.9358177185059</v>
+        <v>10.9358186721802</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G181" t="n">
-        <v>10.8728141784668</v>
+        <v>10.8728132247925</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G182" t="n">
-        <v>10.7918081283569</v>
+        <v>10.7918062210083</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>10.9358177185059</v>
+        <v>10.9358186721802</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G185" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G187" t="n">
-        <v>11.1968383789062</v>
+        <v>11.1968374252319</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G189" t="n">
-        <v>11.2418403625488</v>
+        <v>11.2418413162231</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G191" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G194" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>10.9358177185059</v>
+        <v>10.9358186721802</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808206558228</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>11.3858518600464</v>
+        <v>11.3858509063721</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>11.7908840179443</v>
+        <v>11.79088306427</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G204" t="n">
-        <v>11.8808889389038</v>
+        <v>11.8808879852295</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>11.7908840179443</v>
+        <v>11.79088306427</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>12.5</v>
       </c>
       <c r="G215" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508411407471</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>12.5</v>
       </c>
       <c r="G216" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508411407471</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>10.9358177185059</v>
+        <v>10.9358186721802</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808206558228</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G224" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>12.5</v>
       </c>
       <c r="G225" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508411407471</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>12.5</v>
       </c>
       <c r="G229" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508411407471</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>10.6657981872559</v>
+        <v>10.6657972335815</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>12</v>
       </c>
       <c r="G234" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G236" t="n">
-        <v>10.6657981872559</v>
+        <v>10.6657972335815</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>12</v>
       </c>
       <c r="G239" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>12</v>
       </c>
       <c r="G243" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G249" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>12</v>
       </c>
       <c r="G250" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>12.5</v>
       </c>
       <c r="G253" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508411407471</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G255" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>12.5</v>
       </c>
       <c r="G258" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508411407471</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G260" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>12.5</v>
       </c>
       <c r="G264" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508411407471</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808206558228</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808206558228</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>11.1321249008179</v>
+        <v>11.1321258544922</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>11.7276706695557</v>
+        <v>11.72767162323</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>12.5</v>
       </c>
       <c r="G288" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>11.5</v>
       </c>
       <c r="G293" t="n">
-        <v>10.5365791320801</v>
+        <v>10.5365800857544</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G296" t="n">
-        <v>10.6282024383545</v>
+        <v>10.6282014846802</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>11.75</v>
       </c>
       <c r="G298" t="n">
-        <v>10.7656354904175</v>
+        <v>10.7656364440918</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>11.4069929122925</v>
+        <v>11.4069919586182</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G303" t="n">
-        <v>11.4069929122925</v>
+        <v>11.4069919586182</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G308" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G310" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>11.4069929122925</v>
+        <v>11.4069919586182</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>11.1321249008179</v>
+        <v>11.1321258544922</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>12.5</v>
       </c>
       <c r="G319" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G322" t="n">
-        <v>11.1321249008179</v>
+        <v>11.1321258544922</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>12.5</v>
       </c>
       <c r="G330" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G331" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>12.0025396347046</v>
+        <v>12.0025386810303</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>12.5</v>
       </c>
       <c r="G339" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G342" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>11.4069929122925</v>
+        <v>11.4069919586182</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>12.5</v>
       </c>
       <c r="G347" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>11.1321249008179</v>
+        <v>11.1321258544922</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G354" t="n">
-        <v>11.4069929122925</v>
+        <v>11.4069919586182</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G362" t="n">
-        <v>11.1321249008179</v>
+        <v>11.1321258544922</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>12.5</v>
       </c>
       <c r="G370" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G375" t="n">
-        <v>11.4069929122925</v>
+        <v>11.4069919586182</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>12.5</v>
       </c>
       <c r="G376" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G377" t="n">
-        <v>11.4069929122925</v>
+        <v>11.4069919586182</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>12</v>
       </c>
       <c r="G387" t="n">
-        <v>10.9946918487549</v>
+        <v>10.9946908950806</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>12</v>
       </c>
       <c r="G388" t="n">
-        <v>10.9946918487549</v>
+        <v>10.9946908950806</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>9.528733253479</v>
+        <v>9.52873229980469</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>9.528733253479</v>
+        <v>9.52873229980469</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>8.88737487792969</v>
+        <v>8.887375831604</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G412" t="n">
-        <v>8.57585906982422</v>
+        <v>8.5758581161499</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G413" t="n">
-        <v>8.57585906982422</v>
+        <v>8.5758581161499</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G414" t="n">
-        <v>8.48423671722412</v>
+        <v>8.48423767089844</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9</v>
       </c>
       <c r="G417" t="n">
-        <v>8.24601936340332</v>
+        <v>8.246018409729</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G421" t="n">
-        <v>8.35596466064453</v>
+        <v>8.35596561431885</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G423" t="n">
-        <v>8.74077987670898</v>
+        <v>8.74077892303467</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G426" t="n">
-        <v>8.88737487792969</v>
+        <v>8.887375831604</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G428" t="n">
-        <v>8.90570068359375</v>
+        <v>8.90569972991943</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G432" t="n">
-        <v>8.68580532073975</v>
+        <v>8.68580627441406</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>8.2826681137085</v>
+        <v>8.28266716003418</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G435" t="n">
-        <v>8.19104480743408</v>
+        <v>8.1910457611084</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G451" t="n">
-        <v>8.44758892059326</v>
+        <v>8.44758796691895</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G452" t="n">
-        <v>8.48423671722412</v>
+        <v>8.48423767089844</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G453" t="n">
-        <v>8.44758892059326</v>
+        <v>8.44758796691895</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G454" t="n">
-        <v>8.48423671722412</v>
+        <v>8.48423767089844</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G455" t="n">
-        <v>8.55753517150879</v>
+        <v>8.55753612518311</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G456" t="n">
-        <v>8.61250877380371</v>
+        <v>8.61250782012939</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G457" t="n">
-        <v>8.5208854675293</v>
+        <v>8.52088642120361</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G458" t="n">
-        <v>8.44758892059326</v>
+        <v>8.44758796691895</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G460" t="n">
-        <v>8.55753517150879</v>
+        <v>8.55753612518311</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>8.5208854675293</v>
+        <v>8.52088642120361</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>8.55753517150879</v>
+        <v>8.55753612518311</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G466" t="n">
-        <v>8.61250877380371</v>
+        <v>8.61250782012939</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G467" t="n">
-        <v>8.61250877380371</v>
+        <v>8.61250782012939</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G473" t="n">
-        <v>8.5208854675293</v>
+        <v>8.52088642120361</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G474" t="n">
-        <v>8.48423671722412</v>
+        <v>8.48423767089844</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>8.5208854675293</v>
+        <v>8.52088642120361</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G478" t="n">
-        <v>8.5208854675293</v>
+        <v>8.52088642120361</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G480" t="n">
-        <v>8.30099201202393</v>
+        <v>8.30099296569824</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G482" t="n">
-        <v>8.48423671722412</v>
+        <v>8.48423767089844</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G492" t="n">
-        <v>8.61250877380371</v>
+        <v>8.61250782012939</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G493" t="n">
-        <v>8.88737487792969</v>
+        <v>8.887375831604</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G501" t="n">
-        <v>9.2080545425415</v>
+        <v>9.20805358886719</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G511" t="n">
-        <v>8.81407737731934</v>
+        <v>8.81407833099365</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G513" t="n">
-        <v>8.81407737731934</v>
+        <v>8.81407833099365</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>8.85988807678223</v>
+        <v>8.85988903045654</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G515" t="n">
-        <v>8.88737487792969</v>
+        <v>8.887375831604</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G517" t="n">
-        <v>8.82324123382568</v>
+        <v>8.82324028015137</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G519" t="n">
-        <v>8.88737487792969</v>
+        <v>8.887375831604</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G522" t="n">
-        <v>8.88737487792969</v>
+        <v>8.887375831604</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -62850,6 +62850,32 @@
         <v>1.3400000333786</v>
       </c>
       <c r="H2403" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2404">
+      <c r="A2404" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2404" t="n">
+        <v>330784</v>
+      </c>
+      <c r="C2404" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="D2404" t="n">
+        <v>1.29200005531311</v>
+      </c>
+      <c r="E2404" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="F2404" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="G2404" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="H2404" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -447,7 +447,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G3" t="n">
-        <v>9.27969455718994</v>
+        <v>9.27969551086426</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>10.25</v>
       </c>
       <c r="G4" t="n">
-        <v>9.2256908416748</v>
+        <v>9.22568988800049</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>9.3607006072998</v>
+        <v>9.36069965362549</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G9" t="n">
-        <v>9.40570259094238</v>
+        <v>9.4057035446167</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>9.8107328414917</v>
+        <v>9.81073379516602</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>9.44170665740967</v>
+        <v>9.44170570373535</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.40570259094238</v>
+        <v>9.4057035446167</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>9.40570259094238</v>
+        <v>9.4057035446167</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G20" t="n">
-        <v>9.54071521759033</v>
+        <v>9.54071426391602</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>9.49570941925049</v>
+        <v>9.4957103729248</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>9.49570941925049</v>
+        <v>9.4957103729248</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G25" t="n">
-        <v>9.54071521759033</v>
+        <v>9.54071426391602</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>9.54071521759033</v>
+        <v>9.54071426391602</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G34" t="n">
-        <v>9.6937255859375</v>
+        <v>9.69372463226318</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G35" t="n">
-        <v>9.8107328414917</v>
+        <v>9.81073379516602</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G42" t="n">
-        <v>9.91874313354492</v>
+        <v>9.91874217987061</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G43" t="n">
-        <v>9.91874313354492</v>
+        <v>9.91874217987061</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>12</v>
       </c>
       <c r="G48" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>12.5</v>
       </c>
       <c r="G49" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>12.5</v>
       </c>
       <c r="G50" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>11.0708274841309</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>12</v>
       </c>
       <c r="G52" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G53" t="n">
-        <v>10.6927995681763</v>
+        <v>10.6928005218506</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>12</v>
       </c>
       <c r="G54" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>10.9358186721802</v>
+        <v>10.9358177185059</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G58" t="n">
-        <v>10.6927995681763</v>
+        <v>10.6928005218506</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G60" t="n">
-        <v>10.8368110656738</v>
+        <v>10.8368120193481</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G61" t="n">
-        <v>10.7918062210083</v>
+        <v>10.7918071746826</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G63" t="n">
-        <v>10.8368110656738</v>
+        <v>10.8368120193481</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G67" t="n">
-        <v>10.9358186721802</v>
+        <v>10.9358177185059</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>12</v>
       </c>
       <c r="G77" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>12.5</v>
       </c>
       <c r="G80" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>12.5</v>
       </c>
       <c r="G81" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>11.0708274841309</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G86" t="n">
-        <v>11.0078239440918</v>
+        <v>11.0078229904175</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G87" t="n">
-        <v>11.0078239440918</v>
+        <v>11.0078229904175</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>12</v>
       </c>
       <c r="G89" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>12</v>
       </c>
       <c r="G90" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>11.0708274841309</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>11.0708274841309</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>11.0708274841309</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>10.9808206558228</v>
+        <v>10.9808216094971</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G97" t="n">
-        <v>11.0708274841309</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G98" t="n">
-        <v>11.0978307723999</v>
+        <v>11.0978298187256</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>11.0708274841309</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>10.9808206558228</v>
+        <v>10.9808216094971</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>10.9808206558228</v>
+        <v>10.9808216094971</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>11.0708274841309</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G105" t="n">
-        <v>11.151834487915</v>
+        <v>11.1518335342407</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>11.0708274841309</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G108" t="n">
-        <v>11.0708274841309</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G111" t="n">
-        <v>11.0708274841309</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>11.0708274841309</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G113" t="n">
-        <v>11.0708274841309</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G120" t="n">
-        <v>11.0978307723999</v>
+        <v>11.0978298187256</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G123" t="n">
-        <v>11.151834487915</v>
+        <v>11.1518335342407</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G124" t="n">
-        <v>11.0888290405273</v>
+        <v>11.0888299942017</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G127" t="n">
-        <v>11.0528268814087</v>
+        <v>11.0528259277344</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>11.0978307723999</v>
+        <v>11.0978298187256</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>12</v>
       </c>
       <c r="G130" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G135" t="n">
-        <v>11.0528268814087</v>
+        <v>11.0528259277344</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>12.5</v>
       </c>
       <c r="G140" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>12.5</v>
       </c>
       <c r="G141" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G147" t="n">
-        <v>11.5208625793457</v>
+        <v>11.5208616256714</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G149" t="n">
-        <v>11.6018686294556</v>
+        <v>11.6018676757812</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G150" t="n">
-        <v>11.6828727722168</v>
+        <v>11.6828737258911</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G151" t="n">
-        <v>11.6738729476929</v>
+        <v>11.6738739013672</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G161" t="n">
-        <v>11.4938611984253</v>
+        <v>11.493860244751</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G164" t="n">
-        <v>11.6558713912964</v>
+        <v>11.6558723449707</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G165" t="n">
-        <v>11.8628873825073</v>
+        <v>11.8628883361816</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>11.6558713912964</v>
+        <v>11.6558723449707</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>11.9708957672119</v>
+        <v>11.9708967208862</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>11.9708957672119</v>
+        <v>11.9708967208862</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G170" t="n">
-        <v>11.6828727722168</v>
+        <v>11.6828737258911</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>12.5</v>
       </c>
       <c r="G172" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G173" t="n">
-        <v>11.1878366470337</v>
+        <v>11.187837600708</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G179" t="n">
-        <v>10.989821434021</v>
+        <v>10.9898223876953</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>10.9358186721802</v>
+        <v>10.9358177185059</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G182" t="n">
-        <v>10.7918062210083</v>
+        <v>10.7918071746826</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>10.9358186721802</v>
+        <v>10.9358177185059</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G185" t="n">
-        <v>11.0708274841309</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G187" t="n">
-        <v>11.1968374252319</v>
+        <v>11.1968364715576</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G191" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G194" t="n">
-        <v>11.0708274841309</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>10.9358186721802</v>
+        <v>10.9358177185059</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>10.9808206558228</v>
+        <v>10.9808216094971</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6558713912964</v>
+        <v>11.6558723449707</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>11.79088306427</v>
+        <v>11.7908821105957</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G204" t="n">
-        <v>11.8808879852295</v>
+        <v>11.8808889389038</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>11.6558713912964</v>
+        <v>11.6558723449707</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>11.79088306427</v>
+        <v>11.7908821105957</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>12.5</v>
       </c>
       <c r="G215" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>12.5</v>
       </c>
       <c r="G216" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>10.9358186721802</v>
+        <v>10.9358177185059</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>10.9808206558228</v>
+        <v>10.9808216094971</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>11.0708274841309</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G224" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>12.5</v>
       </c>
       <c r="G225" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>12.75</v>
       </c>
       <c r="G226" t="n">
-        <v>11.4758586883545</v>
+        <v>11.4758577346802</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>12.5</v>
       </c>
       <c r="G229" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>10.6657972335815</v>
+        <v>10.6657981872559</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G233" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>12</v>
       </c>
       <c r="G234" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G235" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G236" t="n">
-        <v>10.6657972335815</v>
+        <v>10.6657981872559</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>11.75</v>
       </c>
       <c r="G237" t="n">
-        <v>10.5757913589478</v>
+        <v>10.5757904052734</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>12</v>
       </c>
       <c r="G239" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>12</v>
       </c>
       <c r="G243" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7108011245728</v>
+        <v>10.7108001708984</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>12</v>
       </c>
       <c r="G250" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>11.0708274841309</v>
+        <v>11.0708284378052</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>12.5</v>
       </c>
       <c r="G253" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G255" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>12.75</v>
       </c>
       <c r="G256" t="n">
-        <v>11.4758586883545</v>
+        <v>11.4758577346802</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>12.75</v>
       </c>
       <c r="G257" t="n">
-        <v>11.4758586883545</v>
+        <v>11.4758577346802</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>12.5</v>
       </c>
       <c r="G258" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>12.5</v>
       </c>
       <c r="G264" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>10.9808206558228</v>
+        <v>10.9808216094971</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>10.9808206558228</v>
+        <v>10.9808216094971</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>11.1321258544922</v>
+        <v>11.1321249008179</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G280" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>11.5902366638184</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>10.6740131378174</v>
+        <v>10.6740121841431</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>11.5</v>
       </c>
       <c r="G293" t="n">
-        <v>10.5365800857544</v>
+        <v>10.5365791320801</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3991451263428</v>
+        <v>10.3991460800171</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>11.75</v>
       </c>
       <c r="G298" t="n">
-        <v>10.7656364440918</v>
+        <v>10.7656354904175</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>10.8114461898804</v>
+        <v>10.8114471435547</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>11.4069919586182</v>
+        <v>11.4069929122925</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G303" t="n">
-        <v>11.4069919586182</v>
+        <v>11.4069929122925</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>11.5902366638184</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>11.4069919586182</v>
+        <v>11.4069929122925</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>11.1321258544922</v>
+        <v>11.1321249008179</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G322" t="n">
-        <v>11.1321258544922</v>
+        <v>11.1321249008179</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G323" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>11.5902366638184</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G331" t="n">
-        <v>11.5902366638184</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>11.5902366638184</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G342" t="n">
-        <v>11.5902366638184</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>11.4069919586182</v>
+        <v>11.4069929122925</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>11.1321258544922</v>
+        <v>11.1321249008179</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G350" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G354" t="n">
-        <v>11.4069919586182</v>
+        <v>11.4069929122925</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G355" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G356" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G359" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G362" t="n">
-        <v>11.1321258544922</v>
+        <v>11.1321249008179</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>11.5902366638184</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G371" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G375" t="n">
-        <v>11.4069919586182</v>
+        <v>11.4069929122925</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G377" t="n">
-        <v>11.4069919586182</v>
+        <v>11.4069929122925</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G379" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G383" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>10.8114461898804</v>
+        <v>10.8114471435547</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>9.25386524200439</v>
+        <v>9.25386619567871</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G400" t="n">
-        <v>9.25386524200439</v>
+        <v>9.25386619567871</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>10.25</v>
       </c>
       <c r="G401" t="n">
-        <v>9.3912992477417</v>
+        <v>9.39129829406738</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>10</v>
       </c>
       <c r="G407" t="n">
-        <v>9.16224384307861</v>
+        <v>9.1622428894043</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>9.08894443511963</v>
+        <v>9.08894538879395</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.5</v>
       </c>
       <c r="G411" t="n">
-        <v>8.70413112640381</v>
+        <v>8.70413017272949</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G414" t="n">
-        <v>8.48423767089844</v>
+        <v>8.48423671722412</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>8.0994234085083</v>
+        <v>8.09942245483398</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9</v>
       </c>
       <c r="G417" t="n">
-        <v>8.246018409729</v>
+        <v>8.24601745605469</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G419" t="n">
-        <v>8.46591281890869</v>
+        <v>8.46591186523438</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G420" t="n">
-        <v>8.39261436462402</v>
+        <v>8.39261531829834</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G422" t="n">
-        <v>8.50256061553955</v>
+        <v>8.50256156921387</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G423" t="n">
-        <v>8.74077892303467</v>
+        <v>8.74077987670898</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>9.08894443511963</v>
+        <v>9.08894538879395</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>9.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.70413112640381</v>
+        <v>8.70413017272949</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G435" t="n">
-        <v>8.1910457611084</v>
+        <v>8.19104480743408</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>8.06277370452881</v>
+        <v>8.06277465820312</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G441" t="n">
-        <v>8.15439605712891</v>
+        <v>8.15439701080322</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G443" t="n">
-        <v>8.33764171600342</v>
+        <v>8.3376407623291</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.5</v>
       </c>
       <c r="G446" t="n">
-        <v>8.70413112640381</v>
+        <v>8.70413017272949</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G449" t="n">
-        <v>8.33764171600342</v>
+        <v>8.3376407623291</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G452" t="n">
-        <v>8.48423767089844</v>
+        <v>8.48423671722412</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G454" t="n">
-        <v>8.48423767089844</v>
+        <v>8.48423671722412</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G455" t="n">
-        <v>8.55753612518311</v>
+        <v>8.55753517150879</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G459" t="n">
-        <v>8.50256061553955</v>
+        <v>8.50256156921387</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G460" t="n">
-        <v>8.55753612518311</v>
+        <v>8.55753517150879</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G463" t="n">
-        <v>8.50256061553955</v>
+        <v>8.50256156921387</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>8.55753612518311</v>
+        <v>8.55753517150879</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G469" t="n">
-        <v>8.64915657043457</v>
+        <v>8.64915752410889</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G470" t="n">
-        <v>8.64915657043457</v>
+        <v>8.64915752410889</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G471" t="n">
-        <v>8.50256061553955</v>
+        <v>8.50256156921387</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G472" t="n">
-        <v>8.50256061553955</v>
+        <v>8.50256156921387</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G474" t="n">
-        <v>8.48423767089844</v>
+        <v>8.48423671722412</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G476" t="n">
-        <v>8.50256061553955</v>
+        <v>8.50256156921387</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G482" t="n">
-        <v>8.48423767089844</v>
+        <v>8.48423671722412</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G484" t="n">
-        <v>8.33764171600342</v>
+        <v>8.3376407623291</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G485" t="n">
-        <v>8.26434326171875</v>
+        <v>8.26434421539307</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G488" t="n">
-        <v>8.26434326171875</v>
+        <v>8.26434421539307</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G491" t="n">
-        <v>8.0994234085083</v>
+        <v>8.09942245483398</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>9.25386524200439</v>
+        <v>9.25386619567871</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G495" t="n">
-        <v>9.25386524200439</v>
+        <v>9.25386619567871</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>9.29967594146729</v>
+        <v>9.2996768951416</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>9.29967594146729</v>
+        <v>9.2996768951416</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>9.29967594146729</v>
+        <v>9.2996768951416</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G501" t="n">
-        <v>9.20805358886719</v>
+        <v>9.2080545425415</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10</v>
       </c>
       <c r="G503" t="n">
-        <v>9.16224384307861</v>
+        <v>9.1622428894043</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G505" t="n">
-        <v>9.10726833343506</v>
+        <v>9.10726928710938</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G511" t="n">
-        <v>8.81407833099365</v>
+        <v>8.81407737731934</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G513" t="n">
-        <v>8.81407833099365</v>
+        <v>8.81407737731934</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G527" t="n">
-        <v>8.66305637359619</v>
+        <v>8.66305541992188</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>9.25</v>
       </c>
       <c r="G528" t="n">
-        <v>8.67243194580078</v>
+        <v>8.67243099212646</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G530" t="n">
-        <v>8.50366973876953</v>
+        <v>8.50367069244385</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G531" t="n">
-        <v>8.3442850112915</v>
+        <v>8.34428596496582</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G533" t="n">
-        <v>8.00676345825195</v>
+        <v>8.00676441192627</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>8.15677261352539</v>
+        <v>8.15677356719971</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>8.5</v>
       </c>
       <c r="G536" t="n">
-        <v>7.96926164627075</v>
+        <v>7.96926116943359</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>7.88488054275513</v>
+        <v>7.88488101959229</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G539" t="n">
-        <v>7.84737873077393</v>
+        <v>7.84737825393677</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G540" t="n">
-        <v>7.85675430297852</v>
+        <v>7.85675477981567</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>7.80987644195557</v>
+        <v>7.80987596511841</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G544" t="n">
-        <v>7.83800268173218</v>
+        <v>7.83800220489502</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G545" t="n">
-        <v>7.85675430297852</v>
+        <v>7.85675477981567</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>7.80987644195557</v>
+        <v>7.80987596511841</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G550" t="n">
-        <v>7.80987644195557</v>
+        <v>7.80987596511841</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G556" t="n">
-        <v>7.55673503875732</v>
+        <v>7.55673551559448</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G558" t="n">
-        <v>7.63174057006836</v>
+        <v>7.6317400932312</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G559" t="n">
-        <v>7.7254958152771</v>
+        <v>7.72549533843994</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G561" t="n">
-        <v>7.60361242294312</v>
+        <v>7.60361289978027</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G562" t="n">
-        <v>7.60361242294312</v>
+        <v>7.60361289978027</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>8.25</v>
       </c>
       <c r="G564" t="n">
-        <v>7.73487138748169</v>
+        <v>7.73487091064453</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G565" t="n">
-        <v>7.77237367630005</v>
+        <v>7.77237415313721</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G567" t="n">
-        <v>7.77237367630005</v>
+        <v>7.77237415313721</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G570" t="n">
-        <v>8.10052013397217</v>
+        <v>8.10052108764648</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G571" t="n">
-        <v>7.85675430297852</v>
+        <v>7.85675477981567</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>8.00676345825195</v>
+        <v>8.00676441192627</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>8.5</v>
       </c>
       <c r="G574" t="n">
-        <v>7.96926164627075</v>
+        <v>7.96926116943359</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G576" t="n">
-        <v>7.87550497055054</v>
+        <v>7.8755054473877</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>8.25</v>
       </c>
       <c r="G578" t="n">
-        <v>7.73487138748169</v>
+        <v>7.73487091064453</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G581" t="n">
-        <v>7.77237367630005</v>
+        <v>7.77237415313721</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>7.80987644195557</v>
+        <v>7.80987596511841</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.25</v>
       </c>
       <c r="G583" t="n">
-        <v>7.73487138748169</v>
+        <v>7.73487091064453</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.25</v>
       </c>
       <c r="G585" t="n">
-        <v>7.73487138748169</v>
+        <v>7.73487091064453</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G592" t="n">
-        <v>7.050452709198</v>
+        <v>7.05045223236084</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G595" t="n">
-        <v>6.6660532951355</v>
+        <v>6.66605281829834</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G597" t="n">
-        <v>6.54416990280151</v>
+        <v>6.54417037963867</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G605" t="n">
-        <v>6.18789672851562</v>
+        <v>6.18789720535278</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G606" t="n">
-        <v>6.37540912628174</v>
+        <v>6.3754096031189</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.5</v>
       </c>
       <c r="G609" t="n">
-        <v>6.09414148330688</v>
+        <v>6.09414100646973</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G610" t="n">
-        <v>6.44103860855103</v>
+        <v>6.44103813171387</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G611" t="n">
-        <v>6.21602439880371</v>
+        <v>6.21602392196655</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G612" t="n">
-        <v>6.30040407180786</v>
+        <v>6.30040454864502</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G615" t="n">
-        <v>6.49729156494141</v>
+        <v>6.49729204177856</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G617" t="n">
-        <v>6.58167266845703</v>
+        <v>6.58167219161987</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G619" t="n">
-        <v>6.75043344497681</v>
+        <v>6.75043296813965</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G632" t="n">
-        <v>6.40353631973267</v>
+        <v>6.40353584289551</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G634" t="n">
-        <v>6.45041370391846</v>
+        <v>6.45041418075562</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G637" t="n">
-        <v>6.37540912628174</v>
+        <v>6.3754096031189</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G638" t="n">
-        <v>6.37540912628174</v>
+        <v>6.3754096031189</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G639" t="n">
-        <v>6.4129114151001</v>
+        <v>6.41291189193726</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>6.4129114151001</v>
+        <v>6.41291189193726</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>6.75043344497681</v>
+        <v>6.75043296813965</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G645" t="n">
-        <v>6.92856979370117</v>
+        <v>6.92856931686401</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G647" t="n">
-        <v>7.09733104705811</v>
+        <v>7.09733057022095</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G649" t="n">
-        <v>6.58167266845703</v>
+        <v>6.58167219161987</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G650" t="n">
-        <v>6.54416990280151</v>
+        <v>6.54417037963867</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G652" t="n">
-        <v>6.51604318618774</v>
+        <v>6.51604270935059</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G655" t="n">
-        <v>6.54416990280151</v>
+        <v>6.54417037963867</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>6.63792610168457</v>
+        <v>6.63792562484741</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G660" t="n">
-        <v>6.54416990280151</v>
+        <v>6.54417037963867</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>6.63792610168457</v>
+        <v>6.63792562484741</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G662" t="n">
-        <v>6.51604318618774</v>
+        <v>6.51604270935059</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G666" t="n">
-        <v>5.30659008026123</v>
+        <v>5.30659055709839</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>4.88468837738037</v>
+        <v>4.88468885421753</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G674" t="n">
-        <v>5.68161487579346</v>
+        <v>5.6816143989563</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G675" t="n">
-        <v>5.84099960327148</v>
+        <v>5.84100008010864</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G677" t="n">
-        <v>6.05663871765137</v>
+        <v>6.05663919448853</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G678" t="n">
-        <v>6.27227783203125</v>
+        <v>6.27227735519409</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>6.05663871765137</v>
+        <v>6.05663919448853</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G683" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G684" t="n">
-        <v>5.76599502563477</v>
+        <v>5.76599550247192</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G685" t="n">
-        <v>5.83162450790405</v>
+        <v>5.83162403106689</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G686" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G687" t="n">
-        <v>5.83162450790405</v>
+        <v>5.83162403106689</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G689" t="n">
-        <v>5.88787794113159</v>
+        <v>5.88787841796875</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G692" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G694" t="n">
-        <v>5.86912727355957</v>
+        <v>5.86912679672241</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G696" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G697" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G706" t="n">
-        <v>6.10351657867432</v>
+        <v>6.10351705551147</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G709" t="n">
-        <v>6.04726314544678</v>
+        <v>6.04726266860962</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>5.84099960327148</v>
+        <v>5.84100008010864</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G711" t="n">
-        <v>5.88787794113159</v>
+        <v>5.88787841796875</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G714" t="n">
-        <v>5.68161487579346</v>
+        <v>5.6816143989563</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G723" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G725" t="n">
-        <v>5.83162450790405</v>
+        <v>5.83162403106689</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G726" t="n">
-        <v>5.76599502563477</v>
+        <v>5.76599550247192</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G728" t="n">
-        <v>5.33471775054932</v>
+        <v>5.33471727371216</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>5.23158550262451</v>
+        <v>5.23158597946167</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G731" t="n">
-        <v>4.69717645645142</v>
+        <v>4.69717693328857</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G732" t="n">
-        <v>4.80030822753906</v>
+        <v>4.8003077507019</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G734" t="n">
-        <v>4.73467874526978</v>
+        <v>4.73467922210693</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G739" t="n">
-        <v>3.93775248527527</v>
+        <v>3.93775272369385</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G741" t="n">
-        <v>3.74086499214172</v>
+        <v>3.7408652305603</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G750" t="n">
-        <v>3.05175828933716</v>
+        <v>3.05175852775574</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G756" t="n">
-        <v>3.15020203590393</v>
+        <v>3.15020227432251</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G764" t="n">
-        <v>3.05644607543945</v>
+        <v>3.05644631385803</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G767" t="n">
-        <v>2.75642704963684</v>
+        <v>2.75642681121826</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G770" t="n">
-        <v>2.66735887527466</v>
+        <v>2.66735863685608</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G779" t="n">
-        <v>3.11738753318787</v>
+        <v>3.11738777160645</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>3.25</v>
       </c>
       <c r="G782" t="n">
-        <v>3.04707074165344</v>
+        <v>3.04707050323486</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G783" t="n">
-        <v>3.09394836425781</v>
+        <v>3.09394860267639</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G784" t="n">
-        <v>3.05644607543945</v>
+        <v>3.05644631385803</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G788" t="n">
-        <v>2.77049016952515</v>
+        <v>2.77049040794373</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G789" t="n">
-        <v>2.75642704963684</v>
+        <v>2.75642681121826</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G790" t="n">
-        <v>2.70954895019531</v>
+        <v>2.70954918861389</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G793" t="n">
-        <v>2.95331478118896</v>
+        <v>2.95331454277039</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G794" t="n">
-        <v>2.95331478118896</v>
+        <v>2.95331454277039</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>3.3752167224884</v>
+        <v>3.37521648406982</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>3.53460168838501</v>
+        <v>3.53460192680359</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G818" t="n">
-        <v>3.65179681777954</v>
+        <v>3.65179705619812</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.63773369789124</v>
+        <v>3.63773345947266</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G833" t="n">
-        <v>3.66586017608643</v>
+        <v>3.665860414505</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G834" t="n">
-        <v>3.66586017608643</v>
+        <v>3.665860414505</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G844" t="n">
-        <v>3.32365083694458</v>
+        <v>3.32365107536316</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G845" t="n">
-        <v>3.46428489685059</v>
+        <v>3.46428465843201</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G851" t="n">
-        <v>3.74086499214172</v>
+        <v>3.7408652305603</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>3.36115312576294</v>
+        <v>3.36115336418152</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G873" t="n">
-        <v>3.48772406578064</v>
+        <v>3.48772382736206</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G874" t="n">
-        <v>3.58616781234741</v>
+        <v>3.58616757392883</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>3.53460168838501</v>
+        <v>3.53460192680359</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>3.31896305084229</v>
+        <v>3.31896281242371</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>3.36115312576294</v>
+        <v>3.36115336418152</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>3.35646557807922</v>
+        <v>3.35646533966064</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G886" t="n">
-        <v>3.29083633422852</v>
+        <v>3.29083609580994</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G887" t="n">
-        <v>3.33302664756775</v>
+        <v>3.33302640914917</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G889" t="n">
-        <v>3.58616781234741</v>
+        <v>3.58616757392883</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G892" t="n">
-        <v>3.49241137504578</v>
+        <v>3.49241161346436</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>3.36115312576294</v>
+        <v>3.36115336418152</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>3.29083633422852</v>
+        <v>3.29083609580994</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G903" t="n">
-        <v>3.02831935882568</v>
+        <v>3.02831959724426</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G906" t="n">
-        <v>2.95331478118896</v>
+        <v>2.95331454277039</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G909" t="n">
-        <v>3.18770456314087</v>
+        <v>3.18770480155945</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>3.36115312576294</v>
+        <v>3.36115336418152</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G920" t="n">
-        <v>3.87681150436401</v>
+        <v>3.87681174278259</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G921" t="n">
-        <v>3.92368936538696</v>
+        <v>3.92368912696838</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G922" t="n">
-        <v>3.82524538040161</v>
+        <v>3.82524561882019</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G924" t="n">
-        <v>3.92837715148926</v>
+        <v>3.92837738990784</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>3.97056770324707</v>
+        <v>3.97056746482849</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>3.91900134086609</v>
+        <v>3.91900110244751</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.75</v>
       </c>
       <c r="G935" t="n">
-        <v>4.45341110229492</v>
+        <v>4.45341062545776</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G942" t="n">
-        <v>4.50966453552246</v>
+        <v>4.5096640586853</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G944" t="n">
-        <v>4.51904010772705</v>
+        <v>4.51904058456421</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G948" t="n">
-        <v>4.47216176986694</v>
+        <v>4.4721622467041</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G949" t="n">
-        <v>4.50497674942017</v>
+        <v>4.50497627258301</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G953" t="n">
-        <v>4.40184497833252</v>
+        <v>4.40184545516968</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G954" t="n">
-        <v>4.34090375900269</v>
+        <v>4.34090328216553</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.5</v>
       </c>
       <c r="G955" t="n">
-        <v>4.21902084350586</v>
+        <v>4.2190203666687</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.5</v>
       </c>
       <c r="G958" t="n">
-        <v>4.21902084350586</v>
+        <v>4.2190203666687</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G961" t="n">
-        <v>4.17214250564575</v>
+        <v>4.17214298248291</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G963" t="n">
-        <v>3.93775248527527</v>
+        <v>3.93775272369385</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G966" t="n">
-        <v>3.97056770324707</v>
+        <v>3.97056746482849</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G967" t="n">
-        <v>4.01744556427002</v>
+        <v>4.01744508743286</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G969" t="n">
-        <v>4.26589918136597</v>
+        <v>4.26589870452881</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G974" t="n">
-        <v>4.61279582977295</v>
+        <v>4.61279630661011</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G978" t="n">
-        <v>5.05344915390015</v>
+        <v>5.0534496307373</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G982" t="n">
-        <v>5.22221040725708</v>
+        <v>5.22220993041992</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G985" t="n">
-        <v>5.1472053527832</v>
+        <v>5.14720487594604</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G986" t="n">
-        <v>5.02532291412354</v>
+        <v>5.02532243728638</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G990" t="n">
-        <v>5.0065712928772</v>
+        <v>5.00657176971436</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G993" t="n">
-        <v>4.95969295501709</v>
+        <v>4.95969343185425</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G995" t="n">
-        <v>5.21283483505249</v>
+        <v>5.21283435821533</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G997" t="n">
-        <v>5.10970258712769</v>
+        <v>5.10970306396484</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G999" t="n">
-        <v>5.05344915390015</v>
+        <v>5.0534496307373</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1000" t="n">
-        <v>5.10970258712769</v>
+        <v>5.10970306396484</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>5.05344915390015</v>
+        <v>5.0534496307373</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.95031833648682</v>
+        <v>4.95031785964966</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.98782062530518</v>
+        <v>4.98782014846802</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.95031833648682</v>
+        <v>4.95031785964966</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1015" t="n">
-        <v>5.05344915390015</v>
+        <v>5.0534496307373</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1019" t="n">
-        <v>5.54098033905029</v>
+        <v>5.54098081588745</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1020" t="n">
-        <v>5.51285409927368</v>
+        <v>5.51285362243652</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>5.30659008026123</v>
+        <v>5.30659055709839</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1025" t="n">
-        <v>5.35346841812134</v>
+        <v>5.3534688949585</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1026" t="n">
-        <v>5.61598491668701</v>
+        <v>5.61598539352417</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1029" t="n">
-        <v>5.49410247802734</v>
+        <v>5.4941029548645</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1035" t="n">
-        <v>5.87850189208984</v>
+        <v>5.878502368927</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1038" t="n">
-        <v>5.68161487579346</v>
+        <v>5.6816143989563</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1044" t="n">
-        <v>5.83162450790405</v>
+        <v>5.83162403106689</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1045" t="n">
-        <v>5.86912727355957</v>
+        <v>5.86912679672241</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1047" t="n">
-        <v>5.7847466468811</v>
+        <v>5.78474617004395</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1052" t="n">
-        <v>6.00976037979126</v>
+        <v>6.00976085662842</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1054" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1060" t="n">
-        <v>5.76599502563477</v>
+        <v>5.76599550247192</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>6.5</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.09414148330688</v>
+        <v>6.09414100646973</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>6.58167266845703</v>
+        <v>6.58167219161987</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G1069" t="n">
-        <v>6.49729156494141</v>
+        <v>6.49729204177856</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.4129114151001</v>
+        <v>6.41291189193726</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1072" t="n">
-        <v>6.37540912628174</v>
+        <v>6.3754096031189</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1073" t="n">
-        <v>6.23477506637573</v>
+        <v>6.23477554321289</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1075" t="n">
-        <v>6.23477506637573</v>
+        <v>6.23477554321289</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1081" t="n">
-        <v>6.27227783203125</v>
+        <v>6.27227735519409</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.87850189208984</v>
+        <v>5.878502368927</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1088" t="n">
-        <v>6.18789672851562</v>
+        <v>6.18789720535278</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.75043344497681</v>
+        <v>6.75043296813965</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1100" t="n">
-        <v>6.75043344497681</v>
+        <v>6.75043296813965</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1103" t="n">
-        <v>6.94732046127319</v>
+        <v>6.94732093811035</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1105" t="n">
-        <v>6.92856979370117</v>
+        <v>6.92856931686401</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1107" t="n">
-        <v>6.72230625152588</v>
+        <v>6.72230672836304</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.97544813156128</v>
+        <v>6.97544765472412</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1110" t="n">
-        <v>6.6660532951355</v>
+        <v>6.66605281829834</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1111" t="n">
-        <v>6.75043344497681</v>
+        <v>6.75043296813965</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>7.42547655105591</v>
+        <v>7.42547702789307</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1122" t="n">
-        <v>7.30359363555908</v>
+        <v>7.30359411239624</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1123" t="n">
-        <v>7.15358448028564</v>
+        <v>7.15358400344849</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1124" t="n">
-        <v>7.30359363555908</v>
+        <v>7.30359411239624</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1126" t="n">
-        <v>6.6660532951355</v>
+        <v>6.66605281829834</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1136" t="n">
-        <v>6.6660532951355</v>
+        <v>6.66605281829834</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1141" t="n">
-        <v>6.45041370391846</v>
+        <v>6.45041418075562</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1150" t="n">
-        <v>7.48172998428345</v>
+        <v>7.48173046112061</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1151" t="n">
-        <v>7.33172035217285</v>
+        <v>7.33172082901001</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1152" t="n">
-        <v>7.32234525680542</v>
+        <v>7.32234477996826</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1157" t="n">
-        <v>7.3785982131958</v>
+        <v>7.37859869003296</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1158" t="n">
-        <v>7.25671529769897</v>
+        <v>7.25671577453613</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1160" t="n">
-        <v>7.28484296798706</v>
+        <v>7.2848424911499</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1162" t="n">
-        <v>7.7254958152771</v>
+        <v>7.72549533843994</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1166" t="n">
-        <v>7.84737873077393</v>
+        <v>7.84737825393677</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1167" t="n">
-        <v>7.66924285888672</v>
+        <v>7.66924238204956</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1175" t="n">
-        <v>7.15358448028564</v>
+        <v>7.15358400344849</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1176" t="n">
-        <v>7.25671529769897</v>
+        <v>7.25671577453613</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1182" t="n">
-        <v>6.92856979370117</v>
+        <v>6.92856931686401</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1191" t="n">
-        <v>7.18171072006226</v>
+        <v>7.18171119689941</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1195" t="n">
-        <v>7.18171072006226</v>
+        <v>7.18171119689941</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1203" t="n">
-        <v>7.18171072006226</v>
+        <v>7.18171119689941</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>7.30359363555908</v>
+        <v>7.30359411239624</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1209" t="n">
-        <v>6.89106702804565</v>
+        <v>6.89106750488281</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.98482275009155</v>
+        <v>6.98482322692871</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1213" t="n">
-        <v>6.98482275009155</v>
+        <v>6.98482322692871</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1214" t="n">
-        <v>7.18171072006226</v>
+        <v>7.18171119689941</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1220" t="n">
-        <v>6.51604318618774</v>
+        <v>6.51604270935059</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.71293115615845</v>
+        <v>6.71293067932129</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.92856979370117</v>
+        <v>6.92856931686401</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1226" t="n">
-        <v>6.92856979370117</v>
+        <v>6.92856931686401</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.37540912628174</v>
+        <v>6.3754096031189</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1230" t="n">
-        <v>6.18789672851562</v>
+        <v>6.18789720535278</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1231" t="n">
-        <v>6.4129114151001</v>
+        <v>6.41291189193726</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>6.11289215087891</v>
+        <v>6.11289262771606</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>6.5</v>
       </c>
       <c r="G1234" t="n">
-        <v>6.09414148330688</v>
+        <v>6.09414100646973</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1235" t="n">
-        <v>6.21602439880371</v>
+        <v>6.21602392196655</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1239" t="n">
-        <v>6.18789672851562</v>
+        <v>6.18789720535278</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1242" t="n">
-        <v>5.75661945343018</v>
+        <v>5.75661897659302</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1245" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1250" t="n">
-        <v>5.21283483505249</v>
+        <v>5.21283435821533</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1255" t="n">
-        <v>5.51285409927368</v>
+        <v>5.51285362243652</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1260" t="n">
-        <v>6.23477506637573</v>
+        <v>6.23477554321289</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1262" t="n">
-        <v>6.21602439880371</v>
+        <v>6.21602392196655</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1264" t="n">
-        <v>6.30040407180786</v>
+        <v>6.30040454864502</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1265" t="n">
-        <v>6.27227783203125</v>
+        <v>6.27227735519409</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1267" t="n">
-        <v>6.1691460609436</v>
+        <v>6.16914558410645</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1268" t="n">
-        <v>6.10351657867432</v>
+        <v>6.10351705551147</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1281" t="n">
-        <v>6.04726314544678</v>
+        <v>6.04726266860962</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.87850189208984</v>
+        <v>5.878502368927</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1283" t="n">
-        <v>5.76599502563477</v>
+        <v>5.76599550247192</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -62876,6 +62876,32 @@
         <v>1.29999995231628</v>
       </c>
       <c r="H2404" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2405">
+      <c r="A2405" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2405" t="n">
+        <v>207044</v>
+      </c>
+      <c r="C2405" t="n">
+        <v>1.33599996566772</v>
+      </c>
+      <c r="D2405" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="E2405" t="n">
+        <v>1.33599996566772</v>
+      </c>
+      <c r="F2405" t="n">
+        <v>1.30599999427795</v>
+      </c>
+      <c r="G2405" t="n">
+        <v>1.30599999427795</v>
+      </c>
+      <c r="H2405" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G2" t="n">
-        <v>9.1356840133667</v>
+        <v>9.13568305969238</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G3" t="n">
-        <v>9.27969551086426</v>
+        <v>9.27969455718994</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>10.25</v>
       </c>
       <c r="G4" t="n">
-        <v>9.22568988800049</v>
+        <v>9.2256908416748</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>9.28869438171387</v>
+        <v>9.28869533538818</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G9" t="n">
-        <v>9.4057035446167</v>
+        <v>9.40570259094238</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G11" t="n">
-        <v>9.52271270751953</v>
+        <v>9.52271175384521</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>9.44170570373535</v>
+        <v>9.44170665740967</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.4057035446167</v>
+        <v>9.40570259094238</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>9.4057035446167</v>
+        <v>9.40570259094238</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G15" t="n">
-        <v>9.36970043182373</v>
+        <v>9.36970138549805</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G22" t="n">
-        <v>9.48670959472656</v>
+        <v>9.48671054840088</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G30" t="n">
-        <v>9.62172031402588</v>
+        <v>9.62171936035156</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>9.72072792053223</v>
+        <v>9.72072887420654</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G34" t="n">
-        <v>9.69372463226318</v>
+        <v>9.69372653961182</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>10.1617603302002</v>
+        <v>10.1617593765259</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G45" t="n">
-        <v>10.1617603302002</v>
+        <v>10.1617593765259</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>9.94574546813965</v>
+        <v>9.94574451446533</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G47" t="n">
-        <v>10.1617603302002</v>
+        <v>10.1617593765259</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>10.9358177185059</v>
+        <v>10.9358186721802</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G57" t="n">
-        <v>10.7648057937622</v>
+        <v>10.7648048400879</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G59" t="n">
-        <v>10.7738056182861</v>
+        <v>10.7738075256348</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G60" t="n">
-        <v>10.8368120193481</v>
+        <v>10.8368110656738</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G61" t="n">
-        <v>10.7918071746826</v>
+        <v>10.7918081283569</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G63" t="n">
-        <v>10.8368120193481</v>
+        <v>10.8368110656738</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G64" t="n">
-        <v>10.7828063964844</v>
+        <v>10.7828054428101</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G67" t="n">
-        <v>10.9358177185059</v>
+        <v>10.9358186721802</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G74" t="n">
-        <v>10.9628210067749</v>
+        <v>10.9628200531006</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G79" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G105" t="n">
-        <v>11.1518335342407</v>
+        <v>11.151834487915</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G107" t="n">
-        <v>11.0348253250122</v>
+        <v>11.0348262786865</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G109" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>10.8458118438721</v>
+        <v>10.8458108901978</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G115" t="n">
-        <v>11.0438270568848</v>
+        <v>11.0438261032104</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G123" t="n">
-        <v>11.1518335342407</v>
+        <v>11.151834487915</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G124" t="n">
-        <v>11.0888299942017</v>
+        <v>11.0888290405273</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G127" t="n">
-        <v>11.0528259277344</v>
+        <v>11.0528268814087</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G131" t="n">
-        <v>11.0438270568848</v>
+        <v>11.0438261032104</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G135" t="n">
-        <v>11.0528259277344</v>
+        <v>11.0528268814087</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G143" t="n">
-        <v>11.2778425216675</v>
+        <v>11.2778434753418</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G148" t="n">
-        <v>11.6918745040894</v>
+        <v>11.691873550415</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G150" t="n">
-        <v>11.6828737258911</v>
+        <v>11.6828746795654</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G155" t="n">
-        <v>11.5748653411865</v>
+        <v>11.5748662948608</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G167" t="n">
-        <v>11.8358850479126</v>
+        <v>11.8358840942383</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>11.9708967208862</v>
+        <v>11.9708957672119</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>11.9708967208862</v>
+        <v>11.9708957672119</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G170" t="n">
-        <v>11.6828737258911</v>
+        <v>11.6828746795654</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G174" t="n">
-        <v>11.0348253250122</v>
+        <v>11.0348262786865</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G178" t="n">
-        <v>11.0348253250122</v>
+        <v>11.0348262786865</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>10.9358177185059</v>
+        <v>10.9358186721802</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G182" t="n">
-        <v>10.7918071746826</v>
+        <v>10.7918081283569</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G183" t="n">
-        <v>10.7198028564453</v>
+        <v>10.719801902771</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>10.9358177185059</v>
+        <v>10.9358186721802</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G187" t="n">
-        <v>11.1968364715576</v>
+        <v>11.1968374252319</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G191" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>10.9358177185059</v>
+        <v>10.9358186721802</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>11.3858509063721</v>
+        <v>11.3858518600464</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>11.7908821105957</v>
+        <v>11.79088306427</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G204" t="n">
-        <v>11.8808889389038</v>
+        <v>11.8808879852295</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>11.7908821105957</v>
+        <v>11.79088306427</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>10.9358177185059</v>
+        <v>10.9358186721802</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G224" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>12.75</v>
       </c>
       <c r="G226" t="n">
-        <v>11.4758577346802</v>
+        <v>11.4758586883545</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G233" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G235" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>11.75</v>
       </c>
       <c r="G237" t="n">
-        <v>10.5757904052734</v>
+        <v>10.5757913589478</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G240" t="n">
-        <v>10.755805015564</v>
+        <v>10.7558040618896</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>10.755805015564</v>
+        <v>10.7558040618896</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7108001708984</v>
+        <v>10.7108011245728</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G247" t="n">
-        <v>10.755805015564</v>
+        <v>10.7558040618896</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G248" t="n">
-        <v>10.755805015564</v>
+        <v>10.7558040618896</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G249" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G255" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>12.75</v>
       </c>
       <c r="G256" t="n">
-        <v>11.4758577346802</v>
+        <v>11.4758586883545</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>12.75</v>
       </c>
       <c r="G257" t="n">
-        <v>11.4758577346802</v>
+        <v>11.4758586883545</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>11.1779365539551</v>
+        <v>11.1779375076294</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G276" t="n">
-        <v>11.0405035018921</v>
+        <v>11.0405025482178</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>11.1321249008179</v>
+        <v>11.1321258544922</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G280" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>12.75</v>
       </c>
       <c r="G285" t="n">
-        <v>11.6818590164185</v>
+        <v>11.6818599700928</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>11.72767162323</v>
+        <v>11.7276706695557</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G287" t="n">
-        <v>11.1779365539551</v>
+        <v>11.1779375076294</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>10.6740121841431</v>
+        <v>10.6740131378174</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G296" t="n">
-        <v>10.6282014846802</v>
+        <v>10.6282024383545</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>10.8114471435547</v>
+        <v>10.8114461898804</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G300" t="n">
-        <v>11.0405035018921</v>
+        <v>11.0405025482178</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>11.1321249008179</v>
+        <v>11.1321258544922</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G317" t="n">
-        <v>11.1779365539551</v>
+        <v>11.1779375076294</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G322" t="n">
-        <v>11.1321249008179</v>
+        <v>11.1321258544922</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G324" t="n">
-        <v>11.1779365539551</v>
+        <v>11.1779375076294</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G331" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>12.75</v>
       </c>
       <c r="G337" t="n">
-        <v>11.6818590164185</v>
+        <v>11.6818599700928</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G342" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>11.1321249008179</v>
+        <v>11.1321258544922</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G350" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G355" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G356" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>11.1779365539551</v>
+        <v>11.1779375076294</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G362" t="n">
-        <v>11.1321249008179</v>
+        <v>11.1321258544922</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>11.1779365539551</v>
+        <v>11.1779375076294</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G371" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>11.1779365539551</v>
+        <v>11.1779375076294</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G383" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G386" t="n">
-        <v>11.0405035018921</v>
+        <v>11.0405025482178</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>10.9488801956177</v>
+        <v>10.9488792419434</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>10.8114471435547</v>
+        <v>10.8114461898804</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G394" t="n">
-        <v>9.89522266387939</v>
+        <v>9.89522361755371</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>9.25386619567871</v>
+        <v>9.25386524200439</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G400" t="n">
-        <v>9.25386619567871</v>
+        <v>9.25386524200439</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>10.25</v>
       </c>
       <c r="G401" t="n">
-        <v>9.39129829406738</v>
+        <v>9.3912992477417</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>9.08894538879395</v>
+        <v>9.08894443511963</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.5</v>
       </c>
       <c r="G411" t="n">
-        <v>8.70413017272949</v>
+        <v>8.70413112640381</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G414" t="n">
-        <v>8.48423671722412</v>
+        <v>8.48423767089844</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G415" t="n">
-        <v>8.31931686401367</v>
+        <v>8.31931591033936</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>8.09942245483398</v>
+        <v>8.0994234085083</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9</v>
       </c>
       <c r="G417" t="n">
-        <v>8.24601745605469</v>
+        <v>8.24601936340332</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G419" t="n">
-        <v>8.46591186523438</v>
+        <v>8.46591281890869</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G420" t="n">
-        <v>8.39261531829834</v>
+        <v>8.39261436462402</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G423" t="n">
-        <v>8.74077987670898</v>
+        <v>8.74077892303467</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>9.08894538879395</v>
+        <v>9.08894443511963</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G426" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G428" t="n">
-        <v>8.90569972991943</v>
+        <v>8.90570068359375</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>9.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.70413017272949</v>
+        <v>8.70413112640381</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>8.06277465820312</v>
+        <v>8.06277370452881</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G441" t="n">
-        <v>8.15439701080322</v>
+        <v>8.15439605712891</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G443" t="n">
-        <v>8.3376407623291</v>
+        <v>8.33764266967773</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.5</v>
       </c>
       <c r="G446" t="n">
-        <v>8.70413017272949</v>
+        <v>8.70413112640381</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G449" t="n">
-        <v>8.3376407623291</v>
+        <v>8.33764266967773</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G452" t="n">
-        <v>8.48423671722412</v>
+        <v>8.48423767089844</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G454" t="n">
-        <v>8.48423671722412</v>
+        <v>8.48423767089844</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G456" t="n">
-        <v>8.61250782012939</v>
+        <v>8.61250877380371</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G466" t="n">
-        <v>8.61250782012939</v>
+        <v>8.61250877380371</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G467" t="n">
-        <v>8.61250782012939</v>
+        <v>8.61250877380371</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G469" t="n">
-        <v>8.64915752410889</v>
+        <v>8.64915657043457</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G470" t="n">
-        <v>8.64915752410889</v>
+        <v>8.64915657043457</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G474" t="n">
-        <v>8.48423671722412</v>
+        <v>8.48423767089844</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G480" t="n">
-        <v>8.30099296569824</v>
+        <v>8.30099201202393</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G482" t="n">
-        <v>8.48423671722412</v>
+        <v>8.48423767089844</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G484" t="n">
-        <v>8.3376407623291</v>
+        <v>8.33764266967773</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G485" t="n">
-        <v>8.26434421539307</v>
+        <v>8.26434326171875</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G488" t="n">
-        <v>8.26434421539307</v>
+        <v>8.26434326171875</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G491" t="n">
-        <v>8.09942245483398</v>
+        <v>8.0994234085083</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G492" t="n">
-        <v>8.61250782012939</v>
+        <v>8.61250877380371</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G493" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>9.25386619567871</v>
+        <v>9.25386524200439</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G495" t="n">
-        <v>9.25386619567871</v>
+        <v>9.25386524200439</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>9.2996768951416</v>
+        <v>9.29967594146729</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>9.2996768951416</v>
+        <v>9.29967594146729</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>9.2996768951416</v>
+        <v>9.29967594146729</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G501" t="n">
-        <v>9.2080545425415</v>
+        <v>9.20805358886719</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G515" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G519" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G522" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -62902,6 +62902,32 @@
         <v>1.30599999427795</v>
       </c>
       <c r="H2405" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2406">
+      <c r="A2406" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2406" t="n">
+        <v>86791</v>
+      </c>
+      <c r="C2406" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="D2406" t="n">
+        <v>1.28799998760223</v>
+      </c>
+      <c r="E2406" t="n">
+        <v>1.30599999427795</v>
+      </c>
+      <c r="F2406" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="G2406" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="H2406" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G2" t="n">
-        <v>9.1356840133667</v>
+        <v>9.13568305969238</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G3" t="n">
-        <v>9.27969551086426</v>
+        <v>9.27969360351562</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>10.25</v>
       </c>
       <c r="G4" t="n">
-        <v>9.22568988800049</v>
+        <v>9.2256908416748</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>9.28869438171387</v>
+        <v>9.28869533538818</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>10.5</v>
       </c>
       <c r="G6" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>9.36069965362549</v>
+        <v>9.3607006072998</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>10.5</v>
       </c>
       <c r="G8" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G9" t="n">
-        <v>9.4057035446167</v>
+        <v>9.40570259094238</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>9.81073379516602</v>
+        <v>9.8107328414917</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.4057035446167</v>
+        <v>9.40570259094238</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>9.4057035446167</v>
+        <v>9.40570259094238</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>10.5</v>
       </c>
       <c r="G17" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>10.5</v>
       </c>
       <c r="G18" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>10.5</v>
       </c>
       <c r="G19" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G20" t="n">
-        <v>9.54071426391602</v>
+        <v>9.54071521759033</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G21" t="n">
-        <v>9.55871486663818</v>
+        <v>9.5587158203125</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G22" t="n">
-        <v>9.48670959472656</v>
+        <v>9.48671054840088</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G25" t="n">
-        <v>9.54071426391602</v>
+        <v>9.54071521759033</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>9.63072109222412</v>
+        <v>9.6307201385498</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>9.54071426391602</v>
+        <v>9.54071521759033</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G28" t="n">
-        <v>9.63072109222412</v>
+        <v>9.6307201385498</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G29" t="n">
-        <v>9.63072109222412</v>
+        <v>9.6307201385498</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G30" t="n">
-        <v>9.62172031402588</v>
+        <v>9.62171936035156</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>9.63072109222412</v>
+        <v>9.6307201385498</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G32" t="n">
-        <v>9.63072109222412</v>
+        <v>9.6307201385498</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G34" t="n">
-        <v>9.69372463226318</v>
+        <v>9.6937255859375</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G35" t="n">
-        <v>9.81073379516602</v>
+        <v>9.8107328414917</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G40" t="n">
-        <v>9.90974140167236</v>
+        <v>9.90974235534668</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G41" t="n">
-        <v>9.90974140167236</v>
+        <v>9.90974235534668</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>9.94574546813965</v>
+        <v>9.94574356079102</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G53" t="n">
-        <v>10.6928005218506</v>
+        <v>10.6927995681763</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G57" t="n">
-        <v>10.7648057937622</v>
+        <v>10.7648048400879</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G58" t="n">
-        <v>10.6928005218506</v>
+        <v>10.6927995681763</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G59" t="n">
-        <v>10.7738056182861</v>
+        <v>10.7738065719604</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G61" t="n">
-        <v>10.7918071746826</v>
+        <v>10.7918081283569</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G66" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G79" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G105" t="n">
-        <v>11.1518335342407</v>
+        <v>11.1518354415894</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G107" t="n">
-        <v>11.0348253250122</v>
+        <v>11.0348262786865</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G109" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G114" t="n">
-        <v>10.9538192749023</v>
+        <v>10.953818321228</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G115" t="n">
-        <v>11.0438270568848</v>
+        <v>11.0438261032104</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>11.2418413162231</v>
+        <v>11.2418403625488</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G123" t="n">
-        <v>11.1518335342407</v>
+        <v>11.1518354415894</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G127" t="n">
-        <v>11.0528259277344</v>
+        <v>11.0528268814087</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G131" t="n">
-        <v>11.0438270568848</v>
+        <v>11.0438261032104</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G135" t="n">
-        <v>11.0528259277344</v>
+        <v>11.0528268814087</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G143" t="n">
-        <v>11.2778425216675</v>
+        <v>11.2778434753418</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G147" t="n">
-        <v>11.5208616256714</v>
+        <v>11.5208625793457</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G149" t="n">
-        <v>11.6018676757812</v>
+        <v>11.6018686294556</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G154" t="n">
-        <v>11.8178844451904</v>
+        <v>11.8178853988647</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G162" t="n">
-        <v>11.5028600692749</v>
+        <v>11.5028610229492</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G164" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>11.9708967208862</v>
+        <v>11.9708948135376</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>11.9708967208862</v>
+        <v>11.9708948135376</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G174" t="n">
-        <v>11.0348253250122</v>
+        <v>11.0348262786865</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G178" t="n">
-        <v>11.0348253250122</v>
+        <v>11.0348262786865</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G179" t="n">
-        <v>10.9898223876953</v>
+        <v>10.989821434021</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G181" t="n">
-        <v>10.8728132247925</v>
+        <v>10.8728141784668</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G182" t="n">
-        <v>10.7918071746826</v>
+        <v>10.7918081283569</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G187" t="n">
-        <v>11.1968364715576</v>
+        <v>11.1968383789062</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G189" t="n">
-        <v>11.2418413162231</v>
+        <v>11.2418403625488</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>11.3858509063721</v>
+        <v>11.3858518600464</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>11.7908821105957</v>
+        <v>11.7908840179443</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>11.7908821105957</v>
+        <v>11.7908840179443</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>12.75</v>
       </c>
       <c r="G226" t="n">
-        <v>11.4758577346802</v>
+        <v>11.4758586883545</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G233" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G235" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>11.75</v>
       </c>
       <c r="G237" t="n">
-        <v>10.5757904052734</v>
+        <v>10.5757913589478</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7108001708984</v>
+        <v>10.7108011245728</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G249" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>12.75</v>
       </c>
       <c r="G256" t="n">
-        <v>11.4758577346802</v>
+        <v>11.4758586883545</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>12.75</v>
       </c>
       <c r="G257" t="n">
-        <v>11.4758577346802</v>
+        <v>11.4758586883545</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G260" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G280" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>11.72767162323</v>
+        <v>11.7276706695557</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>12.5</v>
       </c>
       <c r="G288" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>10.6740121841431</v>
+        <v>10.6740131378174</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3991460800171</v>
+        <v>10.3991451263428</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G296" t="n">
-        <v>10.6282014846802</v>
+        <v>10.6282024383545</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>10.8114471435547</v>
+        <v>10.8114461898804</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G308" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G310" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>12.5</v>
       </c>
       <c r="G319" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G323" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>12.5</v>
       </c>
       <c r="G330" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G331" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>12.0025386810303</v>
+        <v>12.0025396347046</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>12.5</v>
       </c>
       <c r="G339" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G342" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>12.5</v>
       </c>
       <c r="G347" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G350" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G355" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G356" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G359" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>12.5</v>
       </c>
       <c r="G370" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G371" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>12.5</v>
       </c>
       <c r="G376" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G379" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G383" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>12</v>
       </c>
       <c r="G387" t="n">
-        <v>10.9946908950806</v>
+        <v>10.9946918487549</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>12</v>
       </c>
       <c r="G388" t="n">
-        <v>10.9946908950806</v>
+        <v>10.9946918487549</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>10.8114471435547</v>
+        <v>10.8114461898804</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>9.52873229980469</v>
+        <v>9.528733253479</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>9.25386619567871</v>
+        <v>9.25386524200439</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G400" t="n">
-        <v>9.25386619567871</v>
+        <v>9.25386524200439</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>10.25</v>
       </c>
       <c r="G401" t="n">
-        <v>9.39129829406738</v>
+        <v>9.3912992477417</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>9.52873229980469</v>
+        <v>9.528733253479</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>10</v>
       </c>
       <c r="G407" t="n">
-        <v>9.1622428894043</v>
+        <v>9.16224384307861</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>9.08894538879395</v>
+        <v>9.08894443511963</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.5</v>
       </c>
       <c r="G411" t="n">
-        <v>8.70413017272949</v>
+        <v>8.70413112640381</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G412" t="n">
-        <v>8.5758581161499</v>
+        <v>8.57585906982422</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G413" t="n">
-        <v>8.5758581161499</v>
+        <v>8.57585906982422</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>8.09942245483398</v>
+        <v>8.0994234085083</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9</v>
       </c>
       <c r="G417" t="n">
-        <v>8.24601745605469</v>
+        <v>8.24601936340332</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G419" t="n">
-        <v>8.46591186523438</v>
+        <v>8.46591281890869</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G420" t="n">
-        <v>8.39261531829834</v>
+        <v>8.39261436462402</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G421" t="n">
-        <v>8.35596561431885</v>
+        <v>8.35596466064453</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G422" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>9.08894538879395</v>
+        <v>9.08894443511963</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G426" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G428" t="n">
-        <v>8.90569972991943</v>
+        <v>8.90570068359375</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>9.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.70413017272949</v>
+        <v>8.70413112640381</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G432" t="n">
-        <v>8.68580627441406</v>
+        <v>8.68580532073975</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>8.28266716003418</v>
+        <v>8.2826681137085</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>8.06277465820312</v>
+        <v>8.06277370452881</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G441" t="n">
-        <v>8.15439701080322</v>
+        <v>8.15439605712891</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G443" t="n">
-        <v>8.3376407623291</v>
+        <v>8.33764171600342</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.5</v>
       </c>
       <c r="G446" t="n">
-        <v>8.70413017272949</v>
+        <v>8.70413112640381</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G449" t="n">
-        <v>8.3376407623291</v>
+        <v>8.33764171600342</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G451" t="n">
-        <v>8.44758796691895</v>
+        <v>8.44758892059326</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G453" t="n">
-        <v>8.44758796691895</v>
+        <v>8.44758892059326</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G456" t="n">
-        <v>8.61250782012939</v>
+        <v>8.61250877380371</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G457" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G458" t="n">
-        <v>8.44758796691895</v>
+        <v>8.44758892059326</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G459" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G463" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G466" t="n">
-        <v>8.61250782012939</v>
+        <v>8.61250877380371</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G467" t="n">
-        <v>8.61250782012939</v>
+        <v>8.61250877380371</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G469" t="n">
-        <v>8.64915752410889</v>
+        <v>8.64915657043457</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G470" t="n">
-        <v>8.64915752410889</v>
+        <v>8.64915657043457</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G471" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G472" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G473" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G476" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G478" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G480" t="n">
-        <v>8.30099296569824</v>
+        <v>8.30099201202393</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G484" t="n">
-        <v>8.3376407623291</v>
+        <v>8.33764171600342</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G485" t="n">
-        <v>8.26434421539307</v>
+        <v>8.26434326171875</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G488" t="n">
-        <v>8.26434421539307</v>
+        <v>8.26434326171875</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G491" t="n">
-        <v>8.09942245483398</v>
+        <v>8.0994234085083</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G492" t="n">
-        <v>8.61250782012939</v>
+        <v>8.61250877380371</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G493" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>9.25386619567871</v>
+        <v>9.25386524200439</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G495" t="n">
-        <v>9.25386619567871</v>
+        <v>9.25386524200439</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>9.2996768951416</v>
+        <v>9.29967594146729</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>9.2996768951416</v>
+        <v>9.29967594146729</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>9.2996768951416</v>
+        <v>9.29967594146729</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10</v>
       </c>
       <c r="G503" t="n">
-        <v>9.1622428894043</v>
+        <v>9.16224384307861</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G505" t="n">
-        <v>9.10726928710938</v>
+        <v>9.10726833343506</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>8.85988903045654</v>
+        <v>8.85988807678223</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G515" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G517" t="n">
-        <v>8.82324028015137</v>
+        <v>8.82324123382568</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G519" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G522" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G527" t="n">
-        <v>8.66305541992188</v>
+        <v>8.66305637359619</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>9.25</v>
       </c>
       <c r="G528" t="n">
-        <v>8.67243099212646</v>
+        <v>8.67243194580078</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G530" t="n">
-        <v>8.50367069244385</v>
+        <v>8.50366973876953</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G531" t="n">
-        <v>8.34428596496582</v>
+        <v>8.3442850112915</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G533" t="n">
-        <v>8.00676441192627</v>
+        <v>8.00676345825195</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>8.15677356719971</v>
+        <v>8.15677261352539</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>8.5</v>
       </c>
       <c r="G536" t="n">
-        <v>7.96926116943359</v>
+        <v>7.96926164627075</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>7.88488101959229</v>
+        <v>7.88488054275513</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G539" t="n">
-        <v>7.84737825393677</v>
+        <v>7.84737873077393</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G540" t="n">
-        <v>7.85675477981567</v>
+        <v>7.85675430297852</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>7.80987596511841</v>
+        <v>7.80987644195557</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G544" t="n">
-        <v>7.83800220489502</v>
+        <v>7.83800268173218</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G545" t="n">
-        <v>7.85675477981567</v>
+        <v>7.85675430297852</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>7.80987596511841</v>
+        <v>7.80987644195557</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G550" t="n">
-        <v>7.80987596511841</v>
+        <v>7.80987644195557</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G556" t="n">
-        <v>7.55673551559448</v>
+        <v>7.55673503875732</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G558" t="n">
-        <v>7.6317400932312</v>
+        <v>7.63174057006836</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G559" t="n">
-        <v>7.72549533843994</v>
+        <v>7.7254958152771</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G561" t="n">
-        <v>7.60361289978027</v>
+        <v>7.60361242294312</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G562" t="n">
-        <v>7.60361289978027</v>
+        <v>7.60361242294312</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>8.25</v>
       </c>
       <c r="G564" t="n">
-        <v>7.73487091064453</v>
+        <v>7.73487138748169</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G565" t="n">
-        <v>7.77237415313721</v>
+        <v>7.77237367630005</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G567" t="n">
-        <v>7.77237415313721</v>
+        <v>7.77237367630005</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G570" t="n">
-        <v>8.10052108764648</v>
+        <v>8.10052013397217</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G571" t="n">
-        <v>7.85675477981567</v>
+        <v>7.85675430297852</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>8.00676441192627</v>
+        <v>8.00676345825195</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>8.5</v>
       </c>
       <c r="G574" t="n">
-        <v>7.96926116943359</v>
+        <v>7.96926164627075</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G576" t="n">
-        <v>7.8755054473877</v>
+        <v>7.87550497055054</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>8.25</v>
       </c>
       <c r="G578" t="n">
-        <v>7.73487091064453</v>
+        <v>7.73487138748169</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G581" t="n">
-        <v>7.77237415313721</v>
+        <v>7.77237367630005</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>7.80987596511841</v>
+        <v>7.80987644195557</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.25</v>
       </c>
       <c r="G583" t="n">
-        <v>7.73487091064453</v>
+        <v>7.73487138748169</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.25</v>
       </c>
       <c r="G585" t="n">
-        <v>7.73487091064453</v>
+        <v>7.73487138748169</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G592" t="n">
-        <v>7.05045223236084</v>
+        <v>7.050452709198</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G595" t="n">
-        <v>6.66605281829834</v>
+        <v>6.6660532951355</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G597" t="n">
-        <v>6.54417037963867</v>
+        <v>6.54416990280151</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G605" t="n">
-        <v>6.18789720535278</v>
+        <v>6.18789672851562</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G606" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.5</v>
       </c>
       <c r="G609" t="n">
-        <v>6.09414100646973</v>
+        <v>6.09414148330688</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G610" t="n">
-        <v>6.44103813171387</v>
+        <v>6.44103860855103</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G611" t="n">
-        <v>6.21602392196655</v>
+        <v>6.21602439880371</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G612" t="n">
-        <v>6.30040454864502</v>
+        <v>6.30040407180786</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G615" t="n">
-        <v>6.49729204177856</v>
+        <v>6.49729156494141</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G617" t="n">
-        <v>6.58167219161987</v>
+        <v>6.58167266845703</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G619" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G632" t="n">
-        <v>6.40353584289551</v>
+        <v>6.40353631973267</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G634" t="n">
-        <v>6.45041418075562</v>
+        <v>6.45041370391846</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G637" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G638" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G639" t="n">
-        <v>6.41291189193726</v>
+        <v>6.4129114151001</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>6.41291189193726</v>
+        <v>6.4129114151001</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G645" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G647" t="n">
-        <v>7.09733057022095</v>
+        <v>7.09733104705811</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G649" t="n">
-        <v>6.58167219161987</v>
+        <v>6.58167266845703</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G650" t="n">
-        <v>6.54417037963867</v>
+        <v>6.54416990280151</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G652" t="n">
-        <v>6.51604270935059</v>
+        <v>6.51604318618774</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G655" t="n">
-        <v>6.54417037963867</v>
+        <v>6.54416990280151</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>6.63792562484741</v>
+        <v>6.63792610168457</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G660" t="n">
-        <v>6.54417037963867</v>
+        <v>6.54416990280151</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>6.63792562484741</v>
+        <v>6.63792610168457</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G662" t="n">
-        <v>6.51604270935059</v>
+        <v>6.51604318618774</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G666" t="n">
-        <v>5.30659055709839</v>
+        <v>5.30659008026123</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>4.88468885421753</v>
+        <v>4.88468837738037</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G674" t="n">
-        <v>5.6816143989563</v>
+        <v>5.68161487579346</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G675" t="n">
-        <v>5.84100008010864</v>
+        <v>5.84099960327148</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G677" t="n">
-        <v>6.05663919448853</v>
+        <v>6.05663871765137</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G678" t="n">
-        <v>6.27227735519409</v>
+        <v>6.27227783203125</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>6.05663919448853</v>
+        <v>6.05663871765137</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G683" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G684" t="n">
-        <v>5.76599550247192</v>
+        <v>5.76599502563477</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G685" t="n">
-        <v>5.83162403106689</v>
+        <v>5.83162450790405</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G686" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G687" t="n">
-        <v>5.83162403106689</v>
+        <v>5.83162450790405</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G689" t="n">
-        <v>5.88787841796875</v>
+        <v>5.88787794113159</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G692" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G694" t="n">
-        <v>5.86912679672241</v>
+        <v>5.86912727355957</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G696" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G697" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G706" t="n">
-        <v>6.10351705551147</v>
+        <v>6.10351657867432</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G709" t="n">
-        <v>6.04726266860962</v>
+        <v>6.04726314544678</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>5.84100008010864</v>
+        <v>5.84099960327148</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G711" t="n">
-        <v>5.88787841796875</v>
+        <v>5.88787794113159</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G714" t="n">
-        <v>5.6816143989563</v>
+        <v>5.68161487579346</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G723" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G725" t="n">
-        <v>5.83162403106689</v>
+        <v>5.83162450790405</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G726" t="n">
-        <v>5.76599550247192</v>
+        <v>5.76599502563477</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G728" t="n">
-        <v>5.33471727371216</v>
+        <v>5.33471775054932</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>5.23158597946167</v>
+        <v>5.23158550262451</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G731" t="n">
-        <v>4.69717693328857</v>
+        <v>4.69717645645142</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G732" t="n">
-        <v>4.8003077507019</v>
+        <v>4.80030822753906</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G734" t="n">
-        <v>4.73467922210693</v>
+        <v>4.73467874526978</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G739" t="n">
-        <v>3.93775272369385</v>
+        <v>3.93775248527527</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G741" t="n">
-        <v>3.7408652305603</v>
+        <v>3.74086499214172</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G750" t="n">
-        <v>3.05175852775574</v>
+        <v>3.05175828933716</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G756" t="n">
-        <v>3.15020227432251</v>
+        <v>3.15020203590393</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G764" t="n">
-        <v>3.05644631385803</v>
+        <v>3.05644607543945</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G767" t="n">
-        <v>2.75642681121826</v>
+        <v>2.75642704963684</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G770" t="n">
-        <v>2.66735863685608</v>
+        <v>2.66735887527466</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G779" t="n">
-        <v>3.11738777160645</v>
+        <v>3.11738753318787</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>3.25</v>
       </c>
       <c r="G782" t="n">
-        <v>3.04707050323486</v>
+        <v>3.04707074165344</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G783" t="n">
-        <v>3.09394860267639</v>
+        <v>3.09394836425781</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G784" t="n">
-        <v>3.05644631385803</v>
+        <v>3.05644607543945</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G788" t="n">
-        <v>2.77049040794373</v>
+        <v>2.77049016952515</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G789" t="n">
-        <v>2.75642681121826</v>
+        <v>2.75642704963684</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G790" t="n">
-        <v>2.70954918861389</v>
+        <v>2.70954895019531</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G793" t="n">
-        <v>2.95331454277039</v>
+        <v>2.95331478118896</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G794" t="n">
-        <v>2.95331454277039</v>
+        <v>2.95331478118896</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>3.37521648406982</v>
+        <v>3.3752167224884</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>3.53460192680359</v>
+        <v>3.53460168838501</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G818" t="n">
-        <v>3.65179705619812</v>
+        <v>3.65179681777954</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.63773345947266</v>
+        <v>3.63773369789124</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G833" t="n">
-        <v>3.665860414505</v>
+        <v>3.66586017608643</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G834" t="n">
-        <v>3.665860414505</v>
+        <v>3.66586017608643</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G844" t="n">
-        <v>3.32365107536316</v>
+        <v>3.32365083694458</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G845" t="n">
-        <v>3.46428465843201</v>
+        <v>3.46428489685059</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G851" t="n">
-        <v>3.7408652305603</v>
+        <v>3.74086499214172</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>3.36115336418152</v>
+        <v>3.36115312576294</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G873" t="n">
-        <v>3.48772382736206</v>
+        <v>3.48772406578064</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G874" t="n">
-        <v>3.58616757392883</v>
+        <v>3.58616781234741</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>3.53460192680359</v>
+        <v>3.53460168838501</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>3.31896281242371</v>
+        <v>3.31896305084229</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>3.36115336418152</v>
+        <v>3.36115312576294</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>3.35646533966064</v>
+        <v>3.35646557807922</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G886" t="n">
-        <v>3.29083609580994</v>
+        <v>3.29083633422852</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G887" t="n">
-        <v>3.33302640914917</v>
+        <v>3.33302664756775</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G889" t="n">
-        <v>3.58616757392883</v>
+        <v>3.58616781234741</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G892" t="n">
-        <v>3.49241161346436</v>
+        <v>3.49241137504578</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>3.36115336418152</v>
+        <v>3.36115312576294</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>3.29083609580994</v>
+        <v>3.29083633422852</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G903" t="n">
-        <v>3.02831959724426</v>
+        <v>3.02831935882568</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G906" t="n">
-        <v>2.95331454277039</v>
+        <v>2.95331478118896</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G909" t="n">
-        <v>3.18770480155945</v>
+        <v>3.18770456314087</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>3.36115336418152</v>
+        <v>3.36115312576294</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G920" t="n">
-        <v>3.87681174278259</v>
+        <v>3.87681150436401</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G921" t="n">
-        <v>3.92368912696838</v>
+        <v>3.92368936538696</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G922" t="n">
-        <v>3.82524561882019</v>
+        <v>3.82524538040161</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G924" t="n">
-        <v>3.92837738990784</v>
+        <v>3.92837715148926</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>3.97056746482849</v>
+        <v>3.97056770324707</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>3.91900110244751</v>
+        <v>3.91900134086609</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.75</v>
       </c>
       <c r="G935" t="n">
-        <v>4.45341062545776</v>
+        <v>4.45341110229492</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G942" t="n">
-        <v>4.5096640586853</v>
+        <v>4.50966453552246</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G944" t="n">
-        <v>4.51904058456421</v>
+        <v>4.51904010772705</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G948" t="n">
-        <v>4.4721622467041</v>
+        <v>4.47216176986694</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G949" t="n">
-        <v>4.50497627258301</v>
+        <v>4.50497674942017</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G953" t="n">
-        <v>4.40184545516968</v>
+        <v>4.40184497833252</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G954" t="n">
-        <v>4.34090328216553</v>
+        <v>4.34090375900269</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.5</v>
       </c>
       <c r="G955" t="n">
-        <v>4.2190203666687</v>
+        <v>4.21902084350586</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.5</v>
       </c>
       <c r="G958" t="n">
-        <v>4.2190203666687</v>
+        <v>4.21902084350586</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G961" t="n">
-        <v>4.17214298248291</v>
+        <v>4.17214250564575</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G963" t="n">
-        <v>3.93775272369385</v>
+        <v>3.93775248527527</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G966" t="n">
-        <v>3.97056746482849</v>
+        <v>3.97056770324707</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G967" t="n">
-        <v>4.01744508743286</v>
+        <v>4.01744556427002</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G969" t="n">
-        <v>4.26589870452881</v>
+        <v>4.26589918136597</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G974" t="n">
-        <v>4.61279630661011</v>
+        <v>4.61279582977295</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G978" t="n">
-        <v>5.0534496307373</v>
+        <v>5.05344915390015</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G982" t="n">
-        <v>5.22220993041992</v>
+        <v>5.22221040725708</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G985" t="n">
-        <v>5.14720487594604</v>
+        <v>5.1472053527832</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G986" t="n">
-        <v>5.02532243728638</v>
+        <v>5.02532291412354</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G990" t="n">
-        <v>5.00657176971436</v>
+        <v>5.0065712928772</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G993" t="n">
-        <v>4.95969343185425</v>
+        <v>4.95969295501709</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G995" t="n">
-        <v>5.21283435821533</v>
+        <v>5.21283483505249</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G997" t="n">
-        <v>5.10970306396484</v>
+        <v>5.10970258712769</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G999" t="n">
-        <v>5.0534496307373</v>
+        <v>5.05344915390015</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1000" t="n">
-        <v>5.10970306396484</v>
+        <v>5.10970258712769</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>5.0534496307373</v>
+        <v>5.05344915390015</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.95031785964966</v>
+        <v>4.95031833648682</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.98782014846802</v>
+        <v>4.98782062530518</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.95031785964966</v>
+        <v>4.95031833648682</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1015" t="n">
-        <v>5.0534496307373</v>
+        <v>5.05344915390015</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1019" t="n">
-        <v>5.54098081588745</v>
+        <v>5.54098033905029</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1020" t="n">
-        <v>5.51285362243652</v>
+        <v>5.51285409927368</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>5.30659055709839</v>
+        <v>5.30659008026123</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1025" t="n">
-        <v>5.3534688949585</v>
+        <v>5.35346841812134</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1026" t="n">
-        <v>5.61598539352417</v>
+        <v>5.61598491668701</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1029" t="n">
-        <v>5.4941029548645</v>
+        <v>5.49410247802734</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1035" t="n">
-        <v>5.878502368927</v>
+        <v>5.87850189208984</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1038" t="n">
-        <v>5.6816143989563</v>
+        <v>5.68161487579346</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1044" t="n">
-        <v>5.83162403106689</v>
+        <v>5.83162450790405</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1045" t="n">
-        <v>5.86912679672241</v>
+        <v>5.86912727355957</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1047" t="n">
-        <v>5.78474617004395</v>
+        <v>5.7847466468811</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1052" t="n">
-        <v>6.00976085662842</v>
+        <v>6.00976037979126</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1054" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1060" t="n">
-        <v>5.76599550247192</v>
+        <v>5.76599502563477</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>6.5</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.09414100646973</v>
+        <v>6.09414148330688</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>6.58167219161987</v>
+        <v>6.58167266845703</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G1069" t="n">
-        <v>6.49729204177856</v>
+        <v>6.49729156494141</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.41291189193726</v>
+        <v>6.4129114151001</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1072" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1073" t="n">
-        <v>6.23477554321289</v>
+        <v>6.23477506637573</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1075" t="n">
-        <v>6.23477554321289</v>
+        <v>6.23477506637573</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1081" t="n">
-        <v>6.27227735519409</v>
+        <v>6.27227783203125</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.878502368927</v>
+        <v>5.87850189208984</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1088" t="n">
-        <v>6.18789720535278</v>
+        <v>6.18789672851562</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1100" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1103" t="n">
-        <v>6.94732093811035</v>
+        <v>6.94732046127319</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1105" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1107" t="n">
-        <v>6.72230672836304</v>
+        <v>6.72230625152588</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.97544765472412</v>
+        <v>6.97544813156128</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1110" t="n">
-        <v>6.66605281829834</v>
+        <v>6.6660532951355</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1111" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>7.42547702789307</v>
+        <v>7.42547655105591</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1122" t="n">
-        <v>7.30359411239624</v>
+        <v>7.30359363555908</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1123" t="n">
-        <v>7.15358400344849</v>
+        <v>7.15358448028564</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1124" t="n">
-        <v>7.30359411239624</v>
+        <v>7.30359363555908</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1126" t="n">
-        <v>6.66605281829834</v>
+        <v>6.6660532951355</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1136" t="n">
-        <v>6.66605281829834</v>
+        <v>6.6660532951355</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1141" t="n">
-        <v>6.45041418075562</v>
+        <v>6.45041370391846</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1150" t="n">
-        <v>7.48173046112061</v>
+        <v>7.48172998428345</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1151" t="n">
-        <v>7.33172082901001</v>
+        <v>7.33172035217285</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1152" t="n">
-        <v>7.32234477996826</v>
+        <v>7.32234525680542</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1157" t="n">
-        <v>7.37859869003296</v>
+        <v>7.3785982131958</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1158" t="n">
-        <v>7.25671577453613</v>
+        <v>7.25671529769897</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1160" t="n">
-        <v>7.2848424911499</v>
+        <v>7.28484296798706</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1162" t="n">
-        <v>7.72549533843994</v>
+        <v>7.7254958152771</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1166" t="n">
-        <v>7.84737825393677</v>
+        <v>7.84737873077393</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1167" t="n">
-        <v>7.66924238204956</v>
+        <v>7.66924285888672</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1175" t="n">
-        <v>7.15358400344849</v>
+        <v>7.15358448028564</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1176" t="n">
-        <v>7.25671577453613</v>
+        <v>7.25671529769897</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1182" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1191" t="n">
-        <v>7.18171119689941</v>
+        <v>7.18171072006226</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1195" t="n">
-        <v>7.18171119689941</v>
+        <v>7.18171072006226</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1203" t="n">
-        <v>7.18171119689941</v>
+        <v>7.18171072006226</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>7.30359411239624</v>
+        <v>7.30359363555908</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1209" t="n">
-        <v>6.89106750488281</v>
+        <v>6.89106702804565</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.98482322692871</v>
+        <v>6.98482275009155</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1213" t="n">
-        <v>6.98482322692871</v>
+        <v>6.98482275009155</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1214" t="n">
-        <v>7.18171119689941</v>
+        <v>7.18171072006226</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1220" t="n">
-        <v>6.51604270935059</v>
+        <v>6.51604318618774</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.71293067932129</v>
+        <v>6.71293115615845</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1226" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1230" t="n">
-        <v>6.18789720535278</v>
+        <v>6.18789672851562</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1231" t="n">
-        <v>6.41291189193726</v>
+        <v>6.4129114151001</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>6.11289262771606</v>
+        <v>6.11289215087891</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>6.5</v>
       </c>
       <c r="G1234" t="n">
-        <v>6.09414100646973</v>
+        <v>6.09414148330688</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1235" t="n">
-        <v>6.21602392196655</v>
+        <v>6.21602439880371</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1239" t="n">
-        <v>6.18789720535278</v>
+        <v>6.18789672851562</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1242" t="n">
-        <v>5.75661897659302</v>
+        <v>5.75661945343018</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1245" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1250" t="n">
-        <v>5.21283435821533</v>
+        <v>5.21283483505249</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1255" t="n">
-        <v>5.51285362243652</v>
+        <v>5.51285409927368</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1260" t="n">
-        <v>6.23477554321289</v>
+        <v>6.23477506637573</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1262" t="n">
-        <v>6.21602392196655</v>
+        <v>6.21602439880371</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1264" t="n">
-        <v>6.30040454864502</v>
+        <v>6.30040407180786</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1265" t="n">
-        <v>6.27227735519409</v>
+        <v>6.27227783203125</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1267" t="n">
-        <v>6.16914558410645</v>
+        <v>6.1691460609436</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1268" t="n">
-        <v>6.10351705551147</v>
+        <v>6.10351657867432</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1281" t="n">
-        <v>6.04726266860962</v>
+        <v>6.04726314544678</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.878502368927</v>
+        <v>5.87850189208984</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1283" t="n">
-        <v>5.76599550247192</v>
+        <v>5.76599502563477</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -62980,6 +62980,32 @@
         <v>1.30999994277954</v>
       </c>
       <c r="H2408" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2409">
+      <c r="A2409" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2409" t="n">
+        <v>33436</v>
+      </c>
+      <c r="C2409" t="n">
+        <v>1.32599997520447</v>
+      </c>
+      <c r="D2409" t="n">
+        <v>1.30599999427795</v>
+      </c>
+      <c r="E2409" t="n">
+        <v>1.32200002670288</v>
+      </c>
+      <c r="F2409" t="n">
+        <v>1.32799994945526</v>
+      </c>
+      <c r="G2409" t="n">
+        <v>1.32799994945526</v>
+      </c>
+      <c r="H2409" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -55841,8 +55841,31 @@
       <c r="E2412" t="n">
         <v>1.28799998760223</v>
       </c>
-      <c r="F2412"/>
+      <c r="F2412" t="n">
+        <v>1.27600002288818</v>
+      </c>
       <c r="G2412" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2413">
+      <c r="A2413" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2413" t="n">
+        <v>28262</v>
+      </c>
+      <c r="C2413" t="n">
+        <v>1.29799997806549</v>
+      </c>
+      <c r="D2413" t="n">
+        <v>1.27400004863739</v>
+      </c>
+      <c r="E2413" t="n">
+        <v>1.28400003910065</v>
+      </c>
+      <c r="F2413"/>
+      <c r="G2413" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -55864,8 +55864,31 @@
       <c r="E2413" t="n">
         <v>1.28400003910065</v>
       </c>
-      <c r="F2413"/>
+      <c r="F2413" t="n">
+        <v>1.29799997806549</v>
+      </c>
       <c r="G2413" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2414">
+      <c r="A2414" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2414" t="n">
+        <v>73629</v>
+      </c>
+      <c r="C2414" t="n">
+        <v>1.2960000038147</v>
+      </c>
+      <c r="D2414" t="n">
+        <v>1.26199996471405</v>
+      </c>
+      <c r="E2414" t="n">
+        <v>1.2960000038147</v>
+      </c>
+      <c r="F2414"/>
+      <c r="G2414" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -55887,8 +55887,31 @@
       <c r="E2414" t="n">
         <v>1.2960000038147</v>
       </c>
-      <c r="F2414"/>
+      <c r="F2414" t="n">
+        <v>1.27799999713898</v>
+      </c>
       <c r="G2414" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2415">
+      <c r="A2415" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2415" t="n">
+        <v>62214</v>
+      </c>
+      <c r="C2415" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="D2415" t="n">
+        <v>1.26400005817413</v>
+      </c>
+      <c r="E2415" t="n">
+        <v>1.28600001335144</v>
+      </c>
+      <c r="F2415"/>
+      <c r="G2415" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -55910,8 +55910,31 @@
       <c r="E2415" t="n">
         <v>1.28600001335144</v>
       </c>
-      <c r="F2415"/>
+      <c r="F2415" t="n">
+        <v>1.28999996185303</v>
+      </c>
       <c r="G2415" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2416">
+      <c r="A2416" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2416" t="n">
+        <v>62900</v>
+      </c>
+      <c r="C2416" t="n">
+        <v>1.30200004577637</v>
+      </c>
+      <c r="D2416" t="n">
+        <v>1.27199995517731</v>
+      </c>
+      <c r="E2416" t="n">
+        <v>1.29200005531311</v>
+      </c>
+      <c r="F2416"/>
+      <c r="G2416" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -55940,6 +55940,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2417">
+      <c r="A2417" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2417" t="n">
+        <v>80780</v>
+      </c>
+      <c r="C2417" t="n">
+        <v>1.31400001049042</v>
+      </c>
+      <c r="D2417" t="n">
+        <v>1.28199994564056</v>
+      </c>
+      <c r="E2417" t="n">
+        <v>1.30799996852875</v>
+      </c>
+      <c r="F2417" t="n">
+        <v>1.30599999427795</v>
+      </c>
+      <c r="G2417" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G2" t="n">
-        <v>9.1356840133667</v>
+        <v>9.13568305969238</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G3" t="n">
-        <v>9.27969455718994</v>
+        <v>9.27969360351562</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>9.28869438171387</v>
+        <v>9.28869533538818</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G9" t="n">
-        <v>9.4057035446167</v>
+        <v>9.40570259094238</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>9.44170665740967</v>
+        <v>9.44170570373535</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.4057035446167</v>
+        <v>9.40570259094238</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>9.4057035446167</v>
+        <v>9.40570259094238</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G15" t="n">
-        <v>9.36970138549805</v>
+        <v>9.36970043182373</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G20" t="n">
-        <v>9.54071426391602</v>
+        <v>9.54071521759033</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G21" t="n">
-        <v>9.55871486663818</v>
+        <v>9.5587158203125</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G22" t="n">
-        <v>9.48670959472656</v>
+        <v>9.48671054840088</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G25" t="n">
-        <v>9.54071426391602</v>
+        <v>9.54071521759033</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>9.63072109222412</v>
+        <v>9.6307201385498</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>9.54071426391602</v>
+        <v>9.54071521759033</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G28" t="n">
-        <v>9.63072109222412</v>
+        <v>9.6307201385498</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G29" t="n">
-        <v>9.63072109222412</v>
+        <v>9.6307201385498</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G30" t="n">
-        <v>9.62172031402588</v>
+        <v>9.62171936035156</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>9.63072109222412</v>
+        <v>9.6307201385498</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G32" t="n">
-        <v>9.63072109222412</v>
+        <v>9.6307201385498</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G34" t="n">
-        <v>9.69372653961182</v>
+        <v>9.6937255859375</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G42" t="n">
-        <v>9.91874313354492</v>
+        <v>9.91874217987061</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G43" t="n">
-        <v>9.91874313354492</v>
+        <v>9.91874217987061</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>9.94574451446533</v>
+        <v>9.94574356079102</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>12</v>
       </c>
       <c r="G48" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>12</v>
       </c>
       <c r="G52" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G53" t="n">
-        <v>10.6928005218506</v>
+        <v>10.6927995681763</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>12</v>
       </c>
       <c r="G54" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G55" t="n">
-        <v>10.8098096847534</v>
+        <v>10.8098087310791</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G57" t="n">
-        <v>10.7648057937622</v>
+        <v>10.7648048400879</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G58" t="n">
-        <v>10.6928005218506</v>
+        <v>10.6927995681763</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G60" t="n">
-        <v>10.8368110656738</v>
+        <v>10.8368120193481</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G61" t="n">
-        <v>10.7918071746826</v>
+        <v>10.7918081283569</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G63" t="n">
-        <v>10.8368110656738</v>
+        <v>10.8368120193481</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G64" t="n">
-        <v>10.7828054428101</v>
+        <v>10.7828063964844</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G65" t="n">
-        <v>10.8098096847534</v>
+        <v>10.8098087310791</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G66" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>12.25</v>
       </c>
       <c r="G68" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>12.25</v>
       </c>
       <c r="G69" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>12.25</v>
       </c>
       <c r="G70" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>12.25</v>
       </c>
       <c r="G73" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>12.25</v>
       </c>
       <c r="G75" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>12.25</v>
       </c>
       <c r="G76" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>12</v>
       </c>
       <c r="G77" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>10.8908138275146</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G79" t="n">
-        <v>10.8908138275146</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>12.25</v>
       </c>
       <c r="G85" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G86" t="n">
-        <v>11.0078239440918</v>
+        <v>11.0078229904175</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G87" t="n">
-        <v>11.0078239440918</v>
+        <v>11.0078229904175</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>10.8908138275146</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>12</v>
       </c>
       <c r="G89" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>12</v>
       </c>
       <c r="G90" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>10.8908138275146</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G92" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G98" t="n">
-        <v>11.0978307723999</v>
+        <v>11.0978298187256</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G99" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>12.25</v>
       </c>
       <c r="G103" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G105" t="n">
-        <v>11.151834487915</v>
+        <v>11.1518354415894</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G109" t="n">
-        <v>10.8908138275146</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>10.8458108901978</v>
+        <v>10.8458118438721</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G114" t="n">
-        <v>10.9538192749023</v>
+        <v>10.953818321228</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G118" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>11.2418413162231</v>
+        <v>11.2418403625488</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G120" t="n">
-        <v>11.0978307723999</v>
+        <v>11.0978298187256</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G121" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G123" t="n">
-        <v>11.151834487915</v>
+        <v>11.1518354415894</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G124" t="n">
-        <v>11.0888290405273</v>
+        <v>11.0888299942017</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G125" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>12.25</v>
       </c>
       <c r="G126" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>11.0978307723999</v>
+        <v>11.0978298187256</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>12.25</v>
       </c>
       <c r="G129" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>12</v>
       </c>
       <c r="G130" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>12.25</v>
       </c>
       <c r="G132" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G133" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>12.25</v>
       </c>
       <c r="G136" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>11.4308557510376</v>
+        <v>11.4308547973633</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>11.4308557510376</v>
+        <v>11.4308547973633</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G146" t="n">
-        <v>11.4308557510376</v>
+        <v>11.4308547973633</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G150" t="n">
-        <v>11.6828727722168</v>
+        <v>11.6828737258911</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G151" t="n">
-        <v>11.6738729476929</v>
+        <v>11.6738739013672</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G161" t="n">
-        <v>11.4938611984253</v>
+        <v>11.493860244751</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>11.9708957672119</v>
+        <v>11.9708948135376</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>11.9708957672119</v>
+        <v>11.9708948135376</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G170" t="n">
-        <v>11.6828727722168</v>
+        <v>11.6828737258911</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>11.4128541946411</v>
+        <v>11.4128551483154</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G173" t="n">
-        <v>11.1878366470337</v>
+        <v>11.187837600708</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G179" t="n">
-        <v>10.9898223876953</v>
+        <v>10.989821434021</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G181" t="n">
-        <v>10.8728132247925</v>
+        <v>10.8728141784668</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G182" t="n">
-        <v>10.7918071746826</v>
+        <v>10.7918081283569</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G183" t="n">
-        <v>10.719801902771</v>
+        <v>10.7198028564453</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G186" t="n">
-        <v>11.2328405380249</v>
+        <v>11.2328395843506</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G189" t="n">
-        <v>11.2418413162231</v>
+        <v>11.2418403625488</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G191" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>11.3858509063721</v>
+        <v>11.3858518600464</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>11.79088306427</v>
+        <v>11.7908840179443</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>11.79088306427</v>
+        <v>11.7908840179443</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G223" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G224" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>11.4308557510376</v>
+        <v>11.4308547973633</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>10.8908138275146</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G233" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>12</v>
       </c>
       <c r="G234" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G235" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>12</v>
       </c>
       <c r="G239" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>12.25</v>
       </c>
       <c r="G242" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>12</v>
       </c>
       <c r="G243" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7108020782471</v>
+        <v>10.7108011245728</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G249" t="n">
-        <v>10.8908138275146</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>12</v>
       </c>
       <c r="G250" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>10.8908138275146</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G255" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G260" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>10.8908138275146</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>11.1779375076294</v>
+        <v>11.1779365539551</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G276" t="n">
-        <v>11.0405025482178</v>
+        <v>11.0405035018921</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>11.1321258544922</v>
+        <v>11.1321249008179</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>12.75</v>
       </c>
       <c r="G285" t="n">
-        <v>11.6818599700928</v>
+        <v>11.6818590164185</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G287" t="n">
-        <v>11.1779375076294</v>
+        <v>11.1779365539551</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>12.5</v>
       </c>
       <c r="G288" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3991460800171</v>
+        <v>10.3991451263428</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G300" t="n">
-        <v>11.0405025482178</v>
+        <v>11.0405035018921</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G308" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G310" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>11.1321258544922</v>
+        <v>11.1321249008179</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G317" t="n">
-        <v>11.1779375076294</v>
+        <v>11.1779365539551</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>12.5</v>
       </c>
       <c r="G319" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G322" t="n">
-        <v>11.1321258544922</v>
+        <v>11.1321249008179</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G323" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G324" t="n">
-        <v>11.1779375076294</v>
+        <v>11.1779365539551</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>12.5</v>
       </c>
       <c r="G330" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>12.0025386810303</v>
+        <v>12.0025396347046</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>12.75</v>
       </c>
       <c r="G337" t="n">
-        <v>11.6818599700928</v>
+        <v>11.6818590164185</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>12.5</v>
       </c>
       <c r="G339" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>12.5</v>
       </c>
       <c r="G347" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>11.1321258544922</v>
+        <v>11.1321249008179</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>11.1779375076294</v>
+        <v>11.1779365539551</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G359" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G362" t="n">
-        <v>11.1321258544922</v>
+        <v>11.1321249008179</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>11.1779375076294</v>
+        <v>11.1779365539551</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>12.5</v>
       </c>
       <c r="G370" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>12.5</v>
       </c>
       <c r="G376" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>11.1779375076294</v>
+        <v>11.1779365539551</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G379" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G386" t="n">
-        <v>11.0405025482178</v>
+        <v>11.0405035018921</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>12</v>
       </c>
       <c r="G387" t="n">
-        <v>10.9946908950806</v>
+        <v>10.9946918487549</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>12</v>
       </c>
       <c r="G388" t="n">
-        <v>10.9946908950806</v>
+        <v>10.9946918487549</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>10.9488792419434</v>
+        <v>10.9488801956177</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G394" t="n">
-        <v>9.89522361755371</v>
+        <v>9.89522266387939</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>9.52873229980469</v>
+        <v>9.528733253479</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>9.52873229980469</v>
+        <v>9.528733253479</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>10</v>
       </c>
       <c r="G407" t="n">
-        <v>9.1622428894043</v>
+        <v>9.16224384307861</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G412" t="n">
-        <v>8.5758581161499</v>
+        <v>8.57585906982422</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G413" t="n">
-        <v>8.5758581161499</v>
+        <v>8.57585906982422</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G414" t="n">
-        <v>8.48423767089844</v>
+        <v>8.48423671722412</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G415" t="n">
-        <v>8.31931591033936</v>
+        <v>8.31931686401367</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G421" t="n">
-        <v>8.35596561431885</v>
+        <v>8.35596466064453</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G422" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G423" t="n">
-        <v>8.74077892303467</v>
+        <v>8.74077987670898</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G432" t="n">
-        <v>8.68580627441406</v>
+        <v>8.68580532073975</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>8.28266716003418</v>
+        <v>8.2826681137085</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G443" t="n">
-        <v>8.33764266967773</v>
+        <v>8.33764171600342</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G449" t="n">
-        <v>8.33764266967773</v>
+        <v>8.33764171600342</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G451" t="n">
-        <v>8.44758796691895</v>
+        <v>8.44758892059326</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G452" t="n">
-        <v>8.48423767089844</v>
+        <v>8.48423671722412</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G453" t="n">
-        <v>8.44758796691895</v>
+        <v>8.44758892059326</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G454" t="n">
-        <v>8.48423767089844</v>
+        <v>8.48423671722412</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G457" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G458" t="n">
-        <v>8.44758796691895</v>
+        <v>8.44758892059326</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G459" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G463" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G471" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G472" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G473" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G474" t="n">
-        <v>8.48423767089844</v>
+        <v>8.48423671722412</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G476" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G478" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G482" t="n">
-        <v>8.48423767089844</v>
+        <v>8.48423671722412</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G484" t="n">
-        <v>8.33764266967773</v>
+        <v>8.33764171600342</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G501" t="n">
-        <v>9.20805358886719</v>
+        <v>9.2080545425415</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10</v>
       </c>
       <c r="G503" t="n">
-        <v>9.1622428894043</v>
+        <v>9.16224384307861</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G505" t="n">
-        <v>9.10726928710938</v>
+        <v>9.10726833343506</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>8.85988903045654</v>
+        <v>8.85988807678223</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G517" t="n">
-        <v>8.82324028015137</v>
+        <v>8.82324123382568</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G527" t="n">
-        <v>8.66305541992188</v>
+        <v>8.66305637359619</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>9.25</v>
       </c>
       <c r="G528" t="n">
-        <v>8.67243099212646</v>
+        <v>8.67243194580078</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G530" t="n">
-        <v>8.50367069244385</v>
+        <v>8.50366973876953</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G531" t="n">
-        <v>8.34428596496582</v>
+        <v>8.3442850112915</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G533" t="n">
-        <v>8.00676441192627</v>
+        <v>8.00676345825195</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>8.15677356719971</v>
+        <v>8.15677261352539</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>8.5</v>
       </c>
       <c r="G536" t="n">
-        <v>7.96926116943359</v>
+        <v>7.96926164627075</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>7.88488101959229</v>
+        <v>7.88488054275513</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G539" t="n">
-        <v>7.84737825393677</v>
+        <v>7.84737873077393</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G540" t="n">
-        <v>7.85675477981567</v>
+        <v>7.85675430297852</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>7.80987596511841</v>
+        <v>7.80987644195557</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G544" t="n">
-        <v>7.83800220489502</v>
+        <v>7.83800268173218</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G545" t="n">
-        <v>7.85675477981567</v>
+        <v>7.85675430297852</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>7.80987596511841</v>
+        <v>7.80987644195557</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G550" t="n">
-        <v>7.80987596511841</v>
+        <v>7.80987644195557</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G556" t="n">
-        <v>7.55673551559448</v>
+        <v>7.55673503875732</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G558" t="n">
-        <v>7.6317400932312</v>
+        <v>7.63174057006836</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G559" t="n">
-        <v>7.72549533843994</v>
+        <v>7.7254958152771</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G561" t="n">
-        <v>7.60361289978027</v>
+        <v>7.60361242294312</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G562" t="n">
-        <v>7.60361289978027</v>
+        <v>7.60361242294312</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>8.25</v>
       </c>
       <c r="G564" t="n">
-        <v>7.73487091064453</v>
+        <v>7.73487138748169</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G565" t="n">
-        <v>7.77237415313721</v>
+        <v>7.77237367630005</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G567" t="n">
-        <v>7.77237415313721</v>
+        <v>7.77237367630005</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G570" t="n">
-        <v>8.10052108764648</v>
+        <v>8.10052013397217</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G571" t="n">
-        <v>7.85675477981567</v>
+        <v>7.85675430297852</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>8.00676441192627</v>
+        <v>8.00676345825195</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>8.5</v>
       </c>
       <c r="G574" t="n">
-        <v>7.96926116943359</v>
+        <v>7.96926164627075</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G576" t="n">
-        <v>7.8755054473877</v>
+        <v>7.87550497055054</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>8.25</v>
       </c>
       <c r="G578" t="n">
-        <v>7.73487091064453</v>
+        <v>7.73487138748169</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G581" t="n">
-        <v>7.77237415313721</v>
+        <v>7.77237367630005</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>7.80987596511841</v>
+        <v>7.80987644195557</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.25</v>
       </c>
       <c r="G583" t="n">
-        <v>7.73487091064453</v>
+        <v>7.73487138748169</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.25</v>
       </c>
       <c r="G585" t="n">
-        <v>7.73487091064453</v>
+        <v>7.73487138748169</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G592" t="n">
-        <v>7.05045223236084</v>
+        <v>7.050452709198</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G595" t="n">
-        <v>6.66605281829834</v>
+        <v>6.6660532951355</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G597" t="n">
-        <v>6.54417037963867</v>
+        <v>6.54416990280151</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G605" t="n">
-        <v>6.18789720535278</v>
+        <v>6.18789672851562</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G606" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.5</v>
       </c>
       <c r="G609" t="n">
-        <v>6.09414100646973</v>
+        <v>6.09414148330688</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G610" t="n">
-        <v>6.44103813171387</v>
+        <v>6.44103860855103</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G611" t="n">
-        <v>6.21602392196655</v>
+        <v>6.21602439880371</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G612" t="n">
-        <v>6.30040454864502</v>
+        <v>6.30040407180786</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G615" t="n">
-        <v>6.49729204177856</v>
+        <v>6.49729156494141</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G617" t="n">
-        <v>6.58167219161987</v>
+        <v>6.58167266845703</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G619" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G632" t="n">
-        <v>6.40353584289551</v>
+        <v>6.40353631973267</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G634" t="n">
-        <v>6.45041418075562</v>
+        <v>6.45041370391846</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G637" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G638" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G639" t="n">
-        <v>6.41291189193726</v>
+        <v>6.4129114151001</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>6.41291189193726</v>
+        <v>6.4129114151001</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G645" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G647" t="n">
-        <v>7.09733057022095</v>
+        <v>7.09733104705811</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G649" t="n">
-        <v>6.58167219161987</v>
+        <v>6.58167266845703</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G650" t="n">
-        <v>6.54417037963867</v>
+        <v>6.54416990280151</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G652" t="n">
-        <v>6.51604270935059</v>
+        <v>6.51604318618774</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G655" t="n">
-        <v>6.54417037963867</v>
+        <v>6.54416990280151</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>6.63792562484741</v>
+        <v>6.63792610168457</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G660" t="n">
-        <v>6.54417037963867</v>
+        <v>6.54416990280151</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>6.63792562484741</v>
+        <v>6.63792610168457</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G662" t="n">
-        <v>6.51604270935059</v>
+        <v>6.51604318618774</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G666" t="n">
-        <v>5.30659055709839</v>
+        <v>5.30659008026123</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>4.88468885421753</v>
+        <v>4.88468837738037</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G674" t="n">
-        <v>5.6816143989563</v>
+        <v>5.68161487579346</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G675" t="n">
-        <v>5.84100008010864</v>
+        <v>5.84099960327148</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G677" t="n">
-        <v>6.05663919448853</v>
+        <v>6.05663871765137</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G678" t="n">
-        <v>6.27227735519409</v>
+        <v>6.27227783203125</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>6.05663919448853</v>
+        <v>6.05663871765137</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G683" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G684" t="n">
-        <v>5.76599550247192</v>
+        <v>5.76599502563477</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G685" t="n">
-        <v>5.83162403106689</v>
+        <v>5.83162450790405</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G686" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G687" t="n">
-        <v>5.83162403106689</v>
+        <v>5.83162450790405</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G689" t="n">
-        <v>5.88787841796875</v>
+        <v>5.88787794113159</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G692" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G694" t="n">
-        <v>5.86912679672241</v>
+        <v>5.86912727355957</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G696" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G697" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G706" t="n">
-        <v>6.10351705551147</v>
+        <v>6.10351657867432</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G709" t="n">
-        <v>6.04726266860962</v>
+        <v>6.04726314544678</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>5.84100008010864</v>
+        <v>5.84099960327148</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G711" t="n">
-        <v>5.88787841796875</v>
+        <v>5.88787794113159</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G714" t="n">
-        <v>5.6816143989563</v>
+        <v>5.68161487579346</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G723" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G725" t="n">
-        <v>5.83162403106689</v>
+        <v>5.83162450790405</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G726" t="n">
-        <v>5.76599550247192</v>
+        <v>5.76599502563477</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G728" t="n">
-        <v>5.33471727371216</v>
+        <v>5.33471775054932</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>5.23158597946167</v>
+        <v>5.23158550262451</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G731" t="n">
-        <v>4.69717693328857</v>
+        <v>4.69717645645142</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G732" t="n">
-        <v>4.8003077507019</v>
+        <v>4.80030822753906</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G734" t="n">
-        <v>4.73467922210693</v>
+        <v>4.73467874526978</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G739" t="n">
-        <v>3.93775272369385</v>
+        <v>3.93775248527527</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G741" t="n">
-        <v>3.7408652305603</v>
+        <v>3.74086499214172</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G750" t="n">
-        <v>3.05175852775574</v>
+        <v>3.05175828933716</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G756" t="n">
-        <v>3.15020227432251</v>
+        <v>3.15020203590393</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G764" t="n">
-        <v>3.05644631385803</v>
+        <v>3.05644607543945</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G767" t="n">
-        <v>2.75642681121826</v>
+        <v>2.75642704963684</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G770" t="n">
-        <v>2.66735863685608</v>
+        <v>2.66735887527466</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G779" t="n">
-        <v>3.11738777160645</v>
+        <v>3.11738753318787</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>3.25</v>
       </c>
       <c r="G782" t="n">
-        <v>3.04707050323486</v>
+        <v>3.04707074165344</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G783" t="n">
-        <v>3.09394860267639</v>
+        <v>3.09394836425781</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G784" t="n">
-        <v>3.05644631385803</v>
+        <v>3.05644607543945</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G788" t="n">
-        <v>2.77049040794373</v>
+        <v>2.77049016952515</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G789" t="n">
-        <v>2.75642681121826</v>
+        <v>2.75642704963684</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G790" t="n">
-        <v>2.70954918861389</v>
+        <v>2.70954895019531</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G793" t="n">
-        <v>2.95331454277039</v>
+        <v>2.95331478118896</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G794" t="n">
-        <v>2.95331454277039</v>
+        <v>2.95331478118896</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>3.37521648406982</v>
+        <v>3.3752167224884</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>3.53460192680359</v>
+        <v>3.53460168838501</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G818" t="n">
-        <v>3.65179705619812</v>
+        <v>3.65179681777954</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.63773345947266</v>
+        <v>3.63773369789124</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G833" t="n">
-        <v>3.665860414505</v>
+        <v>3.66586017608643</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G834" t="n">
-        <v>3.665860414505</v>
+        <v>3.66586017608643</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G844" t="n">
-        <v>3.32365107536316</v>
+        <v>3.32365083694458</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G845" t="n">
-        <v>3.46428465843201</v>
+        <v>3.46428489685059</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G851" t="n">
-        <v>3.7408652305603</v>
+        <v>3.74086499214172</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>3.36115336418152</v>
+        <v>3.36115312576294</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G873" t="n">
-        <v>3.48772382736206</v>
+        <v>3.48772406578064</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G874" t="n">
-        <v>3.58616757392883</v>
+        <v>3.58616781234741</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>3.53460192680359</v>
+        <v>3.53460168838501</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>3.31896281242371</v>
+        <v>3.31896305084229</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>3.36115336418152</v>
+        <v>3.36115312576294</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>3.35646533966064</v>
+        <v>3.35646557807922</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G886" t="n">
-        <v>3.29083609580994</v>
+        <v>3.29083633422852</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G887" t="n">
-        <v>3.33302640914917</v>
+        <v>3.33302664756775</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G889" t="n">
-        <v>3.58616757392883</v>
+        <v>3.58616781234741</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G892" t="n">
-        <v>3.49241161346436</v>
+        <v>3.49241137504578</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>3.36115336418152</v>
+        <v>3.36115312576294</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>3.29083609580994</v>
+        <v>3.29083633422852</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G903" t="n">
-        <v>3.02831959724426</v>
+        <v>3.02831935882568</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G906" t="n">
-        <v>2.95331454277039</v>
+        <v>2.95331478118896</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G909" t="n">
-        <v>3.18770480155945</v>
+        <v>3.18770456314087</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>3.36115336418152</v>
+        <v>3.36115312576294</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G920" t="n">
-        <v>3.87681174278259</v>
+        <v>3.87681150436401</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G921" t="n">
-        <v>3.92368912696838</v>
+        <v>3.92368936538696</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G922" t="n">
-        <v>3.82524561882019</v>
+        <v>3.82524538040161</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G924" t="n">
-        <v>3.92837738990784</v>
+        <v>3.92837715148926</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>3.97056746482849</v>
+        <v>3.97056770324707</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>3.91900110244751</v>
+        <v>3.91900134086609</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.75</v>
       </c>
       <c r="G935" t="n">
-        <v>4.45341062545776</v>
+        <v>4.45341110229492</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G942" t="n">
-        <v>4.5096640586853</v>
+        <v>4.50966453552246</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G944" t="n">
-        <v>4.51904058456421</v>
+        <v>4.51904010772705</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G948" t="n">
-        <v>4.4721622467041</v>
+        <v>4.47216176986694</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G949" t="n">
-        <v>4.50497627258301</v>
+        <v>4.50497674942017</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G953" t="n">
-        <v>4.40184545516968</v>
+        <v>4.40184497833252</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G954" t="n">
-        <v>4.34090328216553</v>
+        <v>4.34090375900269</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.5</v>
       </c>
       <c r="G955" t="n">
-        <v>4.2190203666687</v>
+        <v>4.21902084350586</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.5</v>
       </c>
       <c r="G958" t="n">
-        <v>4.2190203666687</v>
+        <v>4.21902084350586</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G961" t="n">
-        <v>4.17214298248291</v>
+        <v>4.17214250564575</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G963" t="n">
-        <v>3.93775272369385</v>
+        <v>3.93775248527527</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G966" t="n">
-        <v>3.97056746482849</v>
+        <v>3.97056770324707</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G967" t="n">
-        <v>4.01744508743286</v>
+        <v>4.01744556427002</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G969" t="n">
-        <v>4.26589870452881</v>
+        <v>4.26589918136597</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G974" t="n">
-        <v>4.61279630661011</v>
+        <v>4.61279582977295</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G978" t="n">
-        <v>5.0534496307373</v>
+        <v>5.05344915390015</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G982" t="n">
-        <v>5.22220993041992</v>
+        <v>5.22221040725708</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G985" t="n">
-        <v>5.14720487594604</v>
+        <v>5.1472053527832</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G986" t="n">
-        <v>5.02532243728638</v>
+        <v>5.02532291412354</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G990" t="n">
-        <v>5.00657176971436</v>
+        <v>5.0065712928772</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G993" t="n">
-        <v>4.95969343185425</v>
+        <v>4.95969295501709</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G995" t="n">
-        <v>5.21283435821533</v>
+        <v>5.21283483505249</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G997" t="n">
-        <v>5.10970306396484</v>
+        <v>5.10970258712769</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G999" t="n">
-        <v>5.0534496307373</v>
+        <v>5.05344915390015</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1000" t="n">
-        <v>5.10970306396484</v>
+        <v>5.10970258712769</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>5.0534496307373</v>
+        <v>5.05344915390015</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.95031785964966</v>
+        <v>4.95031833648682</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.98782014846802</v>
+        <v>4.98782062530518</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.95031785964966</v>
+        <v>4.95031833648682</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1015" t="n">
-        <v>5.0534496307373</v>
+        <v>5.05344915390015</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1019" t="n">
-        <v>5.54098081588745</v>
+        <v>5.54098033905029</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1020" t="n">
-        <v>5.51285362243652</v>
+        <v>5.51285409927368</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>5.30659055709839</v>
+        <v>5.30659008026123</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1025" t="n">
-        <v>5.3534688949585</v>
+        <v>5.35346841812134</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1026" t="n">
-        <v>5.61598539352417</v>
+        <v>5.61598491668701</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1029" t="n">
-        <v>5.4941029548645</v>
+        <v>5.49410247802734</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1035" t="n">
-        <v>5.878502368927</v>
+        <v>5.87850189208984</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1038" t="n">
-        <v>5.6816143989563</v>
+        <v>5.68161487579346</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1044" t="n">
-        <v>5.83162403106689</v>
+        <v>5.83162450790405</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1045" t="n">
-        <v>5.86912679672241</v>
+        <v>5.86912727355957</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1047" t="n">
-        <v>5.78474617004395</v>
+        <v>5.7847466468811</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1052" t="n">
-        <v>6.00976085662842</v>
+        <v>6.00976037979126</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1054" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1060" t="n">
-        <v>5.76599550247192</v>
+        <v>5.76599502563477</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>6.5</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.09414100646973</v>
+        <v>6.09414148330688</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>6.58167219161987</v>
+        <v>6.58167266845703</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G1069" t="n">
-        <v>6.49729204177856</v>
+        <v>6.49729156494141</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.41291189193726</v>
+        <v>6.4129114151001</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1072" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1073" t="n">
-        <v>6.23477554321289</v>
+        <v>6.23477506637573</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1075" t="n">
-        <v>6.23477554321289</v>
+        <v>6.23477506637573</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1081" t="n">
-        <v>6.27227735519409</v>
+        <v>6.27227783203125</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.878502368927</v>
+        <v>5.87850189208984</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1088" t="n">
-        <v>6.18789720535278</v>
+        <v>6.18789672851562</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1100" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1103" t="n">
-        <v>6.94732093811035</v>
+        <v>6.94732046127319</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1105" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1107" t="n">
-        <v>6.72230672836304</v>
+        <v>6.72230625152588</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.97544765472412</v>
+        <v>6.97544813156128</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1110" t="n">
-        <v>6.66605281829834</v>
+        <v>6.6660532951355</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1111" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>7.42547702789307</v>
+        <v>7.42547655105591</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1122" t="n">
-        <v>7.30359411239624</v>
+        <v>7.30359363555908</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1123" t="n">
-        <v>7.15358400344849</v>
+        <v>7.15358448028564</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1124" t="n">
-        <v>7.30359411239624</v>
+        <v>7.30359363555908</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1126" t="n">
-        <v>6.66605281829834</v>
+        <v>6.6660532951355</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1136" t="n">
-        <v>6.66605281829834</v>
+        <v>6.6660532951355</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1141" t="n">
-        <v>6.45041418075562</v>
+        <v>6.45041370391846</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1150" t="n">
-        <v>7.48173046112061</v>
+        <v>7.48172998428345</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1151" t="n">
-        <v>7.33172082901001</v>
+        <v>7.33172035217285</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1152" t="n">
-        <v>7.32234477996826</v>
+        <v>7.32234525680542</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1157" t="n">
-        <v>7.37859869003296</v>
+        <v>7.3785982131958</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1158" t="n">
-        <v>7.25671577453613</v>
+        <v>7.25671529769897</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1160" t="n">
-        <v>7.2848424911499</v>
+        <v>7.28484296798706</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1162" t="n">
-        <v>7.72549533843994</v>
+        <v>7.7254958152771</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1166" t="n">
-        <v>7.84737825393677</v>
+        <v>7.84737873077393</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1167" t="n">
-        <v>7.66924238204956</v>
+        <v>7.66924285888672</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1175" t="n">
-        <v>7.15358400344849</v>
+        <v>7.15358448028564</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1176" t="n">
-        <v>7.25671577453613</v>
+        <v>7.25671529769897</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1182" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1191" t="n">
-        <v>7.18171119689941</v>
+        <v>7.18171072006226</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1195" t="n">
-        <v>7.18171119689941</v>
+        <v>7.18171072006226</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1203" t="n">
-        <v>7.18171119689941</v>
+        <v>7.18171072006226</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>7.30359411239624</v>
+        <v>7.30359363555908</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1209" t="n">
-        <v>6.89106750488281</v>
+        <v>6.89106702804565</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.98482322692871</v>
+        <v>6.98482275009155</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1213" t="n">
-        <v>6.98482322692871</v>
+        <v>6.98482275009155</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1214" t="n">
-        <v>7.18171119689941</v>
+        <v>7.18171072006226</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1220" t="n">
-        <v>6.51604270935059</v>
+        <v>6.51604318618774</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.71293067932129</v>
+        <v>6.71293115615845</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1226" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1230" t="n">
-        <v>6.18789720535278</v>
+        <v>6.18789672851562</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1231" t="n">
-        <v>6.41291189193726</v>
+        <v>6.4129114151001</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>6.11289262771606</v>
+        <v>6.11289215087891</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>6.5</v>
       </c>
       <c r="G1234" t="n">
-        <v>6.09414100646973</v>
+        <v>6.09414148330688</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1235" t="n">
-        <v>6.21602392196655</v>
+        <v>6.21602439880371</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1239" t="n">
-        <v>6.18789720535278</v>
+        <v>6.18789672851562</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1242" t="n">
-        <v>5.75661897659302</v>
+        <v>5.75661945343018</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1245" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1250" t="n">
-        <v>5.21283435821533</v>
+        <v>5.21283483505249</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1255" t="n">
-        <v>5.51285362243652</v>
+        <v>5.51285409927368</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1260" t="n">
-        <v>6.23477554321289</v>
+        <v>6.23477506637573</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1262" t="n">
-        <v>6.21602392196655</v>
+        <v>6.21602439880371</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1264" t="n">
-        <v>6.30040454864502</v>
+        <v>6.30040407180786</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1265" t="n">
-        <v>6.27227735519409</v>
+        <v>6.27227783203125</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1267" t="n">
-        <v>6.16914558410645</v>
+        <v>6.1691460609436</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1268" t="n">
-        <v>6.10351705551147</v>
+        <v>6.10351657867432</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1281" t="n">
-        <v>6.04726266860962</v>
+        <v>6.04726314544678</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.878502368927</v>
+        <v>5.87850189208984</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1283" t="n">
-        <v>5.76599550247192</v>
+        <v>5.76599502563477</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -63266,6 +63266,32 @@
         <v>1.33000004291534</v>
       </c>
       <c r="H2419" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2420">
+      <c r="A2420" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2420" t="n">
+        <v>46094</v>
+      </c>
+      <c r="C2420" t="n">
+        <v>1.33200001716614</v>
+      </c>
+      <c r="D2420" t="n">
+        <v>1.31200003623962</v>
+      </c>
+      <c r="E2420" t="n">
+        <v>1.32799994945526</v>
+      </c>
+      <c r="F2420" t="n">
+        <v>1.32200002670288</v>
+      </c>
+      <c r="G2420" t="n">
+        <v>1.32200002670288</v>
+      </c>
+      <c r="H2420" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G2" t="n">
-        <v>9.13568305969238</v>
+        <v>9.1356840133667</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G3" t="n">
-        <v>9.27969360351562</v>
+        <v>9.27969455718994</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>9.28869533538818</v>
+        <v>9.28869438171387</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G9" t="n">
-        <v>9.40570259094238</v>
+        <v>9.4057035446167</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>9.44170570373535</v>
+        <v>9.44170665740967</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.40570259094238</v>
+        <v>9.4057035446167</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>9.40570259094238</v>
+        <v>9.4057035446167</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G16" t="n">
-        <v>9.34269905090332</v>
+        <v>9.34270000457764</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G20" t="n">
-        <v>9.54071521759033</v>
+        <v>9.54071426391602</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G22" t="n">
-        <v>9.48671054840088</v>
+        <v>9.48670959472656</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>9.4957103729248</v>
+        <v>9.49570941925049</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>9.4957103729248</v>
+        <v>9.49570941925049</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G25" t="n">
-        <v>9.54071521759033</v>
+        <v>9.54071426391602</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>9.6307201385498</v>
+        <v>9.63072109222412</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>9.54071521759033</v>
+        <v>9.54071426391602</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G28" t="n">
-        <v>9.6307201385498</v>
+        <v>9.63072109222412</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G29" t="n">
-        <v>9.6307201385498</v>
+        <v>9.63072109222412</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G30" t="n">
-        <v>9.62171936035156</v>
+        <v>9.62172031402588</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>9.6307201385498</v>
+        <v>9.63072109222412</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G32" t="n">
-        <v>9.6307201385498</v>
+        <v>9.63072109222412</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G34" t="n">
-        <v>9.6937255859375</v>
+        <v>9.69372463226318</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>11</v>
       </c>
       <c r="G36" t="n">
-        <v>9.90074062347412</v>
+        <v>9.9007396697998</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>11</v>
       </c>
       <c r="G37" t="n">
-        <v>9.90074062347412</v>
+        <v>9.9007396697998</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>11</v>
       </c>
       <c r="G38" t="n">
-        <v>9.90074062347412</v>
+        <v>9.9007396697998</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>11</v>
       </c>
       <c r="G39" t="n">
-        <v>9.90074062347412</v>
+        <v>9.9007396697998</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G42" t="n">
-        <v>9.91874217987061</v>
+        <v>9.91874313354492</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G43" t="n">
-        <v>9.91874217987061</v>
+        <v>9.91874313354492</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>9.94574356079102</v>
+        <v>9.94574546813965</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>12</v>
       </c>
       <c r="G48" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>12</v>
       </c>
       <c r="G52" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G53" t="n">
-        <v>10.6927995681763</v>
+        <v>10.6928005218506</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>12</v>
       </c>
       <c r="G54" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G55" t="n">
-        <v>10.8098087310791</v>
+        <v>10.8098096847534</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G58" t="n">
-        <v>10.6927995681763</v>
+        <v>10.6928005218506</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G60" t="n">
-        <v>10.8368120193481</v>
+        <v>10.8368110656738</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G61" t="n">
-        <v>10.7918081283569</v>
+        <v>10.7918062210083</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G63" t="n">
-        <v>10.8368120193481</v>
+        <v>10.8368110656738</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G64" t="n">
-        <v>10.7828063964844</v>
+        <v>10.7828054428101</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G65" t="n">
-        <v>10.8098087310791</v>
+        <v>10.8098096847534</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G66" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>12</v>
       </c>
       <c r="G77" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G79" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G86" t="n">
-        <v>11.0078229904175</v>
+        <v>11.0078239440918</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G87" t="n">
-        <v>11.0078229904175</v>
+        <v>11.0078239440918</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>12</v>
       </c>
       <c r="G89" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>12</v>
       </c>
       <c r="G90" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808206558228</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G97" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G98" t="n">
-        <v>11.0978298187256</v>
+        <v>11.0978307723999</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808206558228</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808206558228</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G105" t="n">
-        <v>11.1518354415894</v>
+        <v>11.151834487915</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G107" t="n">
-        <v>11.0348262786865</v>
+        <v>11.0348253250122</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G108" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G109" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>10.8458118438721</v>
+        <v>10.8458127975464</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G111" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G113" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G114" t="n">
-        <v>10.953818321228</v>
+        <v>10.9538192749023</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G115" t="n">
-        <v>11.0438261032104</v>
+        <v>11.0438270568848</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>11.2418403625488</v>
+        <v>11.2418413162231</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G120" t="n">
-        <v>11.0978298187256</v>
+        <v>11.0978307723999</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G123" t="n">
-        <v>11.1518354415894</v>
+        <v>11.151834487915</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G124" t="n">
-        <v>11.0888299942017</v>
+        <v>11.0888290405273</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>11.0978298187256</v>
+        <v>11.0978307723999</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>12</v>
       </c>
       <c r="G130" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G131" t="n">
-        <v>11.0438261032104</v>
+        <v>11.0438270568848</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G148" t="n">
-        <v>11.6918745040894</v>
+        <v>11.6918754577637</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G150" t="n">
-        <v>11.6828737258911</v>
+        <v>11.6828727722168</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>11.5658655166626</v>
+        <v>11.5658664703369</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G154" t="n">
-        <v>11.8178853988647</v>
+        <v>11.8178844451904</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>11.5658655166626</v>
+        <v>11.5658664703369</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>11.5658655166626</v>
+        <v>11.5658664703369</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G161" t="n">
-        <v>11.493860244751</v>
+        <v>11.4938611984253</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G162" t="n">
-        <v>11.5028610229492</v>
+        <v>11.5028600692749</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G165" t="n">
-        <v>11.8628883361816</v>
+        <v>11.8628873825073</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>11.9708948135376</v>
+        <v>11.9708957672119</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>11.9708948135376</v>
+        <v>11.9708957672119</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G170" t="n">
-        <v>11.6828737258911</v>
+        <v>11.6828727722168</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G173" t="n">
-        <v>11.187837600708</v>
+        <v>11.1878366470337</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G174" t="n">
-        <v>11.0348262786865</v>
+        <v>11.0348253250122</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G178" t="n">
-        <v>11.0348262786865</v>
+        <v>11.0348253250122</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G181" t="n">
-        <v>10.8728141784668</v>
+        <v>10.8728122711182</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G182" t="n">
-        <v>10.7918081283569</v>
+        <v>10.7918062210083</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G183" t="n">
-        <v>10.7198028564453</v>
+        <v>10.719801902771</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G185" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G187" t="n">
-        <v>11.1968383789062</v>
+        <v>11.1968374252319</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G189" t="n">
-        <v>11.2418403625488</v>
+        <v>11.2418413162231</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G191" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G194" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808206558228</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>11.3858518600464</v>
+        <v>11.3858509063721</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>11.7908840179443</v>
+        <v>11.79088306427</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G204" t="n">
-        <v>11.8808889389038</v>
+        <v>11.8808879852295</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>11.7908840179443</v>
+        <v>11.79088306427</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G209" t="n">
-        <v>11.5658655166626</v>
+        <v>11.5658664703369</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808206558228</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G224" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G233" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>12</v>
       </c>
       <c r="G234" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G235" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>12</v>
       </c>
       <c r="G239" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>12</v>
       </c>
       <c r="G243" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G249" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>12</v>
       </c>
       <c r="G250" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708274841309</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G255" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808206558228</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808206558228</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G280" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>11.5902376174927</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>11.7276706695557</v>
+        <v>11.72767162323</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>12.5</v>
       </c>
       <c r="G288" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>10.6740131378174</v>
+        <v>10.6740121841431</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3991451263428</v>
+        <v>10.3991460800171</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G296" t="n">
-        <v>10.6282024383545</v>
+        <v>10.6282014846802</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>10.8114461898804</v>
+        <v>10.8114471435547</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>11.5902376174927</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G308" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G310" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>12.5</v>
       </c>
       <c r="G319" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G323" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>11.5902376174927</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>12.5</v>
       </c>
       <c r="G330" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G331" t="n">
-        <v>11.5902376174927</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>12.0025396347046</v>
+        <v>12.0025386810303</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>12.5</v>
       </c>
       <c r="G339" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>11.5902376174927</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G342" t="n">
-        <v>11.5902376174927</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>12.5</v>
       </c>
       <c r="G347" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G350" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G355" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G356" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G359" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>11.5902376174927</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>12.5</v>
       </c>
       <c r="G370" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G371" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>12.5</v>
       </c>
       <c r="G376" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G379" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G383" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>12</v>
       </c>
       <c r="G387" t="n">
-        <v>10.9946918487549</v>
+        <v>10.9946908950806</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>12</v>
       </c>
       <c r="G388" t="n">
-        <v>10.9946918487549</v>
+        <v>10.9946908950806</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>10.8114461898804</v>
+        <v>10.8114471435547</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>9.528733253479</v>
+        <v>9.52873229980469</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>9.25386524200439</v>
+        <v>9.25386619567871</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G400" t="n">
-        <v>9.25386524200439</v>
+        <v>9.25386619567871</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>10.25</v>
       </c>
       <c r="G401" t="n">
-        <v>9.3912992477417</v>
+        <v>9.39129829406738</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>9.528733253479</v>
+        <v>9.52873229980469</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>10</v>
       </c>
       <c r="G407" t="n">
-        <v>9.16224384307861</v>
+        <v>9.1622428894043</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>9.08894443511963</v>
+        <v>9.08894538879395</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>8.88737487792969</v>
+        <v>8.887375831604</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.5</v>
       </c>
       <c r="G411" t="n">
-        <v>8.70413112640381</v>
+        <v>8.70413017272949</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G412" t="n">
-        <v>8.57585906982422</v>
+        <v>8.5758581161499</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G413" t="n">
-        <v>8.57585906982422</v>
+        <v>8.5758581161499</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>8.0994234085083</v>
+        <v>8.09942245483398</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9</v>
       </c>
       <c r="G417" t="n">
-        <v>8.24601936340332</v>
+        <v>8.24601745605469</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G419" t="n">
-        <v>8.46591281890869</v>
+        <v>8.46591186523438</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G420" t="n">
-        <v>8.39261436462402</v>
+        <v>8.39261531829834</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G421" t="n">
-        <v>8.35596466064453</v>
+        <v>8.35596561431885</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G422" t="n">
-        <v>8.50256061553955</v>
+        <v>8.50256156921387</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>9.08894443511963</v>
+        <v>9.08894538879395</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G426" t="n">
-        <v>8.88737487792969</v>
+        <v>8.887375831604</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G428" t="n">
-        <v>8.90570068359375</v>
+        <v>8.90569972991943</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>9.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.70413112640381</v>
+        <v>8.70413017272949</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G432" t="n">
-        <v>8.68580532073975</v>
+        <v>8.68580627441406</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>8.2826681137085</v>
+        <v>8.28266716003418</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>8.06277370452881</v>
+        <v>8.06277465820312</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G441" t="n">
-        <v>8.15439605712891</v>
+        <v>8.15439701080322</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G443" t="n">
-        <v>8.33764171600342</v>
+        <v>8.3376407623291</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.5</v>
       </c>
       <c r="G446" t="n">
-        <v>8.70413112640381</v>
+        <v>8.70413017272949</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G449" t="n">
-        <v>8.33764171600342</v>
+        <v>8.3376407623291</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G451" t="n">
-        <v>8.44758892059326</v>
+        <v>8.44758796691895</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G453" t="n">
-        <v>8.44758892059326</v>
+        <v>8.44758796691895</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G456" t="n">
-        <v>8.61250877380371</v>
+        <v>8.61250782012939</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G457" t="n">
-        <v>8.5208854675293</v>
+        <v>8.52088642120361</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G458" t="n">
-        <v>8.44758892059326</v>
+        <v>8.44758796691895</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G459" t="n">
-        <v>8.50256061553955</v>
+        <v>8.50256156921387</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>8.5208854675293</v>
+        <v>8.52088642120361</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G463" t="n">
-        <v>8.50256061553955</v>
+        <v>8.50256156921387</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G466" t="n">
-        <v>8.61250877380371</v>
+        <v>8.61250782012939</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G467" t="n">
-        <v>8.61250877380371</v>
+        <v>8.61250782012939</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G469" t="n">
-        <v>8.64915657043457</v>
+        <v>8.64915752410889</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G470" t="n">
-        <v>8.64915657043457</v>
+        <v>8.64915752410889</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G471" t="n">
-        <v>8.50256061553955</v>
+        <v>8.50256156921387</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G472" t="n">
-        <v>8.50256061553955</v>
+        <v>8.50256156921387</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G473" t="n">
-        <v>8.5208854675293</v>
+        <v>8.52088642120361</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G476" t="n">
-        <v>8.50256061553955</v>
+        <v>8.50256156921387</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>8.5208854675293</v>
+        <v>8.52088642120361</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G478" t="n">
-        <v>8.5208854675293</v>
+        <v>8.52088642120361</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G480" t="n">
-        <v>8.30099201202393</v>
+        <v>8.30099296569824</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G484" t="n">
-        <v>8.33764171600342</v>
+        <v>8.3376407623291</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G485" t="n">
-        <v>8.26434326171875</v>
+        <v>8.26434421539307</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G488" t="n">
-        <v>8.26434326171875</v>
+        <v>8.26434421539307</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G491" t="n">
-        <v>8.0994234085083</v>
+        <v>8.09942245483398</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G492" t="n">
-        <v>8.61250877380371</v>
+        <v>8.61250782012939</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G493" t="n">
-        <v>8.88737487792969</v>
+        <v>8.887375831604</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>9.25386524200439</v>
+        <v>9.25386619567871</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G495" t="n">
-        <v>9.25386524200439</v>
+        <v>9.25386619567871</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>9.29967594146729</v>
+        <v>9.2996768951416</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>9.29967594146729</v>
+        <v>9.2996768951416</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>9.29967594146729</v>
+        <v>9.2996768951416</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10</v>
       </c>
       <c r="G503" t="n">
-        <v>9.16224384307861</v>
+        <v>9.1622428894043</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G505" t="n">
-        <v>9.10726833343506</v>
+        <v>9.10726928710938</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>8.85988807678223</v>
+        <v>8.85988903045654</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G515" t="n">
-        <v>8.88737487792969</v>
+        <v>8.887375831604</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G517" t="n">
-        <v>8.82324123382568</v>
+        <v>8.82324028015137</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G519" t="n">
-        <v>8.88737487792969</v>
+        <v>8.887375831604</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G522" t="n">
-        <v>8.88737487792969</v>
+        <v>8.887375831604</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G527" t="n">
-        <v>8.66305637359619</v>
+        <v>8.66305541992188</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>9.25</v>
       </c>
       <c r="G528" t="n">
-        <v>8.67243194580078</v>
+        <v>8.67243099212646</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G530" t="n">
-        <v>8.50366973876953</v>
+        <v>8.50367069244385</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G531" t="n">
-        <v>8.3442850112915</v>
+        <v>8.34428596496582</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G533" t="n">
-        <v>8.00676345825195</v>
+        <v>8.00676441192627</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>8.15677261352539</v>
+        <v>8.15677356719971</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>8.5</v>
       </c>
       <c r="G536" t="n">
-        <v>7.96926164627075</v>
+        <v>7.96926116943359</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>7.88488054275513</v>
+        <v>7.88488101959229</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G539" t="n">
-        <v>7.84737873077393</v>
+        <v>7.84737825393677</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G540" t="n">
-        <v>7.85675430297852</v>
+        <v>7.85675477981567</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>7.80987644195557</v>
+        <v>7.80987596511841</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G544" t="n">
-        <v>7.83800268173218</v>
+        <v>7.83800220489502</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G545" t="n">
-        <v>7.85675430297852</v>
+        <v>7.85675477981567</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>7.80987644195557</v>
+        <v>7.80987596511841</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G550" t="n">
-        <v>7.80987644195557</v>
+        <v>7.80987596511841</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G556" t="n">
-        <v>7.55673503875732</v>
+        <v>7.55673551559448</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G558" t="n">
-        <v>7.63174057006836</v>
+        <v>7.6317400932312</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G559" t="n">
-        <v>7.7254958152771</v>
+        <v>7.72549533843994</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G561" t="n">
-        <v>7.60361242294312</v>
+        <v>7.60361289978027</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G562" t="n">
-        <v>7.60361242294312</v>
+        <v>7.60361289978027</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>8.25</v>
       </c>
       <c r="G564" t="n">
-        <v>7.73487138748169</v>
+        <v>7.73487091064453</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G565" t="n">
-        <v>7.77237367630005</v>
+        <v>7.77237415313721</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G567" t="n">
-        <v>7.77237367630005</v>
+        <v>7.77237415313721</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G570" t="n">
-        <v>8.10052013397217</v>
+        <v>8.10052108764648</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G571" t="n">
-        <v>7.85675430297852</v>
+        <v>7.85675477981567</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>8.00676345825195</v>
+        <v>8.00676441192627</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>8.5</v>
       </c>
       <c r="G574" t="n">
-        <v>7.96926164627075</v>
+        <v>7.96926116943359</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G576" t="n">
-        <v>7.87550497055054</v>
+        <v>7.8755054473877</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>8.25</v>
       </c>
       <c r="G578" t="n">
-        <v>7.73487138748169</v>
+        <v>7.73487091064453</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G581" t="n">
-        <v>7.77237367630005</v>
+        <v>7.77237415313721</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>7.80987644195557</v>
+        <v>7.80987596511841</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.25</v>
       </c>
       <c r="G583" t="n">
-        <v>7.73487138748169</v>
+        <v>7.73487091064453</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.25</v>
       </c>
       <c r="G585" t="n">
-        <v>7.73487138748169</v>
+        <v>7.73487091064453</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G592" t="n">
-        <v>7.050452709198</v>
+        <v>7.05045223236084</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G595" t="n">
-        <v>6.6660532951355</v>
+        <v>6.66605281829834</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G597" t="n">
-        <v>6.54416990280151</v>
+        <v>6.54417037963867</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G605" t="n">
-        <v>6.18789672851562</v>
+        <v>6.18789720535278</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G606" t="n">
-        <v>6.37540912628174</v>
+        <v>6.3754096031189</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.5</v>
       </c>
       <c r="G609" t="n">
-        <v>6.09414148330688</v>
+        <v>6.09414100646973</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G610" t="n">
-        <v>6.44103860855103</v>
+        <v>6.44103813171387</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G611" t="n">
-        <v>6.21602439880371</v>
+        <v>6.21602392196655</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G612" t="n">
-        <v>6.30040407180786</v>
+        <v>6.30040454864502</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G615" t="n">
-        <v>6.49729156494141</v>
+        <v>6.49729204177856</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G617" t="n">
-        <v>6.58167266845703</v>
+        <v>6.58167219161987</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G619" t="n">
-        <v>6.75043344497681</v>
+        <v>6.75043296813965</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G632" t="n">
-        <v>6.40353631973267</v>
+        <v>6.40353584289551</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G634" t="n">
-        <v>6.45041370391846</v>
+        <v>6.45041418075562</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G637" t="n">
-        <v>6.37540912628174</v>
+        <v>6.3754096031189</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G638" t="n">
-        <v>6.37540912628174</v>
+        <v>6.3754096031189</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G639" t="n">
-        <v>6.4129114151001</v>
+        <v>6.41291189193726</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>6.4129114151001</v>
+        <v>6.41291189193726</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>6.75043344497681</v>
+        <v>6.75043296813965</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G645" t="n">
-        <v>6.92856979370117</v>
+        <v>6.92856931686401</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G647" t="n">
-        <v>7.09733104705811</v>
+        <v>7.09733057022095</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G649" t="n">
-        <v>6.58167266845703</v>
+        <v>6.58167219161987</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G650" t="n">
-        <v>6.54416990280151</v>
+        <v>6.54417037963867</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G652" t="n">
-        <v>6.51604318618774</v>
+        <v>6.51604270935059</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G655" t="n">
-        <v>6.54416990280151</v>
+        <v>6.54417037963867</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>6.63792610168457</v>
+        <v>6.63792562484741</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G660" t="n">
-        <v>6.54416990280151</v>
+        <v>6.54417037963867</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>6.63792610168457</v>
+        <v>6.63792562484741</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G662" t="n">
-        <v>6.51604318618774</v>
+        <v>6.51604270935059</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G666" t="n">
-        <v>5.30659008026123</v>
+        <v>5.30659055709839</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>4.88468837738037</v>
+        <v>4.88468885421753</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G674" t="n">
-        <v>5.68161487579346</v>
+        <v>5.6816143989563</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G675" t="n">
-        <v>5.84099960327148</v>
+        <v>5.84100008010864</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G677" t="n">
-        <v>6.05663871765137</v>
+        <v>6.05663919448853</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G678" t="n">
-        <v>6.27227783203125</v>
+        <v>6.27227735519409</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>6.05663871765137</v>
+        <v>6.05663919448853</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G683" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G684" t="n">
-        <v>5.76599502563477</v>
+        <v>5.76599550247192</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G685" t="n">
-        <v>5.83162450790405</v>
+        <v>5.83162403106689</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G686" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G687" t="n">
-        <v>5.83162450790405</v>
+        <v>5.83162403106689</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G689" t="n">
-        <v>5.88787794113159</v>
+        <v>5.88787841796875</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G692" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G694" t="n">
-        <v>5.86912727355957</v>
+        <v>5.86912679672241</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G696" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G697" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G706" t="n">
-        <v>6.10351657867432</v>
+        <v>6.10351705551147</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G709" t="n">
-        <v>6.04726314544678</v>
+        <v>6.04726266860962</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>5.84099960327148</v>
+        <v>5.84100008010864</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G711" t="n">
-        <v>5.88787794113159</v>
+        <v>5.88787841796875</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G714" t="n">
-        <v>5.68161487579346</v>
+        <v>5.6816143989563</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G723" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G725" t="n">
-        <v>5.83162450790405</v>
+        <v>5.83162403106689</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G726" t="n">
-        <v>5.76599502563477</v>
+        <v>5.76599550247192</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G728" t="n">
-        <v>5.33471775054932</v>
+        <v>5.33471727371216</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>5.23158550262451</v>
+        <v>5.23158597946167</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G731" t="n">
-        <v>4.69717645645142</v>
+        <v>4.69717693328857</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G732" t="n">
-        <v>4.80030822753906</v>
+        <v>4.8003077507019</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G734" t="n">
-        <v>4.73467874526978</v>
+        <v>4.73467922210693</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G739" t="n">
-        <v>3.93775248527527</v>
+        <v>3.93775272369385</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G741" t="n">
-        <v>3.74086499214172</v>
+        <v>3.7408652305603</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G750" t="n">
-        <v>3.05175828933716</v>
+        <v>3.05175852775574</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G756" t="n">
-        <v>3.15020203590393</v>
+        <v>3.15020227432251</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G764" t="n">
-        <v>3.05644607543945</v>
+        <v>3.05644631385803</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G767" t="n">
-        <v>2.75642704963684</v>
+        <v>2.75642681121826</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G770" t="n">
-        <v>2.66735887527466</v>
+        <v>2.66735863685608</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G779" t="n">
-        <v>3.11738753318787</v>
+        <v>3.11738777160645</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>3.25</v>
       </c>
       <c r="G782" t="n">
-        <v>3.04707074165344</v>
+        <v>3.04707050323486</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G783" t="n">
-        <v>3.09394836425781</v>
+        <v>3.09394860267639</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G784" t="n">
-        <v>3.05644607543945</v>
+        <v>3.05644631385803</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G788" t="n">
-        <v>2.77049016952515</v>
+        <v>2.77049040794373</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G789" t="n">
-        <v>2.75642704963684</v>
+        <v>2.75642681121826</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G790" t="n">
-        <v>2.70954895019531</v>
+        <v>2.70954918861389</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G793" t="n">
-        <v>2.95331478118896</v>
+        <v>2.95331454277039</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G794" t="n">
-        <v>2.95331478118896</v>
+        <v>2.95331454277039</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>3.3752167224884</v>
+        <v>3.37521648406982</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>3.53460168838501</v>
+        <v>3.53460192680359</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G818" t="n">
-        <v>3.65179681777954</v>
+        <v>3.65179705619812</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.63773369789124</v>
+        <v>3.63773345947266</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G833" t="n">
-        <v>3.66586017608643</v>
+        <v>3.665860414505</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G834" t="n">
-        <v>3.66586017608643</v>
+        <v>3.665860414505</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G844" t="n">
-        <v>3.32365083694458</v>
+        <v>3.32365107536316</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G845" t="n">
-        <v>3.46428489685059</v>
+        <v>3.46428465843201</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G851" t="n">
-        <v>3.74086499214172</v>
+        <v>3.7408652305603</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>3.36115312576294</v>
+        <v>3.36115336418152</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G873" t="n">
-        <v>3.48772406578064</v>
+        <v>3.48772382736206</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G874" t="n">
-        <v>3.58616781234741</v>
+        <v>3.58616757392883</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>3.53460168838501</v>
+        <v>3.53460192680359</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>3.31896305084229</v>
+        <v>3.31896281242371</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>3.36115312576294</v>
+        <v>3.36115336418152</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>3.35646557807922</v>
+        <v>3.35646533966064</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G886" t="n">
-        <v>3.29083633422852</v>
+        <v>3.29083609580994</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G887" t="n">
-        <v>3.33302664756775</v>
+        <v>3.33302640914917</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G889" t="n">
-        <v>3.58616781234741</v>
+        <v>3.58616757392883</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G892" t="n">
-        <v>3.49241137504578</v>
+        <v>3.49241161346436</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>3.36115312576294</v>
+        <v>3.36115336418152</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>3.29083633422852</v>
+        <v>3.29083609580994</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G903" t="n">
-        <v>3.02831935882568</v>
+        <v>3.02831959724426</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G906" t="n">
-        <v>2.95331478118896</v>
+        <v>2.95331454277039</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G909" t="n">
-        <v>3.18770456314087</v>
+        <v>3.18770480155945</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>3.36115312576294</v>
+        <v>3.36115336418152</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G920" t="n">
-        <v>3.87681150436401</v>
+        <v>3.87681174278259</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G921" t="n">
-        <v>3.92368936538696</v>
+        <v>3.92368912696838</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G922" t="n">
-        <v>3.82524538040161</v>
+        <v>3.82524561882019</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G924" t="n">
-        <v>3.92837715148926</v>
+        <v>3.92837738990784</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>3.97056770324707</v>
+        <v>3.97056746482849</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>3.91900134086609</v>
+        <v>3.91900110244751</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.75</v>
       </c>
       <c r="G935" t="n">
-        <v>4.45341110229492</v>
+        <v>4.45341062545776</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G942" t="n">
-        <v>4.50966453552246</v>
+        <v>4.5096640586853</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G944" t="n">
-        <v>4.51904010772705</v>
+        <v>4.51904058456421</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G948" t="n">
-        <v>4.47216176986694</v>
+        <v>4.4721622467041</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G949" t="n">
-        <v>4.50497674942017</v>
+        <v>4.50497627258301</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G953" t="n">
-        <v>4.40184497833252</v>
+        <v>4.40184545516968</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G954" t="n">
-        <v>4.34090375900269</v>
+        <v>4.34090328216553</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.5</v>
       </c>
       <c r="G955" t="n">
-        <v>4.21902084350586</v>
+        <v>4.2190203666687</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.5</v>
       </c>
       <c r="G958" t="n">
-        <v>4.21902084350586</v>
+        <v>4.2190203666687</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G961" t="n">
-        <v>4.17214250564575</v>
+        <v>4.17214298248291</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G963" t="n">
-        <v>3.93775248527527</v>
+        <v>3.93775272369385</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G966" t="n">
-        <v>3.97056770324707</v>
+        <v>3.97056746482849</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G967" t="n">
-        <v>4.01744556427002</v>
+        <v>4.01744508743286</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G969" t="n">
-        <v>4.26589918136597</v>
+        <v>4.26589870452881</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G974" t="n">
-        <v>4.61279582977295</v>
+        <v>4.61279630661011</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G978" t="n">
-        <v>5.05344915390015</v>
+        <v>5.0534496307373</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G982" t="n">
-        <v>5.22221040725708</v>
+        <v>5.22220993041992</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G985" t="n">
-        <v>5.1472053527832</v>
+        <v>5.14720487594604</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G986" t="n">
-        <v>5.02532291412354</v>
+        <v>5.02532243728638</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G990" t="n">
-        <v>5.0065712928772</v>
+        <v>5.00657176971436</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G993" t="n">
-        <v>4.95969295501709</v>
+        <v>4.95969343185425</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G995" t="n">
-        <v>5.21283483505249</v>
+        <v>5.21283435821533</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G997" t="n">
-        <v>5.10970258712769</v>
+        <v>5.10970306396484</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G999" t="n">
-        <v>5.05344915390015</v>
+        <v>5.0534496307373</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1000" t="n">
-        <v>5.10970258712769</v>
+        <v>5.10970306396484</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>5.05344915390015</v>
+        <v>5.0534496307373</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.95031833648682</v>
+        <v>4.95031785964966</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.98782062530518</v>
+        <v>4.98782014846802</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.95031833648682</v>
+        <v>4.95031785964966</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1015" t="n">
-        <v>5.05344915390015</v>
+        <v>5.0534496307373</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1019" t="n">
-        <v>5.54098033905029</v>
+        <v>5.54098081588745</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1020" t="n">
-        <v>5.51285409927368</v>
+        <v>5.51285362243652</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>5.30659008026123</v>
+        <v>5.30659055709839</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1025" t="n">
-        <v>5.35346841812134</v>
+        <v>5.3534688949585</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1026" t="n">
-        <v>5.61598491668701</v>
+        <v>5.61598539352417</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1029" t="n">
-        <v>5.49410247802734</v>
+        <v>5.4941029548645</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1035" t="n">
-        <v>5.87850189208984</v>
+        <v>5.878502368927</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1038" t="n">
-        <v>5.68161487579346</v>
+        <v>5.6816143989563</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1044" t="n">
-        <v>5.83162450790405</v>
+        <v>5.83162403106689</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1045" t="n">
-        <v>5.86912727355957</v>
+        <v>5.86912679672241</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1047" t="n">
-        <v>5.7847466468811</v>
+        <v>5.78474617004395</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1052" t="n">
-        <v>6.00976037979126</v>
+        <v>6.00976085662842</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1054" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1060" t="n">
-        <v>5.76599502563477</v>
+        <v>5.76599550247192</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>6.5</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.09414148330688</v>
+        <v>6.09414100646973</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>6.58167266845703</v>
+        <v>6.58167219161987</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G1069" t="n">
-        <v>6.49729156494141</v>
+        <v>6.49729204177856</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.4129114151001</v>
+        <v>6.41291189193726</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1072" t="n">
-        <v>6.37540912628174</v>
+        <v>6.3754096031189</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1073" t="n">
-        <v>6.23477506637573</v>
+        <v>6.23477554321289</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1075" t="n">
-        <v>6.23477506637573</v>
+        <v>6.23477554321289</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1081" t="n">
-        <v>6.27227783203125</v>
+        <v>6.27227735519409</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.87850189208984</v>
+        <v>5.878502368927</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1088" t="n">
-        <v>6.18789672851562</v>
+        <v>6.18789720535278</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.75043344497681</v>
+        <v>6.75043296813965</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1100" t="n">
-        <v>6.75043344497681</v>
+        <v>6.75043296813965</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1103" t="n">
-        <v>6.94732046127319</v>
+        <v>6.94732093811035</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1105" t="n">
-        <v>6.92856979370117</v>
+        <v>6.92856931686401</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1107" t="n">
-        <v>6.72230625152588</v>
+        <v>6.72230672836304</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.97544813156128</v>
+        <v>6.97544765472412</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1110" t="n">
-        <v>6.6660532951355</v>
+        <v>6.66605281829834</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1111" t="n">
-        <v>6.75043344497681</v>
+        <v>6.75043296813965</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>7.42547655105591</v>
+        <v>7.42547702789307</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1122" t="n">
-        <v>7.30359363555908</v>
+        <v>7.30359411239624</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1123" t="n">
-        <v>7.15358448028564</v>
+        <v>7.15358400344849</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1124" t="n">
-        <v>7.30359363555908</v>
+        <v>7.30359411239624</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1126" t="n">
-        <v>6.6660532951355</v>
+        <v>6.66605281829834</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1136" t="n">
-        <v>6.6660532951355</v>
+        <v>6.66605281829834</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1141" t="n">
-        <v>6.45041370391846</v>
+        <v>6.45041418075562</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1150" t="n">
-        <v>7.48172998428345</v>
+        <v>7.48173046112061</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1151" t="n">
-        <v>7.33172035217285</v>
+        <v>7.33172082901001</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1152" t="n">
-        <v>7.32234525680542</v>
+        <v>7.32234477996826</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1157" t="n">
-        <v>7.3785982131958</v>
+        <v>7.37859869003296</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1158" t="n">
-        <v>7.25671529769897</v>
+        <v>7.25671577453613</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1160" t="n">
-        <v>7.28484296798706</v>
+        <v>7.2848424911499</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1162" t="n">
-        <v>7.7254958152771</v>
+        <v>7.72549533843994</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1166" t="n">
-        <v>7.84737873077393</v>
+        <v>7.84737825393677</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1167" t="n">
-        <v>7.66924285888672</v>
+        <v>7.66924238204956</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1175" t="n">
-        <v>7.15358448028564</v>
+        <v>7.15358400344849</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1176" t="n">
-        <v>7.25671529769897</v>
+        <v>7.25671577453613</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1182" t="n">
-        <v>6.92856979370117</v>
+        <v>6.92856931686401</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1191" t="n">
-        <v>7.18171072006226</v>
+        <v>7.18171119689941</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1195" t="n">
-        <v>7.18171072006226</v>
+        <v>7.18171119689941</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1203" t="n">
-        <v>7.18171072006226</v>
+        <v>7.18171119689941</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>7.30359363555908</v>
+        <v>7.30359411239624</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1209" t="n">
-        <v>6.89106702804565</v>
+        <v>6.89106750488281</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.98482275009155</v>
+        <v>6.98482322692871</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1213" t="n">
-        <v>6.98482275009155</v>
+        <v>6.98482322692871</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1214" t="n">
-        <v>7.18171072006226</v>
+        <v>7.18171119689941</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1220" t="n">
-        <v>6.51604318618774</v>
+        <v>6.51604270935059</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.71293115615845</v>
+        <v>6.71293067932129</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.92856979370117</v>
+        <v>6.92856931686401</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1226" t="n">
-        <v>6.92856979370117</v>
+        <v>6.92856931686401</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.37540912628174</v>
+        <v>6.3754096031189</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1230" t="n">
-        <v>6.18789672851562</v>
+        <v>6.18789720535278</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1231" t="n">
-        <v>6.4129114151001</v>
+        <v>6.41291189193726</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>6.11289215087891</v>
+        <v>6.11289262771606</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>6.5</v>
       </c>
       <c r="G1234" t="n">
-        <v>6.09414148330688</v>
+        <v>6.09414100646973</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1235" t="n">
-        <v>6.21602439880371</v>
+        <v>6.21602392196655</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1239" t="n">
-        <v>6.18789672851562</v>
+        <v>6.18789720535278</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1242" t="n">
-        <v>5.75661945343018</v>
+        <v>5.75661897659302</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1245" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1250" t="n">
-        <v>5.21283483505249</v>
+        <v>5.21283435821533</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1255" t="n">
-        <v>5.51285409927368</v>
+        <v>5.51285362243652</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1260" t="n">
-        <v>6.23477506637573</v>
+        <v>6.23477554321289</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1262" t="n">
-        <v>6.21602439880371</v>
+        <v>6.21602392196655</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1264" t="n">
-        <v>6.30040407180786</v>
+        <v>6.30040454864502</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1265" t="n">
-        <v>6.27227783203125</v>
+        <v>6.27227735519409</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1267" t="n">
-        <v>6.1691460609436</v>
+        <v>6.16914558410645</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1268" t="n">
-        <v>6.10351657867432</v>
+        <v>6.10351705551147</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1281" t="n">
-        <v>6.04726314544678</v>
+        <v>6.04726266860962</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.87850189208984</v>
+        <v>5.878502368927</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1283" t="n">
-        <v>5.76599502563477</v>
+        <v>5.76599550247192</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -63274,7 +63274,7 @@
         <v>46310.2916666667</v>
       </c>
       <c r="B2420" t="n">
-        <v>46094</v>
+        <v>46779</v>
       </c>
       <c r="C2420" t="n">
         <v>1.33200001716614</v>
@@ -63292,6 +63292,32 @@
         <v>1.32200002670288</v>
       </c>
       <c r="H2420" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2421">
+      <c r="A2421" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2421" t="n">
+        <v>63888</v>
+      </c>
+      <c r="C2421" t="n">
+        <v>1.35199999809265</v>
+      </c>
+      <c r="D2421" t="n">
+        <v>1.33200001716614</v>
+      </c>
+      <c r="E2421" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="F2421" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="G2421" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="H2421" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -485,7 +485,7 @@
         <v>10.25</v>
       </c>
       <c r="G4" t="n">
-        <v>9.22568988800049</v>
+        <v>9.2256908416748</v>
       </c>
       <c r="H4" t="n">
         <v>116483</v>
@@ -572,7 +572,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>9.36069965362549</v>
+        <v>9.3607006072998</v>
       </c>
       <c r="H7" t="n">
         <v>22546</v>
@@ -659,7 +659,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>9.81073474884033</v>
+        <v>9.8107328414917</v>
       </c>
       <c r="H10" t="n">
         <v>8225</v>
@@ -978,7 +978,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G21" t="n">
-        <v>9.55871391296387</v>
+        <v>9.55871486663818</v>
       </c>
       <c r="H21" t="n">
         <v>3705</v>
@@ -1239,7 +1239,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G30" t="n">
-        <v>9.62171936035156</v>
+        <v>9.62172031402588</v>
       </c>
       <c r="H30" t="n">
         <v>11222</v>
@@ -1355,7 +1355,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G34" t="n">
-        <v>9.6937255859375</v>
+        <v>9.69372653961182</v>
       </c>
       <c r="H34" t="n">
         <v>17123</v>
@@ -1384,7 +1384,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G35" t="n">
-        <v>9.81073474884033</v>
+        <v>9.8107328414917</v>
       </c>
       <c r="H35" t="n">
         <v>17570</v>
@@ -1587,7 +1587,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G42" t="n">
-        <v>9.91874217987061</v>
+        <v>9.91874313354492</v>
       </c>
       <c r="H42" t="n">
         <v>130</v>
@@ -1616,7 +1616,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G43" t="n">
-        <v>9.91874217987061</v>
+        <v>9.91874313354492</v>
       </c>
       <c r="H43" t="n">
         <v>980</v>
@@ -1761,7 +1761,7 @@
         <v>12</v>
       </c>
       <c r="G48" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H48" t="n">
         <v>2330</v>
@@ -1790,7 +1790,7 @@
         <v>12.5</v>
       </c>
       <c r="G49" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H49" t="n">
         <v>19250</v>
@@ -1819,7 +1819,7 @@
         <v>12.5</v>
       </c>
       <c r="G50" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H50" t="n">
         <v>8165</v>
@@ -1877,7 +1877,7 @@
         <v>12</v>
       </c>
       <c r="G52" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H52" t="n">
         <v>6600</v>
@@ -1906,7 +1906,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G53" t="n">
-        <v>10.6927995681763</v>
+        <v>10.6928005218506</v>
       </c>
       <c r="H53" t="n">
         <v>10522</v>
@@ -1935,7 +1935,7 @@
         <v>12</v>
       </c>
       <c r="G54" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H54" t="n">
         <v>11262</v>
@@ -1964,7 +1964,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G55" t="n">
-        <v>10.8098087310791</v>
+        <v>10.8098096847534</v>
       </c>
       <c r="H55" t="n">
         <v>30919</v>
@@ -2051,7 +2051,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G58" t="n">
-        <v>10.6927995681763</v>
+        <v>10.6928005218506</v>
       </c>
       <c r="H58" t="n">
         <v>19515</v>
@@ -2080,7 +2080,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G59" t="n">
-        <v>10.7738056182861</v>
+        <v>10.7738065719604</v>
       </c>
       <c r="H59" t="n">
         <v>2335</v>
@@ -2109,7 +2109,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G60" t="n">
-        <v>10.8368120193481</v>
+        <v>10.8368110656738</v>
       </c>
       <c r="H60" t="n">
         <v>361</v>
@@ -2167,7 +2167,7 @@
         <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H62" t="n">
         <v>8081</v>
@@ -2196,7 +2196,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G63" t="n">
-        <v>10.8368120193481</v>
+        <v>10.8368110656738</v>
       </c>
       <c r="H63" t="n">
         <v>6516</v>
@@ -2254,7 +2254,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G65" t="n">
-        <v>10.8098087310791</v>
+        <v>10.8098096847534</v>
       </c>
       <c r="H65" t="n">
         <v>43558</v>
@@ -2283,7 +2283,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G66" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H66" t="n">
         <v>2413</v>
@@ -2457,7 +2457,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H72" t="n">
         <v>17517</v>
@@ -2602,7 +2602,7 @@
         <v>12</v>
       </c>
       <c r="G77" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H77" t="n">
         <v>21843</v>
@@ -2631,7 +2631,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908138275146</v>
       </c>
       <c r="H78" t="n">
         <v>16304</v>
@@ -2660,7 +2660,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G79" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908138275146</v>
       </c>
       <c r="H79" t="n">
         <v>27515</v>
@@ -2689,7 +2689,7 @@
         <v>12.5</v>
       </c>
       <c r="G80" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H80" t="n">
         <v>22926</v>
@@ -2718,7 +2718,7 @@
         <v>12.5</v>
       </c>
       <c r="G81" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H81" t="n">
         <v>4837</v>
@@ -2747,7 +2747,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H82" t="n">
         <v>21926</v>
@@ -2776,7 +2776,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G83" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H83" t="n">
         <v>1172</v>
@@ -2863,7 +2863,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G86" t="n">
-        <v>11.0078229904175</v>
+        <v>11.0078239440918</v>
       </c>
       <c r="H86" t="n">
         <v>617</v>
@@ -2892,7 +2892,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G87" t="n">
-        <v>11.0078229904175</v>
+        <v>11.0078239440918</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908138275146</v>
       </c>
       <c r="H88" t="n">
         <v>125</v>
@@ -2950,7 +2950,7 @@
         <v>12</v>
       </c>
       <c r="G89" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H89" t="n">
         <v>2</v>
@@ -2979,7 +2979,7 @@
         <v>12</v>
       </c>
       <c r="G90" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H90" t="n">
         <v>132646</v>
@@ -3008,7 +3008,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908138275146</v>
       </c>
       <c r="H91" t="n">
         <v>29894</v>
@@ -3530,7 +3530,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G109" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908138275146</v>
       </c>
       <c r="H109" t="n">
         <v>196</v>
@@ -3559,7 +3559,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>10.8458118438721</v>
+        <v>10.8458108901978</v>
       </c>
       <c r="H110" t="n">
         <v>400</v>
@@ -3675,7 +3675,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G114" t="n">
-        <v>10.9538202285767</v>
+        <v>10.9538192749023</v>
       </c>
       <c r="H114" t="n">
         <v>1013</v>
@@ -3762,7 +3762,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H117" t="n">
         <v>12190</v>
@@ -3820,7 +3820,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>11.2418403625488</v>
+        <v>11.2418413162231</v>
       </c>
       <c r="H119" t="n">
         <v>10255</v>
@@ -3907,7 +3907,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H122" t="n">
         <v>2200</v>
@@ -3965,7 +3965,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G124" t="n">
-        <v>11.0888299942017</v>
+        <v>11.0888290405273</v>
       </c>
       <c r="H124" t="n">
         <v>20229</v>
@@ -4052,7 +4052,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G127" t="n">
-        <v>11.0528259277344</v>
+        <v>11.0528268814087</v>
       </c>
       <c r="H127" t="n">
         <v>9639</v>
@@ -4139,7 +4139,7 @@
         <v>12</v>
       </c>
       <c r="G130" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H130" t="n">
         <v>10740</v>
@@ -4284,7 +4284,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G135" t="n">
-        <v>11.0528259277344</v>
+        <v>11.0528268814087</v>
       </c>
       <c r="H135" t="n">
         <v>12316</v>
@@ -4429,7 +4429,7 @@
         <v>12.5</v>
       </c>
       <c r="G140" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H140" t="n">
         <v>50941</v>
@@ -4458,7 +4458,7 @@
         <v>12.5</v>
       </c>
       <c r="G141" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H141" t="n">
         <v>28615</v>
@@ -4487,7 +4487,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H142" t="n">
         <v>10378</v>
@@ -4516,7 +4516,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G143" t="n">
-        <v>11.2778425216675</v>
+        <v>11.2778434753418</v>
       </c>
       <c r="H143" t="n">
         <v>19219</v>
@@ -4661,7 +4661,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G148" t="n">
-        <v>11.6918754577637</v>
+        <v>11.6918745040894</v>
       </c>
       <c r="H148" t="n">
         <v>50666</v>
@@ -4719,7 +4719,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G150" t="n">
-        <v>11.6828737258911</v>
+        <v>11.6828727722168</v>
       </c>
       <c r="H150" t="n">
         <v>102168</v>
@@ -4748,7 +4748,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G151" t="n">
-        <v>11.6738739013672</v>
+        <v>11.6738729476929</v>
       </c>
       <c r="H151" t="n">
         <v>25392</v>
@@ -4835,7 +4835,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G154" t="n">
-        <v>11.8178844451904</v>
+        <v>11.8178853988647</v>
       </c>
       <c r="H154" t="n">
         <v>13313</v>
@@ -4922,7 +4922,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H157" t="n">
         <v>13919</v>
@@ -5038,7 +5038,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G161" t="n">
-        <v>11.493860244751</v>
+        <v>11.4938611984253</v>
       </c>
       <c r="H161" t="n">
         <v>12761</v>
@@ -5067,7 +5067,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G162" t="n">
-        <v>11.5028600692749</v>
+        <v>11.5028610229492</v>
       </c>
       <c r="H162" t="n">
         <v>8549</v>
@@ -5125,7 +5125,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G164" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H164" t="n">
         <v>7000</v>
@@ -5183,7 +5183,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H166" t="n">
         <v>436</v>
@@ -5212,7 +5212,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G167" t="n">
-        <v>11.8358840942383</v>
+        <v>11.8358850479126</v>
       </c>
       <c r="H167" t="n">
         <v>5902</v>
@@ -5241,7 +5241,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>11.9708967208862</v>
+        <v>11.9708957672119</v>
       </c>
       <c r="H168" t="n">
         <v>3334</v>
@@ -5270,7 +5270,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>11.9708967208862</v>
+        <v>11.9708957672119</v>
       </c>
       <c r="H169" t="n">
         <v>25389</v>
@@ -5299,7 +5299,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G170" t="n">
-        <v>11.6828737258911</v>
+        <v>11.6828727722168</v>
       </c>
       <c r="H170" t="n">
         <v>11344</v>
@@ -5328,7 +5328,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>11.4128551483154</v>
+        <v>11.4128541946411</v>
       </c>
       <c r="H171" t="n">
         <v>91681</v>
@@ -5357,7 +5357,7 @@
         <v>12.5</v>
       </c>
       <c r="G172" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H172" t="n">
         <v>252282</v>
@@ -5386,7 +5386,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G173" t="n">
-        <v>11.187837600708</v>
+        <v>11.1878366470337</v>
       </c>
       <c r="H173" t="n">
         <v>47087</v>
@@ -5444,7 +5444,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H175" t="n">
         <v>17680</v>
@@ -5821,7 +5821,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G188" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H188" t="n">
         <v>13977</v>
@@ -5850,7 +5850,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G189" t="n">
-        <v>11.2418403625488</v>
+        <v>11.2418413162231</v>
       </c>
       <c r="H189" t="n">
         <v>6735</v>
@@ -5879,7 +5879,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H190" t="n">
         <v>289408</v>
@@ -5937,7 +5937,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H192" t="n">
         <v>3564</v>
@@ -5966,7 +5966,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H193" t="n">
         <v>33122</v>
@@ -6053,7 +6053,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H196" t="n">
         <v>20113</v>
@@ -6227,7 +6227,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H202" t="n">
         <v>63641</v>
@@ -6314,7 +6314,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H205" t="n">
         <v>29232</v>
@@ -6459,7 +6459,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G210" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H210" t="n">
         <v>60992</v>
@@ -6488,7 +6488,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H211" t="n">
         <v>191239</v>
@@ -6517,7 +6517,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H212" t="n">
         <v>37366</v>
@@ -6546,7 +6546,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H213" t="n">
         <v>58848</v>
@@ -6604,7 +6604,7 @@
         <v>12.5</v>
       </c>
       <c r="G215" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H215" t="n">
         <v>18114</v>
@@ -6633,7 +6633,7 @@
         <v>12.5</v>
       </c>
       <c r="G216" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H216" t="n">
         <v>32596</v>
@@ -6691,7 +6691,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H218" t="n">
         <v>23902</v>
@@ -6807,7 +6807,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H222" t="n">
         <v>33108</v>
@@ -6894,7 +6894,7 @@
         <v>12.5</v>
       </c>
       <c r="G225" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H225" t="n">
         <v>5055</v>
@@ -6981,7 +6981,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G228" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H228" t="n">
         <v>11596</v>
@@ -7010,7 +7010,7 @@
         <v>12.5</v>
       </c>
       <c r="G229" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H229" t="n">
         <v>380956</v>
@@ -7068,7 +7068,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908138275146</v>
       </c>
       <c r="H231" t="n">
         <v>32508</v>
@@ -7097,7 +7097,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>10.6657991409302</v>
+        <v>10.6657981872559</v>
       </c>
       <c r="H232" t="n">
         <v>39008</v>
@@ -7155,7 +7155,7 @@
         <v>12</v>
       </c>
       <c r="G234" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H234" t="n">
         <v>28217</v>
@@ -7213,7 +7213,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G236" t="n">
-        <v>10.6657991409302</v>
+        <v>10.6657981872559</v>
       </c>
       <c r="H236" t="n">
         <v>11658</v>
@@ -7300,7 +7300,7 @@
         <v>12</v>
       </c>
       <c r="G239" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H239" t="n">
         <v>39939</v>
@@ -7416,7 +7416,7 @@
         <v>12</v>
       </c>
       <c r="G243" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H243" t="n">
         <v>48611</v>
@@ -7445,7 +7445,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7108001708984</v>
+        <v>10.7108020782471</v>
       </c>
       <c r="H244" t="n">
         <v>25326</v>
@@ -7590,7 +7590,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G249" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908138275146</v>
       </c>
       <c r="H249" t="n">
         <v>87545</v>
@@ -7619,7 +7619,7 @@
         <v>12</v>
       </c>
       <c r="G250" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H250" t="n">
         <v>31759</v>
@@ -7648,7 +7648,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908138275146</v>
       </c>
       <c r="H251" t="n">
         <v>71726</v>
@@ -7706,7 +7706,7 @@
         <v>12.5</v>
       </c>
       <c r="G253" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H253" t="n">
         <v>21093</v>
@@ -7851,7 +7851,7 @@
         <v>12.5</v>
       </c>
       <c r="G258" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H258" t="n">
         <v>43297</v>
@@ -7880,7 +7880,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H259" t="n">
         <v>37114</v>
@@ -7938,7 +7938,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G261" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H261" t="n">
         <v>21777</v>
@@ -7967,7 +7967,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>11.3408479690552</v>
+        <v>11.3408489227295</v>
       </c>
       <c r="H262" t="n">
         <v>40370</v>
@@ -8025,7 +8025,7 @@
         <v>12.5</v>
       </c>
       <c r="G264" t="n">
-        <v>11.2508411407471</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H264" t="n">
         <v>19560</v>
@@ -8054,7 +8054,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H265" t="n">
         <v>13029</v>
@@ -8170,7 +8170,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908138275146</v>
       </c>
       <c r="H269" t="n">
         <v>7285</v>
@@ -8344,7 +8344,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>11.1779365539551</v>
+        <v>11.1779375076294</v>
       </c>
       <c r="H275" t="n">
         <v>13564</v>
@@ -8373,7 +8373,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G276" t="n">
-        <v>11.0405035018921</v>
+        <v>11.0405025482178</v>
       </c>
       <c r="H276" t="n">
         <v>26541</v>
@@ -8431,7 +8431,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>11.1321249008179</v>
+        <v>11.1321258544922</v>
       </c>
       <c r="H278" t="n">
         <v>15038</v>
@@ -8518,7 +8518,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>11.5902366638184</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H281" t="n">
         <v>154139</v>
@@ -8547,7 +8547,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H282" t="n">
         <v>21107</v>
@@ -8692,7 +8692,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G287" t="n">
-        <v>11.1779365539551</v>
+        <v>11.1779375076294</v>
       </c>
       <c r="H287" t="n">
         <v>41668</v>
@@ -9040,7 +9040,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>10.8114471435547</v>
+        <v>10.8114461898804</v>
       </c>
       <c r="H299" t="n">
         <v>6920</v>
@@ -9069,7 +9069,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G300" t="n">
-        <v>11.0405035018921</v>
+        <v>11.0405025482178</v>
       </c>
       <c r="H300" t="n">
         <v>228509</v>
@@ -9243,7 +9243,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H306" t="n">
         <v>83168</v>
@@ -9272,7 +9272,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>11.5902366638184</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H307" t="n">
         <v>35606</v>
@@ -9301,7 +9301,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G308" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H308" t="n">
         <v>26383</v>
@@ -9359,7 +9359,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G310" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H310" t="n">
         <v>23793</v>
@@ -9504,7 +9504,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H315" t="n">
         <v>60996</v>
@@ -9533,7 +9533,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>11.1321249008179</v>
+        <v>11.1321258544922</v>
       </c>
       <c r="H316" t="n">
         <v>31108</v>
@@ -9562,7 +9562,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G317" t="n">
-        <v>11.1779365539551</v>
+        <v>11.1779375076294</v>
       </c>
       <c r="H317" t="n">
         <v>23909</v>
@@ -9649,7 +9649,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H320" t="n">
         <v>26167</v>
@@ -9707,7 +9707,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G322" t="n">
-        <v>11.1321249008179</v>
+        <v>11.1321258544922</v>
       </c>
       <c r="H322" t="n">
         <v>19539</v>
@@ -9765,7 +9765,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G324" t="n">
-        <v>11.1779365539551</v>
+        <v>11.1779375076294</v>
       </c>
       <c r="H324" t="n">
         <v>7392</v>
@@ -9881,7 +9881,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H328" t="n">
         <v>12057</v>
@@ -9910,7 +9910,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>11.5902366638184</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H329" t="n">
         <v>118877</v>
@@ -9968,7 +9968,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G331" t="n">
-        <v>11.5902366638184</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H331" t="n">
         <v>21852</v>
@@ -9997,7 +9997,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H332" t="n">
         <v>98903</v>
@@ -10258,7 +10258,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>11.5902366638184</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H341" t="n">
         <v>4404</v>
@@ -10287,7 +10287,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G342" t="n">
-        <v>11.5902366638184</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H342" t="n">
         <v>4793</v>
@@ -10461,7 +10461,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>11.1321249008179</v>
+        <v>11.1321258544922</v>
       </c>
       <c r="H348" t="n">
         <v>2813</v>
@@ -10751,7 +10751,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>11.1779365539551</v>
+        <v>11.1779375076294</v>
       </c>
       <c r="H358" t="n">
         <v>8030</v>
@@ -10867,7 +10867,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G362" t="n">
-        <v>11.1321249008179</v>
+        <v>11.1321258544922</v>
       </c>
       <c r="H362" t="n">
         <v>31361</v>
@@ -10896,7 +10896,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>11.1779365539551</v>
+        <v>11.1779375076294</v>
       </c>
       <c r="H363" t="n">
         <v>193750</v>
@@ -10925,7 +10925,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H364" t="n">
         <v>63021</v>
@@ -10983,7 +10983,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H366" t="n">
         <v>8248</v>
@@ -11041,7 +11041,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>11.5902366638184</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H368" t="n">
         <v>57147</v>
@@ -11070,7 +11070,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H369" t="n">
         <v>35300</v>
@@ -11128,7 +11128,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G371" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H371" t="n">
         <v>59329</v>
@@ -11186,7 +11186,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H373" t="n">
         <v>33947</v>
@@ -11215,7 +11215,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H374" t="n">
         <v>42858</v>
@@ -11331,7 +11331,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>11.1779365539551</v>
+        <v>11.1779375076294</v>
       </c>
       <c r="H378" t="n">
         <v>21188</v>
@@ -11563,7 +11563,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G386" t="n">
-        <v>11.0405035018921</v>
+        <v>11.0405025482178</v>
       </c>
       <c r="H386" t="n">
         <v>36409</v>
@@ -11679,7 +11679,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>10.9488801956177</v>
+        <v>10.9488792419434</v>
       </c>
       <c r="H390" t="n">
         <v>24606</v>
@@ -11708,7 +11708,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>10.8114471435547</v>
+        <v>10.8114461898804</v>
       </c>
       <c r="H391" t="n">
         <v>40022</v>
@@ -11766,7 +11766,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>9.94103336334229</v>
+        <v>9.9410343170166</v>
       </c>
       <c r="H393" t="n">
         <v>74407</v>
@@ -12172,7 +12172,7 @@
         <v>10</v>
       </c>
       <c r="G407" t="n">
-        <v>9.16224193572998</v>
+        <v>9.1622428894043</v>
       </c>
       <c r="H407" t="n">
         <v>15357</v>
@@ -12201,7 +12201,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>9.08894538879395</v>
+        <v>9.08894443511963</v>
       </c>
       <c r="H408" t="n">
         <v>21952</v>
@@ -12288,7 +12288,7 @@
         <v>9.5</v>
       </c>
       <c r="G411" t="n">
-        <v>8.70413017272949</v>
+        <v>8.70413112640381</v>
       </c>
       <c r="H411" t="n">
         <v>58798</v>
@@ -12375,7 +12375,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G414" t="n">
-        <v>8.48423671722412</v>
+        <v>8.48423767089844</v>
       </c>
       <c r="H414" t="n">
         <v>7680</v>
@@ -12433,7 +12433,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>8.09942245483398</v>
+        <v>8.0994234085083</v>
       </c>
       <c r="H416" t="n">
         <v>54469</v>
@@ -12462,7 +12462,7 @@
         <v>9</v>
       </c>
       <c r="G417" t="n">
-        <v>8.246018409729</v>
+        <v>8.24601936340332</v>
       </c>
       <c r="H417" t="n">
         <v>37510</v>
@@ -12491,7 +12491,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G418" t="n">
-        <v>8.37429141998291</v>
+        <v>8.37429046630859</v>
       </c>
       <c r="H418" t="n">
         <v>16525</v>
@@ -12636,7 +12636,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G423" t="n">
-        <v>8.74077987670898</v>
+        <v>8.74077892303467</v>
       </c>
       <c r="H423" t="n">
         <v>61251</v>
@@ -12694,7 +12694,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>9.08894538879395</v>
+        <v>9.08894443511963</v>
       </c>
       <c r="H425" t="n">
         <v>24400</v>
@@ -12810,7 +12810,7 @@
         <v>9.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.70413017272949</v>
+        <v>8.70413112640381</v>
       </c>
       <c r="H429" t="n">
         <v>51975</v>
@@ -12897,7 +12897,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G432" t="n">
-        <v>8.68580532073975</v>
+        <v>8.68580627441406</v>
       </c>
       <c r="H432" t="n">
         <v>8025</v>
@@ -13042,7 +13042,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>8.06277465820312</v>
+        <v>8.06277370452881</v>
       </c>
       <c r="H437" t="n">
         <v>28367</v>
@@ -13216,7 +13216,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G443" t="n">
-        <v>8.33764171600342</v>
+        <v>8.33764266967773</v>
       </c>
       <c r="H443" t="n">
         <v>21963</v>
@@ -13303,7 +13303,7 @@
         <v>9.5</v>
       </c>
       <c r="G446" t="n">
-        <v>8.70413017272949</v>
+        <v>8.70413112640381</v>
       </c>
       <c r="H446" t="n">
         <v>17748</v>
@@ -13361,7 +13361,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G448" t="n">
-        <v>8.59418296813965</v>
+        <v>8.59418392181396</v>
       </c>
       <c r="H448" t="n">
         <v>10460</v>
@@ -13390,7 +13390,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G449" t="n">
-        <v>8.33764171600342</v>
+        <v>8.33764266967773</v>
       </c>
       <c r="H449" t="n">
         <v>15514</v>
@@ -13477,7 +13477,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G452" t="n">
-        <v>8.48423671722412</v>
+        <v>8.48423767089844</v>
       </c>
       <c r="H452" t="n">
         <v>69659</v>
@@ -13535,7 +13535,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G454" t="n">
-        <v>8.48423671722412</v>
+        <v>8.48423767089844</v>
       </c>
       <c r="H454" t="n">
         <v>22696</v>
@@ -13970,7 +13970,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G469" t="n">
-        <v>8.64915752410889</v>
+        <v>8.64915657043457</v>
       </c>
       <c r="H469" t="n">
         <v>20305</v>
@@ -13999,7 +13999,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G470" t="n">
-        <v>8.64915752410889</v>
+        <v>8.64915657043457</v>
       </c>
       <c r="H470" t="n">
         <v>14362</v>
@@ -14115,7 +14115,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G474" t="n">
-        <v>8.48423671722412</v>
+        <v>8.48423767089844</v>
       </c>
       <c r="H474" t="n">
         <v>12437</v>
@@ -14347,7 +14347,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G482" t="n">
-        <v>8.48423671722412</v>
+        <v>8.48423767089844</v>
       </c>
       <c r="H482" t="n">
         <v>21665</v>
@@ -14405,7 +14405,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G484" t="n">
-        <v>8.33764171600342</v>
+        <v>8.33764266967773</v>
       </c>
       <c r="H484" t="n">
         <v>11503</v>
@@ -14434,7 +14434,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G485" t="n">
-        <v>8.26434421539307</v>
+        <v>8.26434326171875</v>
       </c>
       <c r="H485" t="n">
         <v>62090</v>
@@ -14521,7 +14521,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G488" t="n">
-        <v>8.26434421539307</v>
+        <v>8.26434326171875</v>
       </c>
       <c r="H488" t="n">
         <v>18615</v>
@@ -14608,7 +14608,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G491" t="n">
-        <v>8.09942245483398</v>
+        <v>8.0994234085083</v>
       </c>
       <c r="H491" t="n">
         <v>17335</v>
@@ -14753,7 +14753,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>9.2996768951416</v>
+        <v>9.29967594146729</v>
       </c>
       <c r="H496" t="n">
         <v>110828</v>
@@ -14782,7 +14782,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>9.2996768951416</v>
+        <v>9.29967594146729</v>
       </c>
       <c r="H497" t="n">
         <v>140545</v>
@@ -14811,7 +14811,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>9.2996768951416</v>
+        <v>9.29967594146729</v>
       </c>
       <c r="H498" t="n">
         <v>88225</v>
@@ -14898,7 +14898,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G501" t="n">
-        <v>9.2080545425415</v>
+        <v>9.20805358886719</v>
       </c>
       <c r="H501" t="n">
         <v>83469</v>
@@ -14927,7 +14927,7 @@
         <v>10.5</v>
       </c>
       <c r="G502" t="n">
-        <v>9.6203556060791</v>
+        <v>9.62035465240479</v>
       </c>
       <c r="H502" t="n">
         <v>175754</v>
@@ -14956,7 +14956,7 @@
         <v>10</v>
       </c>
       <c r="G503" t="n">
-        <v>9.16224193572998</v>
+        <v>9.1622428894043</v>
       </c>
       <c r="H503" t="n">
         <v>586410</v>
@@ -70613,6 +70613,35 @@
         <v>51911</v>
       </c>
       <c r="I2422" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2423">
+      <c r="A2423" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2423" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2423" t="n">
+        <v>1.35199999809265</v>
+      </c>
+      <c r="D2423" t="n">
+        <v>1.35199999809265</v>
+      </c>
+      <c r="E2423" t="n">
+        <v>1.31200003623962</v>
+      </c>
+      <c r="F2423" t="n">
+        <v>1.34800004959106</v>
+      </c>
+      <c r="G2423" t="n">
+        <v>1.34800004959106</v>
+      </c>
+      <c r="H2423" t="n">
+        <v>122110</v>
+      </c>
+      <c r="I2423" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G2" t="n">
-        <v>9.1356840133667</v>
+        <v>9.13568305969238</v>
       </c>
       <c r="H2" t="n">
         <v>48343</v>
@@ -514,7 +514,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>9.28869438171387</v>
+        <v>9.28869533538818</v>
       </c>
       <c r="H5" t="n">
         <v>264710</v>
@@ -543,7 +543,7 @@
         <v>10.5</v>
       </c>
       <c r="G6" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H6" t="n">
         <v>50252</v>
@@ -572,7 +572,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>9.3607006072998</v>
+        <v>9.36069965362549</v>
       </c>
       <c r="H7" t="n">
         <v>22546</v>
@@ -601,7 +601,7 @@
         <v>10.5</v>
       </c>
       <c r="G8" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H8" t="n">
         <v>12361</v>
@@ -630,7 +630,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G9" t="n">
-        <v>9.4057035446167</v>
+        <v>9.40570259094238</v>
       </c>
       <c r="H9" t="n">
         <v>1874</v>
@@ -659,7 +659,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>9.8107328414917</v>
+        <v>9.81073379516602</v>
       </c>
       <c r="H10" t="n">
         <v>8225</v>
@@ -688,7 +688,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G11" t="n">
-        <v>9.52271270751953</v>
+        <v>9.52271175384521</v>
       </c>
       <c r="H11" t="n">
         <v>34524</v>
@@ -746,7 +746,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.4057035446167</v>
+        <v>9.40570259094238</v>
       </c>
       <c r="H13" t="n">
         <v>11246</v>
@@ -775,7 +775,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>9.4057035446167</v>
+        <v>9.40570259094238</v>
       </c>
       <c r="H14" t="n">
         <v>51250</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="G17" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H17" t="n">
         <v>9239</v>
@@ -891,7 +891,7 @@
         <v>10.5</v>
       </c>
       <c r="G18" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H18" t="n">
         <v>21485</v>
@@ -920,7 +920,7 @@
         <v>10.5</v>
       </c>
       <c r="G19" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H19" t="n">
         <v>143074</v>
@@ -1007,7 +1007,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G22" t="n">
-        <v>9.48670959472656</v>
+        <v>9.48671054840088</v>
       </c>
       <c r="H22" t="n">
         <v>1993</v>
@@ -1239,7 +1239,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G30" t="n">
-        <v>9.62172031402588</v>
+        <v>9.62171936035156</v>
       </c>
       <c r="H30" t="n">
         <v>11222</v>
@@ -1326,7 +1326,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>9.72072792053223</v>
+        <v>9.72072887420654</v>
       </c>
       <c r="H33" t="n">
         <v>17312</v>
@@ -1384,7 +1384,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G35" t="n">
-        <v>9.8107328414917</v>
+        <v>9.81073379516602</v>
       </c>
       <c r="H35" t="n">
         <v>17570</v>
@@ -1529,7 +1529,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G40" t="n">
-        <v>9.90974235534668</v>
+        <v>9.90974140167236</v>
       </c>
       <c r="H40" t="n">
         <v>20802</v>
@@ -1558,7 +1558,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G41" t="n">
-        <v>9.90974235534668</v>
+        <v>9.90974140167236</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G42" t="n">
-        <v>9.91874313354492</v>
+        <v>9.91874217987061</v>
       </c>
       <c r="H42" t="n">
         <v>130</v>
@@ -1616,7 +1616,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G43" t="n">
-        <v>9.91874313354492</v>
+        <v>9.91874217987061</v>
       </c>
       <c r="H43" t="n">
         <v>980</v>
@@ -1645,7 +1645,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>10.1617603302002</v>
+        <v>10.1617593765259</v>
       </c>
       <c r="H44" t="n">
         <v>905</v>
@@ -1674,7 +1674,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G45" t="n">
-        <v>10.1617603302002</v>
+        <v>10.1617593765259</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G47" t="n">
-        <v>10.1617603302002</v>
+        <v>10.1617593765259</v>
       </c>
       <c r="H47" t="n">
         <v>6500</v>
@@ -1761,7 +1761,7 @@
         <v>12</v>
       </c>
       <c r="G48" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H48" t="n">
         <v>2330</v>
@@ -1877,7 +1877,7 @@
         <v>12</v>
       </c>
       <c r="G52" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H52" t="n">
         <v>6600</v>
@@ -1935,7 +1935,7 @@
         <v>12</v>
       </c>
       <c r="G54" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H54" t="n">
         <v>11262</v>
@@ -1964,7 +1964,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G55" t="n">
-        <v>10.8098096847534</v>
+        <v>10.8098087310791</v>
       </c>
       <c r="H55" t="n">
         <v>30919</v>
@@ -1993,7 +1993,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>10.9358177185059</v>
+        <v>10.9358186721802</v>
       </c>
       <c r="H56" t="n">
         <v>69800</v>
@@ -2022,7 +2022,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G57" t="n">
-        <v>10.7648057937622</v>
+        <v>10.7648048400879</v>
       </c>
       <c r="H57" t="n">
         <v>32694</v>
@@ -2080,7 +2080,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G59" t="n">
-        <v>10.7738065719604</v>
+        <v>10.7738075256348</v>
       </c>
       <c r="H59" t="n">
         <v>2335</v>
@@ -2138,7 +2138,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G61" t="n">
-        <v>10.7918071746826</v>
+        <v>10.7918081283569</v>
       </c>
       <c r="H61" t="n">
         <v>118200</v>
@@ -2167,7 +2167,7 @@
         <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H62" t="n">
         <v>8081</v>
@@ -2254,7 +2254,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G65" t="n">
-        <v>10.8098096847534</v>
+        <v>10.8098087310791</v>
       </c>
       <c r="H65" t="n">
         <v>43558</v>
@@ -2312,7 +2312,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G67" t="n">
-        <v>10.9358177185059</v>
+        <v>10.9358186721802</v>
       </c>
       <c r="H67" t="n">
         <v>23723</v>
@@ -2341,7 +2341,7 @@
         <v>12.25</v>
       </c>
       <c r="G68" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H68" t="n">
         <v>11800</v>
@@ -2370,7 +2370,7 @@
         <v>12.25</v>
       </c>
       <c r="G69" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H69" t="n">
         <v>10830</v>
@@ -2399,7 +2399,7 @@
         <v>12.25</v>
       </c>
       <c r="G70" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H70" t="n">
         <v>19079</v>
@@ -2486,7 +2486,7 @@
         <v>12.25</v>
       </c>
       <c r="G73" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H73" t="n">
         <v>10849</v>
@@ -2515,7 +2515,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G74" t="n">
-        <v>10.9628210067749</v>
+        <v>10.9628200531006</v>
       </c>
       <c r="H74" t="n">
         <v>45474</v>
@@ -2544,7 +2544,7 @@
         <v>12.25</v>
       </c>
       <c r="G75" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H75" t="n">
         <v>23178</v>
@@ -2573,7 +2573,7 @@
         <v>12.25</v>
       </c>
       <c r="G76" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H76" t="n">
         <v>77850</v>
@@ -2602,7 +2602,7 @@
         <v>12</v>
       </c>
       <c r="G77" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H77" t="n">
         <v>21843</v>
@@ -2631,7 +2631,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>10.8908138275146</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H78" t="n">
         <v>16304</v>
@@ -2660,7 +2660,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G79" t="n">
-        <v>10.8908138275146</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H79" t="n">
         <v>27515</v>
@@ -2834,7 +2834,7 @@
         <v>12.25</v>
       </c>
       <c r="G85" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H85" t="n">
         <v>7351</v>
@@ -2863,7 +2863,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G86" t="n">
-        <v>11.0078239440918</v>
+        <v>11.0078229904175</v>
       </c>
       <c r="H86" t="n">
         <v>617</v>
@@ -2892,7 +2892,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G87" t="n">
-        <v>11.0078239440918</v>
+        <v>11.0078229904175</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>10.8908138275146</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H88" t="n">
         <v>125</v>
@@ -2950,7 +2950,7 @@
         <v>12</v>
       </c>
       <c r="G89" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H89" t="n">
         <v>2</v>
@@ -2979,7 +2979,7 @@
         <v>12</v>
       </c>
       <c r="G90" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H90" t="n">
         <v>132646</v>
@@ -3008,7 +3008,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>10.8908138275146</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H91" t="n">
         <v>29894</v>
@@ -3037,7 +3037,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G92" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H92" t="n">
         <v>3303</v>
@@ -3153,7 +3153,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H96" t="n">
         <v>95</v>
@@ -3211,7 +3211,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G98" t="n">
-        <v>11.0978307723999</v>
+        <v>11.0978298187256</v>
       </c>
       <c r="H98" t="n">
         <v>3490</v>
@@ -3240,7 +3240,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G99" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H99" t="n">
         <v>4100</v>
@@ -3298,7 +3298,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H101" t="n">
         <v>13000</v>
@@ -3327,7 +3327,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H102" t="n">
         <v>49869</v>
@@ -3356,7 +3356,7 @@
         <v>12.25</v>
       </c>
       <c r="G103" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H103" t="n">
         <v>800</v>
@@ -3530,7 +3530,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G109" t="n">
-        <v>10.8908138275146</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H109" t="n">
         <v>196</v>
@@ -3791,7 +3791,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G118" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H118" t="n">
         <v>5884</v>
@@ -3849,7 +3849,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G120" t="n">
-        <v>11.0978307723999</v>
+        <v>11.0978298187256</v>
       </c>
       <c r="H120" t="n">
         <v>23000</v>
@@ -3878,7 +3878,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G121" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H121" t="n">
         <v>95700</v>
@@ -3994,7 +3994,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G125" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H125" t="n">
         <v>53861</v>
@@ -4023,7 +4023,7 @@
         <v>12.25</v>
       </c>
       <c r="G126" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H126" t="n">
         <v>7500</v>
@@ -4081,7 +4081,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>11.0978307723999</v>
+        <v>11.0978298187256</v>
       </c>
       <c r="H128" t="n">
         <v>24331</v>
@@ -4110,7 +4110,7 @@
         <v>12.25</v>
       </c>
       <c r="G129" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H129" t="n">
         <v>6915</v>
@@ -4139,7 +4139,7 @@
         <v>12</v>
       </c>
       <c r="G130" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H130" t="n">
         <v>10740</v>
@@ -4197,7 +4197,7 @@
         <v>12.25</v>
       </c>
       <c r="G132" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H132" t="n">
         <v>496</v>
@@ -4226,7 +4226,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G133" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H133" t="n">
         <v>1516</v>
@@ -4255,7 +4255,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>12.25</v>
       </c>
       <c r="G136" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H136" t="n">
         <v>37117</v>
@@ -4545,7 +4545,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>11.4308557510376</v>
+        <v>11.4308547973633</v>
       </c>
       <c r="H144" t="n">
         <v>15034</v>
@@ -4574,7 +4574,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>11.4308557510376</v>
+        <v>11.4308547973633</v>
       </c>
       <c r="H145" t="n">
         <v>800</v>
@@ -4603,7 +4603,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G146" t="n">
-        <v>11.4308557510376</v>
+        <v>11.4308547973633</v>
       </c>
       <c r="H146" t="n">
         <v>1600</v>
@@ -4632,7 +4632,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G147" t="n">
-        <v>11.5208625793457</v>
+        <v>11.5208616256714</v>
       </c>
       <c r="H147" t="n">
         <v>40959</v>
@@ -4661,7 +4661,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G148" t="n">
-        <v>11.6918745040894</v>
+        <v>11.691873550415</v>
       </c>
       <c r="H148" t="n">
         <v>50666</v>
@@ -4690,7 +4690,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G149" t="n">
-        <v>11.6018686294556</v>
+        <v>11.6018676757812</v>
       </c>
       <c r="H149" t="n">
         <v>19162</v>
@@ -4719,7 +4719,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G150" t="n">
-        <v>11.6828727722168</v>
+        <v>11.6828746795654</v>
       </c>
       <c r="H150" t="n">
         <v>102168</v>
@@ -4748,7 +4748,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G151" t="n">
-        <v>11.6738729476929</v>
+        <v>11.6738739013672</v>
       </c>
       <c r="H151" t="n">
         <v>25392</v>
@@ -4835,7 +4835,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G154" t="n">
-        <v>11.8178853988647</v>
+        <v>11.8178844451904</v>
       </c>
       <c r="H154" t="n">
         <v>13313</v>
@@ -4864,7 +4864,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G155" t="n">
-        <v>11.5748653411865</v>
+        <v>11.5748662948608</v>
       </c>
       <c r="H155" t="n">
         <v>9271</v>
@@ -5038,7 +5038,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G161" t="n">
-        <v>11.4938611984253</v>
+        <v>11.493860244751</v>
       </c>
       <c r="H161" t="n">
         <v>12761</v>
@@ -5067,7 +5067,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G162" t="n">
-        <v>11.5028610229492</v>
+        <v>11.5028600692749</v>
       </c>
       <c r="H162" t="n">
         <v>8549</v>
@@ -5125,7 +5125,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G164" t="n">
-        <v>11.6558713912964</v>
+        <v>11.6558723449707</v>
       </c>
       <c r="H164" t="n">
         <v>7000</v>
@@ -5183,7 +5183,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>11.6558713912964</v>
+        <v>11.6558723449707</v>
       </c>
       <c r="H166" t="n">
         <v>436</v>
@@ -5212,7 +5212,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G167" t="n">
-        <v>11.8358850479126</v>
+        <v>11.8358840942383</v>
       </c>
       <c r="H167" t="n">
         <v>5902</v>
@@ -5299,7 +5299,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G170" t="n">
-        <v>11.6828727722168</v>
+        <v>11.6828746795654</v>
       </c>
       <c r="H170" t="n">
         <v>11344</v>
@@ -5328,7 +5328,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>11.4128541946411</v>
+        <v>11.4128551483154</v>
       </c>
       <c r="H171" t="n">
         <v>91681</v>
@@ -5386,7 +5386,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G173" t="n">
-        <v>11.1878366470337</v>
+        <v>11.187837600708</v>
       </c>
       <c r="H173" t="n">
         <v>47087</v>
@@ -5502,7 +5502,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H177" t="n">
         <v>97611</v>
@@ -5589,7 +5589,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>10.9358177185059</v>
+        <v>10.9358186721802</v>
       </c>
       <c r="H180" t="n">
         <v>53250</v>
@@ -5647,7 +5647,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G182" t="n">
-        <v>10.7918071746826</v>
+        <v>10.7918081283569</v>
       </c>
       <c r="H182" t="n">
         <v>45769</v>
@@ -5705,7 +5705,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>10.9358177185059</v>
+        <v>10.9358186721802</v>
       </c>
       <c r="H184" t="n">
         <v>264783</v>
@@ -5763,7 +5763,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G186" t="n">
-        <v>11.2328405380249</v>
+        <v>11.2328395843506</v>
       </c>
       <c r="H186" t="n">
         <v>31039</v>
@@ -5792,7 +5792,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G187" t="n">
-        <v>11.1968383789062</v>
+        <v>11.1968374252319</v>
       </c>
       <c r="H187" t="n">
         <v>35264</v>
@@ -6024,7 +6024,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>10.9358177185059</v>
+        <v>10.9358186721802</v>
       </c>
       <c r="H195" t="n">
         <v>36226</v>
@@ -6082,7 +6082,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H197" t="n">
         <v>24111</v>
@@ -6111,7 +6111,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H198" t="n">
         <v>19135</v>
@@ -6140,7 +6140,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H199" t="n">
         <v>10780</v>
@@ -6198,7 +6198,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>11.3858509063721</v>
+        <v>11.3858518600464</v>
       </c>
       <c r="H201" t="n">
         <v>341100</v>
@@ -6227,7 +6227,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6558713912964</v>
+        <v>11.6558723449707</v>
       </c>
       <c r="H202" t="n">
         <v>63641</v>
@@ -6285,7 +6285,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G204" t="n">
-        <v>11.8808889389038</v>
+        <v>11.8808879852295</v>
       </c>
       <c r="H204" t="n">
         <v>50580</v>
@@ -6314,7 +6314,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>11.6558713912964</v>
+        <v>11.6558723449707</v>
       </c>
       <c r="H205" t="n">
         <v>29232</v>
@@ -6575,7 +6575,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H214" t="n">
         <v>42154</v>
@@ -6720,7 +6720,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>10.9358177185059</v>
+        <v>10.9358186721802</v>
       </c>
       <c r="H219" t="n">
         <v>34983</v>
@@ -6749,7 +6749,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H220" t="n">
         <v>32924</v>
@@ -6836,7 +6836,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G223" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H223" t="n">
         <v>32411</v>
@@ -6952,7 +6952,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>11.4308557510376</v>
+        <v>11.4308547973633</v>
       </c>
       <c r="H227" t="n">
         <v>64055</v>
@@ -7039,7 +7039,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H230" t="n">
         <v>49113</v>
@@ -7068,7 +7068,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>10.8908138275146</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H231" t="n">
         <v>32508</v>
@@ -7126,7 +7126,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G233" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H233" t="n">
         <v>17885</v>
@@ -7155,7 +7155,7 @@
         <v>12</v>
       </c>
       <c r="G234" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H234" t="n">
         <v>28217</v>
@@ -7184,7 +7184,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G235" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H235" t="n">
         <v>16566</v>
@@ -7271,7 +7271,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H238" t="n">
         <v>18095</v>
@@ -7300,7 +7300,7 @@
         <v>12</v>
       </c>
       <c r="G239" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H239" t="n">
         <v>39939</v>
@@ -7329,7 +7329,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G240" t="n">
-        <v>10.755805015564</v>
+        <v>10.7558040618896</v>
       </c>
       <c r="H240" t="n">
         <v>29999</v>
@@ -7358,7 +7358,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>10.755805015564</v>
+        <v>10.7558040618896</v>
       </c>
       <c r="H241" t="n">
         <v>6931</v>
@@ -7387,7 +7387,7 @@
         <v>12.25</v>
       </c>
       <c r="G242" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H242" t="n">
         <v>26025</v>
@@ -7416,7 +7416,7 @@
         <v>12</v>
       </c>
       <c r="G243" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H243" t="n">
         <v>48611</v>
@@ -7445,7 +7445,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7108020782471</v>
+        <v>10.7108011245728</v>
       </c>
       <c r="H244" t="n">
         <v>25326</v>
@@ -7474,7 +7474,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H245" t="n">
         <v>15122</v>
@@ -7503,7 +7503,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H246" t="n">
         <v>5465</v>
@@ -7532,7 +7532,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G247" t="n">
-        <v>10.755805015564</v>
+        <v>10.7558040618896</v>
       </c>
       <c r="H247" t="n">
         <v>29917</v>
@@ -7561,7 +7561,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G248" t="n">
-        <v>10.755805015564</v>
+        <v>10.7558040618896</v>
       </c>
       <c r="H248" t="n">
         <v>47974</v>
@@ -7590,7 +7590,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G249" t="n">
-        <v>10.8908138275146</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H249" t="n">
         <v>87545</v>
@@ -7619,7 +7619,7 @@
         <v>12</v>
       </c>
       <c r="G250" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H250" t="n">
         <v>31759</v>
@@ -7648,7 +7648,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>10.8908138275146</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H251" t="n">
         <v>71726</v>
@@ -8112,7 +8112,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H267" t="n">
         <v>7336</v>
@@ -8170,7 +8170,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>10.8908138275146</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H269" t="n">
         <v>7285</v>
@@ -8199,7 +8199,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H270" t="n">
         <v>12370</v>
@@ -8228,7 +8228,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H271" t="n">
         <v>4989</v>
@@ -8257,7 +8257,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H272" t="n">
         <v>17619</v>
@@ -8286,7 +8286,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H273" t="n">
         <v>16739</v>
@@ -70642,6 +70642,35 @@
         <v>122110</v>
       </c>
       <c r="I2423" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2424">
+      <c r="A2424" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2424" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2424" t="n">
+        <v>1.32200002670288</v>
+      </c>
+      <c r="D2424" t="n">
+        <v>1.34800004959106</v>
+      </c>
+      <c r="E2424" t="n">
+        <v>1.32200002670288</v>
+      </c>
+      <c r="F2424" t="n">
+        <v>1.34399998188019</v>
+      </c>
+      <c r="G2424" t="n">
+        <v>1.34399998188019</v>
+      </c>
+      <c r="H2424" t="n">
+        <v>62347</v>
+      </c>
+      <c r="I2424" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G2" t="n">
-        <v>9.13568305969238</v>
+        <v>9.1356840133667</v>
       </c>
       <c r="H2" t="n">
         <v>48343</v>
@@ -456,7 +456,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G3" t="n">
-        <v>9.27969455718994</v>
+        <v>9.27969360351562</v>
       </c>
       <c r="H3" t="n">
         <v>73034</v>
@@ -572,7 +572,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>9.36069965362549</v>
+        <v>9.3607006072998</v>
       </c>
       <c r="H7" t="n">
         <v>22546</v>
@@ -630,7 +630,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G9" t="n">
-        <v>9.40570259094238</v>
+        <v>9.4057035446167</v>
       </c>
       <c r="H9" t="n">
         <v>1874</v>
@@ -659,7 +659,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>9.81073379516602</v>
+        <v>9.8107328414917</v>
       </c>
       <c r="H10" t="n">
         <v>8225</v>
@@ -688,7 +688,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G11" t="n">
-        <v>9.52271175384521</v>
+        <v>9.52271270751953</v>
       </c>
       <c r="H11" t="n">
         <v>34524</v>
@@ -746,7 +746,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.40570259094238</v>
+        <v>9.4057035446167</v>
       </c>
       <c r="H13" t="n">
         <v>11246</v>
@@ -775,7 +775,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>9.40570259094238</v>
+        <v>9.4057035446167</v>
       </c>
       <c r="H14" t="n">
         <v>51250</v>
@@ -949,7 +949,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G20" t="n">
-        <v>9.54071426391602</v>
+        <v>9.5407133102417</v>
       </c>
       <c r="H20" t="n">
         <v>8555</v>
@@ -1007,7 +1007,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G22" t="n">
-        <v>9.48671054840088</v>
+        <v>9.48670959472656</v>
       </c>
       <c r="H22" t="n">
         <v>1993</v>
@@ -1094,7 +1094,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G25" t="n">
-        <v>9.54071426391602</v>
+        <v>9.5407133102417</v>
       </c>
       <c r="H25" t="n">
         <v>17860</v>
@@ -1152,7 +1152,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>9.54071426391602</v>
+        <v>9.5407133102417</v>
       </c>
       <c r="H27" t="n">
         <v>16080</v>
@@ -1239,7 +1239,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G30" t="n">
-        <v>9.62171936035156</v>
+        <v>9.62172031402588</v>
       </c>
       <c r="H30" t="n">
         <v>11222</v>
@@ -1326,7 +1326,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>9.72072887420654</v>
+        <v>9.72072792053223</v>
       </c>
       <c r="H33" t="n">
         <v>17312</v>
@@ -1384,7 +1384,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G35" t="n">
-        <v>9.81073379516602</v>
+        <v>9.8107328414917</v>
       </c>
       <c r="H35" t="n">
         <v>17570</v>
@@ -1529,7 +1529,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G40" t="n">
-        <v>9.90974140167236</v>
+        <v>9.90974235534668</v>
       </c>
       <c r="H40" t="n">
         <v>20802</v>
@@ -1558,7 +1558,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G41" t="n">
-        <v>9.90974140167236</v>
+        <v>9.90974235534668</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G42" t="n">
-        <v>9.91874217987061</v>
+        <v>9.91874313354492</v>
       </c>
       <c r="H42" t="n">
         <v>130</v>
@@ -1616,7 +1616,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G43" t="n">
-        <v>9.91874217987061</v>
+        <v>9.91874313354492</v>
       </c>
       <c r="H43" t="n">
         <v>980</v>
@@ -1645,7 +1645,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>10.1617593765259</v>
+        <v>10.1617603302002</v>
       </c>
       <c r="H44" t="n">
         <v>905</v>
@@ -1674,7 +1674,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G45" t="n">
-        <v>10.1617593765259</v>
+        <v>10.1617603302002</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G47" t="n">
-        <v>10.1617593765259</v>
+        <v>10.1617603302002</v>
       </c>
       <c r="H47" t="n">
         <v>6500</v>
@@ -1906,7 +1906,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G53" t="n">
-        <v>10.6928005218506</v>
+        <v>10.6927995681763</v>
       </c>
       <c r="H53" t="n">
         <v>10522</v>
@@ -2022,7 +2022,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G57" t="n">
-        <v>10.7648048400879</v>
+        <v>10.7648057937622</v>
       </c>
       <c r="H57" t="n">
         <v>32694</v>
@@ -2051,7 +2051,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G58" t="n">
-        <v>10.6928005218506</v>
+        <v>10.6927995681763</v>
       </c>
       <c r="H58" t="n">
         <v>19515</v>
@@ -2080,7 +2080,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G59" t="n">
-        <v>10.7738075256348</v>
+        <v>10.7738065719604</v>
       </c>
       <c r="H59" t="n">
         <v>2335</v>
@@ -2283,7 +2283,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G66" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H66" t="n">
         <v>2413</v>
@@ -2341,7 +2341,7 @@
         <v>12.25</v>
       </c>
       <c r="G68" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H68" t="n">
         <v>11800</v>
@@ -2370,7 +2370,7 @@
         <v>12.25</v>
       </c>
       <c r="G69" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H69" t="n">
         <v>10830</v>
@@ -2399,7 +2399,7 @@
         <v>12.25</v>
       </c>
       <c r="G70" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H70" t="n">
         <v>19079</v>
@@ -2428,7 +2428,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H71" t="n">
         <v>19479</v>
@@ -2457,7 +2457,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H72" t="n">
         <v>17517</v>
@@ -2486,7 +2486,7 @@
         <v>12.25</v>
       </c>
       <c r="G73" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H73" t="n">
         <v>10849</v>
@@ -2515,7 +2515,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G74" t="n">
-        <v>10.9628200531006</v>
+        <v>10.9628210067749</v>
       </c>
       <c r="H74" t="n">
         <v>45474</v>
@@ -2544,7 +2544,7 @@
         <v>12.25</v>
       </c>
       <c r="G75" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H75" t="n">
         <v>23178</v>
@@ -2573,7 +2573,7 @@
         <v>12.25</v>
       </c>
       <c r="G76" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H76" t="n">
         <v>77850</v>
@@ -2834,7 +2834,7 @@
         <v>12.25</v>
       </c>
       <c r="G85" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H85" t="n">
         <v>7351</v>
@@ -2863,7 +2863,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G86" t="n">
-        <v>11.0078229904175</v>
+        <v>11.0078239440918</v>
       </c>
       <c r="H86" t="n">
         <v>617</v>
@@ -2892,7 +2892,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G87" t="n">
-        <v>11.0078229904175</v>
+        <v>11.0078239440918</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G92" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H92" t="n">
         <v>3303</v>
@@ -3240,7 +3240,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G99" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H99" t="n">
         <v>4100</v>
@@ -3356,7 +3356,7 @@
         <v>12.25</v>
       </c>
       <c r="G103" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H103" t="n">
         <v>800</v>
@@ -3414,7 +3414,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G105" t="n">
-        <v>11.151834487915</v>
+        <v>11.1518354415894</v>
       </c>
       <c r="H105" t="n">
         <v>6308</v>
@@ -3559,7 +3559,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>10.8458108901978</v>
+        <v>10.8458118438721</v>
       </c>
       <c r="H110" t="n">
         <v>400</v>
@@ -3733,7 +3733,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H116" t="n">
         <v>2</v>
@@ -3762,7 +3762,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H117" t="n">
         <v>12190</v>
@@ -3791,7 +3791,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G118" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H118" t="n">
         <v>5884</v>
@@ -3820,7 +3820,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>11.2418413162231</v>
+        <v>11.2418422698975</v>
       </c>
       <c r="H119" t="n">
         <v>10255</v>
@@ -3878,7 +3878,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G121" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H121" t="n">
         <v>95700</v>
@@ -3907,7 +3907,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H122" t="n">
         <v>2200</v>
@@ -3936,7 +3936,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G123" t="n">
-        <v>11.151834487915</v>
+        <v>11.1518354415894</v>
       </c>
       <c r="H123" t="n">
         <v>6225</v>
@@ -3965,7 +3965,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G124" t="n">
-        <v>11.0888290405273</v>
+        <v>11.0888299942017</v>
       </c>
       <c r="H124" t="n">
         <v>20229</v>
@@ -3994,7 +3994,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G125" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H125" t="n">
         <v>53861</v>
@@ -4023,7 +4023,7 @@
         <v>12.25</v>
       </c>
       <c r="G126" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H126" t="n">
         <v>7500</v>
@@ -4110,7 +4110,7 @@
         <v>12.25</v>
       </c>
       <c r="G129" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H129" t="n">
         <v>6915</v>
@@ -4197,7 +4197,7 @@
         <v>12.25</v>
       </c>
       <c r="G132" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H132" t="n">
         <v>496</v>
@@ -4226,7 +4226,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G133" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H133" t="n">
         <v>1516</v>
@@ -4255,7 +4255,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>12.25</v>
       </c>
       <c r="G136" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H136" t="n">
         <v>37117</v>
@@ -4342,7 +4342,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H137" t="n">
         <v>11453</v>
@@ -4371,7 +4371,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G139" t="n">
-        <v>11.1428337097168</v>
+        <v>11.1428327560425</v>
       </c>
       <c r="H139" t="n">
         <v>42117</v>
@@ -4632,7 +4632,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G147" t="n">
-        <v>11.5208616256714</v>
+        <v>11.5208625793457</v>
       </c>
       <c r="H147" t="n">
         <v>40959</v>
@@ -4661,7 +4661,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G148" t="n">
-        <v>11.691873550415</v>
+        <v>11.6918745040894</v>
       </c>
       <c r="H148" t="n">
         <v>50666</v>
@@ -4690,7 +4690,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G149" t="n">
-        <v>11.6018676757812</v>
+        <v>11.6018686294556</v>
       </c>
       <c r="H149" t="n">
         <v>19162</v>
@@ -4719,7 +4719,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G150" t="n">
-        <v>11.6828746795654</v>
+        <v>11.6828727722168</v>
       </c>
       <c r="H150" t="n">
         <v>102168</v>
@@ -4835,7 +4835,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G154" t="n">
-        <v>11.8178844451904</v>
+        <v>11.8178853988647</v>
       </c>
       <c r="H154" t="n">
         <v>13313</v>
@@ -4864,7 +4864,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G155" t="n">
-        <v>11.5748662948608</v>
+        <v>11.5748653411865</v>
       </c>
       <c r="H155" t="n">
         <v>9271</v>
@@ -5125,7 +5125,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G164" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H164" t="n">
         <v>7000</v>
@@ -5183,7 +5183,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H166" t="n">
         <v>436</v>
@@ -5299,7 +5299,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G170" t="n">
-        <v>11.6828746795654</v>
+        <v>11.6828727722168</v>
       </c>
       <c r="H170" t="n">
         <v>11344</v>
@@ -5328,7 +5328,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>11.4128551483154</v>
+        <v>11.4128541946411</v>
       </c>
       <c r="H171" t="n">
         <v>91681</v>
@@ -5386,7 +5386,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G173" t="n">
-        <v>11.187837600708</v>
+        <v>11.1878366470337</v>
       </c>
       <c r="H173" t="n">
         <v>47087</v>
@@ -5444,7 +5444,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H175" t="n">
         <v>17680</v>
@@ -5473,7 +5473,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G176" t="n">
-        <v>11.1428337097168</v>
+        <v>11.1428327560425</v>
       </c>
       <c r="H176" t="n">
         <v>35894</v>
@@ -5502,7 +5502,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H177" t="n">
         <v>97611</v>
@@ -5792,7 +5792,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G187" t="n">
-        <v>11.1968374252319</v>
+        <v>11.1968383789062</v>
       </c>
       <c r="H187" t="n">
         <v>35264</v>
@@ -5850,7 +5850,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G189" t="n">
-        <v>11.2418413162231</v>
+        <v>11.2418422698975</v>
       </c>
       <c r="H189" t="n">
         <v>6735</v>
@@ -5908,7 +5908,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G191" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H191" t="n">
         <v>43427</v>
@@ -5966,7 +5966,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H193" t="n">
         <v>33122</v>
@@ -6053,7 +6053,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H196" t="n">
         <v>20113</v>
@@ -6082,7 +6082,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H197" t="n">
         <v>24111</v>
@@ -6111,7 +6111,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H198" t="n">
         <v>19135</v>
@@ -6169,7 +6169,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H200" t="n">
         <v>40377</v>
@@ -6198,7 +6198,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>11.3858518600464</v>
+        <v>11.3858509063721</v>
       </c>
       <c r="H201" t="n">
         <v>341100</v>
@@ -6227,7 +6227,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H202" t="n">
         <v>63641</v>
@@ -6285,7 +6285,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G204" t="n">
-        <v>11.8808879852295</v>
+        <v>11.8808889389038</v>
       </c>
       <c r="H204" t="n">
         <v>50580</v>
@@ -6314,7 +6314,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H205" t="n">
         <v>29232</v>
@@ -6575,7 +6575,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H214" t="n">
         <v>42154</v>
@@ -6662,7 +6662,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H217" t="n">
         <v>100153</v>
@@ -6691,7 +6691,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H218" t="n">
         <v>23902</v>
@@ -6807,7 +6807,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H222" t="n">
         <v>33108</v>
@@ -6836,7 +6836,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G223" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H223" t="n">
         <v>32411</v>
@@ -6865,7 +6865,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G224" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H224" t="n">
         <v>38565</v>
@@ -7039,7 +7039,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H230" t="n">
         <v>49113</v>
@@ -7242,7 +7242,7 @@
         <v>11.75</v>
       </c>
       <c r="G237" t="n">
-        <v>10.5757913589478</v>
+        <v>10.5757923126221</v>
       </c>
       <c r="H237" t="n">
         <v>38013</v>
@@ -7329,7 +7329,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G240" t="n">
-        <v>10.7558040618896</v>
+        <v>10.755805015564</v>
       </c>
       <c r="H240" t="n">
         <v>29999</v>
@@ -7358,7 +7358,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>10.7558040618896</v>
+        <v>10.755805015564</v>
       </c>
       <c r="H241" t="n">
         <v>6931</v>
@@ -7387,7 +7387,7 @@
         <v>12.25</v>
       </c>
       <c r="G242" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H242" t="n">
         <v>26025</v>
@@ -7532,7 +7532,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G247" t="n">
-        <v>10.7558040618896</v>
+        <v>10.755805015564</v>
       </c>
       <c r="H247" t="n">
         <v>29917</v>
@@ -7561,7 +7561,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G248" t="n">
-        <v>10.7558040618896</v>
+        <v>10.755805015564</v>
       </c>
       <c r="H248" t="n">
         <v>47974</v>
@@ -7735,7 +7735,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H254" t="n">
         <v>40241</v>
@@ -7764,7 +7764,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G255" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H255" t="n">
         <v>5284</v>
@@ -7909,7 +7909,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G260" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H260" t="n">
         <v>17724</v>
@@ -7996,7 +7996,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H263" t="n">
         <v>27661</v>
@@ -8054,7 +8054,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H265" t="n">
         <v>13029</v>
@@ -8083,7 +8083,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H266" t="n">
         <v>6743</v>
@@ -8112,7 +8112,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H267" t="n">
         <v>7336</v>
@@ -8141,7 +8141,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H268" t="n">
         <v>5138</v>
@@ -8257,7 +8257,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H272" t="n">
         <v>17619</v>
@@ -8286,7 +8286,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H273" t="n">
         <v>16739</v>
@@ -8315,7 +8315,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H274" t="n">
         <v>27992</v>
@@ -70668,9 +70668,38 @@
         <v>1.34399998188019</v>
       </c>
       <c r="H2424" t="n">
-        <v>62347</v>
+        <v>63485</v>
       </c>
       <c r="I2424" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2425">
+      <c r="A2425" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2425" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2425" t="n">
+        <v>1.34599995613098</v>
+      </c>
+      <c r="D2425" t="n">
+        <v>1.34800004959106</v>
+      </c>
+      <c r="E2425" t="n">
+        <v>1.32599997520447</v>
+      </c>
+      <c r="F2425" t="n">
+        <v>1.33800005912781</v>
+      </c>
+      <c r="G2425" t="n">
+        <v>1.33800005912781</v>
+      </c>
+      <c r="H2425" t="n">
+        <v>29350</v>
+      </c>
+      <c r="I2425" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -514,7 +514,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>9.28869533538818</v>
+        <v>9.28869438171387</v>
       </c>
       <c r="H5" t="n">
         <v>264710</v>
@@ -543,7 +543,7 @@
         <v>10.5</v>
       </c>
       <c r="G6" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H6" t="n">
         <v>50252</v>
@@ -601,7 +601,7 @@
         <v>10.5</v>
       </c>
       <c r="G8" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H8" t="n">
         <v>12361</v>
@@ -833,7 +833,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G16" t="n">
-        <v>9.34269905090332</v>
+        <v>9.34270000457764</v>
       </c>
       <c r="H16" t="n">
         <v>99540</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="G17" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H17" t="n">
         <v>9239</v>
@@ -891,7 +891,7 @@
         <v>10.5</v>
       </c>
       <c r="G18" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H18" t="n">
         <v>21485</v>
@@ -920,7 +920,7 @@
         <v>10.5</v>
       </c>
       <c r="G19" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H19" t="n">
         <v>143074</v>
@@ -1036,7 +1036,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>9.4957103729248</v>
+        <v>9.49570941925049</v>
       </c>
       <c r="H23" t="n">
         <v>24798</v>
@@ -1065,7 +1065,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>9.4957103729248</v>
+        <v>9.49570941925049</v>
       </c>
       <c r="H24" t="n">
         <v>15509</v>
@@ -1355,7 +1355,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G34" t="n">
-        <v>9.69372653961182</v>
+        <v>9.6937255859375</v>
       </c>
       <c r="H34" t="n">
         <v>17123</v>
@@ -1761,7 +1761,7 @@
         <v>12</v>
       </c>
       <c r="G48" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H48" t="n">
         <v>2330</v>
@@ -1877,7 +1877,7 @@
         <v>12</v>
       </c>
       <c r="G52" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H52" t="n">
         <v>6600</v>
@@ -1935,7 +1935,7 @@
         <v>12</v>
       </c>
       <c r="G54" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H54" t="n">
         <v>11262</v>
@@ -1964,7 +1964,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G55" t="n">
-        <v>10.8098087310791</v>
+        <v>10.8098096847534</v>
       </c>
       <c r="H55" t="n">
         <v>30919</v>
@@ -1993,7 +1993,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>10.9358186721802</v>
+        <v>10.9358177185059</v>
       </c>
       <c r="H56" t="n">
         <v>69800</v>
@@ -2138,7 +2138,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G61" t="n">
-        <v>10.7918081283569</v>
+        <v>10.7918071746826</v>
       </c>
       <c r="H61" t="n">
         <v>118200</v>
@@ -2167,7 +2167,7 @@
         <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H62" t="n">
         <v>8081</v>
@@ -2254,7 +2254,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G65" t="n">
-        <v>10.8098087310791</v>
+        <v>10.8098096847534</v>
       </c>
       <c r="H65" t="n">
         <v>43558</v>
@@ -2312,7 +2312,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G67" t="n">
-        <v>10.9358186721802</v>
+        <v>10.9358177185059</v>
       </c>
       <c r="H67" t="n">
         <v>23723</v>
@@ -2428,7 +2428,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H71" t="n">
         <v>19479</v>
@@ -2515,7 +2515,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G74" t="n">
-        <v>10.9628210067749</v>
+        <v>10.9628200531006</v>
       </c>
       <c r="H74" t="n">
         <v>45474</v>
@@ -2602,7 +2602,7 @@
         <v>12</v>
       </c>
       <c r="G77" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H77" t="n">
         <v>21843</v>
@@ -2950,7 +2950,7 @@
         <v>12</v>
       </c>
       <c r="G89" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H89" t="n">
         <v>2</v>
@@ -2979,7 +2979,7 @@
         <v>12</v>
       </c>
       <c r="G90" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H90" t="n">
         <v>132646</v>
@@ -3153,7 +3153,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>10.9808225631714</v>
+        <v>10.9808216094971</v>
       </c>
       <c r="H96" t="n">
         <v>95</v>
@@ -3211,7 +3211,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G98" t="n">
-        <v>11.0978298187256</v>
+        <v>11.0978307723999</v>
       </c>
       <c r="H98" t="n">
         <v>3490</v>
@@ -3298,7 +3298,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>10.9808225631714</v>
+        <v>10.9808216094971</v>
       </c>
       <c r="H101" t="n">
         <v>13000</v>
@@ -3327,7 +3327,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>10.9808225631714</v>
+        <v>10.9808216094971</v>
       </c>
       <c r="H102" t="n">
         <v>49869</v>
@@ -3733,7 +3733,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H116" t="n">
         <v>2</v>
@@ -3820,7 +3820,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>11.2418422698975</v>
+        <v>11.2418403625488</v>
       </c>
       <c r="H119" t="n">
         <v>10255</v>
@@ -3849,7 +3849,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G120" t="n">
-        <v>11.0978298187256</v>
+        <v>11.0978307723999</v>
       </c>
       <c r="H120" t="n">
         <v>23000</v>
@@ -3965,7 +3965,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G124" t="n">
-        <v>11.0888299942017</v>
+        <v>11.0888290405273</v>
       </c>
       <c r="H124" t="n">
         <v>20229</v>
@@ -4081,7 +4081,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>11.0978298187256</v>
+        <v>11.0978307723999</v>
       </c>
       <c r="H128" t="n">
         <v>24331</v>
@@ -4139,7 +4139,7 @@
         <v>12</v>
       </c>
       <c r="G130" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H130" t="n">
         <v>10740</v>
@@ -4342,7 +4342,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H137" t="n">
         <v>11453</v>
@@ -4371,7 +4371,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G139" t="n">
-        <v>11.1428327560425</v>
+        <v>11.1428337097168</v>
       </c>
       <c r="H139" t="n">
         <v>42117</v>
@@ -4545,7 +4545,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>11.4308547973633</v>
+        <v>11.4308557510376</v>
       </c>
       <c r="H144" t="n">
         <v>15034</v>
@@ -4574,7 +4574,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>11.4308547973633</v>
+        <v>11.4308557510376</v>
       </c>
       <c r="H145" t="n">
         <v>800</v>
@@ -4603,7 +4603,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G146" t="n">
-        <v>11.4308547973633</v>
+        <v>11.4308557510376</v>
       </c>
       <c r="H146" t="n">
         <v>1600</v>
@@ -4661,7 +4661,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G148" t="n">
-        <v>11.6918745040894</v>
+        <v>11.6918754577637</v>
       </c>
       <c r="H148" t="n">
         <v>50666</v>
@@ -4777,7 +4777,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>11.5658655166626</v>
+        <v>11.5658664703369</v>
       </c>
       <c r="H152" t="n">
         <v>7751</v>
@@ -4806,7 +4806,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G153" t="n">
-        <v>11.5118618011475</v>
+        <v>11.5118608474731</v>
       </c>
       <c r="H153" t="n">
         <v>15226</v>
@@ -4893,7 +4893,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>11.5658655166626</v>
+        <v>11.5658664703369</v>
       </c>
       <c r="H156" t="n">
         <v>15491</v>
@@ -4980,7 +4980,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>11.5658655166626</v>
+        <v>11.5658664703369</v>
       </c>
       <c r="H159" t="n">
         <v>810</v>
@@ -5212,7 +5212,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G167" t="n">
-        <v>11.8358840942383</v>
+        <v>11.8358850479126</v>
       </c>
       <c r="H167" t="n">
         <v>5902</v>
@@ -5328,7 +5328,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>11.4128541946411</v>
+        <v>11.4128551483154</v>
       </c>
       <c r="H171" t="n">
         <v>91681</v>
@@ -5473,7 +5473,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G176" t="n">
-        <v>11.1428327560425</v>
+        <v>11.1428337097168</v>
       </c>
       <c r="H176" t="n">
         <v>35894</v>
@@ -5589,7 +5589,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>10.9358186721802</v>
+        <v>10.9358177185059</v>
       </c>
       <c r="H180" t="n">
         <v>53250</v>
@@ -5647,7 +5647,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G182" t="n">
-        <v>10.7918081283569</v>
+        <v>10.7918071746826</v>
       </c>
       <c r="H182" t="n">
         <v>45769</v>
@@ -5705,7 +5705,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>10.9358186721802</v>
+        <v>10.9358177185059</v>
       </c>
       <c r="H184" t="n">
         <v>264783</v>
@@ -5792,7 +5792,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G187" t="n">
-        <v>11.1968383789062</v>
+        <v>11.1968374252319</v>
       </c>
       <c r="H187" t="n">
         <v>35264</v>
@@ -5850,7 +5850,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G189" t="n">
-        <v>11.2418422698975</v>
+        <v>11.2418403625488</v>
       </c>
       <c r="H189" t="n">
         <v>6735</v>
@@ -5908,7 +5908,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G191" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H191" t="n">
         <v>43427</v>
@@ -6024,7 +6024,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>10.9358186721802</v>
+        <v>10.9358177185059</v>
       </c>
       <c r="H195" t="n">
         <v>36226</v>
@@ -6140,7 +6140,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>10.9808225631714</v>
+        <v>10.9808216094971</v>
       </c>
       <c r="H199" t="n">
         <v>10780</v>
@@ -6169,7 +6169,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H200" t="n">
         <v>40377</v>
@@ -6256,7 +6256,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>11.79088306427</v>
+        <v>11.7908821105957</v>
       </c>
       <c r="H203" t="n">
         <v>38065</v>
@@ -6372,7 +6372,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>11.79088306427</v>
+        <v>11.7908821105957</v>
       </c>
       <c r="H207" t="n">
         <v>18452</v>
@@ -6430,7 +6430,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G209" t="n">
-        <v>11.5658655166626</v>
+        <v>11.5658664703369</v>
       </c>
       <c r="H209" t="n">
         <v>27077</v>
@@ -6662,7 +6662,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H217" t="n">
         <v>100153</v>
@@ -6720,7 +6720,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>10.9358186721802</v>
+        <v>10.9358177185059</v>
       </c>
       <c r="H219" t="n">
         <v>34983</v>
@@ -6749,7 +6749,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>10.9808225631714</v>
+        <v>10.9808216094971</v>
       </c>
       <c r="H220" t="n">
         <v>32924</v>
@@ -6865,7 +6865,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G224" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H224" t="n">
         <v>38565</v>
@@ -6952,7 +6952,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>11.4308547973633</v>
+        <v>11.4308557510376</v>
       </c>
       <c r="H227" t="n">
         <v>64055</v>
@@ -7126,7 +7126,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G233" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H233" t="n">
         <v>17885</v>
@@ -7155,7 +7155,7 @@
         <v>12</v>
       </c>
       <c r="G234" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H234" t="n">
         <v>28217</v>
@@ -7184,7 +7184,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G235" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H235" t="n">
         <v>16566</v>
@@ -7242,7 +7242,7 @@
         <v>11.75</v>
       </c>
       <c r="G237" t="n">
-        <v>10.5757923126221</v>
+        <v>10.5757913589478</v>
       </c>
       <c r="H237" t="n">
         <v>38013</v>
@@ -7271,7 +7271,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H238" t="n">
         <v>18095</v>
@@ -7300,7 +7300,7 @@
         <v>12</v>
       </c>
       <c r="G239" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H239" t="n">
         <v>39939</v>
@@ -7416,7 +7416,7 @@
         <v>12</v>
       </c>
       <c r="G243" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H243" t="n">
         <v>48611</v>
@@ -7445,7 +7445,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7108011245728</v>
+        <v>10.7108020782471</v>
       </c>
       <c r="H244" t="n">
         <v>25326</v>
@@ -7474,7 +7474,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H245" t="n">
         <v>15122</v>
@@ -7503,7 +7503,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H246" t="n">
         <v>5465</v>
@@ -7619,7 +7619,7 @@
         <v>12</v>
       </c>
       <c r="G250" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H250" t="n">
         <v>31759</v>
@@ -7735,7 +7735,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H254" t="n">
         <v>40241</v>
@@ -7764,7 +7764,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G255" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H255" t="n">
         <v>5284</v>
@@ -7909,7 +7909,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G260" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H260" t="n">
         <v>17724</v>
@@ -7996,7 +7996,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H263" t="n">
         <v>27661</v>
@@ -8083,7 +8083,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H266" t="n">
         <v>6743</v>
@@ -8141,7 +8141,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H268" t="n">
         <v>5138</v>
@@ -8199,7 +8199,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>10.9808225631714</v>
+        <v>10.9808216094971</v>
       </c>
       <c r="H270" t="n">
         <v>12370</v>
@@ -8228,7 +8228,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>10.9808225631714</v>
+        <v>10.9808216094971</v>
       </c>
       <c r="H271" t="n">
         <v>4989</v>
@@ -8315,7 +8315,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H274" t="n">
         <v>27992</v>
@@ -8344,7 +8344,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>11.1779375076294</v>
+        <v>11.1779365539551</v>
       </c>
       <c r="H275" t="n">
         <v>13564</v>
@@ -8373,7 +8373,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G276" t="n">
-        <v>11.0405025482178</v>
+        <v>11.0405035018921</v>
       </c>
       <c r="H276" t="n">
         <v>26541</v>
@@ -8431,7 +8431,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>11.1321258544922</v>
+        <v>11.1321249008179</v>
       </c>
       <c r="H278" t="n">
         <v>15038</v>
@@ -8518,7 +8518,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H281" t="n">
         <v>154139</v>
@@ -8547,7 +8547,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H282" t="n">
         <v>21107</v>
@@ -8692,7 +8692,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G287" t="n">
-        <v>11.1779375076294</v>
+        <v>11.1779365539551</v>
       </c>
       <c r="H287" t="n">
         <v>41668</v>
@@ -9040,7 +9040,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>10.8114461898804</v>
+        <v>10.8114471435547</v>
       </c>
       <c r="H299" t="n">
         <v>6920</v>
@@ -9069,7 +9069,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G300" t="n">
-        <v>11.0405025482178</v>
+        <v>11.0405035018921</v>
       </c>
       <c r="H300" t="n">
         <v>228509</v>
@@ -9243,7 +9243,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H306" t="n">
         <v>83168</v>
@@ -9272,7 +9272,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H307" t="n">
         <v>35606</v>
@@ -9301,7 +9301,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G308" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H308" t="n">
         <v>26383</v>
@@ -9359,7 +9359,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G310" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H310" t="n">
         <v>23793</v>
@@ -9504,7 +9504,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H315" t="n">
         <v>60996</v>
@@ -9533,7 +9533,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>11.1321258544922</v>
+        <v>11.1321249008179</v>
       </c>
       <c r="H316" t="n">
         <v>31108</v>
@@ -9562,7 +9562,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G317" t="n">
-        <v>11.1779375076294</v>
+        <v>11.1779365539551</v>
       </c>
       <c r="H317" t="n">
         <v>23909</v>
@@ -9649,7 +9649,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H320" t="n">
         <v>26167</v>
@@ -9707,7 +9707,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G322" t="n">
-        <v>11.1321258544922</v>
+        <v>11.1321249008179</v>
       </c>
       <c r="H322" t="n">
         <v>19539</v>
@@ -9765,7 +9765,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G324" t="n">
-        <v>11.1779375076294</v>
+        <v>11.1779365539551</v>
       </c>
       <c r="H324" t="n">
         <v>7392</v>
@@ -9881,7 +9881,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H328" t="n">
         <v>12057</v>
@@ -9910,7 +9910,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H329" t="n">
         <v>118877</v>
@@ -9968,7 +9968,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G331" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H331" t="n">
         <v>21852</v>
@@ -9997,7 +9997,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H332" t="n">
         <v>98903</v>
@@ -10258,7 +10258,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H341" t="n">
         <v>4404</v>
@@ -10287,7 +10287,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G342" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H342" t="n">
         <v>4793</v>
@@ -10461,7 +10461,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>11.1321258544922</v>
+        <v>11.1321249008179</v>
       </c>
       <c r="H348" t="n">
         <v>2813</v>
@@ -10751,7 +10751,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>11.1779375076294</v>
+        <v>11.1779365539551</v>
       </c>
       <c r="H358" t="n">
         <v>8030</v>
@@ -10867,7 +10867,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G362" t="n">
-        <v>11.1321258544922</v>
+        <v>11.1321249008179</v>
       </c>
       <c r="H362" t="n">
         <v>31361</v>
@@ -10896,7 +10896,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>11.1779375076294</v>
+        <v>11.1779365539551</v>
       </c>
       <c r="H363" t="n">
         <v>193750</v>
@@ -10925,7 +10925,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H364" t="n">
         <v>63021</v>
@@ -10983,7 +10983,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H366" t="n">
         <v>8248</v>
@@ -11041,7 +11041,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H368" t="n">
         <v>57147</v>
@@ -11070,7 +11070,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H369" t="n">
         <v>35300</v>
@@ -11128,7 +11128,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G371" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H371" t="n">
         <v>59329</v>
@@ -11186,7 +11186,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H373" t="n">
         <v>33947</v>
@@ -11215,7 +11215,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H374" t="n">
         <v>42858</v>
@@ -11331,7 +11331,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>11.1779375076294</v>
+        <v>11.1779365539551</v>
       </c>
       <c r="H378" t="n">
         <v>21188</v>
@@ -11563,7 +11563,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G386" t="n">
-        <v>11.0405025482178</v>
+        <v>11.0405035018921</v>
       </c>
       <c r="H386" t="n">
         <v>36409</v>
@@ -11679,7 +11679,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>10.9488792419434</v>
+        <v>10.9488801956177</v>
       </c>
       <c r="H390" t="n">
         <v>24606</v>
@@ -11708,7 +11708,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>10.8114461898804</v>
+        <v>10.8114471435547</v>
       </c>
       <c r="H391" t="n">
         <v>40022</v>
@@ -11766,7 +11766,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>9.9410343170166</v>
+        <v>9.94103336334229</v>
       </c>
       <c r="H393" t="n">
         <v>74407</v>
@@ -12172,7 +12172,7 @@
         <v>10</v>
       </c>
       <c r="G407" t="n">
-        <v>9.1622428894043</v>
+        <v>9.16224193572998</v>
       </c>
       <c r="H407" t="n">
         <v>15357</v>
@@ -12201,7 +12201,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>9.08894443511963</v>
+        <v>9.08894538879395</v>
       </c>
       <c r="H408" t="n">
         <v>21952</v>
@@ -12288,7 +12288,7 @@
         <v>9.5</v>
       </c>
       <c r="G411" t="n">
-        <v>8.70413112640381</v>
+        <v>8.70413017272949</v>
       </c>
       <c r="H411" t="n">
         <v>58798</v>
@@ -12375,7 +12375,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G414" t="n">
-        <v>8.48423767089844</v>
+        <v>8.48423671722412</v>
       </c>
       <c r="H414" t="n">
         <v>7680</v>
@@ -12433,7 +12433,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>8.0994234085083</v>
+        <v>8.09942245483398</v>
       </c>
       <c r="H416" t="n">
         <v>54469</v>
@@ -12462,7 +12462,7 @@
         <v>9</v>
       </c>
       <c r="G417" t="n">
-        <v>8.24601936340332</v>
+        <v>8.246018409729</v>
       </c>
       <c r="H417" t="n">
         <v>37510</v>
@@ -12491,7 +12491,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G418" t="n">
-        <v>8.37429046630859</v>
+        <v>8.37429141998291</v>
       </c>
       <c r="H418" t="n">
         <v>16525</v>
@@ -12636,7 +12636,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G423" t="n">
-        <v>8.74077892303467</v>
+        <v>8.74077987670898</v>
       </c>
       <c r="H423" t="n">
         <v>61251</v>
@@ -12694,7 +12694,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>9.08894443511963</v>
+        <v>9.08894538879395</v>
       </c>
       <c r="H425" t="n">
         <v>24400</v>
@@ -12810,7 +12810,7 @@
         <v>9.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.70413112640381</v>
+        <v>8.70413017272949</v>
       </c>
       <c r="H429" t="n">
         <v>51975</v>
@@ -12897,7 +12897,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G432" t="n">
-        <v>8.68580627441406</v>
+        <v>8.68580532073975</v>
       </c>
       <c r="H432" t="n">
         <v>8025</v>
@@ -13042,7 +13042,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>8.06277370452881</v>
+        <v>8.06277465820312</v>
       </c>
       <c r="H437" t="n">
         <v>28367</v>
@@ -13216,7 +13216,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G443" t="n">
-        <v>8.33764266967773</v>
+        <v>8.33764171600342</v>
       </c>
       <c r="H443" t="n">
         <v>21963</v>
@@ -13303,7 +13303,7 @@
         <v>9.5</v>
       </c>
       <c r="G446" t="n">
-        <v>8.70413112640381</v>
+        <v>8.70413017272949</v>
       </c>
       <c r="H446" t="n">
         <v>17748</v>
@@ -13361,7 +13361,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G448" t="n">
-        <v>8.59418392181396</v>
+        <v>8.59418296813965</v>
       </c>
       <c r="H448" t="n">
         <v>10460</v>
@@ -13390,7 +13390,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G449" t="n">
-        <v>8.33764266967773</v>
+        <v>8.33764171600342</v>
       </c>
       <c r="H449" t="n">
         <v>15514</v>
@@ -13477,7 +13477,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G452" t="n">
-        <v>8.48423767089844</v>
+        <v>8.48423671722412</v>
       </c>
       <c r="H452" t="n">
         <v>69659</v>
@@ -13535,7 +13535,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G454" t="n">
-        <v>8.48423767089844</v>
+        <v>8.48423671722412</v>
       </c>
       <c r="H454" t="n">
         <v>22696</v>
@@ -13970,7 +13970,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G469" t="n">
-        <v>8.64915657043457</v>
+        <v>8.64915752410889</v>
       </c>
       <c r="H469" t="n">
         <v>20305</v>
@@ -13999,7 +13999,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G470" t="n">
-        <v>8.64915657043457</v>
+        <v>8.64915752410889</v>
       </c>
       <c r="H470" t="n">
         <v>14362</v>
@@ -14115,7 +14115,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G474" t="n">
-        <v>8.48423767089844</v>
+        <v>8.48423671722412</v>
       </c>
       <c r="H474" t="n">
         <v>12437</v>
@@ -14347,7 +14347,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G482" t="n">
-        <v>8.48423767089844</v>
+        <v>8.48423671722412</v>
       </c>
       <c r="H482" t="n">
         <v>21665</v>
@@ -14405,7 +14405,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G484" t="n">
-        <v>8.33764266967773</v>
+        <v>8.33764171600342</v>
       </c>
       <c r="H484" t="n">
         <v>11503</v>
@@ -14434,7 +14434,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G485" t="n">
-        <v>8.26434326171875</v>
+        <v>8.26434421539307</v>
       </c>
       <c r="H485" t="n">
         <v>62090</v>
@@ -14521,7 +14521,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G488" t="n">
-        <v>8.26434326171875</v>
+        <v>8.26434421539307</v>
       </c>
       <c r="H488" t="n">
         <v>18615</v>
@@ -14608,7 +14608,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G491" t="n">
-        <v>8.0994234085083</v>
+        <v>8.09942245483398</v>
       </c>
       <c r="H491" t="n">
         <v>17335</v>
@@ -14753,7 +14753,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>9.29967594146729</v>
+        <v>9.2996768951416</v>
       </c>
       <c r="H496" t="n">
         <v>110828</v>
@@ -14782,7 +14782,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>9.29967594146729</v>
+        <v>9.2996768951416</v>
       </c>
       <c r="H497" t="n">
         <v>140545</v>
@@ -14811,7 +14811,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>9.29967594146729</v>
+        <v>9.2996768951416</v>
       </c>
       <c r="H498" t="n">
         <v>88225</v>
@@ -14898,7 +14898,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G501" t="n">
-        <v>9.20805358886719</v>
+        <v>9.2080545425415</v>
       </c>
       <c r="H501" t="n">
         <v>83469</v>
@@ -14927,7 +14927,7 @@
         <v>10.5</v>
       </c>
       <c r="G502" t="n">
-        <v>9.62035465240479</v>
+        <v>9.6203556060791</v>
       </c>
       <c r="H502" t="n">
         <v>175754</v>
@@ -14956,7 +14956,7 @@
         <v>10</v>
       </c>
       <c r="G503" t="n">
-        <v>9.1622428894043</v>
+        <v>9.16224193572998</v>
       </c>
       <c r="H503" t="n">
         <v>586410</v>
@@ -70700,6 +70700,35 @@
         <v>29350</v>
       </c>
       <c r="I2425" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2426">
+      <c r="A2426" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2426" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2426" t="n">
+        <v>1.34599995613098</v>
+      </c>
+      <c r="D2426" t="n">
+        <v>1.34599995613098</v>
+      </c>
+      <c r="E2426" t="n">
+        <v>1.31599998474121</v>
+      </c>
+      <c r="F2426" t="n">
+        <v>1.34399998188019</v>
+      </c>
+      <c r="G2426" t="n">
+        <v>1.34399998188019</v>
+      </c>
+      <c r="H2426" t="n">
+        <v>56400</v>
+      </c>
+      <c r="I2426" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -456,7 +456,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G3" t="n">
-        <v>9.27969360351562</v>
+        <v>9.27969551086426</v>
       </c>
       <c r="H3" t="n">
         <v>73034</v>
@@ -485,7 +485,7 @@
         <v>10.25</v>
       </c>
       <c r="G4" t="n">
-        <v>9.2256908416748</v>
+        <v>9.22568988800049</v>
       </c>
       <c r="H4" t="n">
         <v>116483</v>
@@ -543,7 +543,7 @@
         <v>10.5</v>
       </c>
       <c r="G6" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H6" t="n">
         <v>50252</v>
@@ -572,7 +572,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>9.3607006072998</v>
+        <v>9.36069965362549</v>
       </c>
       <c r="H7" t="n">
         <v>22546</v>
@@ -601,7 +601,7 @@
         <v>10.5</v>
       </c>
       <c r="G8" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H8" t="n">
         <v>12361</v>
@@ -659,7 +659,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>9.8107328414917</v>
+        <v>9.81073379516602</v>
       </c>
       <c r="H10" t="n">
         <v>8225</v>
@@ -717,7 +717,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>9.44170665740967</v>
+        <v>9.44170570373535</v>
       </c>
       <c r="H12" t="n">
         <v>74921</v>
@@ -804,7 +804,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G15" t="n">
-        <v>9.36970138549805</v>
+        <v>9.36970043182373</v>
       </c>
       <c r="H15" t="n">
         <v>10916</v>
@@ -833,7 +833,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G16" t="n">
-        <v>9.34270000457764</v>
+        <v>9.34269905090332</v>
       </c>
       <c r="H16" t="n">
         <v>99540</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="G17" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H17" t="n">
         <v>9239</v>
@@ -891,7 +891,7 @@
         <v>10.5</v>
       </c>
       <c r="G18" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H18" t="n">
         <v>21485</v>
@@ -920,7 +920,7 @@
         <v>10.5</v>
       </c>
       <c r="G19" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H19" t="n">
         <v>143074</v>
@@ -949,7 +949,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G20" t="n">
-        <v>9.5407133102417</v>
+        <v>9.54071426391602</v>
       </c>
       <c r="H20" t="n">
         <v>8555</v>
@@ -1036,7 +1036,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>9.49570941925049</v>
+        <v>9.4957103729248</v>
       </c>
       <c r="H23" t="n">
         <v>24798</v>
@@ -1065,7 +1065,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>9.49570941925049</v>
+        <v>9.4957103729248</v>
       </c>
       <c r="H24" t="n">
         <v>15509</v>
@@ -1094,7 +1094,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G25" t="n">
-        <v>9.5407133102417</v>
+        <v>9.54071426391602</v>
       </c>
       <c r="H25" t="n">
         <v>17860</v>
@@ -1152,7 +1152,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>9.5407133102417</v>
+        <v>9.54071426391602</v>
       </c>
       <c r="H27" t="n">
         <v>16080</v>
@@ -1355,7 +1355,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G34" t="n">
-        <v>9.6937255859375</v>
+        <v>9.69372463226318</v>
       </c>
       <c r="H34" t="n">
         <v>17123</v>
@@ -1384,7 +1384,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G35" t="n">
-        <v>9.8107328414917</v>
+        <v>9.81073379516602</v>
       </c>
       <c r="H35" t="n">
         <v>17570</v>
@@ -1529,7 +1529,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G40" t="n">
-        <v>9.90974235534668</v>
+        <v>9.90974140167236</v>
       </c>
       <c r="H40" t="n">
         <v>20802</v>
@@ -1558,7 +1558,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G41" t="n">
-        <v>9.90974235534668</v>
+        <v>9.90974140167236</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G42" t="n">
-        <v>9.91874313354492</v>
+        <v>9.91874217987061</v>
       </c>
       <c r="H42" t="n">
         <v>130</v>
@@ -1616,7 +1616,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G43" t="n">
-        <v>9.91874313354492</v>
+        <v>9.91874217987061</v>
       </c>
       <c r="H43" t="n">
         <v>980</v>
@@ -1703,7 +1703,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>9.94574451446533</v>
+        <v>9.94574546813965</v>
       </c>
       <c r="H46" t="n">
         <v>8</v>
@@ -1761,7 +1761,7 @@
         <v>12</v>
       </c>
       <c r="G48" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H48" t="n">
         <v>2330</v>
@@ -1877,7 +1877,7 @@
         <v>12</v>
       </c>
       <c r="G52" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H52" t="n">
         <v>6600</v>
@@ -1906,7 +1906,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G53" t="n">
-        <v>10.6927995681763</v>
+        <v>10.6928005218506</v>
       </c>
       <c r="H53" t="n">
         <v>10522</v>
@@ -1935,7 +1935,7 @@
         <v>12</v>
       </c>
       <c r="G54" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H54" t="n">
         <v>11262</v>
@@ -1964,7 +1964,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G55" t="n">
-        <v>10.8098096847534</v>
+        <v>10.8098087310791</v>
       </c>
       <c r="H55" t="n">
         <v>30919</v>
@@ -2051,7 +2051,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G58" t="n">
-        <v>10.6927995681763</v>
+        <v>10.6928005218506</v>
       </c>
       <c r="H58" t="n">
         <v>19515</v>
@@ -2080,7 +2080,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G59" t="n">
-        <v>10.7738065719604</v>
+        <v>10.7738056182861</v>
       </c>
       <c r="H59" t="n">
         <v>2335</v>
@@ -2109,7 +2109,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G60" t="n">
-        <v>10.8368110656738</v>
+        <v>10.8368120193481</v>
       </c>
       <c r="H60" t="n">
         <v>361</v>
@@ -2167,7 +2167,7 @@
         <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H62" t="n">
         <v>8081</v>
@@ -2196,7 +2196,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G63" t="n">
-        <v>10.8368110656738</v>
+        <v>10.8368120193481</v>
       </c>
       <c r="H63" t="n">
         <v>6516</v>
@@ -2225,7 +2225,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G64" t="n">
-        <v>10.7828054428101</v>
+        <v>10.7828063964844</v>
       </c>
       <c r="H64" t="n">
         <v>11664</v>
@@ -2254,7 +2254,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G65" t="n">
-        <v>10.8098096847534</v>
+        <v>10.8098087310791</v>
       </c>
       <c r="H65" t="n">
         <v>43558</v>
@@ -2283,7 +2283,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G66" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H66" t="n">
         <v>2413</v>
@@ -2341,7 +2341,7 @@
         <v>12.25</v>
       </c>
       <c r="G68" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H68" t="n">
         <v>11800</v>
@@ -2370,7 +2370,7 @@
         <v>12.25</v>
       </c>
       <c r="G69" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H69" t="n">
         <v>10830</v>
@@ -2399,7 +2399,7 @@
         <v>12.25</v>
       </c>
       <c r="G70" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H70" t="n">
         <v>19079</v>
@@ -2457,7 +2457,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H72" t="n">
         <v>17517</v>
@@ -2486,7 +2486,7 @@
         <v>12.25</v>
       </c>
       <c r="G73" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H73" t="n">
         <v>10849</v>
@@ -2515,7 +2515,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G74" t="n">
-        <v>10.9628200531006</v>
+        <v>10.9628210067749</v>
       </c>
       <c r="H74" t="n">
         <v>45474</v>
@@ -2544,7 +2544,7 @@
         <v>12.25</v>
       </c>
       <c r="G75" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H75" t="n">
         <v>23178</v>
@@ -2573,7 +2573,7 @@
         <v>12.25</v>
       </c>
       <c r="G76" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H76" t="n">
         <v>77850</v>
@@ -2602,7 +2602,7 @@
         <v>12</v>
       </c>
       <c r="G77" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H77" t="n">
         <v>21843</v>
@@ -2631,7 +2631,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H78" t="n">
         <v>16304</v>
@@ -2660,7 +2660,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G79" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H79" t="n">
         <v>27515</v>
@@ -2834,7 +2834,7 @@
         <v>12.25</v>
       </c>
       <c r="G85" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H85" t="n">
         <v>7351</v>
@@ -2863,7 +2863,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G86" t="n">
-        <v>11.0078239440918</v>
+        <v>11.0078229904175</v>
       </c>
       <c r="H86" t="n">
         <v>617</v>
@@ -2892,7 +2892,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G87" t="n">
-        <v>11.0078239440918</v>
+        <v>11.0078229904175</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H88" t="n">
         <v>125</v>
@@ -2950,7 +2950,7 @@
         <v>12</v>
       </c>
       <c r="G89" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H89" t="n">
         <v>2</v>
@@ -2979,7 +2979,7 @@
         <v>12</v>
       </c>
       <c r="G90" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H90" t="n">
         <v>132646</v>
@@ -3008,7 +3008,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H91" t="n">
         <v>29894</v>
@@ -3037,7 +3037,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G92" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H92" t="n">
         <v>3303</v>
@@ -3211,7 +3211,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G98" t="n">
-        <v>11.0978307723999</v>
+        <v>11.0978298187256</v>
       </c>
       <c r="H98" t="n">
         <v>3490</v>
@@ -3240,7 +3240,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G99" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H99" t="n">
         <v>4100</v>
@@ -3356,7 +3356,7 @@
         <v>12.25</v>
       </c>
       <c r="G103" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H103" t="n">
         <v>800</v>
@@ -3414,7 +3414,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G105" t="n">
-        <v>11.1518354415894</v>
+        <v>11.1518335342407</v>
       </c>
       <c r="H105" t="n">
         <v>6308</v>
@@ -3472,7 +3472,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G107" t="n">
-        <v>11.0348262786865</v>
+        <v>11.0348253250122</v>
       </c>
       <c r="H107" t="n">
         <v>1001</v>
@@ -3530,7 +3530,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G109" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H109" t="n">
         <v>196</v>
@@ -3704,7 +3704,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G115" t="n">
-        <v>11.0438261032104</v>
+        <v>11.0438270568848</v>
       </c>
       <c r="H115" t="n">
         <v>761</v>
@@ -3762,7 +3762,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H117" t="n">
         <v>12190</v>
@@ -3791,7 +3791,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G118" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H118" t="n">
         <v>5884</v>
@@ -3820,7 +3820,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>11.2418403625488</v>
+        <v>11.2418413162231</v>
       </c>
       <c r="H119" t="n">
         <v>10255</v>
@@ -3849,7 +3849,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G120" t="n">
-        <v>11.0978307723999</v>
+        <v>11.0978298187256</v>
       </c>
       <c r="H120" t="n">
         <v>23000</v>
@@ -3878,7 +3878,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G121" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H121" t="n">
         <v>95700</v>
@@ -3907,7 +3907,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H122" t="n">
         <v>2200</v>
@@ -3936,7 +3936,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G123" t="n">
-        <v>11.1518354415894</v>
+        <v>11.1518335342407</v>
       </c>
       <c r="H123" t="n">
         <v>6225</v>
@@ -3965,7 +3965,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G124" t="n">
-        <v>11.0888290405273</v>
+        <v>11.0888299942017</v>
       </c>
       <c r="H124" t="n">
         <v>20229</v>
@@ -3994,7 +3994,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G125" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H125" t="n">
         <v>53861</v>
@@ -4023,7 +4023,7 @@
         <v>12.25</v>
       </c>
       <c r="G126" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H126" t="n">
         <v>7500</v>
@@ -4052,7 +4052,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G127" t="n">
-        <v>11.0528268814087</v>
+        <v>11.0528259277344</v>
       </c>
       <c r="H127" t="n">
         <v>9639</v>
@@ -4081,7 +4081,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>11.0978307723999</v>
+        <v>11.0978298187256</v>
       </c>
       <c r="H128" t="n">
         <v>24331</v>
@@ -4110,7 +4110,7 @@
         <v>12.25</v>
       </c>
       <c r="G129" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H129" t="n">
         <v>6915</v>
@@ -4139,7 +4139,7 @@
         <v>12</v>
       </c>
       <c r="G130" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H130" t="n">
         <v>10740</v>
@@ -4168,7 +4168,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G131" t="n">
-        <v>11.0438261032104</v>
+        <v>11.0438270568848</v>
       </c>
       <c r="H131" t="n">
         <v>1475</v>
@@ -4197,7 +4197,7 @@
         <v>12.25</v>
       </c>
       <c r="G132" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H132" t="n">
         <v>496</v>
@@ -4226,7 +4226,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G133" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H133" t="n">
         <v>1516</v>
@@ -4255,7 +4255,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G135" t="n">
-        <v>11.0528268814087</v>
+        <v>11.0528259277344</v>
       </c>
       <c r="H135" t="n">
         <v>12316</v>
@@ -4313,7 +4313,7 @@
         <v>12.25</v>
       </c>
       <c r="G136" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H136" t="n">
         <v>37117</v>
@@ -4516,7 +4516,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G143" t="n">
-        <v>11.2778434753418</v>
+        <v>11.2778425216675</v>
       </c>
       <c r="H143" t="n">
         <v>19219</v>
@@ -4545,7 +4545,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>11.4308557510376</v>
+        <v>11.4308547973633</v>
       </c>
       <c r="H144" t="n">
         <v>15034</v>
@@ -4574,7 +4574,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>11.4308557510376</v>
+        <v>11.4308547973633</v>
       </c>
       <c r="H145" t="n">
         <v>800</v>
@@ -4603,7 +4603,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G146" t="n">
-        <v>11.4308557510376</v>
+        <v>11.4308547973633</v>
       </c>
       <c r="H146" t="n">
         <v>1600</v>
@@ -4632,7 +4632,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G147" t="n">
-        <v>11.5208625793457</v>
+        <v>11.5208616256714</v>
       </c>
       <c r="H147" t="n">
         <v>40959</v>
@@ -4661,7 +4661,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G148" t="n">
-        <v>11.6918754577637</v>
+        <v>11.6918745040894</v>
       </c>
       <c r="H148" t="n">
         <v>50666</v>
@@ -4690,7 +4690,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G149" t="n">
-        <v>11.6018686294556</v>
+        <v>11.6018676757812</v>
       </c>
       <c r="H149" t="n">
         <v>19162</v>
@@ -4719,7 +4719,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G150" t="n">
-        <v>11.6828727722168</v>
+        <v>11.6828737258911</v>
       </c>
       <c r="H150" t="n">
         <v>102168</v>
@@ -4777,7 +4777,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>11.5658664703369</v>
+        <v>11.5658655166626</v>
       </c>
       <c r="H152" t="n">
         <v>7751</v>
@@ -4806,7 +4806,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G153" t="n">
-        <v>11.5118608474731</v>
+        <v>11.5118618011475</v>
       </c>
       <c r="H153" t="n">
         <v>15226</v>
@@ -4835,7 +4835,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G154" t="n">
-        <v>11.8178853988647</v>
+        <v>11.8178844451904</v>
       </c>
       <c r="H154" t="n">
         <v>13313</v>
@@ -4893,7 +4893,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>11.5658664703369</v>
+        <v>11.5658655166626</v>
       </c>
       <c r="H156" t="n">
         <v>15491</v>
@@ -4980,7 +4980,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>11.5658664703369</v>
+        <v>11.5658655166626</v>
       </c>
       <c r="H159" t="n">
         <v>810</v>
@@ -5125,7 +5125,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G164" t="n">
-        <v>11.6558713912964</v>
+        <v>11.6558723449707</v>
       </c>
       <c r="H164" t="n">
         <v>7000</v>
@@ -5183,7 +5183,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>11.6558713912964</v>
+        <v>11.6558723449707</v>
       </c>
       <c r="H166" t="n">
         <v>436</v>
@@ -5241,7 +5241,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>11.9708957672119</v>
+        <v>11.9708967208862</v>
       </c>
       <c r="H168" t="n">
         <v>3334</v>
@@ -5270,7 +5270,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>11.9708957672119</v>
+        <v>11.9708967208862</v>
       </c>
       <c r="H169" t="n">
         <v>25389</v>
@@ -5299,7 +5299,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G170" t="n">
-        <v>11.6828727722168</v>
+        <v>11.6828737258911</v>
       </c>
       <c r="H170" t="n">
         <v>11344</v>
@@ -5386,7 +5386,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G173" t="n">
-        <v>11.1878366470337</v>
+        <v>11.187837600708</v>
       </c>
       <c r="H173" t="n">
         <v>47087</v>
@@ -5415,7 +5415,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G174" t="n">
-        <v>11.0348262786865</v>
+        <v>11.0348253250122</v>
       </c>
       <c r="H174" t="n">
         <v>38220</v>
@@ -5444,7 +5444,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H175" t="n">
         <v>17680</v>
@@ -5502,7 +5502,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H177" t="n">
         <v>97611</v>
@@ -5531,7 +5531,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G178" t="n">
-        <v>11.0348262786865</v>
+        <v>11.0348253250122</v>
       </c>
       <c r="H178" t="n">
         <v>86579</v>
@@ -5676,7 +5676,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G183" t="n">
-        <v>10.719801902771</v>
+        <v>10.7198028564453</v>
       </c>
       <c r="H183" t="n">
         <v>21068</v>
@@ -5792,7 +5792,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G187" t="n">
-        <v>11.1968374252319</v>
+        <v>11.1968364715576</v>
       </c>
       <c r="H187" t="n">
         <v>35264</v>
@@ -5850,7 +5850,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G189" t="n">
-        <v>11.2418403625488</v>
+        <v>11.2418413162231</v>
       </c>
       <c r="H189" t="n">
         <v>6735</v>
@@ -5908,7 +5908,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G191" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H191" t="n">
         <v>43427</v>
@@ -5966,7 +5966,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H193" t="n">
         <v>33122</v>
@@ -6053,7 +6053,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H196" t="n">
         <v>20113</v>
@@ -6082,7 +6082,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H197" t="n">
         <v>24111</v>
@@ -6111,7 +6111,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H198" t="n">
         <v>19135</v>
@@ -6227,7 +6227,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6558713912964</v>
+        <v>11.6558723449707</v>
       </c>
       <c r="H202" t="n">
         <v>63641</v>
@@ -6314,7 +6314,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>11.6558713912964</v>
+        <v>11.6558723449707</v>
       </c>
       <c r="H205" t="n">
         <v>29232</v>
@@ -6430,7 +6430,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G209" t="n">
-        <v>11.5658664703369</v>
+        <v>11.5658655166626</v>
       </c>
       <c r="H209" t="n">
         <v>27077</v>
@@ -6575,7 +6575,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H214" t="n">
         <v>42154</v>
@@ -6662,7 +6662,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H217" t="n">
         <v>100153</v>
@@ -6691,7 +6691,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H218" t="n">
         <v>23902</v>
@@ -6807,7 +6807,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H222" t="n">
         <v>33108</v>
@@ -6836,7 +6836,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G223" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H223" t="n">
         <v>32411</v>
@@ -6865,7 +6865,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G224" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H224" t="n">
         <v>38565</v>
@@ -6923,7 +6923,7 @@
         <v>12.75</v>
       </c>
       <c r="G226" t="n">
-        <v>11.4758586883545</v>
+        <v>11.4758577346802</v>
       </c>
       <c r="H226" t="n">
         <v>83399</v>
@@ -6952,7 +6952,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>11.4308557510376</v>
+        <v>11.4308547973633</v>
       </c>
       <c r="H227" t="n">
         <v>64055</v>
@@ -7039,7 +7039,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H230" t="n">
         <v>49113</v>
@@ -7068,7 +7068,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H231" t="n">
         <v>32508</v>
@@ -7155,7 +7155,7 @@
         <v>12</v>
       </c>
       <c r="G234" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H234" t="n">
         <v>28217</v>
@@ -7242,7 +7242,7 @@
         <v>11.75</v>
       </c>
       <c r="G237" t="n">
-        <v>10.5757913589478</v>
+        <v>10.5757904052734</v>
       </c>
       <c r="H237" t="n">
         <v>38013</v>
@@ -7300,7 +7300,7 @@
         <v>12</v>
       </c>
       <c r="G239" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H239" t="n">
         <v>39939</v>
@@ -7387,7 +7387,7 @@
         <v>12.25</v>
       </c>
       <c r="G242" t="n">
-        <v>11.0258255004883</v>
+        <v>11.025824546814</v>
       </c>
       <c r="H242" t="n">
         <v>26025</v>
@@ -7416,7 +7416,7 @@
         <v>12</v>
       </c>
       <c r="G243" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H243" t="n">
         <v>48611</v>
@@ -7445,7 +7445,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7108020782471</v>
+        <v>10.7108001708984</v>
       </c>
       <c r="H244" t="n">
         <v>25326</v>
@@ -7590,7 +7590,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G249" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H249" t="n">
         <v>87545</v>
@@ -7619,7 +7619,7 @@
         <v>12</v>
       </c>
       <c r="G250" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H250" t="n">
         <v>31759</v>
@@ -7648,7 +7648,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H251" t="n">
         <v>71726</v>
@@ -7735,7 +7735,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H254" t="n">
         <v>40241</v>
@@ -7764,7 +7764,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G255" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H255" t="n">
         <v>5284</v>
@@ -7793,7 +7793,7 @@
         <v>12.75</v>
       </c>
       <c r="G256" t="n">
-        <v>11.4758586883545</v>
+        <v>11.4758577346802</v>
       </c>
       <c r="H256" t="n">
         <v>26163</v>
@@ -7822,7 +7822,7 @@
         <v>12.75</v>
       </c>
       <c r="G257" t="n">
-        <v>11.4758586883545</v>
+        <v>11.4758577346802</v>
       </c>
       <c r="H257" t="n">
         <v>16349</v>
@@ -7996,7 +7996,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H263" t="n">
         <v>27661</v>
@@ -8054,7 +8054,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H265" t="n">
         <v>13029</v>
@@ -8083,7 +8083,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>11.2958459854126</v>
+        <v>11.2958450317383</v>
       </c>
       <c r="H266" t="n">
         <v>6743</v>
@@ -8112,7 +8112,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H267" t="n">
         <v>7336</v>
@@ -8170,7 +8170,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>10.890814781189</v>
+        <v>10.8908157348633</v>
       </c>
       <c r="H269" t="n">
         <v>7285</v>
@@ -8257,7 +8257,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H272" t="n">
         <v>17619</v>
@@ -8286,7 +8286,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>11.160834312439</v>
+        <v>11.1608352661133</v>
       </c>
       <c r="H273" t="n">
         <v>16739</v>
@@ -8402,7 +8402,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H277" t="n">
         <v>33704</v>
@@ -8489,7 +8489,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G280" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H280" t="n">
         <v>31987</v>
@@ -8518,7 +8518,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>11.5902366638184</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H281" t="n">
         <v>154139</v>
@@ -8634,7 +8634,7 @@
         <v>12.75</v>
       </c>
       <c r="G285" t="n">
-        <v>11.6818599700928</v>
+        <v>11.6818590164185</v>
       </c>
       <c r="H285" t="n">
         <v>28076</v>
@@ -8663,7 +8663,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>11.7276706695557</v>
+        <v>11.72767162323</v>
       </c>
       <c r="H286" t="n">
         <v>29283</v>
@@ -8750,7 +8750,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H289" t="n">
         <v>31489</v>
@@ -8808,7 +8808,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>10.6740131378174</v>
+        <v>10.6740121841431</v>
       </c>
       <c r="H291" t="n">
         <v>35242</v>
@@ -8953,7 +8953,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G296" t="n">
-        <v>10.6282024383545</v>
+        <v>10.6282014846802</v>
       </c>
       <c r="H296" t="n">
         <v>24205</v>
@@ -9098,7 +9098,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H301" t="n">
         <v>18809</v>
@@ -9214,7 +9214,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H305" t="n">
         <v>30136</v>
@@ -9272,7 +9272,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>11.5902366638184</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H307" t="n">
         <v>35606</v>
@@ -9301,7 +9301,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G308" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H308" t="n">
         <v>26383</v>
@@ -9359,7 +9359,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G310" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H310" t="n">
         <v>23793</v>
@@ -9446,7 +9446,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H313" t="n">
         <v>19003</v>
@@ -9649,7 +9649,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H320" t="n">
         <v>26167</v>
@@ -9678,7 +9678,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H321" t="n">
         <v>20721</v>
@@ -9823,7 +9823,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H326" t="n">
         <v>18013</v>
@@ -9881,7 +9881,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H328" t="n">
         <v>12057</v>
@@ -9910,7 +9910,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>11.5902366638184</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H329" t="n">
         <v>118877</v>
@@ -9968,7 +9968,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G331" t="n">
-        <v>11.5902366638184</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H331" t="n">
         <v>21852</v>
@@ -10142,7 +10142,7 @@
         <v>12.75</v>
       </c>
       <c r="G337" t="n">
-        <v>11.6818599700928</v>
+        <v>11.6818590164185</v>
       </c>
       <c r="H337" t="n">
         <v>8463</v>
@@ -10258,7 +10258,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>11.5902366638184</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H341" t="n">
         <v>4404</v>
@@ -10287,7 +10287,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G342" t="n">
-        <v>11.5902366638184</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H342" t="n">
         <v>4793</v>
@@ -10519,7 +10519,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G350" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H350" t="n">
         <v>4156</v>
@@ -10548,7 +10548,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H351" t="n">
         <v>11827</v>
@@ -10664,7 +10664,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G355" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H355" t="n">
         <v>32441</v>
@@ -10693,7 +10693,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G356" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H356" t="n">
         <v>32166</v>
@@ -10722,7 +10722,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H357" t="n">
         <v>8521</v>
@@ -10925,7 +10925,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H364" t="n">
         <v>63021</v>
@@ -11041,7 +11041,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>11.5902366638184</v>
+        <v>11.590235710144</v>
       </c>
       <c r="H368" t="n">
         <v>57147</v>
@@ -11215,7 +11215,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>11.361180305481</v>
+        <v>11.3611812591553</v>
       </c>
       <c r="H374" t="n">
         <v>42858</v>
@@ -11389,7 +11389,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H380" t="n">
         <v>23902</v>
@@ -11476,7 +11476,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G383" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H383" t="n">
         <v>55014</v>
@@ -11534,7 +11534,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>11.2695589065552</v>
+        <v>11.2695598602295</v>
       </c>
       <c r="H385" t="n">
         <v>74508</v>
@@ -11766,7 +11766,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>9.94103336334229</v>
+        <v>9.9410343170166</v>
       </c>
       <c r="H393" t="n">
         <v>74407</v>
@@ -11795,7 +11795,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G394" t="n">
-        <v>9.89522361755371</v>
+        <v>9.89522266387939</v>
       </c>
       <c r="H394" t="n">
         <v>9913</v>
@@ -11911,7 +11911,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>9.25386524200439</v>
+        <v>9.25386619567871</v>
       </c>
       <c r="H398" t="n">
         <v>10481</v>
@@ -11969,7 +11969,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G400" t="n">
-        <v>9.25386524200439</v>
+        <v>9.25386619567871</v>
       </c>
       <c r="H400" t="n">
         <v>9106</v>
@@ -11998,7 +11998,7 @@
         <v>10.25</v>
       </c>
       <c r="G401" t="n">
-        <v>9.3912992477417</v>
+        <v>9.39129829406738</v>
       </c>
       <c r="H401" t="n">
         <v>11455</v>
@@ -12172,7 +12172,7 @@
         <v>10</v>
       </c>
       <c r="G407" t="n">
-        <v>9.16224193572998</v>
+        <v>9.1622428894043</v>
       </c>
       <c r="H407" t="n">
         <v>15357</v>
@@ -12230,7 +12230,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>8.88737487792969</v>
+        <v>8.887375831604</v>
       </c>
       <c r="H409" t="n">
         <v>15627</v>
@@ -12404,7 +12404,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G415" t="n">
-        <v>8.31931591033936</v>
+        <v>8.31931686401367</v>
       </c>
       <c r="H415" t="n">
         <v>34723</v>
@@ -12462,7 +12462,7 @@
         <v>9</v>
       </c>
       <c r="G417" t="n">
-        <v>8.246018409729</v>
+        <v>8.24601745605469</v>
       </c>
       <c r="H417" t="n">
         <v>37510</v>
@@ -12491,7 +12491,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G418" t="n">
-        <v>8.37429141998291</v>
+        <v>8.37429046630859</v>
       </c>
       <c r="H418" t="n">
         <v>16525</v>
@@ -12520,7 +12520,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G419" t="n">
-        <v>8.46591281890869</v>
+        <v>8.46591186523438</v>
       </c>
       <c r="H419" t="n">
         <v>35706</v>
@@ -12549,7 +12549,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G420" t="n">
-        <v>8.39261436462402</v>
+        <v>8.39261531829834</v>
       </c>
       <c r="H420" t="n">
         <v>10342</v>
@@ -12723,7 +12723,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G426" t="n">
-        <v>8.88737487792969</v>
+        <v>8.887375831604</v>
       </c>
       <c r="H426" t="n">
         <v>23965</v>
@@ -12781,7 +12781,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G428" t="n">
-        <v>8.90570068359375</v>
+        <v>8.90569972991943</v>
       </c>
       <c r="H428" t="n">
         <v>18031</v>
@@ -12897,7 +12897,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G432" t="n">
-        <v>8.68580532073975</v>
+        <v>8.68580627441406</v>
       </c>
       <c r="H432" t="n">
         <v>8025</v>
@@ -13158,7 +13158,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G441" t="n">
-        <v>8.15439605712891</v>
+        <v>8.15439701080322</v>
       </c>
       <c r="H441" t="n">
         <v>6510</v>
@@ -13216,7 +13216,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G443" t="n">
-        <v>8.33764171600342</v>
+        <v>8.3376407623291</v>
       </c>
       <c r="H443" t="n">
         <v>21963</v>
@@ -13361,7 +13361,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G448" t="n">
-        <v>8.59418296813965</v>
+        <v>8.59418392181396</v>
       </c>
       <c r="H448" t="n">
         <v>10460</v>
@@ -13390,7 +13390,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G449" t="n">
-        <v>8.33764171600342</v>
+        <v>8.3376407623291</v>
       </c>
       <c r="H449" t="n">
         <v>15514</v>
@@ -13593,7 +13593,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G456" t="n">
-        <v>8.61250877380371</v>
+        <v>8.61250782012939</v>
       </c>
       <c r="H456" t="n">
         <v>8112</v>
@@ -13883,7 +13883,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G466" t="n">
-        <v>8.61250877380371</v>
+        <v>8.61250782012939</v>
       </c>
       <c r="H466" t="n">
         <v>14235</v>
@@ -13912,7 +13912,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G467" t="n">
-        <v>8.61250877380371</v>
+        <v>8.61250782012939</v>
       </c>
       <c r="H467" t="n">
         <v>40595</v>
@@ -14289,7 +14289,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G480" t="n">
-        <v>8.30099201202393</v>
+        <v>8.30099296569824</v>
       </c>
       <c r="H480" t="n">
         <v>29108</v>
@@ -14405,7 +14405,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G484" t="n">
-        <v>8.33764171600342</v>
+        <v>8.3376407623291</v>
       </c>
       <c r="H484" t="n">
         <v>11503</v>
@@ -14637,7 +14637,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G492" t="n">
-        <v>8.61250877380371</v>
+        <v>8.61250782012939</v>
       </c>
       <c r="H492" t="n">
         <v>129615</v>
@@ -14666,7 +14666,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G493" t="n">
-        <v>8.88737487792969</v>
+        <v>8.887375831604</v>
       </c>
       <c r="H493" t="n">
         <v>139699</v>
@@ -14695,7 +14695,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>9.25386524200439</v>
+        <v>9.25386619567871</v>
       </c>
       <c r="H494" t="n">
         <v>99854</v>
@@ -14724,7 +14724,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G495" t="n">
-        <v>9.25386524200439</v>
+        <v>9.25386619567871</v>
       </c>
       <c r="H495" t="n">
         <v>23938</v>
@@ -14927,7 +14927,7 @@
         <v>10.5</v>
       </c>
       <c r="G502" t="n">
-        <v>9.6203556060791</v>
+        <v>9.62035465240479</v>
       </c>
       <c r="H502" t="n">
         <v>175754</v>
@@ -14956,7 +14956,7 @@
         <v>10</v>
       </c>
       <c r="G503" t="n">
-        <v>9.16224193572998</v>
+        <v>9.1622428894043</v>
       </c>
       <c r="H503" t="n">
         <v>586410</v>
@@ -15304,7 +15304,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G515" t="n">
-        <v>8.88737487792969</v>
+        <v>8.887375831604</v>
       </c>
       <c r="H515" t="n">
         <v>93940</v>
@@ -15420,7 +15420,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G519" t="n">
-        <v>8.88737487792969</v>
+        <v>8.887375831604</v>
       </c>
       <c r="H519" t="n">
         <v>48371</v>
@@ -15507,7 +15507,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G522" t="n">
-        <v>8.88737487792969</v>
+        <v>8.887375831604</v>
       </c>
       <c r="H522" t="n">
         <v>24410</v>
@@ -70729,6 +70729,35 @@
         <v>56400</v>
       </c>
       <c r="I2426" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2427">
+      <c r="A2427" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2427" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2427" t="n">
+        <v>1.33399999141693</v>
+      </c>
+      <c r="D2427" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="E2427" t="n">
+        <v>1.33200001716614</v>
+      </c>
+      <c r="F2427" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="G2427" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="H2427" t="n">
+        <v>116635</v>
+      </c>
+      <c r="I2427" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G2" t="n">
-        <v>9.1356840133667</v>
+        <v>9.13568305969238</v>
       </c>
       <c r="H2" t="n">
         <v>48343</v>
@@ -456,7 +456,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G3" t="n">
-        <v>9.27969551086426</v>
+        <v>9.27969360351562</v>
       </c>
       <c r="H3" t="n">
         <v>73034</v>
@@ -485,7 +485,7 @@
         <v>10.25</v>
       </c>
       <c r="G4" t="n">
-        <v>9.22568988800049</v>
+        <v>9.2256908416748</v>
       </c>
       <c r="H4" t="n">
         <v>116483</v>
@@ -514,7 +514,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>9.28869438171387</v>
+        <v>9.28869533538818</v>
       </c>
       <c r="H5" t="n">
         <v>264710</v>
@@ -543,7 +543,7 @@
         <v>10.5</v>
       </c>
       <c r="G6" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H6" t="n">
         <v>50252</v>
@@ -572,7 +572,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>9.36069965362549</v>
+        <v>9.3607006072998</v>
       </c>
       <c r="H7" t="n">
         <v>22546</v>
@@ -601,7 +601,7 @@
         <v>10.5</v>
       </c>
       <c r="G8" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H8" t="n">
         <v>12361</v>
@@ -630,7 +630,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G9" t="n">
-        <v>9.4057035446167</v>
+        <v>9.40570259094238</v>
       </c>
       <c r="H9" t="n">
         <v>1874</v>
@@ -659,7 +659,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>9.81073379516602</v>
+        <v>9.8107328414917</v>
       </c>
       <c r="H10" t="n">
         <v>8225</v>
@@ -746,7 +746,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.4057035446167</v>
+        <v>9.40570259094238</v>
       </c>
       <c r="H13" t="n">
         <v>11246</v>
@@ -775,7 +775,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>9.4057035446167</v>
+        <v>9.40570259094238</v>
       </c>
       <c r="H14" t="n">
         <v>51250</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="G17" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H17" t="n">
         <v>9239</v>
@@ -891,7 +891,7 @@
         <v>10.5</v>
       </c>
       <c r="G18" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H18" t="n">
         <v>21485</v>
@@ -920,7 +920,7 @@
         <v>10.5</v>
       </c>
       <c r="G19" t="n">
-        <v>9.45070648193359</v>
+        <v>9.45070743560791</v>
       </c>
       <c r="H19" t="n">
         <v>143074</v>
@@ -949,7 +949,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G20" t="n">
-        <v>9.54071426391602</v>
+        <v>9.54071521759033</v>
       </c>
       <c r="H20" t="n">
         <v>8555</v>
@@ -978,7 +978,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G21" t="n">
-        <v>9.55871486663818</v>
+        <v>9.5587158203125</v>
       </c>
       <c r="H21" t="n">
         <v>3705</v>
@@ -1007,7 +1007,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G22" t="n">
-        <v>9.48670959472656</v>
+        <v>9.48671054840088</v>
       </c>
       <c r="H22" t="n">
         <v>1993</v>
@@ -1094,7 +1094,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G25" t="n">
-        <v>9.54071426391602</v>
+        <v>9.54071521759033</v>
       </c>
       <c r="H25" t="n">
         <v>17860</v>
@@ -1123,7 +1123,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>9.63072109222412</v>
+        <v>9.6307201385498</v>
       </c>
       <c r="H26" t="n">
         <v>7000</v>
@@ -1152,7 +1152,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>9.54071426391602</v>
+        <v>9.54071521759033</v>
       </c>
       <c r="H27" t="n">
         <v>16080</v>
@@ -1181,7 +1181,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G28" t="n">
-        <v>9.63072109222412</v>
+        <v>9.6307201385498</v>
       </c>
       <c r="H28" t="n">
         <v>1105</v>
@@ -1210,7 +1210,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G29" t="n">
-        <v>9.63072109222412</v>
+        <v>9.6307201385498</v>
       </c>
       <c r="H29" t="n">
         <v>3091</v>
@@ -1239,7 +1239,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G30" t="n">
-        <v>9.62172031402588</v>
+        <v>9.62171936035156</v>
       </c>
       <c r="H30" t="n">
         <v>11222</v>
@@ -1268,7 +1268,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>9.63072109222412</v>
+        <v>9.6307201385498</v>
       </c>
       <c r="H31" t="n">
         <v>6000</v>
@@ -1297,7 +1297,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G32" t="n">
-        <v>9.63072109222412</v>
+        <v>9.6307201385498</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G34" t="n">
-        <v>9.69372463226318</v>
+        <v>9.6937255859375</v>
       </c>
       <c r="H34" t="n">
         <v>17123</v>
@@ -1384,7 +1384,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G35" t="n">
-        <v>9.81073379516602</v>
+        <v>9.8107328414917</v>
       </c>
       <c r="H35" t="n">
         <v>17570</v>
@@ -1529,7 +1529,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G40" t="n">
-        <v>9.90974140167236</v>
+        <v>9.90974235534668</v>
       </c>
       <c r="H40" t="n">
         <v>20802</v>
@@ -1558,7 +1558,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G41" t="n">
-        <v>9.90974140167236</v>
+        <v>9.90974235534668</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>9.94574546813965</v>
+        <v>9.94574356079102</v>
       </c>
       <c r="H46" t="n">
         <v>8</v>
@@ -1906,7 +1906,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G53" t="n">
-        <v>10.6928005218506</v>
+        <v>10.6927995681763</v>
       </c>
       <c r="H53" t="n">
         <v>10522</v>
@@ -2022,7 +2022,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G57" t="n">
-        <v>10.7648057937622</v>
+        <v>10.7648048400879</v>
       </c>
       <c r="H57" t="n">
         <v>32694</v>
@@ -2051,7 +2051,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G58" t="n">
-        <v>10.6928005218506</v>
+        <v>10.6927995681763</v>
       </c>
       <c r="H58" t="n">
         <v>19515</v>
@@ -2080,7 +2080,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G59" t="n">
-        <v>10.7738056182861</v>
+        <v>10.7738065719604</v>
       </c>
       <c r="H59" t="n">
         <v>2335</v>
@@ -2138,7 +2138,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G61" t="n">
-        <v>10.7918071746826</v>
+        <v>10.7918081283569</v>
       </c>
       <c r="H61" t="n">
         <v>118200</v>
@@ -2283,7 +2283,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G66" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H66" t="n">
         <v>2413</v>
@@ -2428,7 +2428,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H71" t="n">
         <v>19479</v>
@@ -2457,7 +2457,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H72" t="n">
         <v>17517</v>
@@ -2631,7 +2631,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H78" t="n">
         <v>16304</v>
@@ -2660,7 +2660,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G79" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H79" t="n">
         <v>27515</v>
@@ -2921,7 +2921,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H88" t="n">
         <v>125</v>
@@ -3008,7 +3008,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H91" t="n">
         <v>29894</v>
@@ -3414,7 +3414,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G105" t="n">
-        <v>11.1518335342407</v>
+        <v>11.1518354415894</v>
       </c>
       <c r="H105" t="n">
         <v>6308</v>
@@ -3472,7 +3472,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G107" t="n">
-        <v>11.0348253250122</v>
+        <v>11.0348262786865</v>
       </c>
       <c r="H107" t="n">
         <v>1001</v>
@@ -3530,7 +3530,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G109" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H109" t="n">
         <v>196</v>
@@ -3675,7 +3675,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G114" t="n">
-        <v>10.9538192749023</v>
+        <v>10.953818321228</v>
       </c>
       <c r="H114" t="n">
         <v>1013</v>
@@ -3704,7 +3704,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G115" t="n">
-        <v>11.0438270568848</v>
+        <v>11.0438261032104</v>
       </c>
       <c r="H115" t="n">
         <v>761</v>
@@ -3733,7 +3733,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H116" t="n">
         <v>2</v>
@@ -3762,7 +3762,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H117" t="n">
         <v>12190</v>
@@ -3820,7 +3820,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>11.2418413162231</v>
+        <v>11.2418403625488</v>
       </c>
       <c r="H119" t="n">
         <v>10255</v>
@@ -3907,7 +3907,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H122" t="n">
         <v>2200</v>
@@ -3936,7 +3936,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G123" t="n">
-        <v>11.1518335342407</v>
+        <v>11.1518354415894</v>
       </c>
       <c r="H123" t="n">
         <v>6225</v>
@@ -4052,7 +4052,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G127" t="n">
-        <v>11.0528259277344</v>
+        <v>11.0528268814087</v>
       </c>
       <c r="H127" t="n">
         <v>9639</v>
@@ -4168,7 +4168,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G131" t="n">
-        <v>11.0438270568848</v>
+        <v>11.0438261032104</v>
       </c>
       <c r="H131" t="n">
         <v>1475</v>
@@ -4284,7 +4284,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G135" t="n">
-        <v>11.0528259277344</v>
+        <v>11.0528268814087</v>
       </c>
       <c r="H135" t="n">
         <v>12316</v>
@@ -4342,7 +4342,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H137" t="n">
         <v>11453</v>
@@ -4371,7 +4371,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G143" t="n">
-        <v>11.2778425216675</v>
+        <v>11.2778434753418</v>
       </c>
       <c r="H143" t="n">
         <v>19219</v>
@@ -4632,7 +4632,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G147" t="n">
-        <v>11.5208616256714</v>
+        <v>11.5208625793457</v>
       </c>
       <c r="H147" t="n">
         <v>40959</v>
@@ -4690,7 +4690,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G149" t="n">
-        <v>11.6018676757812</v>
+        <v>11.6018686294556</v>
       </c>
       <c r="H149" t="n">
         <v>19162</v>
@@ -4835,7 +4835,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G154" t="n">
-        <v>11.8178844451904</v>
+        <v>11.8178853988647</v>
       </c>
       <c r="H154" t="n">
         <v>13313</v>
@@ -5067,7 +5067,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G162" t="n">
-        <v>11.5028600692749</v>
+        <v>11.5028610229492</v>
       </c>
       <c r="H162" t="n">
         <v>8549</v>
@@ -5125,7 +5125,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G164" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H164" t="n">
         <v>7000</v>
@@ -5183,7 +5183,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H166" t="n">
         <v>436</v>
@@ -5241,7 +5241,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>11.9708967208862</v>
+        <v>11.9708948135376</v>
       </c>
       <c r="H168" t="n">
         <v>3334</v>
@@ -5270,7 +5270,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>11.9708967208862</v>
+        <v>11.9708948135376</v>
       </c>
       <c r="H169" t="n">
         <v>25389</v>
@@ -5415,7 +5415,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G174" t="n">
-        <v>11.0348253250122</v>
+        <v>11.0348262786865</v>
       </c>
       <c r="H174" t="n">
         <v>38220</v>
@@ -5444,7 +5444,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H175" t="n">
         <v>17680</v>
@@ -5531,7 +5531,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G178" t="n">
-        <v>11.0348253250122</v>
+        <v>11.0348262786865</v>
       </c>
       <c r="H178" t="n">
         <v>86579</v>
@@ -5560,7 +5560,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G179" t="n">
-        <v>10.9898223876953</v>
+        <v>10.989821434021</v>
       </c>
       <c r="H179" t="n">
         <v>71095</v>
@@ -5618,7 +5618,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G181" t="n">
-        <v>10.8728132247925</v>
+        <v>10.8728141784668</v>
       </c>
       <c r="H181" t="n">
         <v>10043</v>
@@ -5647,7 +5647,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G182" t="n">
-        <v>10.7918071746826</v>
+        <v>10.7918081283569</v>
       </c>
       <c r="H182" t="n">
         <v>45769</v>
@@ -5792,7 +5792,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G187" t="n">
-        <v>11.1968364715576</v>
+        <v>11.1968383789062</v>
       </c>
       <c r="H187" t="n">
         <v>35264</v>
@@ -5850,7 +5850,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G189" t="n">
-        <v>11.2418413162231</v>
+        <v>11.2418403625488</v>
       </c>
       <c r="H189" t="n">
         <v>6735</v>
@@ -5966,7 +5966,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H193" t="n">
         <v>33122</v>
@@ -6053,7 +6053,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H196" t="n">
         <v>20113</v>
@@ -6169,7 +6169,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H200" t="n">
         <v>40377</v>
@@ -6198,7 +6198,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>11.3858509063721</v>
+        <v>11.3858518600464</v>
       </c>
       <c r="H201" t="n">
         <v>341100</v>
@@ -6227,7 +6227,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H202" t="n">
         <v>63641</v>
@@ -6256,7 +6256,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>11.7908821105957</v>
+        <v>11.7908840179443</v>
       </c>
       <c r="H203" t="n">
         <v>38065</v>
@@ -6314,7 +6314,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>11.6558723449707</v>
+        <v>11.6558713912964</v>
       </c>
       <c r="H205" t="n">
         <v>29232</v>
@@ -6372,7 +6372,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>11.7908821105957</v>
+        <v>11.7908840179443</v>
       </c>
       <c r="H207" t="n">
         <v>18452</v>
@@ -6691,7 +6691,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H218" t="n">
         <v>23902</v>
@@ -6807,7 +6807,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H222" t="n">
         <v>33108</v>
@@ -6923,7 +6923,7 @@
         <v>12.75</v>
       </c>
       <c r="G226" t="n">
-        <v>11.4758577346802</v>
+        <v>11.4758586883545</v>
       </c>
       <c r="H226" t="n">
         <v>83399</v>
@@ -7068,7 +7068,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H231" t="n">
         <v>32508</v>
@@ -7126,7 +7126,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G233" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H233" t="n">
         <v>17885</v>
@@ -7184,7 +7184,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G235" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H235" t="n">
         <v>16566</v>
@@ -7242,7 +7242,7 @@
         <v>11.75</v>
       </c>
       <c r="G237" t="n">
-        <v>10.5757904052734</v>
+        <v>10.5757913589478</v>
       </c>
       <c r="H237" t="n">
         <v>38013</v>
@@ -7271,7 +7271,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H238" t="n">
         <v>18095</v>
@@ -7445,7 +7445,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7108001708984</v>
+        <v>10.7108011245728</v>
       </c>
       <c r="H244" t="n">
         <v>25326</v>
@@ -7474,7 +7474,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H245" t="n">
         <v>15122</v>
@@ -7503,7 +7503,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>10.620795249939</v>
+        <v>10.6207942962646</v>
       </c>
       <c r="H246" t="n">
         <v>5465</v>
@@ -7590,7 +7590,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G249" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H249" t="n">
         <v>87545</v>
@@ -7648,7 +7648,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H251" t="n">
         <v>71726</v>
@@ -7793,7 +7793,7 @@
         <v>12.75</v>
       </c>
       <c r="G256" t="n">
-        <v>11.4758577346802</v>
+        <v>11.4758586883545</v>
       </c>
       <c r="H256" t="n">
         <v>26163</v>
@@ -7822,7 +7822,7 @@
         <v>12.75</v>
       </c>
       <c r="G257" t="n">
-        <v>11.4758577346802</v>
+        <v>11.4758586883545</v>
       </c>
       <c r="H257" t="n">
         <v>16349</v>
@@ -7909,7 +7909,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G260" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H260" t="n">
         <v>17724</v>
@@ -8054,7 +8054,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H265" t="n">
         <v>13029</v>
@@ -8141,7 +8141,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H268" t="n">
         <v>5138</v>
@@ -8170,7 +8170,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>10.8908157348633</v>
+        <v>10.890814781189</v>
       </c>
       <c r="H269" t="n">
         <v>7285</v>
@@ -8315,7 +8315,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>11.1158323287964</v>
+        <v>11.1158313751221</v>
       </c>
       <c r="H274" t="n">
         <v>27992</v>
@@ -8402,7 +8402,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H277" t="n">
         <v>33704</v>
@@ -8489,7 +8489,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G280" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H280" t="n">
         <v>31987</v>
@@ -8518,7 +8518,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H281" t="n">
         <v>154139</v>
@@ -8547,7 +8547,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H282" t="n">
         <v>21107</v>
@@ -8663,7 +8663,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>11.72767162323</v>
+        <v>11.7276706695557</v>
       </c>
       <c r="H286" t="n">
         <v>29283</v>
@@ -8721,7 +8721,7 @@
         <v>12.5</v>
       </c>
       <c r="G288" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H288" t="n">
         <v>31033</v>
@@ -8750,7 +8750,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H289" t="n">
         <v>31489</v>
@@ -8779,7 +8779,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H290" t="n">
         <v>51613</v>
@@ -8808,7 +8808,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>10.6740121841431</v>
+        <v>10.6740131378174</v>
       </c>
       <c r="H291" t="n">
         <v>35242</v>
@@ -8895,7 +8895,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3991460800171</v>
+        <v>10.3991451263428</v>
       </c>
       <c r="H294" t="n">
         <v>66099</v>
@@ -8953,7 +8953,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G296" t="n">
-        <v>10.6282014846802</v>
+        <v>10.6282024383545</v>
       </c>
       <c r="H296" t="n">
         <v>24205</v>
@@ -9040,7 +9040,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>10.8114471435547</v>
+        <v>10.8114461898804</v>
       </c>
       <c r="H299" t="n">
         <v>6920</v>
@@ -9098,7 +9098,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H301" t="n">
         <v>18809</v>
@@ -9214,7 +9214,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H305" t="n">
         <v>30136</v>
@@ -9243,7 +9243,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H306" t="n">
         <v>83168</v>
@@ -9272,7 +9272,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H307" t="n">
         <v>35606</v>
@@ -9301,7 +9301,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G308" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H308" t="n">
         <v>26383</v>
@@ -9359,7 +9359,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G310" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H310" t="n">
         <v>23793</v>
@@ -9446,7 +9446,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H313" t="n">
         <v>19003</v>
@@ -9475,7 +9475,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H314" t="n">
         <v>24864</v>
@@ -9504,7 +9504,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H315" t="n">
         <v>60996</v>
@@ -9620,7 +9620,7 @@
         <v>12.5</v>
       </c>
       <c r="G319" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H319" t="n">
         <v>29752</v>
@@ -9649,7 +9649,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H320" t="n">
         <v>26167</v>
@@ -9678,7 +9678,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H321" t="n">
         <v>20721</v>
@@ -9736,7 +9736,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G323" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H323" t="n">
         <v>9841</v>
@@ -9823,7 +9823,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H326" t="n">
         <v>18013</v>
@@ -9852,7 +9852,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H327" t="n">
         <v>41583</v>
@@ -9881,7 +9881,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H328" t="n">
         <v>12057</v>
@@ -9910,7 +9910,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H329" t="n">
         <v>118877</v>
@@ -9939,7 +9939,7 @@
         <v>12.5</v>
       </c>
       <c r="G330" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H330" t="n">
         <v>16305</v>
@@ -9968,7 +9968,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G331" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H331" t="n">
         <v>21852</v>
@@ -9997,7 +9997,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H332" t="n">
         <v>98903</v>
@@ -10055,7 +10055,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>12.0025386810303</v>
+        <v>12.0025396347046</v>
       </c>
       <c r="H334" t="n">
         <v>337229</v>
@@ -10200,7 +10200,7 @@
         <v>12.5</v>
       </c>
       <c r="G339" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H339" t="n">
         <v>18856</v>
@@ -10258,7 +10258,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H341" t="n">
         <v>4404</v>
@@ -10287,7 +10287,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G342" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H342" t="n">
         <v>4793</v>
@@ -10432,7 +10432,7 @@
         <v>12.5</v>
       </c>
       <c r="G347" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H347" t="n">
         <v>28995</v>
@@ -10490,7 +10490,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H349" t="n">
         <v>8309</v>
@@ -10519,7 +10519,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G350" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H350" t="n">
         <v>4156</v>
@@ -10548,7 +10548,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H351" t="n">
         <v>11827</v>
@@ -10664,7 +10664,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G355" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H355" t="n">
         <v>32441</v>
@@ -10693,7 +10693,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G356" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H356" t="n">
         <v>32166</v>
@@ -10722,7 +10722,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H357" t="n">
         <v>8521</v>
@@ -10780,7 +10780,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G359" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H359" t="n">
         <v>29957</v>
@@ -10809,7 +10809,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H360" t="n">
         <v>63557</v>
@@ -10925,7 +10925,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H364" t="n">
         <v>63021</v>
@@ -10983,7 +10983,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H366" t="n">
         <v>8248</v>
@@ -11041,7 +11041,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>11.590235710144</v>
+        <v>11.5902376174927</v>
       </c>
       <c r="H368" t="n">
         <v>57147</v>
@@ -11070,7 +11070,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H369" t="n">
         <v>35300</v>
@@ -11099,7 +11099,7 @@
         <v>12.5</v>
       </c>
       <c r="G370" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H370" t="n">
         <v>18058</v>
@@ -11128,7 +11128,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G371" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H371" t="n">
         <v>59329</v>
@@ -11186,7 +11186,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>11.5444259643555</v>
+        <v>11.5444269180298</v>
       </c>
       <c r="H373" t="n">
         <v>33947</v>
@@ -11215,7 +11215,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>11.3611812591553</v>
+        <v>11.361180305481</v>
       </c>
       <c r="H374" t="n">
         <v>42858</v>
@@ -11273,7 +11273,7 @@
         <v>12.5</v>
       </c>
       <c r="G376" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H376" t="n">
         <v>47155</v>
@@ -11360,7 +11360,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G379" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H379" t="n">
         <v>70147</v>
@@ -11389,7 +11389,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H380" t="n">
         <v>23902</v>
@@ -11418,7 +11418,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H381" t="n">
         <v>24797</v>
@@ -11447,7 +11447,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>11.3153705596924</v>
+        <v>11.3153696060181</v>
       </c>
       <c r="H382" t="n">
         <v>54013</v>
@@ -11476,7 +11476,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G383" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H383" t="n">
         <v>55014</v>
@@ -11534,7 +11534,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>11.2695598602295</v>
+        <v>11.2695589065552</v>
       </c>
       <c r="H385" t="n">
         <v>74508</v>
@@ -11592,7 +11592,7 @@
         <v>12</v>
       </c>
       <c r="G387" t="n">
-        <v>10.9946908950806</v>
+        <v>10.9946918487549</v>
       </c>
       <c r="H387" t="n">
         <v>91692</v>
@@ -11621,7 +11621,7 @@
         <v>12</v>
       </c>
       <c r="G388" t="n">
-        <v>10.9946908950806</v>
+        <v>10.9946918487549</v>
       </c>
       <c r="H388" t="n">
         <v>34295</v>
@@ -11708,7 +11708,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>10.8114471435547</v>
+        <v>10.8114461898804</v>
       </c>
       <c r="H391" t="n">
         <v>40022</v>
@@ -11853,7 +11853,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>9.52873229980469</v>
+        <v>9.528733253479</v>
       </c>
       <c r="H396" t="n">
         <v>37602</v>
@@ -11911,7 +11911,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>9.25386619567871</v>
+        <v>9.25386524200439</v>
       </c>
       <c r="H398" t="n">
         <v>10481</v>
@@ -11969,7 +11969,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G400" t="n">
-        <v>9.25386619567871</v>
+        <v>9.25386524200439</v>
       </c>
       <c r="H400" t="n">
         <v>9106</v>
@@ -11998,7 +11998,7 @@
         <v>10.25</v>
       </c>
       <c r="G401" t="n">
-        <v>9.39129829406738</v>
+        <v>9.3912992477417</v>
       </c>
       <c r="H401" t="n">
         <v>11455</v>
@@ -12085,7 +12085,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>9.52873229980469</v>
+        <v>9.528733253479</v>
       </c>
       <c r="H404" t="n">
         <v>7740</v>
@@ -12172,7 +12172,7 @@
         <v>10</v>
       </c>
       <c r="G407" t="n">
-        <v>9.1622428894043</v>
+        <v>9.16224384307861</v>
       </c>
       <c r="H407" t="n">
         <v>15357</v>
@@ -12201,7 +12201,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>9.08894538879395</v>
+        <v>9.08894443511963</v>
       </c>
       <c r="H408" t="n">
         <v>21952</v>
@@ -12230,7 +12230,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H409" t="n">
         <v>15627</v>
@@ -12288,7 +12288,7 @@
         <v>9.5</v>
       </c>
       <c r="G411" t="n">
-        <v>8.70413017272949</v>
+        <v>8.70413112640381</v>
       </c>
       <c r="H411" t="n">
         <v>58798</v>
@@ -12317,7 +12317,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G412" t="n">
-        <v>8.5758581161499</v>
+        <v>8.57585906982422</v>
       </c>
       <c r="H412" t="n">
         <v>20574</v>
@@ -12346,7 +12346,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G413" t="n">
-        <v>8.5758581161499</v>
+        <v>8.57585906982422</v>
       </c>
       <c r="H413" t="n">
         <v>11329</v>
@@ -12433,7 +12433,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>8.09942245483398</v>
+        <v>8.0994234085083</v>
       </c>
       <c r="H416" t="n">
         <v>54469</v>
@@ -12462,7 +12462,7 @@
         <v>9</v>
       </c>
       <c r="G417" t="n">
-        <v>8.24601745605469</v>
+        <v>8.24601936340332</v>
       </c>
       <c r="H417" t="n">
         <v>37510</v>
@@ -12520,7 +12520,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G419" t="n">
-        <v>8.46591186523438</v>
+        <v>8.46591281890869</v>
       </c>
       <c r="H419" t="n">
         <v>35706</v>
@@ -12549,7 +12549,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G420" t="n">
-        <v>8.39261531829834</v>
+        <v>8.39261436462402</v>
       </c>
       <c r="H420" t="n">
         <v>10342</v>
@@ -12578,7 +12578,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G421" t="n">
-        <v>8.35596561431885</v>
+        <v>8.35596466064453</v>
       </c>
       <c r="H421" t="n">
         <v>18133</v>
@@ -12607,7 +12607,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G422" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H422" t="n">
         <v>18370</v>
@@ -12694,7 +12694,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>9.08894538879395</v>
+        <v>9.08894443511963</v>
       </c>
       <c r="H425" t="n">
         <v>24400</v>
@@ -12723,7 +12723,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G426" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H426" t="n">
         <v>23965</v>
@@ -12781,7 +12781,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G428" t="n">
-        <v>8.90569972991943</v>
+        <v>8.90570068359375</v>
       </c>
       <c r="H428" t="n">
         <v>18031</v>
@@ -12810,7 +12810,7 @@
         <v>9.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.70413017272949</v>
+        <v>8.70413112640381</v>
       </c>
       <c r="H429" t="n">
         <v>51975</v>
@@ -12897,7 +12897,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G432" t="n">
-        <v>8.68580627441406</v>
+        <v>8.68580532073975</v>
       </c>
       <c r="H432" t="n">
         <v>8025</v>
@@ -12955,7 +12955,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>8.28266716003418</v>
+        <v>8.2826681137085</v>
       </c>
       <c r="H434" t="n">
         <v>27709</v>
@@ -13042,7 +13042,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>8.06277465820312</v>
+        <v>8.06277370452881</v>
       </c>
       <c r="H437" t="n">
         <v>28367</v>
@@ -13158,7 +13158,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G441" t="n">
-        <v>8.15439701080322</v>
+        <v>8.15439605712891</v>
       </c>
       <c r="H441" t="n">
         <v>6510</v>
@@ -13216,7 +13216,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G443" t="n">
-        <v>8.3376407623291</v>
+        <v>8.33764171600342</v>
       </c>
       <c r="H443" t="n">
         <v>21963</v>
@@ -13303,7 +13303,7 @@
         <v>9.5</v>
       </c>
       <c r="G446" t="n">
-        <v>8.70413017272949</v>
+        <v>8.70413112640381</v>
       </c>
       <c r="H446" t="n">
         <v>17748</v>
@@ -13390,7 +13390,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G449" t="n">
-        <v>8.3376407623291</v>
+        <v>8.33764171600342</v>
       </c>
       <c r="H449" t="n">
         <v>15514</v>
@@ -13448,7 +13448,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G451" t="n">
-        <v>8.44758796691895</v>
+        <v>8.44758892059326</v>
       </c>
       <c r="H451" t="n">
         <v>22486</v>
@@ -13506,7 +13506,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G453" t="n">
-        <v>8.44758796691895</v>
+        <v>8.44758892059326</v>
       </c>
       <c r="H453" t="n">
         <v>46077</v>
@@ -13593,7 +13593,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G456" t="n">
-        <v>8.61250782012939</v>
+        <v>8.61250877380371</v>
       </c>
       <c r="H456" t="n">
         <v>8112</v>
@@ -13622,7 +13622,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G457" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H457" t="n">
         <v>35751</v>
@@ -13651,7 +13651,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G458" t="n">
-        <v>8.44758796691895</v>
+        <v>8.44758892059326</v>
       </c>
       <c r="H458" t="n">
         <v>18909</v>
@@ -13680,7 +13680,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G459" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H459" t="n">
         <v>10164</v>
@@ -13767,7 +13767,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H462" t="n">
         <v>11004</v>
@@ -13796,7 +13796,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G463" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H463" t="n">
         <v>4864</v>
@@ -13883,7 +13883,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G466" t="n">
-        <v>8.61250782012939</v>
+        <v>8.61250877380371</v>
       </c>
       <c r="H466" t="n">
         <v>14235</v>
@@ -13912,7 +13912,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G467" t="n">
-        <v>8.61250782012939</v>
+        <v>8.61250877380371</v>
       </c>
       <c r="H467" t="n">
         <v>40595</v>
@@ -13970,7 +13970,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G469" t="n">
-        <v>8.64915752410889</v>
+        <v>8.64915657043457</v>
       </c>
       <c r="H469" t="n">
         <v>20305</v>
@@ -13999,7 +13999,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G470" t="n">
-        <v>8.64915752410889</v>
+        <v>8.64915657043457</v>
       </c>
       <c r="H470" t="n">
         <v>14362</v>
@@ -14028,7 +14028,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G471" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H471" t="n">
         <v>18355</v>
@@ -14057,7 +14057,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G472" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H472" t="n">
         <v>6724</v>
@@ -14086,7 +14086,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G473" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H473" t="n">
         <v>12739</v>
@@ -14173,7 +14173,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G476" t="n">
-        <v>8.50256156921387</v>
+        <v>8.50256061553955</v>
       </c>
       <c r="H476" t="n">
         <v>55693</v>
@@ -14202,7 +14202,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H477" t="n">
         <v>3956</v>
@@ -14231,7 +14231,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G478" t="n">
-        <v>8.52088642120361</v>
+        <v>8.5208854675293</v>
       </c>
       <c r="H478" t="n">
         <v>8323</v>
@@ -14289,7 +14289,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G480" t="n">
-        <v>8.30099296569824</v>
+        <v>8.30099201202393</v>
       </c>
       <c r="H480" t="n">
         <v>29108</v>
@@ -14405,7 +14405,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G484" t="n">
-        <v>8.3376407623291</v>
+        <v>8.33764171600342</v>
       </c>
       <c r="H484" t="n">
         <v>11503</v>
@@ -14434,7 +14434,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G485" t="n">
-        <v>8.26434421539307</v>
+        <v>8.26434326171875</v>
       </c>
       <c r="H485" t="n">
         <v>62090</v>
@@ -14521,7 +14521,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G488" t="n">
-        <v>8.26434421539307</v>
+        <v>8.26434326171875</v>
       </c>
       <c r="H488" t="n">
         <v>18615</v>
@@ -14608,7 +14608,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G491" t="n">
-        <v>8.09942245483398</v>
+        <v>8.0994234085083</v>
       </c>
       <c r="H491" t="n">
         <v>17335</v>
@@ -14637,7 +14637,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G492" t="n">
-        <v>8.61250782012939</v>
+        <v>8.61250877380371</v>
       </c>
       <c r="H492" t="n">
         <v>129615</v>
@@ -14666,7 +14666,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G493" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H493" t="n">
         <v>139699</v>
@@ -14695,7 +14695,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>9.25386619567871</v>
+        <v>9.25386524200439</v>
       </c>
       <c r="H494" t="n">
         <v>99854</v>
@@ -14724,7 +14724,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G495" t="n">
-        <v>9.25386619567871</v>
+        <v>9.25386524200439</v>
       </c>
       <c r="H495" t="n">
         <v>23938</v>
@@ -14753,7 +14753,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>9.2996768951416</v>
+        <v>9.29967594146729</v>
       </c>
       <c r="H496" t="n">
         <v>110828</v>
@@ -14782,7 +14782,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>9.2996768951416</v>
+        <v>9.29967594146729</v>
       </c>
       <c r="H497" t="n">
         <v>140545</v>
@@ -14811,7 +14811,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>9.2996768951416</v>
+        <v>9.29967594146729</v>
       </c>
       <c r="H498" t="n">
         <v>88225</v>
@@ -14956,7 +14956,7 @@
         <v>10</v>
       </c>
       <c r="G503" t="n">
-        <v>9.1622428894043</v>
+        <v>9.16224384307861</v>
       </c>
       <c r="H503" t="n">
         <v>586410</v>
@@ -15014,7 +15014,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G505" t="n">
-        <v>9.10726928710938</v>
+        <v>9.10726833343506</v>
       </c>
       <c r="H505" t="n">
         <v>95256</v>
@@ -15275,7 +15275,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>8.85988903045654</v>
+        <v>8.85988807678223</v>
       </c>
       <c r="H514" t="n">
         <v>26730</v>
@@ -15304,7 +15304,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G515" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H515" t="n">
         <v>93940</v>
@@ -15362,7 +15362,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G517" t="n">
-        <v>8.82324028015137</v>
+        <v>8.82324123382568</v>
       </c>
       <c r="H517" t="n">
         <v>46713</v>
@@ -15420,7 +15420,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G519" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H519" t="n">
         <v>48371</v>
@@ -15507,7 +15507,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G522" t="n">
-        <v>8.887375831604</v>
+        <v>8.88737487792969</v>
       </c>
       <c r="H522" t="n">
         <v>24410</v>
@@ -15652,7 +15652,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G527" t="n">
-        <v>8.66305541992188</v>
+        <v>8.66305637359619</v>
       </c>
       <c r="H527" t="n">
         <v>56480</v>
@@ -15681,7 +15681,7 @@
         <v>9.25</v>
       </c>
       <c r="G528" t="n">
-        <v>8.67243099212646</v>
+        <v>8.67243194580078</v>
       </c>
       <c r="H528" t="n">
         <v>69422</v>
@@ -15739,7 +15739,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G530" t="n">
-        <v>8.50367069244385</v>
+        <v>8.50366973876953</v>
       </c>
       <c r="H530" t="n">
         <v>39713</v>
@@ -15768,7 +15768,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G531" t="n">
-        <v>8.34428596496582</v>
+        <v>8.3442850112915</v>
       </c>
       <c r="H531" t="n">
         <v>20305</v>
@@ -15826,7 +15826,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G533" t="n">
-        <v>8.00676441192627</v>
+        <v>8.00676345825195</v>
       </c>
       <c r="H533" t="n">
         <v>49926</v>
@@ -15884,7 +15884,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>8.15677356719971</v>
+        <v>8.15677261352539</v>
       </c>
       <c r="H535" t="n">
         <v>24993</v>
@@ -15913,7 +15913,7 @@
         <v>8.5</v>
       </c>
       <c r="G536" t="n">
-        <v>7.96926116943359</v>
+        <v>7.96926164627075</v>
       </c>
       <c r="H536" t="n">
         <v>18660</v>
@@ -15971,7 +15971,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>7.88488101959229</v>
+        <v>7.88488054275513</v>
       </c>
       <c r="H538" t="n">
         <v>7745</v>
@@ -16000,7 +16000,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G539" t="n">
-        <v>7.84737825393677</v>
+        <v>7.84737873077393</v>
       </c>
       <c r="H539" t="n">
         <v>51647</v>
@@ -16029,7 +16029,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G540" t="n">
-        <v>7.85675477981567</v>
+        <v>7.85675430297852</v>
       </c>
       <c r="H540" t="n">
         <v>12650</v>
@@ -16058,7 +16058,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>7.80987596511841</v>
+        <v>7.80987644195557</v>
       </c>
       <c r="H541" t="n">
         <v>29138</v>
@@ -16145,7 +16145,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G544" t="n">
-        <v>7.83800220489502</v>
+        <v>7.83800268173218</v>
       </c>
       <c r="H544" t="n">
         <v>14637</v>
@@ -16174,7 +16174,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G545" t="n">
-        <v>7.85675477981567</v>
+        <v>7.85675430297852</v>
       </c>
       <c r="H545" t="n">
         <v>19620</v>
@@ -16290,7 +16290,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>7.80987596511841</v>
+        <v>7.80987644195557</v>
       </c>
       <c r="H549" t="n">
         <v>47708</v>
@@ -16319,7 +16319,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G550" t="n">
-        <v>7.80987596511841</v>
+        <v>7.80987644195557</v>
       </c>
       <c r="H550" t="n">
         <v>33490</v>
@@ -16493,7 +16493,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G556" t="n">
-        <v>7.55673551559448</v>
+        <v>7.55673503875732</v>
       </c>
       <c r="H556" t="n">
         <v>45345</v>
@@ -16551,7 +16551,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G558" t="n">
-        <v>7.6317400932312</v>
+        <v>7.63174057006836</v>
       </c>
       <c r="H558" t="n">
         <v>84786</v>
@@ -16580,7 +16580,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G559" t="n">
-        <v>7.72549533843994</v>
+        <v>7.7254958152771</v>
       </c>
       <c r="H559" t="n">
         <v>40797</v>
@@ -16638,7 +16638,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G561" t="n">
-        <v>7.60361289978027</v>
+        <v>7.60361242294312</v>
       </c>
       <c r="H561" t="n">
         <v>28836</v>
@@ -16667,7 +16667,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G562" t="n">
-        <v>7.60361289978027</v>
+        <v>7.60361242294312</v>
       </c>
       <c r="H562" t="n">
         <v>62515</v>
@@ -16725,7 +16725,7 @@
         <v>8.25</v>
       </c>
       <c r="G564" t="n">
-        <v>7.73487091064453</v>
+        <v>7.73487138748169</v>
       </c>
       <c r="H564" t="n">
         <v>38929</v>
@@ -16754,7 +16754,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G565" t="n">
-        <v>7.77237415313721</v>
+        <v>7.77237367630005</v>
       </c>
       <c r="H565" t="n">
         <v>20455</v>
@@ -16812,7 +16812,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G567" t="n">
-        <v>7.77237415313721</v>
+        <v>7.77237367630005</v>
       </c>
       <c r="H567" t="n">
         <v>23817</v>
@@ -16899,7 +16899,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G570" t="n">
-        <v>8.10052108764648</v>
+        <v>8.10052013397217</v>
       </c>
       <c r="H570" t="n">
         <v>75886</v>
@@ -16928,7 +16928,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G571" t="n">
-        <v>7.85675477981567</v>
+        <v>7.85675430297852</v>
       </c>
       <c r="H571" t="n">
         <v>54680</v>
@@ -16986,7 +16986,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>8.00676441192627</v>
+        <v>8.00676345825195</v>
       </c>
       <c r="H573" t="n">
         <v>30698</v>
@@ -17015,7 +17015,7 @@
         <v>8.5</v>
       </c>
       <c r="G574" t="n">
-        <v>7.96926116943359</v>
+        <v>7.96926164627075</v>
       </c>
       <c r="H574" t="n">
         <v>15609</v>
@@ -17073,7 +17073,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G576" t="n">
-        <v>7.8755054473877</v>
+        <v>7.87550497055054</v>
       </c>
       <c r="H576" t="n">
         <v>10737</v>
@@ -17131,7 +17131,7 @@
         <v>8.25</v>
       </c>
       <c r="G578" t="n">
-        <v>7.73487091064453</v>
+        <v>7.73487138748169</v>
       </c>
       <c r="H578" t="n">
         <v>15413</v>
@@ -17218,7 +17218,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G581" t="n">
-        <v>7.77237415313721</v>
+        <v>7.77237367630005</v>
       </c>
       <c r="H581" t="n">
         <v>46260</v>
@@ -17247,7 +17247,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>7.80987596511841</v>
+        <v>7.80987644195557</v>
       </c>
       <c r="H582" t="n">
         <v>21018</v>
@@ -17276,7 +17276,7 @@
         <v>8.25</v>
       </c>
       <c r="G583" t="n">
-        <v>7.73487091064453</v>
+        <v>7.73487138748169</v>
       </c>
       <c r="H583" t="n">
         <v>10524</v>
@@ -17334,7 +17334,7 @@
         <v>8.25</v>
       </c>
       <c r="G585" t="n">
-        <v>7.73487091064453</v>
+        <v>7.73487138748169</v>
       </c>
       <c r="H585" t="n">
         <v>6395</v>
@@ -17537,7 +17537,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G592" t="n">
-        <v>7.05045223236084</v>
+        <v>7.050452709198</v>
       </c>
       <c r="H592" t="n">
         <v>39430</v>
@@ -17624,7 +17624,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G595" t="n">
-        <v>6.66605281829834</v>
+        <v>6.6660532951355</v>
       </c>
       <c r="H595" t="n">
         <v>20018</v>
@@ -17682,7 +17682,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G597" t="n">
-        <v>6.54417037963867</v>
+        <v>6.54416990280151</v>
       </c>
       <c r="H597" t="n">
         <v>22822</v>
@@ -17914,7 +17914,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G605" t="n">
-        <v>6.18789720535278</v>
+        <v>6.18789672851562</v>
       </c>
       <c r="H605" t="n">
         <v>114219</v>
@@ -17943,7 +17943,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G606" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H606" t="n">
         <v>266451</v>
@@ -18030,7 +18030,7 @@
         <v>6.5</v>
       </c>
       <c r="G609" t="n">
-        <v>6.09414100646973</v>
+        <v>6.09414148330688</v>
       </c>
       <c r="H609" t="n">
         <v>61300</v>
@@ -18059,7 +18059,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G610" t="n">
-        <v>6.44103813171387</v>
+        <v>6.44103860855103</v>
       </c>
       <c r="H610" t="n">
         <v>59780</v>
@@ -18088,7 +18088,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G611" t="n">
-        <v>6.21602392196655</v>
+        <v>6.21602439880371</v>
       </c>
       <c r="H611" t="n">
         <v>45335</v>
@@ -18117,7 +18117,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G612" t="n">
-        <v>6.30040454864502</v>
+        <v>6.30040407180786</v>
       </c>
       <c r="H612" t="n">
         <v>26883</v>
@@ -18204,7 +18204,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G615" t="n">
-        <v>6.49729204177856</v>
+        <v>6.49729156494141</v>
       </c>
       <c r="H615" t="n">
         <v>23258</v>
@@ -18262,7 +18262,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G617" t="n">
-        <v>6.58167219161987</v>
+        <v>6.58167266845703</v>
       </c>
       <c r="H617" t="n">
         <v>57117</v>
@@ -18320,7 +18320,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G619" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H619" t="n">
         <v>56581</v>
@@ -18697,7 +18697,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G632" t="n">
-        <v>6.40353584289551</v>
+        <v>6.40353631973267</v>
       </c>
       <c r="H632" t="n">
         <v>30364</v>
@@ -18755,7 +18755,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G634" t="n">
-        <v>6.45041418075562</v>
+        <v>6.45041370391846</v>
       </c>
       <c r="H634" t="n">
         <v>23667</v>
@@ -18842,7 +18842,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G637" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H637" t="n">
         <v>86665</v>
@@ -18871,7 +18871,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G638" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H638" t="n">
         <v>15458</v>
@@ -18900,7 +18900,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G639" t="n">
-        <v>6.41291189193726</v>
+        <v>6.4129114151001</v>
       </c>
       <c r="H639" t="n">
         <v>20258</v>
@@ -18929,7 +18929,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>6.41291189193726</v>
+        <v>6.4129114151001</v>
       </c>
       <c r="H640" t="n">
         <v>15641</v>
@@ -18987,7 +18987,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H642" t="n">
         <v>46331</v>
@@ -19074,7 +19074,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G645" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H645" t="n">
         <v>84803</v>
@@ -19132,7 +19132,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G647" t="n">
-        <v>7.09733057022095</v>
+        <v>7.09733104705811</v>
       </c>
       <c r="H647" t="n">
         <v>62367</v>
@@ -19190,7 +19190,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G649" t="n">
-        <v>6.58167219161987</v>
+        <v>6.58167266845703</v>
       </c>
       <c r="H649" t="n">
         <v>109205</v>
@@ -19219,7 +19219,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G650" t="n">
-        <v>6.54417037963867</v>
+        <v>6.54416990280151</v>
       </c>
       <c r="H650" t="n">
         <v>99872</v>
@@ -19277,7 +19277,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G652" t="n">
-        <v>6.51604270935059</v>
+        <v>6.51604318618774</v>
       </c>
       <c r="H652" t="n">
         <v>96786</v>
@@ -19364,7 +19364,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G655" t="n">
-        <v>6.54417037963867</v>
+        <v>6.54416990280151</v>
       </c>
       <c r="H655" t="n">
         <v>65532</v>
@@ -19393,7 +19393,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>6.63792562484741</v>
+        <v>6.63792610168457</v>
       </c>
       <c r="H656" t="n">
         <v>50583</v>
@@ -19509,7 +19509,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G660" t="n">
-        <v>6.54417037963867</v>
+        <v>6.54416990280151</v>
       </c>
       <c r="H660" t="n">
         <v>26357</v>
@@ -19538,7 +19538,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>6.63792562484741</v>
+        <v>6.63792610168457</v>
       </c>
       <c r="H661" t="n">
         <v>62110</v>
@@ -19567,7 +19567,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G662" t="n">
-        <v>6.51604270935059</v>
+        <v>6.51604318618774</v>
       </c>
       <c r="H662" t="n">
         <v>40926</v>
@@ -19683,7 +19683,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G666" t="n">
-        <v>5.30659055709839</v>
+        <v>5.30659008026123</v>
       </c>
       <c r="H666" t="n">
         <v>336194</v>
@@ -19741,7 +19741,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>4.88468885421753</v>
+        <v>4.88468837738037</v>
       </c>
       <c r="H668" t="n">
         <v>314198</v>
@@ -19915,7 +19915,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G674" t="n">
-        <v>5.6816143989563</v>
+        <v>5.68161487579346</v>
       </c>
       <c r="H674" t="n">
         <v>384952</v>
@@ -19944,7 +19944,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G675" t="n">
-        <v>5.84100008010864</v>
+        <v>5.84099960327148</v>
       </c>
       <c r="H675" t="n">
         <v>602374</v>
@@ -20002,7 +20002,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G677" t="n">
-        <v>6.05663919448853</v>
+        <v>6.05663871765137</v>
       </c>
       <c r="H677" t="n">
         <v>387855</v>
@@ -20031,7 +20031,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G678" t="n">
-        <v>6.27227735519409</v>
+        <v>6.27227783203125</v>
       </c>
       <c r="H678" t="n">
         <v>384243</v>
@@ -20060,7 +20060,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>6.05663919448853</v>
+        <v>6.05663871765137</v>
       </c>
       <c r="H679" t="n">
         <v>267454</v>
@@ -20176,7 +20176,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G683" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H683" t="n">
         <v>112229</v>
@@ -20205,7 +20205,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G684" t="n">
-        <v>5.76599550247192</v>
+        <v>5.76599502563477</v>
       </c>
       <c r="H684" t="n">
         <v>109749</v>
@@ -20234,7 +20234,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G685" t="n">
-        <v>5.83162403106689</v>
+        <v>5.83162450790405</v>
       </c>
       <c r="H685" t="n">
         <v>123066</v>
@@ -20263,7 +20263,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G686" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H686" t="n">
         <v>53656</v>
@@ -20292,7 +20292,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G687" t="n">
-        <v>5.83162403106689</v>
+        <v>5.83162450790405</v>
       </c>
       <c r="H687" t="n">
         <v>147677</v>
@@ -20350,7 +20350,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G689" t="n">
-        <v>5.88787841796875</v>
+        <v>5.88787794113159</v>
       </c>
       <c r="H689" t="n">
         <v>56687</v>
@@ -20437,7 +20437,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G692" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H692" t="n">
         <v>38852</v>
@@ -20466,7 +20466,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H693" t="n">
         <v>30885</v>
@@ -20495,7 +20495,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G694" t="n">
-        <v>5.86912679672241</v>
+        <v>5.86912727355957</v>
       </c>
       <c r="H694" t="n">
         <v>26728</v>
@@ -20553,7 +20553,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G696" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H696" t="n">
         <v>59798</v>
@@ -20582,7 +20582,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G697" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H697" t="n">
         <v>58922</v>
@@ -20843,7 +20843,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G706" t="n">
-        <v>6.10351705551147</v>
+        <v>6.10351657867432</v>
       </c>
       <c r="H706" t="n">
         <v>46753</v>
@@ -20930,7 +20930,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G709" t="n">
-        <v>6.04726266860962</v>
+        <v>6.04726314544678</v>
       </c>
       <c r="H709" t="n">
         <v>68499</v>
@@ -20959,7 +20959,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>5.84100008010864</v>
+        <v>5.84099960327148</v>
       </c>
       <c r="H710" t="n">
         <v>66068</v>
@@ -20988,7 +20988,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G711" t="n">
-        <v>5.88787841796875</v>
+        <v>5.88787794113159</v>
       </c>
       <c r="H711" t="n">
         <v>114258</v>
@@ -21017,7 +21017,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H712" t="n">
         <v>47336</v>
@@ -21075,7 +21075,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G714" t="n">
-        <v>5.6816143989563</v>
+        <v>5.68161487579346</v>
       </c>
       <c r="H714" t="n">
         <v>80044</v>
@@ -21336,7 +21336,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G723" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H723" t="n">
         <v>34191</v>
@@ -21394,7 +21394,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G725" t="n">
-        <v>5.83162403106689</v>
+        <v>5.83162450790405</v>
       </c>
       <c r="H725" t="n">
         <v>112869</v>
@@ -21423,7 +21423,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G726" t="n">
-        <v>5.76599550247192</v>
+        <v>5.76599502563477</v>
       </c>
       <c r="H726" t="n">
         <v>47899</v>
@@ -21481,7 +21481,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G728" t="n">
-        <v>5.33471727371216</v>
+        <v>5.33471775054932</v>
       </c>
       <c r="H728" t="n">
         <v>558937</v>
@@ -21510,7 +21510,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>5.23158597946167</v>
+        <v>5.23158550262451</v>
       </c>
       <c r="H729" t="n">
         <v>187003</v>
@@ -21568,7 +21568,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G731" t="n">
-        <v>4.69717693328857</v>
+        <v>4.69717645645142</v>
       </c>
       <c r="H731" t="n">
         <v>383863</v>
@@ -21597,7 +21597,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G732" t="n">
-        <v>4.8003077507019</v>
+        <v>4.80030822753906</v>
       </c>
       <c r="H732" t="n">
         <v>258378</v>
@@ -21655,7 +21655,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G734" t="n">
-        <v>4.73467922210693</v>
+        <v>4.73467874526978</v>
       </c>
       <c r="H734" t="n">
         <v>62891</v>
@@ -21800,7 +21800,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G739" t="n">
-        <v>3.93775272369385</v>
+        <v>3.93775248527527</v>
       </c>
       <c r="H739" t="n">
         <v>114786</v>
@@ -21858,7 +21858,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G741" t="n">
-        <v>3.7408652305603</v>
+        <v>3.74086499214172</v>
       </c>
       <c r="H741" t="n">
         <v>58761</v>
@@ -22119,7 +22119,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G750" t="n">
-        <v>3.05175852775574</v>
+        <v>3.05175828933716</v>
       </c>
       <c r="H750" t="n">
         <v>72240</v>
@@ -22293,7 +22293,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G756" t="n">
-        <v>3.15020227432251</v>
+        <v>3.15020203590393</v>
       </c>
       <c r="H756" t="n">
         <v>52031</v>
@@ -22525,7 +22525,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G764" t="n">
-        <v>3.05644631385803</v>
+        <v>3.05644607543945</v>
       </c>
       <c r="H764" t="n">
         <v>97203</v>
@@ -22612,7 +22612,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G767" t="n">
-        <v>2.75642681121826</v>
+        <v>2.75642704963684</v>
       </c>
       <c r="H767" t="n">
         <v>93848</v>
@@ -22699,7 +22699,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G770" t="n">
-        <v>2.66735863685608</v>
+        <v>2.66735887527466</v>
       </c>
       <c r="H770" t="n">
         <v>36105</v>
@@ -22960,7 +22960,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G779" t="n">
-        <v>3.11738777160645</v>
+        <v>3.11738753318787</v>
       </c>
       <c r="H779" t="n">
         <v>35868</v>
@@ -23047,7 +23047,7 @@
         <v>3.25</v>
       </c>
       <c r="G782" t="n">
-        <v>3.04707050323486</v>
+        <v>3.04707074165344</v>
       </c>
       <c r="H782" t="n">
         <v>114461</v>
@@ -23076,7 +23076,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G783" t="n">
-        <v>3.09394860267639</v>
+        <v>3.09394836425781</v>
       </c>
       <c r="H783" t="n">
         <v>50573</v>
@@ -23105,7 +23105,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G784" t="n">
-        <v>3.05644631385803</v>
+        <v>3.05644607543945</v>
       </c>
       <c r="H784" t="n">
         <v>51754</v>
@@ -23221,7 +23221,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G788" t="n">
-        <v>2.77049040794373</v>
+        <v>2.77049016952515</v>
       </c>
       <c r="H788" t="n">
         <v>263344</v>
@@ -23250,7 +23250,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G789" t="n">
-        <v>2.75642681121826</v>
+        <v>2.75642704963684</v>
       </c>
       <c r="H789" t="n">
         <v>105392</v>
@@ -23279,7 +23279,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G790" t="n">
-        <v>2.70954918861389</v>
+        <v>2.70954895019531</v>
       </c>
       <c r="H790" t="n">
         <v>55133</v>
@@ -23366,7 +23366,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G793" t="n">
-        <v>2.95331454277039</v>
+        <v>2.95331478118896</v>
       </c>
       <c r="H793" t="n">
         <v>269826</v>
@@ -23395,7 +23395,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G794" t="n">
-        <v>2.95331454277039</v>
+        <v>2.95331478118896</v>
       </c>
       <c r="H794" t="n">
         <v>192048</v>
@@ -23714,7 +23714,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>3.37521648406982</v>
+        <v>3.3752167224884</v>
       </c>
       <c r="H805" t="n">
         <v>219067</v>
@@ -24004,7 +24004,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>3.53460192680359</v>
+        <v>3.53460168838501</v>
       </c>
       <c r="H815" t="n">
         <v>83963</v>
@@ -24091,7 +24091,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G818" t="n">
-        <v>3.65179705619812</v>
+        <v>3.65179681777954</v>
       </c>
       <c r="H818" t="n">
         <v>103929</v>
@@ -24207,7 +24207,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.63773345947266</v>
+        <v>3.63773369789124</v>
       </c>
       <c r="H822" t="n">
         <v>64264</v>
@@ -24526,7 +24526,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G833" t="n">
-        <v>3.665860414505</v>
+        <v>3.66586017608643</v>
       </c>
       <c r="H833" t="n">
         <v>83318</v>
@@ -24555,7 +24555,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G834" t="n">
-        <v>3.665860414505</v>
+        <v>3.66586017608643</v>
       </c>
       <c r="H834" t="n">
         <v>30259</v>
@@ -24845,7 +24845,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G844" t="n">
-        <v>3.32365107536316</v>
+        <v>3.32365083694458</v>
       </c>
       <c r="H844" t="n">
         <v>26683</v>
@@ -24874,7 +24874,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G845" t="n">
-        <v>3.46428465843201</v>
+        <v>3.46428489685059</v>
       </c>
       <c r="H845" t="n">
         <v>66739</v>
@@ -25048,7 +25048,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G851" t="n">
-        <v>3.7408652305603</v>
+        <v>3.74086499214172</v>
       </c>
       <c r="H851" t="n">
         <v>67538</v>
@@ -25570,7 +25570,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>3.36115336418152</v>
+        <v>3.36115312576294</v>
       </c>
       <c r="H869" t="n">
         <v>31331</v>
@@ -25686,7 +25686,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G873" t="n">
-        <v>3.48772382736206</v>
+        <v>3.48772406578064</v>
       </c>
       <c r="H873" t="n">
         <v>27789</v>
@@ -25715,7 +25715,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G874" t="n">
-        <v>3.58616757392883</v>
+        <v>3.58616781234741</v>
       </c>
       <c r="H874" t="n">
         <v>145369</v>
@@ -25744,7 +25744,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>3.53460192680359</v>
+        <v>3.53460168838501</v>
       </c>
       <c r="H875" t="n">
         <v>28511</v>
@@ -25802,7 +25802,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>3.31896281242371</v>
+        <v>3.31896305084229</v>
       </c>
       <c r="H877" t="n">
         <v>109874</v>
@@ -25831,7 +25831,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>3.36115336418152</v>
+        <v>3.36115312576294</v>
       </c>
       <c r="H878" t="n">
         <v>12689</v>
@@ -25976,7 +25976,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>3.35646533966064</v>
+        <v>3.35646557807922</v>
       </c>
       <c r="H883" t="n">
         <v>24798</v>
@@ -26063,7 +26063,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G886" t="n">
-        <v>3.29083609580994</v>
+        <v>3.29083633422852</v>
       </c>
       <c r="H886" t="n">
         <v>16486</v>
@@ -26092,7 +26092,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G887" t="n">
-        <v>3.33302640914917</v>
+        <v>3.33302664756775</v>
       </c>
       <c r="H887" t="n">
         <v>16362</v>
@@ -26150,7 +26150,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G889" t="n">
-        <v>3.58616757392883</v>
+        <v>3.58616781234741</v>
       </c>
       <c r="H889" t="n">
         <v>108103</v>
@@ -26237,7 +26237,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G892" t="n">
-        <v>3.49241161346436</v>
+        <v>3.49241137504578</v>
       </c>
       <c r="H892" t="n">
         <v>20443</v>
@@ -26324,7 +26324,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>3.36115336418152</v>
+        <v>3.36115312576294</v>
       </c>
       <c r="H895" t="n">
         <v>25977</v>
@@ -26440,7 +26440,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>3.29083609580994</v>
+        <v>3.29083633422852</v>
       </c>
       <c r="H899" t="n">
         <v>20434</v>
@@ -26556,7 +26556,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G903" t="n">
-        <v>3.02831959724426</v>
+        <v>3.02831935882568</v>
       </c>
       <c r="H903" t="n">
         <v>47586</v>
@@ -26643,7 +26643,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G906" t="n">
-        <v>2.95331454277039</v>
+        <v>2.95331478118896</v>
       </c>
       <c r="H906" t="n">
         <v>25182</v>
@@ -26730,7 +26730,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G909" t="n">
-        <v>3.18770480155945</v>
+        <v>3.18770456314087</v>
       </c>
       <c r="H909" t="n">
         <v>23020</v>
@@ -26904,7 +26904,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>3.36115336418152</v>
+        <v>3.36115312576294</v>
       </c>
       <c r="H915" t="n">
         <v>15443</v>
@@ -27049,7 +27049,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G920" t="n">
-        <v>3.87681174278259</v>
+        <v>3.87681150436401</v>
       </c>
       <c r="H920" t="n">
         <v>245709</v>
@@ -27078,7 +27078,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G921" t="n">
-        <v>3.92368912696838</v>
+        <v>3.92368936538696</v>
       </c>
       <c r="H921" t="n">
         <v>77394</v>
@@ -27107,7 +27107,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G922" t="n">
-        <v>3.82524561882019</v>
+        <v>3.82524538040161</v>
       </c>
       <c r="H922" t="n">
         <v>55872</v>
@@ -27165,7 +27165,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G924" t="n">
-        <v>3.92837738990784</v>
+        <v>3.92837715148926</v>
       </c>
       <c r="H924" t="n">
         <v>130552</v>
@@ -27223,7 +27223,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>3.97056746482849</v>
+        <v>3.97056770324707</v>
       </c>
       <c r="H926" t="n">
         <v>57005</v>
@@ -27339,7 +27339,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>3.91900110244751</v>
+        <v>3.91900134086609</v>
       </c>
       <c r="H930" t="n">
         <v>69316</v>
@@ -27484,7 +27484,7 @@
         <v>4.75</v>
       </c>
       <c r="G935" t="n">
-        <v>4.45341062545776</v>
+        <v>4.45341110229492</v>
       </c>
       <c r="H935" t="n">
         <v>91659</v>
@@ -27687,7 +27687,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G942" t="n">
-        <v>4.5096640586853</v>
+        <v>4.50966453552246</v>
       </c>
       <c r="H942" t="n">
         <v>182016</v>
@@ -27745,7 +27745,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G944" t="n">
-        <v>4.51904058456421</v>
+        <v>4.51904010772705</v>
       </c>
       <c r="H944" t="n">
         <v>34706</v>
@@ -27861,7 +27861,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G948" t="n">
-        <v>4.4721622467041</v>
+        <v>4.47216176986694</v>
       </c>
       <c r="H948" t="n">
         <v>42524</v>
@@ -27890,7 +27890,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G949" t="n">
-        <v>4.50497627258301</v>
+        <v>4.50497674942017</v>
       </c>
       <c r="H949" t="n">
         <v>26355</v>
@@ -28006,7 +28006,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G953" t="n">
-        <v>4.40184545516968</v>
+        <v>4.40184497833252</v>
       </c>
       <c r="H953" t="n">
         <v>53796</v>
@@ -28035,7 +28035,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G954" t="n">
-        <v>4.34090328216553</v>
+        <v>4.34090375900269</v>
       </c>
       <c r="H954" t="n">
         <v>39023</v>
@@ -28064,7 +28064,7 @@
         <v>4.5</v>
       </c>
       <c r="G955" t="n">
-        <v>4.2190203666687</v>
+        <v>4.21902084350586</v>
       </c>
       <c r="H955" t="n">
         <v>63329</v>
@@ -28151,7 +28151,7 @@
         <v>4.5</v>
       </c>
       <c r="G958" t="n">
-        <v>4.2190203666687</v>
+        <v>4.21902084350586</v>
       </c>
       <c r="H958" t="n">
         <v>28205</v>
@@ -28238,7 +28238,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G961" t="n">
-        <v>4.17214298248291</v>
+        <v>4.17214250564575</v>
       </c>
       <c r="H961" t="n">
         <v>16978</v>
@@ -28296,7 +28296,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G963" t="n">
-        <v>3.93775272369385</v>
+        <v>3.93775248527527</v>
       </c>
       <c r="H963" t="n">
         <v>254500</v>
@@ -28383,7 +28383,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G966" t="n">
-        <v>3.97056746482849</v>
+        <v>3.97056770324707</v>
       </c>
       <c r="H966" t="n">
         <v>30908</v>
@@ -28412,7 +28412,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G967" t="n">
-        <v>4.01744508743286</v>
+        <v>4.01744556427002</v>
       </c>
       <c r="H967" t="n">
         <v>12677</v>
@@ -28470,7 +28470,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G969" t="n">
-        <v>4.26589870452881</v>
+        <v>4.26589918136597</v>
       </c>
       <c r="H969" t="n">
         <v>257364</v>
@@ -28615,7 +28615,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G974" t="n">
-        <v>4.61279630661011</v>
+        <v>4.61279582977295</v>
       </c>
       <c r="H974" t="n">
         <v>48179</v>
@@ -28731,7 +28731,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G978" t="n">
-        <v>5.0534496307373</v>
+        <v>5.05344915390015</v>
       </c>
       <c r="H978" t="n">
         <v>410174</v>
@@ -28847,7 +28847,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G982" t="n">
-        <v>5.22220993041992</v>
+        <v>5.22221040725708</v>
       </c>
       <c r="H982" t="n">
         <v>205889</v>
@@ -28934,7 +28934,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G985" t="n">
-        <v>5.14720487594604</v>
+        <v>5.1472053527832</v>
       </c>
       <c r="H985" t="n">
         <v>83264</v>
@@ -28963,7 +28963,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G986" t="n">
-        <v>5.02532243728638</v>
+        <v>5.02532291412354</v>
       </c>
       <c r="H986" t="n">
         <v>138460</v>
@@ -29079,7 +29079,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G990" t="n">
-        <v>5.00657176971436</v>
+        <v>5.0065712928772</v>
       </c>
       <c r="H990" t="n">
         <v>101262</v>
@@ -29166,7 +29166,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G993" t="n">
-        <v>4.95969343185425</v>
+        <v>4.95969295501709</v>
       </c>
       <c r="H993" t="n">
         <v>72969</v>
@@ -29224,7 +29224,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G995" t="n">
-        <v>5.21283435821533</v>
+        <v>5.21283483505249</v>
       </c>
       <c r="H995" t="n">
         <v>144614</v>
@@ -29282,7 +29282,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G997" t="n">
-        <v>5.10970306396484</v>
+        <v>5.10970258712769</v>
       </c>
       <c r="H997" t="n">
         <v>279320</v>
@@ -29340,7 +29340,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G999" t="n">
-        <v>5.0534496307373</v>
+        <v>5.05344915390015</v>
       </c>
       <c r="H999" t="n">
         <v>72666</v>
@@ -29369,7 +29369,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1000" t="n">
-        <v>5.10970306396484</v>
+        <v>5.10970258712769</v>
       </c>
       <c r="H1000" t="n">
         <v>137169</v>
@@ -29398,7 +29398,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>5.0534496307373</v>
+        <v>5.05344915390015</v>
       </c>
       <c r="H1001" t="n">
         <v>77912</v>
@@ -29456,7 +29456,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.95031785964966</v>
+        <v>4.95031833648682</v>
       </c>
       <c r="H1003" t="n">
         <v>46287</v>
@@ -29485,7 +29485,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.98782014846802</v>
+        <v>4.98782062530518</v>
       </c>
       <c r="H1004" t="n">
         <v>86205</v>
@@ -29572,7 +29572,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.95031785964966</v>
+        <v>4.95031833648682</v>
       </c>
       <c r="H1007" t="n">
         <v>30859</v>
@@ -29804,7 +29804,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1015" t="n">
-        <v>5.0534496307373</v>
+        <v>5.05344915390015</v>
       </c>
       <c r="H1015" t="n">
         <v>49146</v>
@@ -29920,7 +29920,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1019" t="n">
-        <v>5.54098081588745</v>
+        <v>5.54098033905029</v>
       </c>
       <c r="H1019" t="n">
         <v>113262</v>
@@ -29949,7 +29949,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1020" t="n">
-        <v>5.51285362243652</v>
+        <v>5.51285409927368</v>
       </c>
       <c r="H1020" t="n">
         <v>59853</v>
@@ -30007,7 +30007,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>5.30659055709839</v>
+        <v>5.30659008026123</v>
       </c>
       <c r="H1022" t="n">
         <v>61984</v>
@@ -30094,7 +30094,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1025" t="n">
-        <v>5.3534688949585</v>
+        <v>5.35346841812134</v>
       </c>
       <c r="H1025" t="n">
         <v>58350</v>
@@ -30123,7 +30123,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1026" t="n">
-        <v>5.61598539352417</v>
+        <v>5.61598491668701</v>
       </c>
       <c r="H1026" t="n">
         <v>107582</v>
@@ -30210,7 +30210,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1029" t="n">
-        <v>5.4941029548645</v>
+        <v>5.49410247802734</v>
       </c>
       <c r="H1029" t="n">
         <v>58734</v>
@@ -30384,7 +30384,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1035" t="n">
-        <v>5.878502368927</v>
+        <v>5.87850189208984</v>
       </c>
       <c r="H1035" t="n">
         <v>98328</v>
@@ -30471,7 +30471,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1038" t="n">
-        <v>5.6816143989563</v>
+        <v>5.68161487579346</v>
       </c>
       <c r="H1038" t="n">
         <v>65582</v>
@@ -30645,7 +30645,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1044" t="n">
-        <v>5.83162403106689</v>
+        <v>5.83162450790405</v>
       </c>
       <c r="H1044" t="n">
         <v>25238</v>
@@ -30674,7 +30674,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1045" t="n">
-        <v>5.86912679672241</v>
+        <v>5.86912727355957</v>
       </c>
       <c r="H1045" t="n">
         <v>26217</v>
@@ -30732,7 +30732,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1047" t="n">
-        <v>5.78474617004395</v>
+        <v>5.7847466468811</v>
       </c>
       <c r="H1047" t="n">
         <v>49030</v>
@@ -30848,7 +30848,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H1051" t="n">
         <v>41127</v>
@@ -30877,7 +30877,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1052" t="n">
-        <v>6.00976085662842</v>
+        <v>6.00976037979126</v>
       </c>
       <c r="H1052" t="n">
         <v>85695</v>
@@ -30935,7 +30935,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1054" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H1054" t="n">
         <v>61811</v>
@@ -31109,7 +31109,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1060" t="n">
-        <v>5.76599550247192</v>
+        <v>5.76599502563477</v>
       </c>
       <c r="H1060" t="n">
         <v>36169</v>
@@ -31225,7 +31225,7 @@
         <v>6.5</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.09414100646973</v>
+        <v>6.09414148330688</v>
       </c>
       <c r="H1064" t="n">
         <v>132793</v>
@@ -31254,7 +31254,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>6.58167219161987</v>
+        <v>6.58167266845703</v>
       </c>
       <c r="H1065" t="n">
         <v>492479</v>
@@ -31370,7 +31370,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G1069" t="n">
-        <v>6.49729204177856</v>
+        <v>6.49729156494141</v>
       </c>
       <c r="H1069" t="n">
         <v>76882</v>
@@ -31399,7 +31399,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.41291189193726</v>
+        <v>6.4129114151001</v>
       </c>
       <c r="H1070" t="n">
         <v>46006</v>
@@ -31457,7 +31457,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1072" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H1072" t="n">
         <v>51967</v>
@@ -31486,7 +31486,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1073" t="n">
-        <v>6.23477554321289</v>
+        <v>6.23477506637573</v>
       </c>
       <c r="H1073" t="n">
         <v>54286</v>
@@ -31544,7 +31544,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1075" t="n">
-        <v>6.23477554321289</v>
+        <v>6.23477506637573</v>
       </c>
       <c r="H1075" t="n">
         <v>26275</v>
@@ -31718,7 +31718,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1081" t="n">
-        <v>6.27227735519409</v>
+        <v>6.27227783203125</v>
       </c>
       <c r="H1081" t="n">
         <v>42764</v>
@@ -31805,7 +31805,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.878502368927</v>
+        <v>5.87850189208984</v>
       </c>
       <c r="H1084" t="n">
         <v>48664</v>
@@ -31921,7 +31921,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1088" t="n">
-        <v>6.18789720535278</v>
+        <v>6.18789672851562</v>
       </c>
       <c r="H1088" t="n">
         <v>179609</v>
@@ -31950,7 +31950,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H1089" t="n">
         <v>514710</v>
@@ -32269,7 +32269,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1100" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H1100" t="n">
         <v>45627</v>
@@ -32356,7 +32356,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1103" t="n">
-        <v>6.94732093811035</v>
+        <v>6.94732046127319</v>
       </c>
       <c r="H1103" t="n">
         <v>35767</v>
@@ -32414,7 +32414,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1105" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H1105" t="n">
         <v>40210</v>
@@ -32472,7 +32472,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1107" t="n">
-        <v>6.72230672836304</v>
+        <v>6.72230625152588</v>
       </c>
       <c r="H1107" t="n">
         <v>22423</v>
@@ -32501,7 +32501,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.97544765472412</v>
+        <v>6.97544813156128</v>
       </c>
       <c r="H1108" t="n">
         <v>77442</v>
@@ -32559,7 +32559,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1110" t="n">
-        <v>6.66605281829834</v>
+        <v>6.6660532951355</v>
       </c>
       <c r="H1110" t="n">
         <v>46760</v>
@@ -32588,7 +32588,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1111" t="n">
-        <v>6.75043296813965</v>
+        <v>6.75043344497681</v>
       </c>
       <c r="H1111" t="n">
         <v>56922</v>
@@ -32878,7 +32878,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>7.42547702789307</v>
+        <v>7.42547655105591</v>
       </c>
       <c r="H1121" t="n">
         <v>95716</v>
@@ -32907,7 +32907,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1122" t="n">
-        <v>7.30359411239624</v>
+        <v>7.30359363555908</v>
       </c>
       <c r="H1122" t="n">
         <v>66396</v>
@@ -32936,7 +32936,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1123" t="n">
-        <v>7.15358400344849</v>
+        <v>7.15358448028564</v>
       </c>
       <c r="H1123" t="n">
         <v>70423</v>
@@ -32965,7 +32965,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1124" t="n">
-        <v>7.30359411239624</v>
+        <v>7.30359363555908</v>
       </c>
       <c r="H1124" t="n">
         <v>81777</v>
@@ -33023,7 +33023,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1126" t="n">
-        <v>6.66605281829834</v>
+        <v>6.6660532951355</v>
       </c>
       <c r="H1126" t="n">
         <v>279700</v>
@@ -33313,7 +33313,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1136" t="n">
-        <v>6.66605281829834</v>
+        <v>6.6660532951355</v>
       </c>
       <c r="H1136" t="n">
         <v>43116</v>
@@ -33458,7 +33458,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1141" t="n">
-        <v>6.45041418075562</v>
+        <v>6.45041370391846</v>
       </c>
       <c r="H1141" t="n">
         <v>31312</v>
@@ -33719,7 +33719,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1150" t="n">
-        <v>7.48173046112061</v>
+        <v>7.48172998428345</v>
       </c>
       <c r="H1150" t="n">
         <v>134941</v>
@@ -33748,7 +33748,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1151" t="n">
-        <v>7.33172082901001</v>
+        <v>7.33172035217285</v>
       </c>
       <c r="H1151" t="n">
         <v>98063</v>
@@ -33777,7 +33777,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1152" t="n">
-        <v>7.32234477996826</v>
+        <v>7.32234525680542</v>
       </c>
       <c r="H1152" t="n">
         <v>56002</v>
@@ -33922,7 +33922,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1157" t="n">
-        <v>7.37859869003296</v>
+        <v>7.3785982131958</v>
       </c>
       <c r="H1157" t="n">
         <v>103207</v>
@@ -33951,7 +33951,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1158" t="n">
-        <v>7.25671577453613</v>
+        <v>7.25671529769897</v>
       </c>
       <c r="H1158" t="n">
         <v>77714</v>
@@ -34009,7 +34009,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1160" t="n">
-        <v>7.2848424911499</v>
+        <v>7.28484296798706</v>
       </c>
       <c r="H1160" t="n">
         <v>58676</v>
@@ -34067,7 +34067,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1162" t="n">
-        <v>7.72549533843994</v>
+        <v>7.7254958152771</v>
       </c>
       <c r="H1162" t="n">
         <v>199951</v>
@@ -34183,7 +34183,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1166" t="n">
-        <v>7.84737825393677</v>
+        <v>7.84737873077393</v>
       </c>
       <c r="H1166" t="n">
         <v>108516</v>
@@ -34212,7 +34212,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1167" t="n">
-        <v>7.66924238204956</v>
+        <v>7.66924285888672</v>
       </c>
       <c r="H1167" t="n">
         <v>155477</v>
@@ -34444,7 +34444,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1175" t="n">
-        <v>7.15358400344849</v>
+        <v>7.15358448028564</v>
       </c>
       <c r="H1175" t="n">
         <v>112746</v>
@@ -34473,7 +34473,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1176" t="n">
-        <v>7.25671577453613</v>
+        <v>7.25671529769897</v>
       </c>
       <c r="H1176" t="n">
         <v>154249</v>
@@ -34647,7 +34647,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1182" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H1182" t="n">
         <v>74528</v>
@@ -34908,7 +34908,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1191" t="n">
-        <v>7.18171119689941</v>
+        <v>7.18171072006226</v>
       </c>
       <c r="H1191" t="n">
         <v>36444</v>
@@ -35024,7 +35024,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1195" t="n">
-        <v>7.18171119689941</v>
+        <v>7.18171072006226</v>
       </c>
       <c r="H1195" t="n">
         <v>55985</v>
@@ -35256,7 +35256,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1203" t="n">
-        <v>7.18171119689941</v>
+        <v>7.18171072006226</v>
       </c>
       <c r="H1203" t="n">
         <v>14575</v>
@@ -35372,7 +35372,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>7.30359411239624</v>
+        <v>7.30359363555908</v>
       </c>
       <c r="H1207" t="n">
         <v>21658</v>
@@ -35430,7 +35430,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1209" t="n">
-        <v>6.89106750488281</v>
+        <v>6.89106702804565</v>
       </c>
       <c r="H1209" t="n">
         <v>54359</v>
@@ -35459,7 +35459,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.98482322692871</v>
+        <v>6.98482275009155</v>
       </c>
       <c r="H1210" t="n">
         <v>34698</v>
@@ -35546,7 +35546,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1213" t="n">
-        <v>6.98482322692871</v>
+        <v>6.98482275009155</v>
       </c>
       <c r="H1213" t="n">
         <v>28965</v>
@@ -35575,7 +35575,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1214" t="n">
-        <v>7.18171119689941</v>
+        <v>7.18171072006226</v>
       </c>
       <c r="H1214" t="n">
         <v>38969</v>
@@ -35749,7 +35749,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1220" t="n">
-        <v>6.51604270935059</v>
+        <v>6.51604318618774</v>
       </c>
       <c r="H1220" t="n">
         <v>84304</v>
@@ -35836,7 +35836,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.71293067932129</v>
+        <v>6.71293115615845</v>
       </c>
       <c r="H1223" t="n">
         <v>24014</v>
@@ -35865,7 +35865,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H1224" t="n">
         <v>48103</v>
@@ -35923,7 +35923,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1226" t="n">
-        <v>6.92856931686401</v>
+        <v>6.92856979370117</v>
       </c>
       <c r="H1226" t="n">
         <v>33391</v>
@@ -36010,7 +36010,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.3754096031189</v>
+        <v>6.37540912628174</v>
       </c>
       <c r="H1229" t="n">
         <v>49048</v>
@@ -36039,7 +36039,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1230" t="n">
-        <v>6.18789720535278</v>
+        <v>6.18789672851562</v>
       </c>
       <c r="H1230" t="n">
         <v>90704</v>
@@ -36068,7 +36068,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1231" t="n">
-        <v>6.41291189193726</v>
+        <v>6.4129114151001</v>
       </c>
       <c r="H1231" t="n">
         <v>31094</v>
@@ -36126,7 +36126,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>6.11289262771606</v>
+        <v>6.11289215087891</v>
       </c>
       <c r="H1233" t="n">
         <v>45872</v>
@@ -36155,7 +36155,7 @@
         <v>6.5</v>
       </c>
       <c r="G1234" t="n">
-        <v>6.09414100646973</v>
+        <v>6.09414148330688</v>
       </c>
       <c r="H1234" t="n">
         <v>77495</v>
@@ -36184,7 +36184,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1235" t="n">
-        <v>6.21602392196655</v>
+        <v>6.21602439880371</v>
       </c>
       <c r="H1235" t="n">
         <v>39474</v>
@@ -36300,7 +36300,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1239" t="n">
-        <v>6.18789720535278</v>
+        <v>6.18789672851562</v>
       </c>
       <c r="H1239" t="n">
         <v>34692</v>
@@ -36387,7 +36387,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1242" t="n">
-        <v>5.75661897659302</v>
+        <v>5.75661945343018</v>
       </c>
       <c r="H1242" t="n">
         <v>150698</v>
@@ -36474,7 +36474,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1245" t="n">
-        <v>5.90662908554077</v>
+        <v>5.90662956237793</v>
       </c>
       <c r="H1245" t="n">
         <v>60938</v>
@@ -36619,7 +36619,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1250" t="n">
-        <v>5.21283435821533</v>
+        <v>5.21283483505249</v>
       </c>
       <c r="H1250" t="n">
         <v>70449</v>
@@ -36764,7 +36764,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1255" t="n">
-        <v>5.51285362243652</v>
+        <v>5.51285409927368</v>
       </c>
       <c r="H1255" t="n">
         <v>41966</v>
@@ -36909,7 +36909,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1260" t="n">
-        <v>6.23477554321289</v>
+        <v>6.23477506637573</v>
       </c>
       <c r="H1260" t="n">
         <v>62278</v>
@@ -36967,7 +36967,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1262" t="n">
-        <v>6.21602392196655</v>
+        <v>6.21602439880371</v>
       </c>
       <c r="H1262" t="n">
         <v>45431</v>
@@ -37025,7 +37025,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1264" t="n">
-        <v>6.30040454864502</v>
+        <v>6.30040407180786</v>
       </c>
       <c r="H1264" t="n">
         <v>58350</v>
@@ -37054,7 +37054,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1265" t="n">
-        <v>6.27227735519409</v>
+        <v>6.27227783203125</v>
       </c>
       <c r="H1265" t="n">
         <v>75070</v>
@@ -37112,7 +37112,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1267" t="n">
-        <v>6.16914558410645</v>
+        <v>6.1691460609436</v>
       </c>
       <c r="H1267" t="n">
         <v>33305</v>
@@ -37141,7 +37141,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1268" t="n">
-        <v>6.10351705551147</v>
+        <v>6.10351657867432</v>
       </c>
       <c r="H1268" t="n">
         <v>30370</v>
@@ -37518,7 +37518,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1281" t="n">
-        <v>6.04726266860962</v>
+        <v>6.04726314544678</v>
       </c>
       <c r="H1281" t="n">
         <v>15651</v>
@@ -37547,7 +37547,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.878502368927</v>
+        <v>5.87850189208984</v>
       </c>
       <c r="H1282" t="n">
         <v>20045</v>
@@ -37576,7 +37576,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1283" t="n">
-        <v>5.76599550247192</v>
+        <v>5.76599502563477</v>
       </c>
       <c r="H1283" t="n">
         <v>45274</v>
@@ -70758,6 +70758,35 @@
         <v>116635</v>
       </c>
       <c r="I2427" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2428">
+      <c r="A2428" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2428" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2428" t="n">
+        <v>1.36600005626678</v>
+      </c>
+      <c r="D2428" t="n">
+        <v>1.36600005626678</v>
+      </c>
+      <c r="E2428" t="n">
+        <v>1.34399998188019</v>
+      </c>
+      <c r="F2428" t="n">
+        <v>1.34599995613098</v>
+      </c>
+      <c r="G2428" t="n">
+        <v>1.34599995613098</v>
+      </c>
+      <c r="H2428" t="n">
+        <v>40160</v>
+      </c>
+      <c r="I2428" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -456,7 +456,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G3" t="n">
-        <v>9.27969360351562</v>
+        <v>9.27969455718994</v>
       </c>
       <c r="H3" t="n">
         <v>73034</v>
@@ -543,7 +543,7 @@
         <v>10.5</v>
       </c>
       <c r="G6" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H6" t="n">
         <v>50252</v>
@@ -601,7 +601,7 @@
         <v>10.5</v>
       </c>
       <c r="G8" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H8" t="n">
         <v>12361</v>
@@ -630,7 +630,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G9" t="n">
-        <v>9.40570259094238</v>
+        <v>9.4057035446167</v>
       </c>
       <c r="H9" t="n">
         <v>1874</v>
@@ -659,7 +659,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>9.8107328414917</v>
+        <v>9.81073379516602</v>
       </c>
       <c r="H10" t="n">
         <v>8225</v>
@@ -688,7 +688,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G11" t="n">
-        <v>9.52271270751953</v>
+        <v>9.52271175384521</v>
       </c>
       <c r="H11" t="n">
         <v>34524</v>
@@ -717,7 +717,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>9.44170570373535</v>
+        <v>9.44170665740967</v>
       </c>
       <c r="H12" t="n">
         <v>74921</v>
@@ -746,7 +746,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.40570259094238</v>
+        <v>9.4057035446167</v>
       </c>
       <c r="H13" t="n">
         <v>11246</v>
@@ -775,7 +775,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>9.40570259094238</v>
+        <v>9.4057035446167</v>
       </c>
       <c r="H14" t="n">
         <v>51250</v>
@@ -804,7 +804,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G15" t="n">
-        <v>9.36970043182373</v>
+        <v>9.36970138549805</v>
       </c>
       <c r="H15" t="n">
         <v>10916</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="G17" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H17" t="n">
         <v>9239</v>
@@ -891,7 +891,7 @@
         <v>10.5</v>
       </c>
       <c r="G18" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H18" t="n">
         <v>21485</v>
@@ -920,7 +920,7 @@
         <v>10.5</v>
       </c>
       <c r="G19" t="n">
-        <v>9.45070743560791</v>
+        <v>9.45070648193359</v>
       </c>
       <c r="H19" t="n">
         <v>143074</v>
@@ -949,7 +949,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G20" t="n">
-        <v>9.54071521759033</v>
+        <v>9.54071426391602</v>
       </c>
       <c r="H20" t="n">
         <v>8555</v>
@@ -978,7 +978,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G21" t="n">
-        <v>9.5587158203125</v>
+        <v>9.55871486663818</v>
       </c>
       <c r="H21" t="n">
         <v>3705</v>
@@ -1094,7 +1094,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G25" t="n">
-        <v>9.54071521759033</v>
+        <v>9.54071426391602</v>
       </c>
       <c r="H25" t="n">
         <v>17860</v>
@@ -1152,7 +1152,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>9.54071521759033</v>
+        <v>9.54071426391602</v>
       </c>
       <c r="H27" t="n">
         <v>16080</v>
@@ -1355,7 +1355,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G34" t="n">
-        <v>9.6937255859375</v>
+        <v>9.69372653961182</v>
       </c>
       <c r="H34" t="n">
         <v>17123</v>
@@ -1384,7 +1384,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G35" t="n">
-        <v>9.8107328414917</v>
+        <v>9.81073379516602</v>
       </c>
       <c r="H35" t="n">
         <v>17570</v>
@@ -1645,7 +1645,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>10.1617603302002</v>
+        <v>10.1617593765259</v>
       </c>
       <c r="H44" t="n">
         <v>905</v>
@@ -1674,7 +1674,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G45" t="n">
-        <v>10.1617603302002</v>
+        <v>10.1617593765259</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>9.94574356079102</v>
+        <v>9.94574451446533</v>
       </c>
       <c r="H46" t="n">
         <v>8</v>
@@ -1732,7 +1732,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G47" t="n">
-        <v>10.1617603302002</v>
+        <v>10.1617593765259</v>
       </c>
       <c r="H47" t="n">
         <v>6500</v>
@@ -1761,7 +1761,7 @@
         <v>12</v>
       </c>
       <c r="G48" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H48" t="n">
         <v>2330</v>
@@ -1790,7 +1790,7 @@
         <v>12.5</v>
       </c>
       <c r="G49" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508430480957</v>
       </c>
       <c r="H49" t="n">
         <v>19250</v>
@@ -1819,7 +1819,7 @@
         <v>12.5</v>
       </c>
       <c r="G50" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508430480957</v>
       </c>
       <c r="H50" t="n">
         <v>8165</v>
@@ -1877,7 +1877,7 @@
         <v>12</v>
       </c>
       <c r="G52" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H52" t="n">
         <v>6600</v>
@@ -1906,7 +1906,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G53" t="n">
-        <v>10.6927995681763</v>
+        <v>10.6928005218506</v>
       </c>
       <c r="H53" t="n">
         <v>10522</v>
@@ -1935,7 +1935,7 @@
         <v>12</v>
       </c>
       <c r="G54" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H54" t="n">
         <v>11262</v>
@@ -2051,7 +2051,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G58" t="n">
-        <v>10.6927995681763</v>
+        <v>10.6928005218506</v>
       </c>
       <c r="H58" t="n">
         <v>19515</v>
@@ -2138,7 +2138,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G61" t="n">
-        <v>10.7918081283569</v>
+        <v>10.7918071746826</v>
       </c>
       <c r="H61" t="n">
         <v>118200</v>
@@ -2167,7 +2167,7 @@
         <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H62" t="n">
         <v>8081</v>
@@ -2225,7 +2225,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G64" t="n">
-        <v>10.7828063964844</v>
+        <v>10.7828054428101</v>
       </c>
       <c r="H64" t="n">
         <v>11664</v>
@@ -2283,7 +2283,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G66" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H66" t="n">
         <v>2413</v>
@@ -2457,7 +2457,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H72" t="n">
         <v>17517</v>
@@ -2602,7 +2602,7 @@
         <v>12</v>
       </c>
       <c r="G77" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H77" t="n">
         <v>21843</v>
@@ -2689,7 +2689,7 @@
         <v>12.5</v>
       </c>
       <c r="G80" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508430480957</v>
       </c>
       <c r="H80" t="n">
         <v>22926</v>
@@ -2718,7 +2718,7 @@
         <v>12.5</v>
       </c>
       <c r="G81" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508430480957</v>
       </c>
       <c r="H81" t="n">
         <v>4837</v>
@@ -2863,7 +2863,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G86" t="n">
-        <v>11.0078229904175</v>
+        <v>11.0078239440918</v>
       </c>
       <c r="H86" t="n">
         <v>617</v>
@@ -2892,7 +2892,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G87" t="n">
-        <v>11.0078229904175</v>
+        <v>11.0078239440918</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>12</v>
       </c>
       <c r="G89" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H89" t="n">
         <v>2</v>
@@ -2979,7 +2979,7 @@
         <v>12</v>
       </c>
       <c r="G90" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H90" t="n">
         <v>132646</v>
@@ -3037,7 +3037,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G92" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H92" t="n">
         <v>3303</v>
@@ -3240,7 +3240,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G99" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H99" t="n">
         <v>4100</v>
@@ -3414,7 +3414,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G105" t="n">
-        <v>11.1518354415894</v>
+        <v>11.151834487915</v>
       </c>
       <c r="H105" t="n">
         <v>6308</v>
@@ -3704,7 +3704,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G115" t="n">
-        <v>11.0438261032104</v>
+        <v>11.0438270568848</v>
       </c>
       <c r="H115" t="n">
         <v>761</v>
@@ -3762,7 +3762,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H117" t="n">
         <v>12190</v>
@@ -3791,7 +3791,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G118" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H118" t="n">
         <v>5884</v>
@@ -3820,7 +3820,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>11.2418403625488</v>
+        <v>11.2418413162231</v>
       </c>
       <c r="H119" t="n">
         <v>10255</v>
@@ -3878,7 +3878,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G121" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H121" t="n">
         <v>95700</v>
@@ -3907,7 +3907,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H122" t="n">
         <v>2200</v>
@@ -3936,7 +3936,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G123" t="n">
-        <v>11.1518354415894</v>
+        <v>11.151834487915</v>
       </c>
       <c r="H123" t="n">
         <v>6225</v>
@@ -3965,7 +3965,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G124" t="n">
-        <v>11.0888299942017</v>
+        <v>11.0888290405273</v>
       </c>
       <c r="H124" t="n">
         <v>20229</v>
@@ -3994,7 +3994,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G125" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H125" t="n">
         <v>53861</v>
@@ -4052,7 +4052,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G127" t="n">
-        <v>11.0528268814087</v>
+        <v>11.052827835083</v>
       </c>
       <c r="H127" t="n">
         <v>9639</v>
@@ -4139,7 +4139,7 @@
         <v>12</v>
       </c>
       <c r="G130" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H130" t="n">
         <v>10740</v>
@@ -4168,7 +4168,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G131" t="n">
-        <v>11.0438261032104</v>
+        <v>11.0438270568848</v>
       </c>
       <c r="H131" t="n">
         <v>1475</v>
@@ -4226,7 +4226,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G133" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H133" t="n">
         <v>1516</v>
@@ -4255,7 +4255,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G135" t="n">
-        <v>11.0528268814087</v>
+        <v>11.052827835083</v>
       </c>
       <c r="H135" t="n">
         <v>12316</v>
@@ -4429,7 +4429,7 @@
         <v>12.5</v>
       </c>
       <c r="G140" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508430480957</v>
       </c>
       <c r="H140" t="n">
         <v>50941</v>
@@ -4458,7 +4458,7 @@
         <v>12.5</v>
       </c>
       <c r="G141" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508430480957</v>
       </c>
       <c r="H141" t="n">
         <v>28615</v>
@@ -4516,7 +4516,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G143" t="n">
-        <v>11.2778434753418</v>
+        <v>11.2778425216675</v>
       </c>
       <c r="H143" t="n">
         <v>19219</v>
@@ -4632,7 +4632,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G147" t="n">
-        <v>11.5208625793457</v>
+        <v>11.5208616256714</v>
       </c>
       <c r="H147" t="n">
         <v>40959</v>
@@ -4661,7 +4661,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G148" t="n">
-        <v>11.6918745040894</v>
+        <v>11.691873550415</v>
       </c>
       <c r="H148" t="n">
         <v>50666</v>
@@ -4835,7 +4835,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G154" t="n">
-        <v>11.8178853988647</v>
+        <v>11.8178844451904</v>
       </c>
       <c r="H154" t="n">
         <v>13313</v>
@@ -4864,7 +4864,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G155" t="n">
-        <v>11.5748653411865</v>
+        <v>11.5748662948608</v>
       </c>
       <c r="H155" t="n">
         <v>9271</v>
@@ -5067,7 +5067,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G162" t="n">
-        <v>11.5028610229492</v>
+        <v>11.5028600692749</v>
       </c>
       <c r="H162" t="n">
         <v>8549</v>
@@ -5125,7 +5125,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G164" t="n">
-        <v>11.6558713912964</v>
+        <v>11.6558723449707</v>
       </c>
       <c r="H164" t="n">
         <v>7000</v>
@@ -5183,7 +5183,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>11.6558713912964</v>
+        <v>11.6558723449707</v>
       </c>
       <c r="H166" t="n">
         <v>436</v>
@@ -5212,7 +5212,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G167" t="n">
-        <v>11.8358850479126</v>
+        <v>11.8358840942383</v>
       </c>
       <c r="H167" t="n">
         <v>5902</v>
@@ -5241,7 +5241,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>11.9708948135376</v>
+        <v>11.9708957672119</v>
       </c>
       <c r="H168" t="n">
         <v>3334</v>
@@ -5270,7 +5270,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>11.9708948135376</v>
+        <v>11.9708957672119</v>
       </c>
       <c r="H169" t="n">
         <v>25389</v>
@@ -5357,7 +5357,7 @@
         <v>12.5</v>
       </c>
       <c r="G172" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508430480957</v>
       </c>
       <c r="H172" t="n">
         <v>252282</v>
@@ -5444,7 +5444,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H175" t="n">
         <v>17680</v>
@@ -5502,7 +5502,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H177" t="n">
         <v>97611</v>
@@ -5560,7 +5560,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G179" t="n">
-        <v>10.989821434021</v>
+        <v>10.9898223876953</v>
       </c>
       <c r="H179" t="n">
         <v>71095</v>
@@ -5618,7 +5618,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G181" t="n">
-        <v>10.8728141784668</v>
+        <v>10.8728132247925</v>
       </c>
       <c r="H181" t="n">
         <v>10043</v>
@@ -5647,7 +5647,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G182" t="n">
-        <v>10.7918081283569</v>
+        <v>10.7918071746826</v>
       </c>
       <c r="H182" t="n">
         <v>45769</v>
@@ -5676,7 +5676,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G183" t="n">
-        <v>10.7198028564453</v>
+        <v>10.719801902771</v>
       </c>
       <c r="H183" t="n">
         <v>21068</v>
@@ -5792,7 +5792,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G187" t="n">
-        <v>11.1968383789062</v>
+        <v>11.1968374252319</v>
       </c>
       <c r="H187" t="n">
         <v>35264</v>
@@ -5850,7 +5850,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G189" t="n">
-        <v>11.2418403625488</v>
+        <v>11.2418413162231</v>
       </c>
       <c r="H189" t="n">
         <v>6735</v>
@@ -5908,7 +5908,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G191" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H191" t="n">
         <v>43427</v>
@@ -5966,7 +5966,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H193" t="n">
         <v>33122</v>
@@ -6053,7 +6053,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H196" t="n">
         <v>20113</v>
@@ -6082,7 +6082,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H197" t="n">
         <v>24111</v>
@@ -6111,7 +6111,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H198" t="n">
         <v>19135</v>
@@ -6227,7 +6227,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6558713912964</v>
+        <v>11.6558723449707</v>
       </c>
       <c r="H202" t="n">
         <v>63641</v>
@@ -6285,7 +6285,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G204" t="n">
-        <v>11.8808889389038</v>
+        <v>11.8808879852295</v>
       </c>
       <c r="H204" t="n">
         <v>50580</v>
@@ -6314,7 +6314,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>11.6558713912964</v>
+        <v>11.6558723449707</v>
       </c>
       <c r="H205" t="n">
         <v>29232</v>
@@ -6575,7 +6575,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H214" t="n">
         <v>42154</v>
@@ -6604,7 +6604,7 @@
         <v>12.5</v>
       </c>
       <c r="G215" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508430480957</v>
       </c>
       <c r="H215" t="n">
         <v>18114</v>
@@ -6633,7 +6633,7 @@
         <v>12.5</v>
       </c>
       <c r="G216" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508430480957</v>
       </c>
       <c r="H216" t="n">
         <v>32596</v>
@@ -6662,7 +6662,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H217" t="n">
         <v>100153</v>
@@ -6691,7 +6691,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H218" t="n">
         <v>23902</v>
@@ -6807,7 +6807,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H222" t="n">
         <v>33108</v>
@@ -6836,7 +6836,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G223" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H223" t="n">
         <v>32411</v>
@@ -6865,7 +6865,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G224" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H224" t="n">
         <v>38565</v>
@@ -6894,7 +6894,7 @@
         <v>12.5</v>
       </c>
       <c r="G225" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508430480957</v>
       </c>
       <c r="H225" t="n">
         <v>5055</v>
@@ -6923,7 +6923,7 @@
         <v>12.75</v>
       </c>
       <c r="G226" t="n">
-        <v>11.4758586883545</v>
+        <v>11.4758577346802</v>
       </c>
       <c r="H226" t="n">
         <v>83399</v>
@@ -7010,7 +7010,7 @@
         <v>12.5</v>
       </c>
       <c r="G229" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508430480957</v>
       </c>
       <c r="H229" t="n">
         <v>380956</v>
@@ -7039,7 +7039,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H230" t="n">
         <v>49113</v>
@@ -7155,7 +7155,7 @@
         <v>12</v>
       </c>
       <c r="G234" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H234" t="n">
         <v>28217</v>
@@ -7300,7 +7300,7 @@
         <v>12</v>
       </c>
       <c r="G239" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H239" t="n">
         <v>39939</v>
@@ -7416,7 +7416,7 @@
         <v>12</v>
       </c>
       <c r="G243" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H243" t="n">
         <v>48611</v>
@@ -7619,7 +7619,7 @@
         <v>12</v>
       </c>
       <c r="G250" t="n">
-        <v>10.8008079528809</v>
+        <v>10.8008089065552</v>
       </c>
       <c r="H250" t="n">
         <v>31759</v>
@@ -7706,7 +7706,7 @@
         <v>12.5</v>
       </c>
       <c r="G253" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508430480957</v>
       </c>
       <c r="H253" t="n">
         <v>21093</v>
@@ -7735,7 +7735,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H254" t="n">
         <v>40241</v>
@@ -7764,7 +7764,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G255" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H255" t="n">
         <v>5284</v>
@@ -7793,7 +7793,7 @@
         <v>12.75</v>
       </c>
       <c r="G256" t="n">
-        <v>11.4758586883545</v>
+        <v>11.4758577346802</v>
       </c>
       <c r="H256" t="n">
         <v>26163</v>
@@ -7822,7 +7822,7 @@
         <v>12.75</v>
       </c>
       <c r="G257" t="n">
-        <v>11.4758586883545</v>
+        <v>11.4758577346802</v>
       </c>
       <c r="H257" t="n">
         <v>16349</v>
@@ -7851,7 +7851,7 @@
         <v>12.5</v>
       </c>
       <c r="G258" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508430480957</v>
       </c>
       <c r="H258" t="n">
         <v>43297</v>
@@ -7996,7 +7996,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H263" t="n">
         <v>27661</v>
@@ -8025,7 +8025,7 @@
         <v>12.5</v>
       </c>
       <c r="G264" t="n">
-        <v>11.2508420944214</v>
+        <v>11.2508430480957</v>
       </c>
       <c r="H264" t="n">
         <v>19560</v>
@@ -8054,7 +8054,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>11.2058382034302</v>
+        <v>11.2058391571045</v>
       </c>
       <c r="H265" t="n">
         <v>13029</v>
@@ -8083,7 +8083,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>11.2958450317383</v>
+        <v>11.2958459854126</v>
       </c>
       <c r="H266" t="n">
         <v>6743</v>
@@ -8112,7 +8112,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H267" t="n">
         <v>7336</v>
@@ -8257,7 +8257,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H272" t="n">
         <v>17619</v>
@@ -8286,7 +8286,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>11.1608352661133</v>
+        <v>11.160834312439</v>
       </c>
       <c r="H273" t="n">
         <v>16739</v>
@@ -12984,7 +12984,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G435" t="n">
-        <v>8.19104480743408</v>
+        <v>8.19104385375977</v>
       </c>
       <c r="H435" t="n">
         <v>22985</v>
@@ -70787,6 +70787,35 @@
         <v>40160</v>
       </c>
       <c r="I2428" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2429">
+      <c r="A2429" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2429" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2429" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="D2429" t="n">
+        <v>1.38399994373322</v>
+      </c>
+      <c r="E2429" t="n">
+        <v>1.34599995613098</v>
+      </c>
+      <c r="F2429" t="n">
+        <v>1.36199998855591</v>
+      </c>
+      <c r="G2429" t="n">
+        <v>1.36199998855591</v>
+      </c>
+      <c r="H2429" t="n">
+        <v>99067</v>
+      </c>
+      <c r="I2429" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -70813,9 +70813,38 @@
         <v>1.36199998855591</v>
       </c>
       <c r="H2429" t="n">
-        <v>99067</v>
+        <v>99462</v>
       </c>
       <c r="I2429" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2430">
+      <c r="A2430" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2430" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2430" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="D2430" t="n">
+        <v>1.37399995326996</v>
+      </c>
+      <c r="E2430" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="F2430" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="G2430" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="H2430" t="n">
+        <v>26664</v>
+      </c>
+      <c r="I2430" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ECNL.MI.xlsx
+++ b/data/ECNL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G2" t="n">
-        <v>9.13568305969238</v>
+        <v>9.1356840133667</v>
       </c>
       <c r="H2" t="n">
         <v>48343</v>
@@ -485,7 +485,7 @@
         <v>10.25</v>
       </c>
       <c r="G4" t="n">
-        <v>9.2256908416748</v>
+        <v>9.22568988800049</v>
       </c>
       <c r="H4" t="n">
         <v>116483</v>
@@ -514,7 +514,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>9.28869533538818</v>
+        <v>9.28869438171387</v>
       </c>
       <c r="H5" t="n">
         <v>264710</v>
@@ -688,7 +688,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G11" t="n">
-        <v>9.52271175384521</v>
+        <v>9.52271270751953</v>
       </c>
       <c r="H11" t="n">
         <v>34524</v>
@@ -717,7 +717,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>9.44170665740967</v>
+        <v>9.44170570373535</v>
       </c>
       <c r="H12" t="n">
         <v>74921</v>
@@ -949,7 +949,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G20" t="n">
-        <v>9.54071426391602</v>
+        <v>9.5407133102417</v>
       </c>
       <c r="H20" t="n">
         <v>8555</v>
@@ -978,7 +978,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G21" t="n">
-        <v>9.55871486663818</v>
+        <v>9.55871391296387</v>
       </c>
       <c r="H21" t="n">
         <v>3705</v>
@@ -1007,7 +1007,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G22" t="n">
-        <v>9.48671054840088</v>
+        <v>9.48670959472656</v>
       </c>
       <c r="H22" t="n">
         <v>1993</v>
@@ -1094,7 +1094,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G25" t="n">
-        <v>9.54071426391602</v>
+        <v>9.5407133102417</v>
       </c>
       <c r="H25" t="n">
         <v>17860</v>
@@ -1123,7 +1123,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>9.6307201385498</v>
+        <v>9.63072109222412</v>
       </c>
       <c r="H26" t="n">
         <v>7000</v>
@@ -1152,7 +1152,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>9.54071426391602</v>
+        <v>9.5407133102417</v>
       </c>
       <c r="H27" t="n">
         <v>16080</v>
@@ -1181,7 +1181,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G28" t="n">
-        <v>9.6307201385498</v>
+        <v>9.63072109222412</v>
       </c>
       <c r="H28" t="n">
         <v>1105</v>
@@ -1210,7 +1210,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G29" t="n">
-        <v>9.6307201385498</v>
+        <v>9.63072109222412</v>
       </c>
       <c r="H29" t="n">
         <v>3091</v>
@@ -1268,7 +1268,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>9.6307201385498</v>
+        <v>9.63072109222412</v>
       </c>
       <c r="H31" t="n">
         <v>6000</v>
@@ -1297,7 +1297,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G32" t="n">
-        <v>9.6307201385498</v>
+        <v>9.63072109222412</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G34" t="n">
-        <v>9.69372653961182</v>
+        <v>9.6937255859375</v>
       </c>
       <c r="H34" t="n">
         <v>17123</v>
@@ -1645,7 +1645,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>10.1617593765259</v>
+        <v>10.1617603302002</v>
       </c>
       <c r="H44" t="n">
         <v>905</v>
@@ -1674,7 +1674,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G45" t="n">
-        <v>10.1617593765259</v>
+        <v>10.1617603302002</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G47" t="n">
-        <v>10.1617593765259</v>
+        <v>10.1617603302002</v>
       </c>
       <c r="H47" t="n">
         <v>6500</v>
@@ -1761,7 +1761,7 @@
         <v>12</v>
       </c>
       <c r="G48" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H48" t="n">
         <v>2330</v>
@@ -1790,7 +1790,7 @@
         <v>12.5</v>
       </c>
       <c r="G49" t="n">
-        <v>11.2508430480957</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H49" t="n">
         <v>19250</v>
@@ -1819,7 +1819,7 @@
         <v>12.5</v>
       </c>
       <c r="G50" t="n">
-        <v>11.2508430480957</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H50" t="n">
         <v>8165</v>
@@ -1848,7 +1848,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708293914795</v>
       </c>
       <c r="H51" t="n">
         <v>124253</v>
@@ -1877,7 +1877,7 @@
         <v>12</v>
       </c>
       <c r="G52" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H52" t="n">
         <v>6600</v>
@@ -1906,7 +1906,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G53" t="n">
-        <v>10.6928005218506</v>
+        <v>10.6927995681763</v>
       </c>
       <c r="H53" t="n">
         <v>10522</v>
@@ -1935,7 +1935,7 @@
         <v>12</v>
       </c>
       <c r="G54" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H54" t="n">
         <v>11262</v>
@@ -2022,7 +2022,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G57" t="n">
-        <v>10.7648048400879</v>
+        <v>10.7648057937622</v>
       </c>
       <c r="H57" t="n">
         <v>32694</v>
@@ -2051,7 +2051,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G58" t="n">
-        <v>10.6928005218506</v>
+        <v>10.6927995681763</v>
       </c>
       <c r="H58" t="n">
         <v>19515</v>
@@ -2109,7 +2109,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G60" t="n">
-        <v>10.8368120193481</v>
+        <v>10.8368110656738</v>
       </c>
       <c r="H60" t="n">
         <v>361</v>
@@ -2167,7 +2167,7 @@
         <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H62" t="n">
         <v>8081</v>
@@ -2196,7 +2196,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G63" t="n">
-        <v>10.8368120193481</v>
+        <v>10.8368110656738</v>
       </c>
       <c r="H63" t="n">
         <v>6516</v>
@@ -2225,7 +2225,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G64" t="n">
-        <v>10.7828054428101</v>
+        <v>10.7828063964844</v>
       </c>
       <c r="H64" t="n">
         <v>11664</v>
@@ -2283,7 +2283,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G66" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H66" t="n">
         <v>2413</v>
@@ -2341,7 +2341,7 @@
         <v>12.25</v>
       </c>
       <c r="G68" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H68" t="n">
         <v>11800</v>
@@ -2370,7 +2370,7 @@
         <v>12.25</v>
       </c>
       <c r="G69" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H69" t="n">
         <v>10830</v>
@@ -2399,7 +2399,7 @@
         <v>12.25</v>
       </c>
       <c r="G70" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H70" t="n">
         <v>19079</v>
@@ -2428,7 +2428,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H71" t="n">
         <v>19479</v>
@@ -2457,7 +2457,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H72" t="n">
         <v>17517</v>
@@ -2486,7 +2486,7 @@
         <v>12.25</v>
       </c>
       <c r="G73" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H73" t="n">
         <v>10849</v>
@@ -2544,7 +2544,7 @@
         <v>12.25</v>
       </c>
       <c r="G75" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H75" t="n">
         <v>23178</v>
@@ -2573,7 +2573,7 @@
         <v>12.25</v>
       </c>
       <c r="G76" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H76" t="n">
         <v>77850</v>
@@ -2602,7 +2602,7 @@
         <v>12</v>
       </c>
       <c r="G77" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H77" t="n">
         <v>21843</v>
@@ -2689,7 +2689,7 @@
         <v>12.5</v>
       </c>
       <c r="G80" t="n">
-        <v>11.2508430480957</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H80" t="n">
         <v>22926</v>
@@ -2718,7 +2718,7 @@
         <v>12.5</v>
       </c>
       <c r="G81" t="n">
-        <v>11.2508430480957</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H81" t="n">
         <v>4837</v>
@@ -2805,7 +2805,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708293914795</v>
       </c>
       <c r="H84" t="n">
         <v>9646</v>
@@ -2834,7 +2834,7 @@
         <v>12.25</v>
       </c>
       <c r="G85" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H85" t="n">
         <v>7351</v>
@@ -2950,7 +2950,7 @@
         <v>12</v>
       </c>
       <c r="G89" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H89" t="n">
         <v>2</v>
@@ -2979,7 +2979,7 @@
         <v>12</v>
       </c>
       <c r="G90" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H90" t="n">
         <v>132646</v>
@@ -3066,7 +3066,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708293914795</v>
       </c>
       <c r="H93" t="n">
         <v>372</v>
@@ -3095,7 +3095,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708293914795</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -3124,7 +3124,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708293914795</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H96" t="n">
         <v>95</v>
@@ -3182,7 +3182,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G97" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708293914795</v>
       </c>
       <c r="H97" t="n">
         <v>186</v>
@@ -3211,7 +3211,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G98" t="n">
-        <v>11.0978298187256</v>
+        <v>11.0978307723999</v>
       </c>
       <c r="H98" t="n">
         <v>3490</v>
@@ -3269,7 +3269,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708293914795</v>
       </c>
       <c r="H100" t="n">
         <v>2679</v>
@@ -3298,7 +3298,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H101" t="n">
         <v>13000</v>
@@ -3327,7 +3327,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H102" t="n">
         <v>49869</v>
@@ -3356,7 +3356,7 @@
         <v>12.25</v>
       </c>
       <c r="G103" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H103" t="n">
         <v>800</v>
@@ -3385,7 +3385,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708293914795</v>
       </c>
       <c r="H104" t="n">
         <v>6401</v>
@@ -3443,7 +3443,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708293914795</v>
       </c>
       <c r="H106" t="n">
         <v>29860</v>
@@ -3472,7 +3472,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G107" t="n">
-        <v>11.0348262786865</v>
+        <v>11.0348253250122</v>
       </c>
       <c r="H107" t="n">
         <v>1001</v>
@@ -3501,7 +3501,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G108" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708293914795</v>
       </c>
       <c r="H108" t="n">
         <v>2003</v>
@@ -3588,7 +3588,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G111" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708293914795</v>
       </c>
       <c r="H111" t="n">
         <v>1647</v>
@@ -3617,7 +3617,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708293914795</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G113" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708293914795</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G114" t="n">
-        <v>10.953818321228</v>
+        <v>10.9538192749023</v>
       </c>
       <c r="H114" t="n">
         <v>1013</v>
@@ -3704,7 +3704,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G115" t="n">
-        <v>11.0438270568848</v>
+        <v>11.0438261032104</v>
       </c>
       <c r="H115" t="n">
         <v>761</v>
@@ -3733,7 +3733,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H116" t="n">
         <v>2</v>
@@ -3762,7 +3762,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H117" t="n">
         <v>12190</v>
@@ -3820,7 +3820,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>11.2418413162231</v>
+        <v>11.2418403625488</v>
       </c>
       <c r="H119" t="n">
         <v>10255</v>
@@ -3849,7 +3849,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G120" t="n">
-        <v>11.0978298187256</v>
+        <v>11.0978307723999</v>
       </c>
       <c r="H120" t="n">
         <v>23000</v>
@@ -3907,7 +3907,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H122" t="n">
         <v>2200</v>
@@ -3965,7 +3965,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G124" t="n">
-        <v>11.0888290405273</v>
+        <v>11.0888299942017</v>
       </c>
       <c r="H124" t="n">
         <v>20229</v>
@@ -4023,7 +4023,7 @@
         <v>12.25</v>
       </c>
       <c r="G126" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H126" t="n">
         <v>7500</v>
@@ -4052,7 +4052,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G127" t="n">
-        <v>11.052827835083</v>
+        <v>11.0528268814087</v>
       </c>
       <c r="H127" t="n">
         <v>9639</v>
@@ -4081,7 +4081,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>11.0978298187256</v>
+        <v>11.0978307723999</v>
       </c>
       <c r="H128" t="n">
         <v>24331</v>
@@ -4110,7 +4110,7 @@
         <v>12.25</v>
       </c>
       <c r="G129" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H129" t="n">
         <v>6915</v>
@@ -4139,7 +4139,7 @@
         <v>12</v>
       </c>
       <c r="G130" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H130" t="n">
         <v>10740</v>
@@ -4168,7 +4168,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G131" t="n">
-        <v>11.0438270568848</v>
+        <v>11.0438261032104</v>
       </c>
       <c r="H131" t="n">
         <v>1475</v>
@@ -4197,7 +4197,7 @@
         <v>12.25</v>
       </c>
       <c r="G132" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H132" t="n">
         <v>496</v>
@@ -4284,7 +4284,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G135" t="n">
-        <v>11.052827835083</v>
+        <v>11.0528268814087</v>
       </c>
       <c r="H135" t="n">
         <v>12316</v>
@@ -4313,7 +4313,7 @@
         <v>12.25</v>
       </c>
       <c r="G136" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H136" t="n">
         <v>37117</v>
@@ -4342,7 +4342,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H137" t="n">
         <v>11453</v>
@@ -4371,7 +4371,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>12.5</v>
       </c>
       <c r="G140" t="n">
-        <v>11.2508430480957</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H140" t="n">
         <v>50941</v>
@@ -4458,7 +4458,7 @@
         <v>12.5</v>
       </c>
       <c r="G141" t="n">
-        <v>11.2508430480957</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H141" t="n">
         <v>28615</v>
@@ -4516,7 +4516,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G143" t="n">
-        <v>11.2778425216675</v>
+        <v>11.2778434753418</v>
       </c>
       <c r="H143" t="n">
         <v>19219</v>
@@ -4545,7 +4545,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>11.4308547973633</v>
+        <v>11.4308557510376</v>
       </c>
       <c r="H144" t="n">
         <v>15034</v>
@@ -4574,7 +4574,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>11.4308547973633</v>
+        <v>11.4308557510376</v>
       </c>
       <c r="H145" t="n">
         <v>800</v>
@@ -4603,7 +4603,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G146" t="n">
-        <v>11.4308547973633</v>
+        <v>11.4308557510376</v>
       </c>
       <c r="H146" t="n">
         <v>1600</v>
@@ -4632,7 +4632,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G147" t="n">
-        <v>11.5208616256714</v>
+        <v>11.5208625793457</v>
       </c>
       <c r="H147" t="n">
         <v>40959</v>
@@ -4661,7 +4661,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G148" t="n">
-        <v>11.691873550415</v>
+        <v>11.6918745040894</v>
       </c>
       <c r="H148" t="n">
         <v>50666</v>
@@ -4777,7 +4777,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>11.5658655166626</v>
+        <v>11.5658664703369</v>
       </c>
       <c r="H152" t="n">
         <v>7751</v>
@@ -4806,7 +4806,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G153" t="n">
-        <v>11.5118618011475</v>
+        <v>11.5118608474731</v>
       </c>
       <c r="H153" t="n">
         <v>15226</v>
@@ -4835,7 +4835,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G154" t="n">
-        <v>11.8178844451904</v>
+        <v>11.8178853988647</v>
       </c>
       <c r="H154" t="n">
         <v>13313</v>
@@ -4864,7 +4864,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G155" t="n">
-        <v>11.5748662948608</v>
+        <v>11.5748653411865</v>
       </c>
       <c r="H155" t="n">
         <v>9271</v>
@@ -4893,7 +4893,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>11.5658655166626</v>
+        <v>11.5658664703369</v>
       </c>
       <c r="H156" t="n">
         <v>15491</v>
@@ -4980,7 +4980,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>11.5658655166626</v>
+        <v>11.5658664703369</v>
       </c>
       <c r="H159" t="n">
         <v>810</v>
@@ -5038,7 +5038,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G161" t="n">
-        <v>11.493860244751</v>
+        <v>11.4938592910767</v>
       </c>
       <c r="H161" t="n">
         <v>12761</v>
@@ -5154,7 +5154,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G165" t="n">
-        <v>11.8628883361816</v>
+        <v>11.862889289856</v>
       </c>
       <c r="H165" t="n">
         <v>3712</v>
@@ -5212,7 +5212,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G167" t="n">
-        <v>11.8358840942383</v>
+        <v>11.8358850479126</v>
       </c>
       <c r="H167" t="n">
         <v>5902</v>
@@ -5241,7 +5241,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>11.9708957672119</v>
+        <v>11.9708967208862</v>
       </c>
       <c r="H168" t="n">
         <v>3334</v>
@@ -5270,7 +5270,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>11.9708957672119</v>
+        <v>11.9708967208862</v>
       </c>
       <c r="H169" t="n">
         <v>25389</v>
@@ -5357,7 +5357,7 @@
         <v>12.5</v>
       </c>
       <c r="G172" t="n">
-        <v>11.2508430480957</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H172" t="n">
         <v>252282</v>
@@ -5415,7 +5415,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G174" t="n">
-        <v>11.0348262786865</v>
+        <v>11.0348253250122</v>
       </c>
       <c r="H174" t="n">
         <v>38220</v>
@@ -5444,7 +5444,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H175" t="n">
         <v>17680</v>
@@ -5531,7 +5531,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G178" t="n">
-        <v>11.0348262786865</v>
+        <v>11.0348253250122</v>
       </c>
       <c r="H178" t="n">
         <v>86579</v>
@@ -5618,7 +5618,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G181" t="n">
-        <v>10.8728132247925</v>
+        <v>10.8728141784668</v>
       </c>
       <c r="H181" t="n">
         <v>10043</v>
@@ -5734,7 +5734,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G185" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708293914795</v>
       </c>
       <c r="H185" t="n">
         <v>144903</v>
@@ -5850,7 +5850,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G189" t="n">
-        <v>11.2418413162231</v>
+        <v>11.2418403625488</v>
       </c>
       <c r="H189" t="n">
         <v>6735</v>
@@ -5966,7 +5966,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H193" t="n">
         <v>33122</v>
@@ -5995,7 +5995,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G194" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708293914795</v>
       </c>
       <c r="H194" t="n">
         <v>22619</v>
@@ -6053,7 +6053,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H196" t="n">
         <v>20113</v>
@@ -6140,7 +6140,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H199" t="n">
         <v>10780</v>
@@ -6169,7 +6169,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H200" t="n">
         <v>40377</v>
@@ -6198,7 +6198,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>11.3858518600464</v>
+        <v>11.3858509063721</v>
       </c>
       <c r="H201" t="n">
         <v>341100</v>
@@ -6256,7 +6256,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>11.7908840179443</v>
+        <v>11.7908821105957</v>
       </c>
       <c r="H203" t="n">
         <v>38065</v>
@@ -6285,7 +6285,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G204" t="n">
-        <v>11.8808879852295</v>
+        <v>11.8808889389038</v>
       </c>
       <c r="H204" t="n">
         <v>50580</v>
@@ -6372,7 +6372,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>11.7908840179443</v>
+        <v>11.7908821105957</v>
       </c>
       <c r="H207" t="n">
         <v>18452</v>
@@ -6430,7 +6430,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G209" t="n">
-        <v>11.5658655166626</v>
+        <v>11.5658664703369</v>
       </c>
       <c r="H209" t="n">
         <v>27077</v>
@@ -6604,7 +6604,7 @@
         <v>12.5</v>
       </c>
       <c r="G215" t="n">
-        <v>11.2508430480957</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H215" t="n">
         <v>18114</v>
@@ -6633,7 +6633,7 @@
         <v>12.5</v>
       </c>
       <c r="G216" t="n">
-        <v>11.2508430480957</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H216" t="n">
         <v>32596</v>
@@ -6691,7 +6691,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H218" t="n">
         <v>23902</v>
@@ -6749,7 +6749,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H220" t="n">
         <v>32924</v>
@@ -6778,7 +6778,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708293914795</v>
       </c>
       <c r="H221" t="n">
         <v>50085</v>
@@ -6807,7 +6807,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H222" t="n">
         <v>33108</v>
@@ -6894,7 +6894,7 @@
         <v>12.5</v>
       </c>
       <c r="G225" t="n">
-        <v>11.2508430480957</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H225" t="n">
         <v>5055</v>
@@ -6923,7 +6923,7 @@
         <v>12.75</v>
       </c>
       <c r="G226" t="n">
-        <v>11.4758577346802</v>
+        <v>11.4758586883545</v>
       </c>
       <c r="H226" t="n">
         <v>83399</v>
@@ -6952,7 +6952,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>11.4308547973633</v>
+        <v>11.4308557510376</v>
       </c>
       <c r="H227" t="n">
         <v>64055</v>
@@ -7010,7 +7010,7 @@
         <v>12.5</v>
       </c>
       <c r="G229" t="n">
-        <v>11.2508430480957</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H229" t="n">
         <v>380956</v>
@@ -7126,7 +7126,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G233" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H233" t="n">
         <v>17885</v>
@@ -7155,7 +7155,7 @@
         <v>12</v>
       </c>
       <c r="G234" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H234" t="n">
         <v>28217</v>
@@ -7184,7 +7184,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G235" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H235" t="n">
         <v>16566</v>
@@ -7271,7 +7271,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H238" t="n">
         <v>18095</v>
@@ -7300,7 +7300,7 @@
         <v>12</v>
       </c>
       <c r="G239" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H239" t="n">
         <v>39939</v>
@@ -7387,7 +7387,7 @@
         <v>12.25</v>
       </c>
       <c r="G242" t="n">
-        <v>11.025824546814</v>
+        <v>11.0258255004883</v>
       </c>
       <c r="H242" t="n">
         <v>26025</v>
@@ -7416,7 +7416,7 @@
         <v>12</v>
       </c>
       <c r="G243" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H243" t="n">
         <v>48611</v>
@@ -7474,7 +7474,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H245" t="n">
         <v>15122</v>
@@ -7503,7 +7503,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>10.6207942962646</v>
+        <v>10.620795249939</v>
       </c>
       <c r="H246" t="n">
         <v>5465</v>
@@ -7619,7 +7619,7 @@
         <v>12</v>
       </c>
       <c r="G250" t="n">
-        <v>10.8008089065552</v>
+        <v>10.8008079528809</v>
       </c>
       <c r="H250" t="n">
         <v>31759</v>
@@ -7677,7 +7677,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>11.0708284378052</v>
+        <v>11.0708293914795</v>
       </c>
       <c r="H252" t="n">
         <v>8929</v>
@@ -7706,7 +7706,7 @@
         <v>12.5</v>
       </c>
       <c r="G253" t="n">
-        <v>11.2508430480957</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H253" t="n">
         <v>21093</v>
@@ -7793,7 +7793,7 @@
         <v>12.75</v>
       </c>
       <c r="G256" t="n">
-        <v>11.4758577346802</v>
+        <v>11.4758586883545</v>
       </c>
       <c r="H256" t="n">
         <v>26163</v>
@@ -7822,7 +7822,7 @@
         <v>12.75</v>
       </c>
       <c r="G257" t="n">
-        <v>11.4758577346802</v>
+        <v>11.4758586883545</v>
       </c>
       <c r="H257" t="n">
         <v>16349</v>
@@ -7851,7 +7851,7 @@
         <v>12.5</v>
       </c>
       <c r="G258" t="n">
-        <v>11.2508430480957</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H258" t="n">
         <v>43297</v>
@@ -7909,7 +7909,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G260" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H260" t="n">
         <v>17724</v>
@@ -8025,7 +8025,7 @@
         <v>12.5</v>
       </c>
       <c r="G264" t="n">
-        <v>11.2508430480957</v>
+        <v>11.2508420944214</v>
       </c>
       <c r="H264" t="n">
         <v>19560</v>
@@ -8054,7 +8054,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>11.2058391571045</v>
+        <v>11.2058382034302</v>
       </c>
       <c r="H265" t="n">
         <v>13029</v>
@@ -8141,7 +8141,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H268" t="n">
         <v>5138</v>
@@ -8199,7 +8199,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H270" t="n">
         <v>12370</v>
@@ -8228,7 +8228,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>10.9808216094971</v>
+        <v>10.9808225631714</v>
       </c>
       <c r="H271" t="n">
         <v>4989</v>
@@ -8315,7 +8315,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>11.1158313751221</v>
+        <v>11.1158323287964</v>
       </c>
       <c r="H274" t="n">
         <v>27992</v>
@@ -8518,7 +8518,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H281" t="n">
         <v>154139</v>
@@ -8547,7 +8547,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H282" t="n">
         <v>21107</v>
@@ -8634,7 +8634,7 @@
         <v>12.75</v>
       </c>
       <c r="G285" t="n">
-        <v>11.6818590164185</v>
+        <v>11.6818599700928</v>
       </c>
       <c r="H285" t="n">
         <v>28076</v>
@@ -8721,7 +8721,7 @@
         <v>12.5</v>
       </c>
       <c r="G288" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H288" t="n">
         <v>31033</v>
@@ -8779,7 +8779,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H290" t="n">
         <v>51613</v>
@@ -8895,7 +8895,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3991451263428</v>
+        <v>10.3991460800171</v>
       </c>
       <c r="H294" t="n">
         <v>66099</v>
@@ -9040,7 +9040,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>10.8114461898804</v>
+        <v>10.8114471435547</v>
       </c>
       <c r="H299" t="n">
         <v>6920</v>
@@ -9243,7 +9243,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H306" t="n">
         <v>83168</v>
@@ -9272,7 +9272,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H307" t="n">
         <v>35606</v>
@@ -9475,7 +9475,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H314" t="n">
         <v>24864</v>
@@ -9504,7 +9504,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H315" t="n">
         <v>60996</v>
@@ -9620,7 +9620,7 @@
         <v>12.5</v>
       </c>
       <c r="G319" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H319" t="n">
         <v>29752</v>
@@ -9736,7 +9736,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G323" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H323" t="n">
         <v>9841</v>
@@ -9852,7 +9852,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H327" t="n">
         <v>41583</v>
@@ -9910,7 +9910,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H329" t="n">
         <v>118877</v>
@@ -9939,7 +9939,7 @@
         <v>12.5</v>
       </c>
       <c r="G330" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H330" t="n">
         <v>16305</v>
@@ -9968,7 +9968,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G331" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H331" t="n">
         <v>21852</v>
@@ -9997,7 +9997,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H332" t="n">
         <v>98903</v>
@@ -10055,7 +10055,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>12.0025396347046</v>
+        <v>12.0025386810303</v>
       </c>
       <c r="H334" t="n">
         <v>337229</v>
@@ -10142,7 +10142,7 @@
         <v>12.75</v>
       </c>
       <c r="G337" t="n">
-        <v>11.6818590164185</v>
+        <v>11.6818599700928</v>
       </c>
       <c r="H337" t="n">
         <v>8463</v>
@@ -10200,7 +10200,7 @@
         <v>12.5</v>
       </c>
       <c r="G339" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H339" t="n">
         <v>18856</v>
@@ -10258,7 +10258,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H341" t="n">
         <v>4404</v>
@@ -10287,7 +10287,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G342" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H342" t="n">
         <v>4793</v>
@@ -10432,7 +10432,7 @@
         <v>12.5</v>
       </c>
       <c r="G347" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H347" t="n">
         <v>28995</v>
@@ -10490,7 +10490,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H349" t="n">
         <v>8309</v>
@@ -10780,7 +10780,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G359" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H359" t="n">
         <v>29957</v>
@@ -10809,7 +10809,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H360" t="n">
         <v>63557</v>
@@ -10983,7 +10983,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H366" t="n">
         <v>8248</v>
@@ -11041,7 +11041,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>11.5902376174927</v>
+        <v>11.5902366638184</v>
       </c>
       <c r="H368" t="n">
         <v>57147</v>
@@ -11070,7 +11070,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H369" t="n">
         <v>35300</v>
@@ -11099,7 +11099,7 @@
         <v>12.5</v>
       </c>
       <c r="G370" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H370" t="n">
         <v>18058</v>
@@ -11128,7 +11128,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G371" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H371" t="n">
         <v>59329</v>
@@ -11186,7 +11186,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>11.5444269180298</v>
+        <v>11.5444259643555</v>
       </c>
       <c r="H373" t="n">
         <v>33947</v>
@@ -11273,7 +11273,7 @@
         <v>12.5</v>
       </c>
       <c r="G376" t="n">
-        <v>11.4528045654297</v>
+        <v>11.4528036117554</v>
       </c>
       <c r="H376" t="n">
         <v>47155</v>
@@ -11360,7 +11360,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G379" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H379" t="n">
         <v>70147</v>
@@ -11418,7 +11418,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H381" t="n">
         <v>24797</v>
@@ -11447,7 +11447,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>11.3153696060181</v>
+        <v>11.3153705596924</v>
       </c>
       <c r="H382" t="n">
         <v>54013</v>
@@ -11592,7 +11592,7 @@
         <v>12</v>
       </c>
       <c r="G387" t="n">
-        <v>10.9946918487549</v>
+        <v>10.9946908950806</v>
       </c>
       <c r="H387" t="n">
         <v>91692</v>
@@ -11621,7 +11621,7 @@
         <v>12</v>
       </c>
       <c r="G388" t="n">
-        <v>10.9946918487549</v>
+        <v>10.9946908950806</v>
       </c>
       <c r="H388" t="n">
         <v>34295</v>
@@ -11708,7 +11708,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>10.8114461898804</v>
+        <v>10.8114471435547</v>
       </c>
       <c r="H391" t="n">
         <v>40022</v>
@@ -11766,7 +11766,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>9.9410343170166</v>
+        <v>9.94103336334229</v>
       </c>
       <c r="H393" t="n">
         <v>74407</v>
@@ -11795,7 +11795,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G394" t="n">
-        <v>9.89522266387939</v>
+        <v>9.89522361755371</v>
       </c>
       <c r="H394" t="n">
         <v>9913</v>
@@ -11853,7 +11853,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>9.528733253479</v>
+        <v>9.52873229980469</v>
       </c>
       <c r="H396" t="n">
         <v>37602</v>
@@ -12085,7 +12085,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>9.528733253479</v>
+        <v>9.52873229980469</v>
       </c>
       <c r="H404" t="n">
         <v>7740</v>
@@ -12172,7 +12172,7 @@
         <v>10</v>
       </c>
       <c r="G407" t="n">
-        <v>9.16224384307861</v>
+        <v>9.16224193572998</v>
       </c>
       <c r="H407" t="n">
         <v>15357</v>
@@ -12201,7 +12201,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>9.08894443511963</v>
+        <v>9.08894538879395</v>
       </c>
       <c r="H408" t="n">
         <v>21952</v>
@@ -12288,7 +12288,7 @@
         <v>9.5</v>
       </c>
       <c r="G411" t="n">
-        <v>8.70413112640381</v>
+        <v>8.70413017272949</v>
       </c>
       <c r="H411" t="n">
         <v>58798</v>
@@ -12317,7 +12317,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G412" t="n">
-        <v>8.57585906982422</v>
+        <v>8.5758581161499</v>
       </c>
       <c r="H412" t="n">
         <v>20574</v>
@@ -12346,7 +12346,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G413" t="n">
-        <v>8.57585906982422</v>
+        <v>8.5758581161499</v>
       </c>
       <c r="H413" t="n">
         <v>11329</v>
@@ -12404,7 +12404,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G415" t="n">
-        <v>8.31931686401367</v>
+        <v>8.31931591033936</v>
       </c>
       <c r="H415" t="n">
         <v>34723</v>
@@ -12433,7 +12433,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>8.0994234085083</v>
+        <v>8.09942245483398</v>
       </c>
       <c r="H416" t="n">
         <v>54469</v>
@@ -12462,7 +12462,7 @@
         <v>9</v>
       </c>
       <c r="G417" t="n">
-        <v>8.24601936340332</v>
+        <v>8.246018409729</v>
       </c>
       <c r="H417" t="n">
         <v>37510</v>
@@ -12491,7 +12491,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G418" t="n">
-        <v>8.37429046630859</v>
+        <v>8.37429141998291</v>
       </c>
       <c r="H418" t="n">
         <v>16525</v>
@@ -12578,7 +12578,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G421" t="n">
-        <v>8.35596466064453</v>
+        <v>8.35596561431885</v>
       </c>
       <c r="H421" t="n">
         <v>18133</v>
@@ -12607,7 +12607,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G422" t="n">
-        <v>8.50256061553955</v>
+        <v>8.50256156921387</v>
       </c>
       <c r="H422" t="n">
         <v>18370</v>
@@ -12694,7 +12694,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>9.08894443511963</v>
+        <v>9.08894538879395</v>
       </c>
       <c r="H425" t="n">
         <v>24400</v>
@@ -12810,7 +12810,7 @@
         <v>9.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.70413112640381</v>
+        <v>8.70413017272949</v>
       </c>
       <c r="H429" t="n">
         <v>51975</v>
@@ -12955,7 +12955,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>8.2826681137085</v>
+        <v>8.28266716003418</v>
       </c>
       <c r="H434" t="n">
         <v>27709</v>
@@ -12984,7 +12984,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G435" t="n">
-        <v>8.19104385375977</v>
+        <v>8.19104480743408</v>
       </c>
       <c r="H435" t="n">
         <v>22985</v>
@@ -13042,7 +13042,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>8.06277370452881</v>
+        <v>8.06277465820312</v>
       </c>
       <c r="H437" t="n">
         <v>28367</v>
@@ -13303,7 +13303,7 @@
         <v>9.5</v>
       </c>
       <c r="G446" t="n">
-        <v>8.70413112640381</v>
+        <v>8.70413017272949</v>
       </c>
       <c r="H446" t="n">
         <v>17748</v>
@@ -13361,7 +13361,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G448" t="n">
-        <v>8.59418392181396</v>
+        <v>8.59418296813965</v>
       </c>
       <c r="H448" t="n">
         <v>10460</v>
@@ -13448,7 +13448,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G451" t="n">
-        <v>8.44758892059326</v>
+        <v>8.44758796691895</v>
       </c>
       <c r="H451" t="n">
         <v>22486</v>
@@ -13506,7 +13506,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G453" t="n">
-        <v>8.44758892059326</v>
+        <v>8.44758796691895</v>
       </c>
       <c r="H453" t="n">
         <v>46077</v>
@@ -13622,7 +13622,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G457" t="n">
-        <v>8.5208854675293</v>
+        <v>8.52088642120361</v>
       </c>
       <c r="H457" t="n">
         <v>35751</v>
@@ -13651,7 +13651,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G458" t="n">
-        <v>8.44758892059326</v>
+        <v>8.44758796691895</v>
       </c>
       <c r="H458" t="n">
         <v>18909</v>
@@ -13680,7 +13680,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G459" t="n">
-        <v>8.50256061553955</v>
+        <v>8.50256156921387</v>
       </c>
       <c r="H459" t="n">
         <v>10164</v>
@@ -13767,7 +13767,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>8.5208854675293</v>
+        <v>8.52088642120361</v>
       </c>
       <c r="H462" t="n">
         <v>11004</v>
@@ -13796,7 +13796,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G463" t="n">
-        <v>8.50256061553955</v>
+        <v>8.50256156921387</v>
       </c>
       <c r="H463" t="n">
         <v>4864</v>
@@ -13970,7 +13970,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G469" t="n">
-        <v>8.64915657043457</v>
+        <v>8.64915752410889</v>
       </c>
       <c r="H469" t="n">
         <v>20305</v>
@@ -13999,7 +13999,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G470" t="n">
-        <v>8.64915657043457</v>
+        <v>8.64915752410889</v>
       </c>
       <c r="H470" t="n">
         <v>14362</v>
@@ -14028,7 +14028,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G471" t="n">
-        <v>8.50256061553955</v>
+        <v>8.50256156921387</v>
       </c>
       <c r="H471" t="n">
         <v>18355</v>
@@ -14057,7 +14057,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G472" t="n">
-        <v>8.50256061553955</v>
+        <v>8.50256156921387</v>
       </c>
       <c r="H472" t="n">
         <v>6724</v>
@@ -14086,7 +14086,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G473" t="n">
-        <v>8.5208854675293</v>
+        <v>8.52088642120361</v>
       </c>
       <c r="H473" t="n">
         <v>12739</v>
@@ -14173,7 +14173,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G476" t="n">
-        <v>8.50256061553955</v>
+        <v>8.50256156921387</v>
       </c>
       <c r="H476" t="n">
         <v>55693</v>
@@ -14202,7 +14202,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>8.5208854675293</v>
+        <v>8.52088642120361</v>
       </c>
       <c r="H477" t="n">
         <v>3956</v>
@@ -14231,7 +14231,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G478" t="n">
-        <v>8.5208854675293</v>
+        <v>8.52088642120361</v>
       </c>
       <c r="H478" t="n">
         <v>8323</v>
@@ -14434,7 +14434,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G485" t="n">
-        <v>8.26434326171875</v>
+        <v>8.26434421539307</v>
       </c>
       <c r="H485" t="n">
         <v>62090</v>
@@ -14521,7 +14521,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G488" t="n">
-        <v>8.26434326171875</v>
+        <v>8.26434421539307</v>
       </c>
       <c r="H488" t="n">
         <v>18615</v>
@@ -14608,7 +14608,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G491" t="n">
-        <v>8.0994234085083</v>
+        <v>8.09942245483398</v>
       </c>
       <c r="H491" t="n">
         <v>17335</v>
@@ -14753,7 +14753,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>9.29967594146729</v>
+        <v>9.2996768951416</v>
       </c>
       <c r="H496" t="n">
         <v>110828</v>
@@ -14782,7 +14782,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>9.29967594146729</v>
+        <v>9.2996768951416</v>
       </c>
       <c r="H497" t="n">
         <v>140545</v>
@@ -14811,7 +14811,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>9.29967594146729</v>
+        <v>9.2996768951416</v>
       </c>
       <c r="H498" t="n">
         <v>88225</v>
@@ -14927,7 +14927,7 @@
         <v>10.5</v>
       </c>
       <c r="G502" t="n">
-        <v>9.62035465240479</v>
+        <v>9.6203556060791</v>
       </c>
       <c r="H502" t="n">
         <v>175754</v>
@@ -14956,7 +14956,7 @@
         <v>10</v>
       </c>
       <c r="G503" t="n">
-        <v>9.16224384307861</v>
+        <v>9.16224193572998</v>
       </c>
       <c r="H503" t="n">
         <v>586410</v>
@@ -15014,7 +15014,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G505" t="n">
-        <v>9.10726833343506</v>
+        <v>9.10726928710938</v>
       </c>
       <c r="H505" t="n">
         <v>95256</v>
@@ -15275,7 +15275,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>8.85988807678223</v>
+        <v>8.85988903045654</v>
       </c>
       <c r="H514" t="n">
         <v>26730</v>
@@ -15362,7 +15362,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G517" t="n">
-        <v>8.82324123382568</v>
+        <v>8.82324028015137</v>
       </c>
       <c r="H517" t="n">
         <v>46713</v>
@@ -15652,7 +15652,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G527" t="n">
-        <v>8.66305637359619</v>
+        <v>8.66305541992188</v>
       </c>
       <c r="H527" t="n">
         <v>56480</v>
@@ -15681,7 +15681,7 @@
         <v>9.25</v>
       </c>
       <c r="G528" t="n">
-        <v>8.67243194580078</v>
+        <v>8.67243099212646</v>
       </c>
       <c r="H528" t="n">
         <v>69422</v>
@@ -15739,7 +15739,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G530" t="n">
-        <v>8.50366973876953</v>
+        <v>8.50367069244385</v>
       </c>
       <c r="H530" t="n">
         <v>39713</v>
@@ -15768,7 +15768,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G531" t="n">
-        <v>8.3442850112915</v>
+        <v>8.34428596496582</v>
       </c>
       <c r="H531" t="n">
         <v>20305</v>
@@ -15826,7 +15826,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G533" t="n">
-        <v>8.00676345825195</v>
+        <v>8.00676441192627</v>
       </c>
       <c r="H533" t="n">
         <v>49926</v>
@@ -15884,7 +15884,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>8.15677261352539</v>
+        <v>8.15677356719971</v>
       </c>
       <c r="H535" t="n">
         <v>24993</v>
@@ -15913,7 +15913,7 @@
         <v>8.5</v>
       </c>
       <c r="G536" t="n">
-        <v>7.96926164627075</v>
+        <v>7.96926116943359</v>
       </c>
       <c r="H536" t="n">
         <v>18660</v>
@@ -15971,7 +15971,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>7.88488054275513</v>
+        <v>7.88488101959229</v>
       </c>
       <c r="H538" t="n">
         <v>7745</v>
@@ -16000,7 +16000,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G539" t="n">
-        <v>7.84737873077393</v>
+        <v>7.84737825393677</v>
       </c>
       <c r="H539" t="n">
         <v>51647</v>
@@ -16029,7 +16029,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G540" t="n">
-        <v>7.85675430297852</v>
+        <v>7.85675477981567</v>
       </c>
       <c r="H540" t="n">
         <v>12650</v>
@@ -16058,7 +16058,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>7.80987644195557</v>
+        <v>7.80987596511841</v>
       </c>
       <c r="H541" t="n">
         <v>29138</v>
@@ -16145,7 +16145,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G544" t="n">
-        <v>7.83800268173218</v>
+        <v>7.83800220489502</v>
       </c>
       <c r="H544" t="n">
         <v>14637</v>
@@ -16174,7 +16174,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G545" t="n">
-        <v>7.85675430297852</v>
+        <v>7.85675477981567</v>
       </c>
       <c r="H545" t="n">
         <v>19620</v>
@@ -16290,7 +16290,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>7.80987644195557</v>
+        <v>7.80987596511841</v>
       </c>
       <c r="H549" t="n">
         <v>47708</v>
@@ -16319,7 +16319,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G550" t="n">
-        <v>7.80987644195557</v>
+        <v>7.80987596511841</v>
       </c>
       <c r="H550" t="n">
         <v>33490</v>
@@ -16493,7 +16493,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G556" t="n">
-        <v>7.55673503875732</v>
+        <v>7.55673551559448</v>
       </c>
       <c r="H556" t="n">
         <v>45345</v>
@@ -16551,7 +16551,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G558" t="n">
-        <v>7.63174057006836</v>
+        <v>7.6317400932312</v>
       </c>
       <c r="H558" t="n">
         <v>84786</v>
@@ -16580,7 +16580,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G559" t="n">
-        <v>7.7254958152771</v>
+        <v>7.72549533843994</v>
       </c>
       <c r="H559" t="n">
         <v>40797</v>
@@ -16638,7 +16638,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G561" t="n">
-        <v>7.60361242294312</v>
+        <v>7.60361289978027</v>
       </c>
       <c r="H561" t="n">
         <v>28836</v>
@@ -16667,7 +16667,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G562" t="n">
-        <v>7.60361242294312</v>
+        <v>7.60361289978027</v>
       </c>
       <c r="H562" t="n">
         <v>62515</v>
@@ -16725,7 +16725,7 @@
         <v>8.25</v>
       </c>
       <c r="G564" t="n">
-        <v>7.73487138748169</v>
+        <v>7.73487091064453</v>
       </c>
       <c r="H564" t="n">
         <v>38929</v>
@@ -16754,7 +16754,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G565" t="n">
-        <v>7.77237367630005</v>
+        <v>7.77237415313721</v>
       </c>
       <c r="H565" t="n">
         <v>20455</v>
@@ -16812,7 +16812,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G567" t="n">
-        <v>7.77237367630005</v>
+        <v>7.77237415313721</v>
       </c>
       <c r="H567" t="n">
         <v>23817</v>
@@ -16899,7 +16899,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G570" t="n">
-        <v>8.10052013397217</v>
+        <v>8.10052108764648</v>
       </c>
       <c r="H570" t="n">
         <v>75886</v>
@@ -16928,7 +16928,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G571" t="n">
-        <v>7.85675430297852</v>
+        <v>7.85675477981567</v>
       </c>
       <c r="H571" t="n">
         <v>54680</v>
@@ -16986,7 +16986,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>8.00676345825195</v>
+        <v>8.00676441192627</v>
       </c>
       <c r="H573" t="n">
         <v>30698</v>
@@ -17015,7 +17015,7 @@
         <v>8.5</v>
       </c>
       <c r="G574" t="n">
-        <v>7.96926164627075</v>
+        <v>7.96926116943359</v>
       </c>
       <c r="H574" t="n">
         <v>15609</v>
@@ -17073,7 +17073,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G576" t="n">
-        <v>7.87550497055054</v>
+        <v>7.8755054473877</v>
       </c>
       <c r="H576" t="n">
         <v>10737</v>
@@ -17131,7 +17131,7 @@
         <v>8.25</v>
       </c>
       <c r="G578" t="n">
-        <v>7.73487138748169</v>
+        <v>7.73487091064453</v>
       </c>
       <c r="H578" t="n">
         <v>15413</v>
@@ -17218,7 +17218,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G581" t="n">
-        <v>7.77237367630005</v>
+        <v>7.77237415313721</v>
       </c>
       <c r="H581" t="n">
         <v>46260</v>
@@ -17247,7 +17247,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>7.80987644195557</v>
+        <v>7.80987596511841</v>
       </c>
       <c r="H582" t="n">
         <v>21018</v>
@@ -17276,7 +17276,7 @@
         <v>8.25</v>
       </c>
       <c r="G583" t="n">
-        <v>7.73487138748169</v>
+        <v>7.73487091064453</v>
       </c>
       <c r="H583" t="n">
         <v>10524</v>
@@ -17334,7 +17334,7 @@
         <v>8.25</v>
       </c>
       <c r="G585" t="n">
-        <v>7.73487138748169</v>
+        <v>7.73487091064453</v>
       </c>
       <c r="H585" t="n">
         <v>6395</v>
@@ -17537,7 +17537,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G592" t="n">
-        <v>7.050452709198</v>
+        <v>7.05045223236084</v>
       </c>
       <c r="H592" t="n">
         <v>39430</v>
@@ -17624,7 +17624,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G595" t="n">
-        <v>6.6660532951355</v>
+        <v>6.66605281829834</v>
       </c>
       <c r="H595" t="n">
         <v>20018</v>
@@ -17682,7 +17682,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G597" t="n">
-        <v>6.54416990280151</v>
+        <v>6.54417037963867</v>
       </c>
       <c r="H597" t="n">
         <v>22822</v>
@@ -17914,7 +17914,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G605" t="n">
-        <v>6.18789672851562</v>
+        <v>6.18789720535278</v>
       </c>
       <c r="H605" t="n">
         <v>114219</v>
@@ -17943,7 +17943,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G606" t="n">
-        <v>6.37540912628174</v>
+        <v>6.3754096031189</v>
       </c>
       <c r="H606" t="n">
         <v>266451</v>
@@ -18030,7 +18030,7 @@
         <v>6.5</v>
       </c>
       <c r="G609" t="n">
-        <v>6.09414148330688</v>
+        <v>6.09414100646973</v>
       </c>
       <c r="H609" t="n">
         <v>61300</v>
@@ -18059,7 +18059,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G610" t="n">
-        <v>6.44103860855103</v>
+        <v>6.44103813171387</v>
       </c>
       <c r="H610" t="n">
         <v>59780</v>
@@ -18088,7 +18088,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G611" t="n">
-        <v>6.21602439880371</v>
+        <v>6.21602392196655</v>
       </c>
       <c r="H611" t="n">
         <v>45335</v>
@@ -18117,7 +18117,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G612" t="n">
-        <v>6.30040407180786</v>
+        <v>6.30040454864502</v>
       </c>
       <c r="H612" t="n">
         <v>26883</v>
@@ -18204,7 +18204,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G615" t="n">
-        <v>6.49729156494141</v>
+        <v>6.49729204177856</v>
       </c>
       <c r="H615" t="n">
         <v>23258</v>
@@ -18262,7 +18262,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G617" t="n">
-        <v>6.58167266845703</v>
+        <v>6.58167219161987</v>
       </c>
       <c r="H617" t="n">
         <v>57117</v>
@@ -18320,7 +18320,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G619" t="n">
-        <v>6.75043344497681</v>
+        <v>6.75043296813965</v>
       </c>
       <c r="H619" t="n">
         <v>56581</v>
@@ -18697,7 +18697,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G632" t="n">
-        <v>6.40353631973267</v>
+        <v>6.40353584289551</v>
       </c>
       <c r="H632" t="n">
         <v>30364</v>
@@ -18755,7 +18755,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G634" t="n">
-        <v>6.45041370391846</v>
+        <v>6.45041418075562</v>
       </c>
       <c r="H634" t="n">
         <v>23667</v>
@@ -18842,7 +18842,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G637" t="n">
-        <v>6.37540912628174</v>
+        <v>6.3754096031189</v>
       </c>
       <c r="H637" t="n">
         <v>86665</v>
@@ -18871,7 +18871,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G638" t="n">
-        <v>6.37540912628174</v>
+        <v>6.3754096031189</v>
       </c>
       <c r="H638" t="n">
         <v>15458</v>
@@ -18900,7 +18900,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G639" t="n">
-        <v>6.4129114151001</v>
+        <v>6.41291189193726</v>
       </c>
       <c r="H639" t="n">
         <v>20258</v>
@@ -18929,7 +18929,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>6.4129114151001</v>
+        <v>6.41291189193726</v>
       </c>
       <c r="H640" t="n">
         <v>15641</v>
@@ -18987,7 +18987,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>6.75043344497681</v>
+        <v>6.75043296813965</v>
       </c>
       <c r="H642" t="n">
         <v>46331</v>
@@ -19074,7 +19074,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G645" t="n">
-        <v>6.92856979370117</v>
+        <v>6.92856931686401</v>
       </c>
       <c r="H645" t="n">
         <v>84803</v>
@@ -19132,7 +19132,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G647" t="n">
-        <v>7.09733104705811</v>
+        <v>7.09733057022095</v>
       </c>
       <c r="H647" t="n">
         <v>62367</v>
@@ -19190,7 +19190,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G649" t="n">
-        <v>6.58167266845703</v>
+        <v>6.58167219161987</v>
       </c>
       <c r="H649" t="n">
         <v>109205</v>
@@ -19219,7 +19219,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G650" t="n">
-        <v>6.54416990280151</v>
+        <v>6.54417037963867</v>
       </c>
       <c r="H650" t="n">
         <v>99872</v>
@@ -19277,7 +19277,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G652" t="n">
-        <v>6.51604318618774</v>
+        <v>6.51604270935059</v>
       </c>
       <c r="H652" t="n">
         <v>96786</v>
@@ -19364,7 +19364,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G655" t="n">
-        <v>6.54416990280151</v>
+        <v>6.54417037963867</v>
       </c>
       <c r="H655" t="n">
         <v>65532</v>
@@ -19393,7 +19393,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>6.63792610168457</v>
+        <v>6.63792562484741</v>
       </c>
       <c r="H656" t="n">
         <v>50583</v>
@@ -19509,7 +19509,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G660" t="n">
-        <v>6.54416990280151</v>
+        <v>6.54417037963867</v>
       </c>
       <c r="H660" t="n">
         <v>26357</v>
@@ -19538,7 +19538,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>6.63792610168457</v>
+        <v>6.63792562484741</v>
       </c>
       <c r="H661" t="n">
         <v>62110</v>
@@ -19567,7 +19567,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G662" t="n">
-        <v>6.51604318618774</v>
+        <v>6.51604270935059</v>
       </c>
       <c r="H662" t="n">
         <v>40926</v>
@@ -19683,7 +19683,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G666" t="n">
-        <v>5.30659008026123</v>
+        <v>5.30659055709839</v>
       </c>
       <c r="H666" t="n">
         <v>336194</v>
@@ -19741,7 +19741,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>4.88468837738037</v>
+        <v>4.88468885421753</v>
       </c>
       <c r="H668" t="n">
         <v>314198</v>
@@ -19915,7 +19915,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G674" t="n">
-        <v>5.68161487579346</v>
+        <v>5.6816143989563</v>
       </c>
       <c r="H674" t="n">
         <v>384952</v>
@@ -19944,7 +19944,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G675" t="n">
-        <v>5.84099960327148</v>
+        <v>5.84100008010864</v>
       </c>
       <c r="H675" t="n">
         <v>602374</v>
@@ -20002,7 +20002,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G677" t="n">
-        <v>6.05663871765137</v>
+        <v>6.05663919448853</v>
       </c>
       <c r="H677" t="n">
         <v>387855</v>
@@ -20031,7 +20031,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G678" t="n">
-        <v>6.27227783203125</v>
+        <v>6.27227735519409</v>
       </c>
       <c r="H678" t="n">
         <v>384243</v>
@@ -20060,7 +20060,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>6.05663871765137</v>
+        <v>6.05663919448853</v>
       </c>
       <c r="H679" t="n">
         <v>267454</v>
@@ -20176,7 +20176,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G683" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H683" t="n">
         <v>112229</v>
@@ -20205,7 +20205,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G684" t="n">
-        <v>5.76599502563477</v>
+        <v>5.76599550247192</v>
       </c>
       <c r="H684" t="n">
         <v>109749</v>
@@ -20234,7 +20234,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G685" t="n">
-        <v>5.83162450790405</v>
+        <v>5.83162403106689</v>
       </c>
       <c r="H685" t="n">
         <v>123066</v>
@@ -20263,7 +20263,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G686" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H686" t="n">
         <v>53656</v>
@@ -20292,7 +20292,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G687" t="n">
-        <v>5.83162450790405</v>
+        <v>5.83162403106689</v>
       </c>
       <c r="H687" t="n">
         <v>147677</v>
@@ -20350,7 +20350,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G689" t="n">
-        <v>5.88787794113159</v>
+        <v>5.88787841796875</v>
       </c>
       <c r="H689" t="n">
         <v>56687</v>
@@ -20437,7 +20437,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G692" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H692" t="n">
         <v>38852</v>
@@ -20466,7 +20466,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H693" t="n">
         <v>30885</v>
@@ -20495,7 +20495,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G694" t="n">
-        <v>5.86912727355957</v>
+        <v>5.86912679672241</v>
       </c>
       <c r="H694" t="n">
         <v>26728</v>
@@ -20553,7 +20553,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G696" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H696" t="n">
         <v>59798</v>
@@ -20582,7 +20582,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G697" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H697" t="n">
         <v>58922</v>
@@ -20843,7 +20843,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G706" t="n">
-        <v>6.10351657867432</v>
+        <v>6.10351705551147</v>
       </c>
       <c r="H706" t="n">
         <v>46753</v>
@@ -20930,7 +20930,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G709" t="n">
-        <v>6.04726314544678</v>
+        <v>6.04726266860962</v>
       </c>
       <c r="H709" t="n">
         <v>68499</v>
@@ -20959,7 +20959,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>5.84099960327148</v>
+        <v>5.84100008010864</v>
       </c>
       <c r="H710" t="n">
         <v>66068</v>
@@ -20988,7 +20988,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G711" t="n">
-        <v>5.88787794113159</v>
+        <v>5.88787841796875</v>
       </c>
       <c r="H711" t="n">
         <v>114258</v>
@@ -21017,7 +21017,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H712" t="n">
         <v>47336</v>
@@ -21075,7 +21075,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G714" t="n">
-        <v>5.68161487579346</v>
+        <v>5.6816143989563</v>
       </c>
       <c r="H714" t="n">
         <v>80044</v>
@@ -21336,7 +21336,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G723" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H723" t="n">
         <v>34191</v>
@@ -21394,7 +21394,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G725" t="n">
-        <v>5.83162450790405</v>
+        <v>5.83162403106689</v>
       </c>
       <c r="H725" t="n">
         <v>112869</v>
@@ -21423,7 +21423,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G726" t="n">
-        <v>5.76599502563477</v>
+        <v>5.76599550247192</v>
       </c>
       <c r="H726" t="n">
         <v>47899</v>
@@ -21481,7 +21481,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G728" t="n">
-        <v>5.33471775054932</v>
+        <v>5.33471727371216</v>
       </c>
       <c r="H728" t="n">
         <v>558937</v>
@@ -21510,7 +21510,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>5.23158550262451</v>
+        <v>5.23158597946167</v>
       </c>
       <c r="H729" t="n">
         <v>187003</v>
@@ -21568,7 +21568,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G731" t="n">
-        <v>4.69717645645142</v>
+        <v>4.69717693328857</v>
       </c>
       <c r="H731" t="n">
         <v>383863</v>
@@ -21597,7 +21597,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G732" t="n">
-        <v>4.80030822753906</v>
+        <v>4.8003077507019</v>
       </c>
       <c r="H732" t="n">
         <v>258378</v>
@@ -21655,7 +21655,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G734" t="n">
-        <v>4.73467874526978</v>
+        <v>4.73467922210693</v>
       </c>
       <c r="H734" t="n">
         <v>62891</v>
@@ -21800,7 +21800,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G739" t="n">
-        <v>3.93775248527527</v>
+        <v>3.93775272369385</v>
       </c>
       <c r="H739" t="n">
         <v>114786</v>
@@ -21858,7 +21858,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G741" t="n">
-        <v>3.74086499214172</v>
+        <v>3.7408652305603</v>
       </c>
       <c r="H741" t="n">
         <v>58761</v>
@@ -22119,7 +22119,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G750" t="n">
-        <v>3.05175828933716</v>
+        <v>3.05175852775574</v>
       </c>
       <c r="H750" t="n">
         <v>72240</v>
@@ -22293,7 +22293,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G756" t="n">
-        <v>3.15020203590393</v>
+        <v>3.15020227432251</v>
       </c>
       <c r="H756" t="n">
         <v>52031</v>
@@ -22525,7 +22525,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G764" t="n">
-        <v>3.05644607543945</v>
+        <v>3.05644631385803</v>
       </c>
       <c r="H764" t="n">
         <v>97203</v>
@@ -22612,7 +22612,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G767" t="n">
-        <v>2.75642704963684</v>
+        <v>2.75642681121826</v>
       </c>
       <c r="H767" t="n">
         <v>93848</v>
@@ -22699,7 +22699,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G770" t="n">
-        <v>2.66735887527466</v>
+        <v>2.66735863685608</v>
       </c>
       <c r="H770" t="n">
         <v>36105</v>
@@ -22960,7 +22960,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G779" t="n">
-        <v>3.11738753318787</v>
+        <v>3.11738777160645</v>
       </c>
       <c r="H779" t="n">
         <v>35868</v>
@@ -23047,7 +23047,7 @@
         <v>3.25</v>
       </c>
       <c r="G782" t="n">
-        <v>3.04707074165344</v>
+        <v>3.04707050323486</v>
       </c>
       <c r="H782" t="n">
         <v>114461</v>
@@ -23076,7 +23076,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G783" t="n">
-        <v>3.09394836425781</v>
+        <v>3.09394860267639</v>
       </c>
       <c r="H783" t="n">
         <v>50573</v>
@@ -23105,7 +23105,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G784" t="n">
-        <v>3.05644607543945</v>
+        <v>3.05644631385803</v>
       </c>
       <c r="H784" t="n">
         <v>51754</v>
@@ -23221,7 +23221,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G788" t="n">
-        <v>2.77049016952515</v>
+        <v>2.77049040794373</v>
       </c>
       <c r="H788" t="n">
         <v>263344</v>
@@ -23250,7 +23250,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G789" t="n">
-        <v>2.75642704963684</v>
+        <v>2.75642681121826</v>
       </c>
       <c r="H789" t="n">
         <v>105392</v>
@@ -23279,7 +23279,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G790" t="n">
-        <v>2.70954895019531</v>
+        <v>2.70954918861389</v>
       </c>
       <c r="H790" t="n">
         <v>55133</v>
@@ -23366,7 +23366,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G793" t="n">
-        <v>2.95331478118896</v>
+        <v>2.95331454277039</v>
       </c>
       <c r="H793" t="n">
         <v>269826</v>
@@ -23395,7 +23395,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G794" t="n">
-        <v>2.95331478118896</v>
+        <v>2.95331454277039</v>
       </c>
       <c r="H794" t="n">
         <v>192048</v>
@@ -23714,7 +23714,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>3.3752167224884</v>
+        <v>3.37521648406982</v>
       </c>
       <c r="H805" t="n">
         <v>219067</v>
@@ -24004,7 +24004,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>3.53460168838501</v>
+        <v>3.53460192680359</v>
       </c>
       <c r="H815" t="n">
         <v>83963</v>
@@ -24091,7 +24091,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G818" t="n">
-        <v>3.65179681777954</v>
+        <v>3.65179705619812</v>
       </c>
       <c r="H818" t="n">
         <v>103929</v>
@@ -24207,7 +24207,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.63773369789124</v>
+        <v>3.63773345947266</v>
       </c>
       <c r="H822" t="n">
         <v>64264</v>
@@ -24526,7 +24526,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G833" t="n">
-        <v>3.66586017608643</v>
+        <v>3.665860414505</v>
       </c>
       <c r="H833" t="n">
         <v>83318</v>
@@ -24555,7 +24555,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G834" t="n">
-        <v>3.66586017608643</v>
+        <v>3.665860414505</v>
       </c>
       <c r="H834" t="n">
         <v>30259</v>
@@ -24845,7 +24845,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G844" t="n">
-        <v>3.32365083694458</v>
+        <v>3.32365107536316</v>
       </c>
       <c r="H844" t="n">
         <v>26683</v>
@@ -24874,7 +24874,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G845" t="n">
-        <v>3.46428489685059</v>
+        <v>3.46428465843201</v>
       </c>
       <c r="H845" t="n">
         <v>66739</v>
@@ -25048,7 +25048,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G851" t="n">
-        <v>3.74086499214172</v>
+        <v>3.7408652305603</v>
       </c>
       <c r="H851" t="n">
         <v>67538</v>
@@ -25570,7 +25570,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>3.36115312576294</v>
+        <v>3.36115336418152</v>
       </c>
       <c r="H869" t="n">
         <v>31331</v>
@@ -25686,7 +25686,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G873" t="n">
-        <v>3.48772406578064</v>
+        <v>3.48772382736206</v>
       </c>
       <c r="H873" t="n">
         <v>27789</v>
@@ -25715,7 +25715,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G874" t="n">
-        <v>3.58616781234741</v>
+        <v>3.58616757392883</v>
       </c>
       <c r="H874" t="n">
         <v>145369</v>
@@ -25744,7 +25744,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>3.53460168838501</v>
+        <v>3.53460192680359</v>
       </c>
       <c r="H875" t="n">
         <v>28511</v>
@@ -25802,7 +25802,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>3.31896305084229</v>
+        <v>3.31896281242371</v>
       </c>
       <c r="H877" t="n">
         <v>109874</v>
@@ -25831,7 +25831,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>3.36115312576294</v>
+        <v>3.36115336418152</v>
       </c>
       <c r="H878" t="n">
         <v>12689</v>
@@ -25976,7 +25976,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>3.35646557807922</v>
+        <v>3.35646533966064</v>
       </c>
       <c r="H883" t="n">
         <v>24798</v>
@@ -26063,7 +26063,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G886" t="n">
-        <v>3.29083633422852</v>
+        <v>3.29083609580994</v>
       </c>
       <c r="H886" t="n">
         <v>16486</v>
@@ -26092,7 +26092,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G887" t="n">
-        <v>3.33302664756775</v>
+        <v>3.33302640914917</v>
       </c>
       <c r="H887" t="n">
         <v>16362</v>
@@ -26150,7 +26150,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G889" t="n">
-        <v>3.58616781234741</v>
+        <v>3.58616757392883</v>
       </c>
       <c r="H889" t="n">
         <v>108103</v>
@@ -26237,7 +26237,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G892" t="n">
-        <v>3.49241137504578</v>
+        <v>3.49241161346436</v>
       </c>
       <c r="H892" t="n">
         <v>20443</v>
@@ -26324,7 +26324,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>3.36115312576294</v>
+        <v>3.36115336418152</v>
       </c>
       <c r="H895" t="n">
         <v>25977</v>
@@ -26440,7 +26440,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>3.29083633422852</v>
+        <v>3.29083609580994</v>
       </c>
       <c r="H899" t="n">
         <v>20434</v>
@@ -26556,7 +26556,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G903" t="n">
-        <v>3.02831935882568</v>
+        <v>3.02831959724426</v>
       </c>
       <c r="H903" t="n">
         <v>47586</v>
@@ -26643,7 +26643,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G906" t="n">
-        <v>2.95331478118896</v>
+        <v>2.95331454277039</v>
       </c>
       <c r="H906" t="n">
         <v>25182</v>
@@ -26730,7 +26730,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G909" t="n">
-        <v>3.18770456314087</v>
+        <v>3.18770480155945</v>
       </c>
       <c r="H909" t="n">
         <v>23020</v>
@@ -26904,7 +26904,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>3.36115312576294</v>
+        <v>3.36115336418152</v>
       </c>
       <c r="H915" t="n">
         <v>15443</v>
@@ -27049,7 +27049,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G920" t="n">
-        <v>3.87681150436401</v>
+        <v>3.87681174278259</v>
       </c>
       <c r="H920" t="n">
         <v>245709</v>
@@ -27078,7 +27078,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G921" t="n">
-        <v>3.92368936538696</v>
+        <v>3.92368912696838</v>
       </c>
       <c r="H921" t="n">
         <v>77394</v>
@@ -27107,7 +27107,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G922" t="n">
-        <v>3.82524538040161</v>
+        <v>3.82524561882019</v>
       </c>
       <c r="H922" t="n">
         <v>55872</v>
@@ -27165,7 +27165,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G924" t="n">
-        <v>3.92837715148926</v>
+        <v>3.92837738990784</v>
       </c>
       <c r="H924" t="n">
         <v>130552</v>
@@ -27223,7 +27223,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>3.97056770324707</v>
+        <v>3.97056746482849</v>
       </c>
       <c r="H926" t="n">
         <v>57005</v>
@@ -27339,7 +27339,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>3.91900134086609</v>
+        <v>3.91900110244751</v>
       </c>
       <c r="H930" t="n">
         <v>69316</v>
@@ -27484,7 +27484,7 @@
         <v>4.75</v>
       </c>
       <c r="G935" t="n">
-        <v>4.45341110229492</v>
+        <v>4.45341062545776</v>
       </c>
       <c r="H935" t="n">
         <v>91659</v>
@@ -27687,7 +27687,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G942" t="n">
-        <v>4.50966453552246</v>
+        <v>4.5096640586853</v>
       </c>
       <c r="H942" t="n">
         <v>182016</v>
@@ -27745,7 +27745,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G944" t="n">
-        <v>4.51904010772705</v>
+        <v>4.51904058456421</v>
       </c>
       <c r="H944" t="n">
         <v>34706</v>
@@ -27861,7 +27861,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G948" t="n">
-        <v>4.47216176986694</v>
+        <v>4.4721622467041</v>
       </c>
       <c r="H948" t="n">
         <v>42524</v>
@@ -27890,7 +27890,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G949" t="n">
-        <v>4.50497674942017</v>
+        <v>4.50497627258301</v>
       </c>
       <c r="H949" t="n">
         <v>26355</v>
@@ -28006,7 +28006,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G953" t="n">
-        <v>4.40184497833252</v>
+        <v>4.40184545516968</v>
       </c>
       <c r="H953" t="n">
         <v>53796</v>
@@ -28035,7 +28035,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G954" t="n">
-        <v>4.34090375900269</v>
+        <v>4.34090328216553</v>
       </c>
       <c r="H954" t="n">
         <v>39023</v>
@@ -28064,7 +28064,7 @@
         <v>4.5</v>
       </c>
       <c r="G955" t="n">
-        <v>4.21902084350586</v>
+        <v>4.2190203666687</v>
       </c>
       <c r="H955" t="n">
         <v>63329</v>
@@ -28151,7 +28151,7 @@
         <v>4.5</v>
       </c>
       <c r="G958" t="n">
-        <v>4.21902084350586</v>
+        <v>4.2190203666687</v>
       </c>
       <c r="H958" t="n">
         <v>28205</v>
@@ -28238,7 +28238,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G961" t="n">
-        <v>4.17214250564575</v>
+        <v>4.17214298248291</v>
       </c>
       <c r="H961" t="n">
         <v>16978</v>
@@ -28296,7 +28296,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G963" t="n">
-        <v>3.93775248527527</v>
+        <v>3.93775272369385</v>
       </c>
       <c r="H963" t="n">
         <v>254500</v>
@@ -28383,7 +28383,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G966" t="n">
-        <v>3.97056770324707</v>
+        <v>3.97056746482849</v>
       </c>
       <c r="H966" t="n">
         <v>30908</v>
@@ -28412,7 +28412,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G967" t="n">
-        <v>4.01744556427002</v>
+        <v>4.01744508743286</v>
       </c>
       <c r="H967" t="n">
         <v>12677</v>
@@ -28470,7 +28470,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G969" t="n">
-        <v>4.26589918136597</v>
+        <v>4.26589870452881</v>
       </c>
       <c r="H969" t="n">
         <v>257364</v>
@@ -28615,7 +28615,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G974" t="n">
-        <v>4.61279582977295</v>
+        <v>4.61279630661011</v>
       </c>
       <c r="H974" t="n">
         <v>48179</v>
@@ -28731,7 +28731,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G978" t="n">
-        <v>5.05344915390015</v>
+        <v>5.0534496307373</v>
       </c>
       <c r="H978" t="n">
         <v>410174</v>
@@ -28847,7 +28847,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G982" t="n">
-        <v>5.22221040725708</v>
+        <v>5.22220993041992</v>
       </c>
       <c r="H982" t="n">
         <v>205889</v>
@@ -28934,7 +28934,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G985" t="n">
-        <v>5.1472053527832</v>
+        <v>5.14720487594604</v>
       </c>
       <c r="H985" t="n">
         <v>83264</v>
@@ -28963,7 +28963,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G986" t="n">
-        <v>5.02532291412354</v>
+        <v>5.02532243728638</v>
       </c>
       <c r="H986" t="n">
         <v>138460</v>
@@ -29079,7 +29079,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G990" t="n">
-        <v>5.0065712928772</v>
+        <v>5.00657176971436</v>
       </c>
       <c r="H990" t="n">
         <v>101262</v>
@@ -29166,7 +29166,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G993" t="n">
-        <v>4.95969295501709</v>
+        <v>4.95969343185425</v>
       </c>
       <c r="H993" t="n">
         <v>72969</v>
@@ -29224,7 +29224,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G995" t="n">
-        <v>5.21283483505249</v>
+        <v>5.21283435821533</v>
       </c>
       <c r="H995" t="n">
         <v>144614</v>
@@ -29282,7 +29282,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G997" t="n">
-        <v>5.10970258712769</v>
+        <v>5.10970306396484</v>
       </c>
       <c r="H997" t="n">
         <v>279320</v>
@@ -29340,7 +29340,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G999" t="n">
-        <v>5.05344915390015</v>
+        <v>5.0534496307373</v>
       </c>
       <c r="H999" t="n">
         <v>72666</v>
@@ -29369,7 +29369,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1000" t="n">
-        <v>5.10970258712769</v>
+        <v>5.10970306396484</v>
       </c>
       <c r="H1000" t="n">
         <v>137169</v>
@@ -29398,7 +29398,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>5.05344915390015</v>
+        <v>5.0534496307373</v>
       </c>
       <c r="H1001" t="n">
         <v>77912</v>
@@ -29456,7 +29456,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.95031833648682</v>
+        <v>4.95031785964966</v>
       </c>
       <c r="H1003" t="n">
         <v>46287</v>
@@ -29485,7 +29485,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.98782062530518</v>
+        <v>4.98782014846802</v>
       </c>
       <c r="H1004" t="n">
         <v>86205</v>
@@ -29572,7 +29572,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.95031833648682</v>
+        <v>4.95031785964966</v>
       </c>
       <c r="H1007" t="n">
         <v>30859</v>
@@ -29804,7 +29804,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1015" t="n">
-        <v>5.05344915390015</v>
+        <v>5.0534496307373</v>
       </c>
       <c r="H1015" t="n">
         <v>49146</v>
@@ -29920,7 +29920,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1019" t="n">
-        <v>5.54098033905029</v>
+        <v>5.54098081588745</v>
       </c>
       <c r="H1019" t="n">
         <v>113262</v>
@@ -29949,7 +29949,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1020" t="n">
-        <v>5.51285409927368</v>
+        <v>5.51285362243652</v>
       </c>
       <c r="H1020" t="n">
         <v>59853</v>
@@ -30007,7 +30007,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>5.30659008026123</v>
+        <v>5.30659055709839</v>
       </c>
       <c r="H1022" t="n">
         <v>61984</v>
@@ -30094,7 +30094,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1025" t="n">
-        <v>5.35346841812134</v>
+        <v>5.3534688949585</v>
       </c>
       <c r="H1025" t="n">
         <v>58350</v>
@@ -30123,7 +30123,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1026" t="n">
-        <v>5.61598491668701</v>
+        <v>5.61598539352417</v>
       </c>
       <c r="H1026" t="n">
         <v>107582</v>
@@ -30210,7 +30210,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1029" t="n">
-        <v>5.49410247802734</v>
+        <v>5.4941029548645</v>
       </c>
       <c r="H1029" t="n">
         <v>58734</v>
@@ -30384,7 +30384,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1035" t="n">
-        <v>5.87850189208984</v>
+        <v>5.878502368927</v>
       </c>
       <c r="H1035" t="n">
         <v>98328</v>
@@ -30471,7 +30471,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1038" t="n">
-        <v>5.68161487579346</v>
+        <v>5.6816143989563</v>
       </c>
       <c r="H1038" t="n">
         <v>65582</v>
@@ -30645,7 +30645,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1044" t="n">
-        <v>5.83162450790405</v>
+        <v>5.83162403106689</v>
       </c>
       <c r="H1044" t="n">
         <v>25238</v>
@@ -30674,7 +30674,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1045" t="n">
-        <v>5.86912727355957</v>
+        <v>5.86912679672241</v>
       </c>
       <c r="H1045" t="n">
         <v>26217</v>
@@ -30732,7 +30732,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1047" t="n">
-        <v>5.7847466468811</v>
+        <v>5.78474617004395</v>
       </c>
       <c r="H1047" t="n">
         <v>49030</v>
@@ -30848,7 +30848,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H1051" t="n">
         <v>41127</v>
@@ -30877,7 +30877,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1052" t="n">
-        <v>6.00976037979126</v>
+        <v>6.00976085662842</v>
       </c>
       <c r="H1052" t="n">
         <v>85695</v>
@@ -30935,7 +30935,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1054" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H1054" t="n">
         <v>61811</v>
@@ -31109,7 +31109,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1060" t="n">
-        <v>5.76599502563477</v>
+        <v>5.76599550247192</v>
       </c>
       <c r="H1060" t="n">
         <v>36169</v>
@@ -31225,7 +31225,7 @@
         <v>6.5</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.09414148330688</v>
+        <v>6.09414100646973</v>
       </c>
       <c r="H1064" t="n">
         <v>132793</v>
@@ -31254,7 +31254,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>6.58167266845703</v>
+        <v>6.58167219161987</v>
       </c>
       <c r="H1065" t="n">
         <v>492479</v>
@@ -31370,7 +31370,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G1069" t="n">
-        <v>6.49729156494141</v>
+        <v>6.49729204177856</v>
       </c>
       <c r="H1069" t="n">
         <v>76882</v>
@@ -31399,7 +31399,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.4129114151001</v>
+        <v>6.41291189193726</v>
       </c>
       <c r="H1070" t="n">
         <v>46006</v>
@@ -31457,7 +31457,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1072" t="n">
-        <v>6.37540912628174</v>
+        <v>6.3754096031189</v>
       </c>
       <c r="H1072" t="n">
         <v>51967</v>
@@ -31486,7 +31486,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1073" t="n">
-        <v>6.23477506637573</v>
+        <v>6.23477554321289</v>
       </c>
       <c r="H1073" t="n">
         <v>54286</v>
@@ -31544,7 +31544,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1075" t="n">
-        <v>6.23477506637573</v>
+        <v>6.23477554321289</v>
       </c>
       <c r="H1075" t="n">
         <v>26275</v>
@@ -31718,7 +31718,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1081" t="n">
-        <v>6.27227783203125</v>
+        <v>6.27227735519409</v>
       </c>
       <c r="H1081" t="n">
         <v>42764</v>
@@ -31805,7 +31805,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.87850189208984</v>
+        <v>5.878502368927</v>
       </c>
       <c r="H1084" t="n">
         <v>48664</v>
@@ -31921,7 +31921,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1088" t="n">
-        <v>6.18789672851562</v>
+        <v>6.18789720535278</v>
       </c>
       <c r="H1088" t="n">
         <v>179609</v>
@@ -31950,7 +31950,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.75043344497681</v>
+        <v>6.75043296813965</v>
       </c>
       <c r="H1089" t="n">
         <v>514710</v>
@@ -32269,7 +32269,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1100" t="n">
-        <v>6.75043344497681</v>
+        <v>6.75043296813965</v>
       </c>
       <c r="H1100" t="n">
         <v>45627</v>
@@ -32356,7 +32356,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1103" t="n">
-        <v>6.94732046127319</v>
+        <v>6.94732093811035</v>
       </c>
       <c r="H1103" t="n">
         <v>35767</v>
@@ -32414,7 +32414,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1105" t="n">
-        <v>6.92856979370117</v>
+        <v>6.92856931686401</v>
       </c>
       <c r="H1105" t="n">
         <v>40210</v>
@@ -32472,7 +32472,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1107" t="n">
-        <v>6.72230625152588</v>
+        <v>6.72230672836304</v>
       </c>
       <c r="H1107" t="n">
         <v>22423</v>
@@ -32501,7 +32501,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.97544813156128</v>
+        <v>6.97544765472412</v>
       </c>
       <c r="H1108" t="n">
         <v>77442</v>
@@ -32559,7 +32559,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1110" t="n">
-        <v>6.6660532951355</v>
+        <v>6.66605281829834</v>
       </c>
       <c r="H1110" t="n">
         <v>46760</v>
@@ -32588,7 +32588,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1111" t="n">
-        <v>6.75043344497681</v>
+        <v>6.75043296813965</v>
       </c>
       <c r="H1111" t="n">
         <v>56922</v>
@@ -32878,7 +32878,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>7.42547655105591</v>
+        <v>7.42547702789307</v>
       </c>
       <c r="H1121" t="n">
         <v>95716</v>
@@ -32907,7 +32907,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1122" t="n">
-        <v>7.30359363555908</v>
+        <v>7.30359411239624</v>
       </c>
       <c r="H1122" t="n">
         <v>66396</v>
@@ -32936,7 +32936,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1123" t="n">
-        <v>7.15358448028564</v>
+        <v>7.15358400344849</v>
       </c>
       <c r="H1123" t="n">
         <v>70423</v>
@@ -32965,7 +32965,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1124" t="n">
-        <v>7.30359363555908</v>
+        <v>7.30359411239624</v>
       </c>
       <c r="H1124" t="n">
         <v>81777</v>
@@ -33023,7 +33023,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1126" t="n">
-        <v>6.6660532951355</v>
+        <v>6.66605281829834</v>
       </c>
       <c r="H1126" t="n">
         <v>279700</v>
@@ -33313,7 +33313,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1136" t="n">
-        <v>6.6660532951355</v>
+        <v>6.66605281829834</v>
       </c>
       <c r="H1136" t="n">
         <v>43116</v>
@@ -33458,7 +33458,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1141" t="n">
-        <v>6.45041370391846</v>
+        <v>6.45041418075562</v>
       </c>
       <c r="H1141" t="n">
         <v>31312</v>
@@ -33719,7 +33719,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1150" t="n">
-        <v>7.48172998428345</v>
+        <v>7.48173046112061</v>
       </c>
       <c r="H1150" t="n">
         <v>134941</v>
@@ -33748,7 +33748,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1151" t="n">
-        <v>7.33172035217285</v>
+        <v>7.33172082901001</v>
       </c>
       <c r="H1151" t="n">
         <v>98063</v>
@@ -33777,7 +33777,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1152" t="n">
-        <v>7.32234525680542</v>
+        <v>7.32234477996826</v>
       </c>
       <c r="H1152" t="n">
         <v>56002</v>
@@ -33922,7 +33922,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1157" t="n">
-        <v>7.3785982131958</v>
+        <v>7.37859869003296</v>
       </c>
       <c r="H1157" t="n">
         <v>103207</v>
@@ -33951,7 +33951,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1158" t="n">
-        <v>7.25671529769897</v>
+        <v>7.25671577453613</v>
       </c>
       <c r="H1158" t="n">
         <v>77714</v>
@@ -34009,7 +34009,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1160" t="n">
-        <v>7.28484296798706</v>
+        <v>7.2848424911499</v>
       </c>
       <c r="H1160" t="n">
         <v>58676</v>
@@ -34067,7 +34067,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1162" t="n">
-        <v>7.7254958152771</v>
+        <v>7.72549533843994</v>
       </c>
       <c r="H1162" t="n">
         <v>199951</v>
@@ -34183,7 +34183,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1166" t="n">
-        <v>7.84737873077393</v>
+        <v>7.84737825393677</v>
       </c>
       <c r="H1166" t="n">
         <v>108516</v>
@@ -34212,7 +34212,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1167" t="n">
-        <v>7.66924285888672</v>
+        <v>7.66924238204956</v>
       </c>
       <c r="H1167" t="n">
         <v>155477</v>
@@ -34444,7 +34444,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1175" t="n">
-        <v>7.15358448028564</v>
+        <v>7.15358400344849</v>
       </c>
       <c r="H1175" t="n">
         <v>112746</v>
@@ -34473,7 +34473,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1176" t="n">
-        <v>7.25671529769897</v>
+        <v>7.25671577453613</v>
       </c>
       <c r="H1176" t="n">
         <v>154249</v>
@@ -34647,7 +34647,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1182" t="n">
-        <v>6.92856979370117</v>
+        <v>6.92856931686401</v>
       </c>
       <c r="H1182" t="n">
         <v>74528</v>
@@ -34908,7 +34908,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1191" t="n">
-        <v>7.18171072006226</v>
+        <v>7.18171119689941</v>
       </c>
       <c r="H1191" t="n">
         <v>36444</v>
@@ -35024,7 +35024,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1195" t="n">
-        <v>7.18171072006226</v>
+        <v>7.18171119689941</v>
       </c>
       <c r="H1195" t="n">
         <v>55985</v>
@@ -35256,7 +35256,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1203" t="n">
-        <v>7.18171072006226</v>
+        <v>7.18171119689941</v>
       </c>
       <c r="H1203" t="n">
         <v>14575</v>
@@ -35372,7 +35372,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>7.30359363555908</v>
+        <v>7.30359411239624</v>
       </c>
       <c r="H1207" t="n">
         <v>21658</v>
@@ -35430,7 +35430,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1209" t="n">
-        <v>6.89106702804565</v>
+        <v>6.89106750488281</v>
       </c>
       <c r="H1209" t="n">
         <v>54359</v>
@@ -35459,7 +35459,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.98482275009155</v>
+        <v>6.98482322692871</v>
       </c>
       <c r="H1210" t="n">
         <v>34698</v>
@@ -35546,7 +35546,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1213" t="n">
-        <v>6.98482275009155</v>
+        <v>6.98482322692871</v>
       </c>
       <c r="H1213" t="n">
         <v>28965</v>
@@ -35575,7 +35575,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1214" t="n">
-        <v>7.18171072006226</v>
+        <v>7.18171119689941</v>
       </c>
       <c r="H1214" t="n">
         <v>38969</v>
@@ -35749,7 +35749,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1220" t="n">
-        <v>6.51604318618774</v>
+        <v>6.51604270935059</v>
       </c>
       <c r="H1220" t="n">
         <v>84304</v>
@@ -35836,7 +35836,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.71293115615845</v>
+        <v>6.71293067932129</v>
       </c>
       <c r="H1223" t="n">
         <v>24014</v>
@@ -35865,7 +35865,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.92856979370117</v>
+        <v>6.92856931686401</v>
       </c>
       <c r="H1224" t="n">
         <v>48103</v>
@@ -35923,7 +35923,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1226" t="n">
-        <v>6.92856979370117</v>
+        <v>6.92856931686401</v>
       </c>
       <c r="H1226" t="n">
         <v>33391</v>
@@ -36010,7 +36010,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.37540912628174</v>
+        <v>6.3754096031189</v>
       </c>
       <c r="H1229" t="n">
         <v>49048</v>
@@ -36039,7 +36039,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1230" t="n">
-        <v>6.18789672851562</v>
+        <v>6.18789720535278</v>
       </c>
       <c r="H1230" t="n">
         <v>90704</v>
@@ -36068,7 +36068,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1231" t="n">
-        <v>6.4129114151001</v>
+        <v>6.41291189193726</v>
       </c>
       <c r="H1231" t="n">
         <v>31094</v>
@@ -36126,7 +36126,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>6.11289215087891</v>
+        <v>6.11289262771606</v>
       </c>
       <c r="H1233" t="n">
         <v>45872</v>
@@ -36155,7 +36155,7 @@
         <v>6.5</v>
       </c>
       <c r="G1234" t="n">
-        <v>6.09414148330688</v>
+        <v>6.09414100646973</v>
       </c>
       <c r="H1234" t="n">
         <v>77495</v>
@@ -36184,7 +36184,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1235" t="n">
-        <v>6.21602439880371</v>
+        <v>6.21602392196655</v>
       </c>
       <c r="H1235" t="n">
         <v>39474</v>
@@ -36300,7 +36300,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1239" t="n">
-        <v>6.18789672851562</v>
+        <v>6.18789720535278</v>
       </c>
       <c r="H1239" t="n">
         <v>34692</v>
@@ -36387,7 +36387,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1242" t="n">
-        <v>5.75661945343018</v>
+        <v>5.75661897659302</v>
       </c>
       <c r="H1242" t="n">
         <v>150698</v>
@@ -36474,7 +36474,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1245" t="n">
-        <v>5.90662956237793</v>
+        <v>5.90662908554077</v>
       </c>
       <c r="H1245" t="n">
         <v>60938</v>
@@ -36619,7 +36619,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1250" t="n">
-        <v>5.21283483505249</v>
+        <v>5.21283435821533</v>
       </c>
       <c r="H1250" t="n">
         <v>70449</v>
@@ -36764,7 +36764,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1255" t="n">
-        <v>5.51285409927368</v>
+        <v>5.51285362243652</v>
       </c>
       <c r="H1255" t="n">
         <v>41966</v>
@@ -36909,7 +36909,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1260" t="n">
-        <v>6.23477506637573</v>
+        <v>6.23477554321289</v>
       </c>
       <c r="H1260" t="n">
         <v>62278</v>
@@ -36967,7 +36967,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1262" t="n">
-        <v>6.21602439880371</v>
+        <v>6.21602392196655</v>
       </c>
       <c r="H1262" t="n">
         <v>45431</v>
@@ -37025,7 +37025,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1264" t="n">
-        <v>6.30040407180786</v>
+        <v>6.30040454864502</v>
       </c>
       <c r="H1264" t="n">
         <v>58350</v>
@@ -37054,7 +37054,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1265" t="n">
-        <v>6.27227783203125</v>
+        <v>6.27227735519409</v>
       </c>
       <c r="H1265" t="n">
         <v>75070</v>
@@ -37112,7 +37112,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1267" t="n">
-        <v>6.1691460609436</v>
+        <v>6.16914558410645</v>
       </c>
       <c r="H1267" t="n">
         <v>33305</v>
@@ -37141,7 +37141,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1268" t="n">
-        <v>6.10351657867432</v>
+        <v>6.10351705551147</v>
       </c>
       <c r="H1268" t="n">
         <v>30370</v>
@@ -37518,7 +37518,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1281" t="n">
-        <v>6.04726314544678</v>
+        <v>6.04726266860962</v>
       </c>
       <c r="H1281" t="n">
         <v>15651</v>
@@ -37547,7 +37547,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.87850189208984</v>
+        <v>5.878502368927</v>
       </c>
       <c r="H1282" t="n">
         <v>20045</v>
@@ -37576,7 +37576,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1283" t="n">
-        <v>5.76599502563477</v>
+        <v>5.76599550247192</v>
       </c>
       <c r="H1283" t="n">
         <v>45274</v>
@@ -70845,6 +70845,35 @@
         <v>26664</v>
       </c>
       <c r="I2430" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2431">
+      <c r="A2431" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2431" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2431" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="D2431" t="n">
+        <v>1.37399995326996</v>
+      </c>
+      <c r="E2431" t="n">
+        <v>1.32799994945526</v>
+      </c>
+      <c r="F2431" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="G2431" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="H2431" t="n">
+        <v>122421</v>
+      </c>
+      <c r="I2431" t="s">
         <v>9</v>
       </c>
     </row>
